--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1284" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E71837B-B8AE-4205-AAB6-E409BB9F6695}"/>
+  <xr:revisionPtr revIDLastSave="1297" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{059BBA56-177A-4633-A0D8-C9B286ACB5B3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$294</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="245">
   <si>
     <t>DATA</t>
   </si>
@@ -8620,7 +8620,9 @@
       </c>
       <c r="K288" s="9"/>
       <c r="L288" s="4"/>
-      <c r="M288" s="4"/>
+      <c r="M288" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N288" s="6">
         <v>3</v>
       </c>
@@ -8635,10 +8637,18 @@
       <c r="I289" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="J289" s="4"/>
-      <c r="K289" s="9"/>
-      <c r="L289" s="4"/>
-      <c r="M289" s="4"/>
+      <c r="J289" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K289" s="9">
+        <v>200</v>
+      </c>
+      <c r="L289" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M289" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N289" s="6">
         <v>2</v>
       </c>
@@ -8698,7 +8708,9 @@
       <c r="J292" s="4"/>
       <c r="K292" s="9"/>
       <c r="L292" s="4"/>
-      <c r="M292" s="4"/>
+      <c r="M292" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N292" s="6">
         <v>2</v>
       </c>
@@ -8713,10 +8725,18 @@
       <c r="I293" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="J293" s="4"/>
-      <c r="K293" s="9"/>
-      <c r="L293" s="4"/>
-      <c r="M293" s="4"/>
+      <c r="J293" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K293" s="9">
+        <v>160</v>
+      </c>
+      <c r="L293" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M293" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N293" s="6">
         <v>4</v>
       </c>
@@ -8736,7 +8756,9 @@
       </c>
       <c r="K294" s="9"/>
       <c r="L294" s="4"/>
-      <c r="M294" s="4"/>
+      <c r="M294" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N294" s="6">
         <v>1</v>
       </c>
@@ -8765,7 +8787,7 @@
       <c r="M302" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N288" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:N294" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
         <dateGroupItem year="2025" month="10" day="6" dateTimeGrouping="day"/>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1297" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{059BBA56-177A-4633-A0D8-C9B286ACB5B3}"/>
+  <xr:revisionPtr revIDLastSave="1298" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF32D39D-A310-4AAB-A93C-E7BB425A1FBD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="245">
   <si>
     <t>DATA</t>
   </si>
@@ -8705,7 +8705,9 @@
       <c r="I292" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J292" s="4"/>
+      <c r="J292" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="K292" s="9"/>
       <c r="L292" s="4"/>
       <c r="M292" s="4" t="s">

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1298" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF32D39D-A310-4AAB-A93C-E7BB425A1FBD}"/>
+  <xr:revisionPtr revIDLastSave="1310" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06537F08-80EA-4E1B-9BE3-481AFAFE9EE7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="246">
   <si>
     <t>DATA</t>
   </si>
@@ -773,6 +773,9 @@
   </si>
   <si>
     <t>HOTEL FELICIDADE</t>
+  </si>
+  <si>
+    <t>LEGALOP</t>
   </si>
 </sst>
 </file>
@@ -8423,7 +8426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8449,7 +8452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8475,7 +8478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8501,7 +8504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8527,7 +8530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8553,7 +8556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8579,7 +8582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8618,8 +8621,12 @@
       <c r="J288" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K288" s="9"/>
-      <c r="L288" s="4"/>
+      <c r="K288" s="9">
+        <v>140</v>
+      </c>
+      <c r="L288" s="4" t="s">
+        <v>245</v>
+      </c>
       <c r="M288" s="4" t="s">
         <v>8</v>
       </c>
@@ -8664,7 +8671,7 @@
         <v>147</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="K290" s="9"/>
       <c r="L290" s="4"/>
@@ -8708,8 +8715,12 @@
       <c r="J292" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="K292" s="9"/>
-      <c r="L292" s="4"/>
+      <c r="K292" s="9">
+        <v>280</v>
+      </c>
+      <c r="L292" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="M292" s="4" t="s">
         <v>8</v>
       </c>
@@ -8792,7 +8803,6 @@
   <autoFilter ref="G5:N294" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="10" day="6" dateTimeGrouping="day"/>
         <dateGroupItem year="2025" month="10" day="7" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1310" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06537F08-80EA-4E1B-9BE3-481AFAFE9EE7}"/>
+  <xr:revisionPtr revIDLastSave="1315" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA88DB1-F3F7-4DEE-981A-0E19305D221E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="247">
   <si>
     <t>DATA</t>
   </si>
@@ -776,6 +776,9 @@
   </si>
   <si>
     <t>LEGALOP</t>
+  </si>
+  <si>
+    <t>HOTEL MARIO ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -8673,8 +8676,12 @@
       <c r="J290" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="K290" s="9"/>
-      <c r="L290" s="4"/>
+      <c r="K290" s="9">
+        <v>179.9</v>
+      </c>
+      <c r="L290" s="4" t="s">
+        <v>246</v>
+      </c>
       <c r="M290" s="4" t="s">
         <v>8</v>
       </c>
@@ -8692,9 +8699,15 @@
       <c r="I291" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="J291" s="4"/>
-      <c r="K291" s="9"/>
-      <c r="L291" s="4"/>
+      <c r="J291" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K291" s="9">
+        <v>200</v>
+      </c>
+      <c r="L291" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="M291" s="4" t="s">
         <v>8</v>
       </c>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1315" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA88DB1-F3F7-4DEE-981A-0E19305D221E}"/>
+  <xr:revisionPtr revIDLastSave="1318" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D072A378-B193-4403-8283-AEFB3FD951A8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="247">
   <si>
     <t>DATA</t>
   </si>
@@ -8778,10 +8778,14 @@
         <v>197</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K294" s="9"/>
-      <c r="L294" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="K294" s="9">
+        <v>220</v>
+      </c>
+      <c r="L294" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="M294" s="4" t="s">
         <v>8</v>
       </c>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1318" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D072A378-B193-4403-8283-AEFB3FD951A8}"/>
+  <xr:revisionPtr revIDLastSave="1353" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29599A41-A61D-48FB-B93E-D0AC35753B0F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$302</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="247">
   <si>
     <t>DATA</t>
   </si>
@@ -932,7 +932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1273,7 +1273,7 @@
   <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O302"/>
+  <dimension ref="G5:O315"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -8611,7 +8611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8794,33 +8794,284 @@
       </c>
     </row>
     <row r="295" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G295" s="3"/>
-      <c r="H295" s="4"/>
-      <c r="I295" s="6"/>
+      <c r="G295" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H295" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I295" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="J295" s="4"/>
       <c r="K295" s="9"/>
       <c r="L295" s="4"/>
       <c r="M295" s="4"/>
-      <c r="N295" s="6"/>
+      <c r="N295" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="296" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G296" s="3"/>
-      <c r="H296" s="4"/>
-      <c r="I296" s="6"/>
+      <c r="G296" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I296" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="J296" s="4"/>
-      <c r="K296" s="9"/>
+      <c r="K296" s="4"/>
       <c r="L296" s="4"/>
       <c r="M296" s="4"/>
-      <c r="N296" s="6"/>
+      <c r="N296" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G297" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H297" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I297" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J297" s="4"/>
+      <c r="K297" s="4"/>
+      <c r="L297" s="4"/>
+      <c r="M297" s="4"/>
+      <c r="N297" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G298" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H298" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I298" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J298" s="4"/>
+      <c r="K298" s="9"/>
+      <c r="L298" s="4"/>
+      <c r="M298" s="4"/>
+      <c r="N298" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G299" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H299" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I299" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J299" s="4"/>
+      <c r="K299" s="9"/>
+      <c r="L299" s="4"/>
+      <c r="M299" s="4"/>
+      <c r="N299" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G300" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H300" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I300" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J300" s="4"/>
+      <c r="K300" s="9"/>
+      <c r="L300" s="4"/>
+      <c r="M300" s="4"/>
+      <c r="N300" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G301" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H301" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I301" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J301" s="4"/>
+      <c r="K301" s="9"/>
+      <c r="L301" s="4"/>
+      <c r="M301" s="4"/>
+      <c r="N301" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="302" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G302" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H302" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I302" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J302" s="4"/>
+      <c r="K302" s="9"/>
+      <c r="L302" s="4"/>
       <c r="M302" s="20"/>
+      <c r="N302" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G303" s="4"/>
+      <c r="H303" s="4"/>
+      <c r="I303" s="6"/>
+      <c r="J303" s="4"/>
+      <c r="K303" s="9"/>
+      <c r="L303" s="4"/>
+      <c r="M303" s="4"/>
+      <c r="N303" s="6"/>
+    </row>
+    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G304" s="4"/>
+      <c r="H304" s="4"/>
+      <c r="I304" s="6"/>
+      <c r="J304" s="4"/>
+      <c r="K304" s="9"/>
+      <c r="L304" s="4"/>
+      <c r="M304" s="4"/>
+      <c r="N304" s="6"/>
+    </row>
+    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G305" s="4"/>
+      <c r="H305" s="4"/>
+      <c r="I305" s="6"/>
+      <c r="J305" s="4"/>
+      <c r="K305" s="9"/>
+      <c r="L305" s="4"/>
+      <c r="M305" s="4"/>
+      <c r="N305" s="6"/>
+    </row>
+    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G306" s="4"/>
+      <c r="H306" s="4"/>
+      <c r="I306" s="6"/>
+      <c r="J306" s="4"/>
+      <c r="K306" s="9"/>
+      <c r="L306" s="4"/>
+      <c r="M306" s="4"/>
+      <c r="N306" s="6"/>
+    </row>
+    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G307" s="4"/>
+      <c r="H307" s="4"/>
+      <c r="I307" s="6"/>
+      <c r="J307" s="4"/>
+      <c r="K307" s="9"/>
+      <c r="L307" s="4"/>
+      <c r="M307" s="4"/>
+      <c r="N307" s="6"/>
+    </row>
+    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G308" s="4"/>
+      <c r="H308" s="4"/>
+      <c r="I308" s="6"/>
+      <c r="J308" s="4"/>
+      <c r="K308" s="9"/>
+      <c r="L308" s="4"/>
+      <c r="M308" s="4"/>
+      <c r="N308" s="6"/>
+    </row>
+    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G309" s="4"/>
+      <c r="H309" s="4"/>
+      <c r="I309" s="6"/>
+      <c r="J309" s="4"/>
+      <c r="K309" s="9"/>
+      <c r="L309" s="4"/>
+      <c r="M309" s="4"/>
+      <c r="N309" s="6"/>
+    </row>
+    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G310" s="4"/>
+      <c r="H310" s="4"/>
+      <c r="I310" s="6"/>
+      <c r="J310" s="4"/>
+      <c r="K310" s="9"/>
+      <c r="L310" s="4"/>
+      <c r="M310" s="4"/>
+      <c r="N310" s="6"/>
+    </row>
+    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G311" s="4"/>
+      <c r="H311" s="4"/>
+      <c r="I311" s="6"/>
+      <c r="J311" s="4"/>
+      <c r="K311" s="9"/>
+      <c r="L311" s="4"/>
+      <c r="M311" s="4"/>
+      <c r="N311" s="6"/>
+    </row>
+    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G312" s="4"/>
+      <c r="H312" s="4"/>
+      <c r="I312" s="6"/>
+      <c r="J312" s="4"/>
+      <c r="K312" s="9"/>
+      <c r="L312" s="4"/>
+      <c r="M312" s="4"/>
+      <c r="N312" s="6"/>
+    </row>
+    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G313" s="4"/>
+      <c r="H313" s="4"/>
+      <c r="I313" s="6"/>
+      <c r="J313" s="4"/>
+      <c r="K313" s="9"/>
+      <c r="L313" s="4"/>
+      <c r="M313" s="4"/>
+      <c r="N313" s="6"/>
+    </row>
+    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G314" s="4"/>
+      <c r="H314" s="4"/>
+      <c r="I314" s="6"/>
+      <c r="J314" s="4"/>
+      <c r="K314" s="9"/>
+      <c r="L314" s="4"/>
+      <c r="M314" s="4"/>
+      <c r="N314" s="6"/>
+    </row>
+    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G315" s="4"/>
+      <c r="H315" s="4"/>
+      <c r="I315" s="6"/>
+      <c r="J315" s="4"/>
+      <c r="K315" s="9"/>
+      <c r="L315" s="4"/>
+      <c r="M315" s="4"/>
+      <c r="N315" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N294" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:N302" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="10" day="7" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="8" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1353" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29599A41-A61D-48FB-B93E-D0AC35753B0F}"/>
+  <xr:revisionPtr revIDLastSave="1357" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63CC10C0-96A9-4905-9476-14CAA7463DD2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="248">
   <si>
     <t>DATA</t>
   </si>
@@ -779,6 +779,9 @@
   </si>
   <si>
     <t>HOTEL MARIO ARMANDO</t>
+  </si>
+  <si>
+    <t>HOTEL COSTA E FILHO</t>
   </si>
 </sst>
 </file>
@@ -8839,10 +8842,18 @@
       <c r="I297" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="J297" s="4"/>
-      <c r="K297" s="4"/>
-      <c r="L297" s="4"/>
-      <c r="M297" s="4"/>
+      <c r="J297" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="K297" s="4">
+        <v>160</v>
+      </c>
+      <c r="L297" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M297" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N297" s="4">
         <v>3</v>
       </c>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1357" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63CC10C0-96A9-4905-9476-14CAA7463DD2}"/>
+  <xr:revisionPtr revIDLastSave="1364" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5F85806-09B3-4E24-9BDF-4AB0900C819A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="246">
   <si>
     <t>DATA</t>
   </si>
@@ -751,9 +751,6 @@
     <t>HOTEL PLAZARO</t>
   </si>
   <si>
-    <t>pix</t>
-  </si>
-  <si>
     <t>IBIA</t>
   </si>
   <si>
@@ -779,9 +776,6 @@
   </si>
   <si>
     <t>HOTEL MARIO ARMANDO</t>
-  </si>
-  <si>
-    <t>HOTEL COSTA E FILHO</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1" filterMode="1">
+  <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="G5:O315"/>
@@ -1316,7 +1310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1342,7 +1336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1368,7 +1362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1394,7 +1388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1420,7 +1414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1446,7 +1440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1472,7 +1466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1498,7 +1492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1524,7 +1518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1550,7 +1544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1576,7 +1570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1602,7 +1596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1628,7 +1622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1654,7 +1648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1680,7 +1674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1706,7 +1700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1732,7 +1726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1758,7 +1752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1784,7 +1778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1810,7 +1804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1836,7 +1830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1862,7 +1856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1888,7 +1882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1914,7 +1908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -1940,7 +1934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -1966,7 +1960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -1992,7 +1986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2018,7 +2012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2044,7 +2038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2070,7 +2064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2096,7 +2090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2122,7 +2116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2148,7 +2142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2174,7 +2168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2200,7 +2194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2226,7 +2220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2252,7 +2246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2278,7 +2272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2304,7 +2298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2330,7 +2324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2356,7 +2350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2380,7 +2374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2406,7 +2400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2432,7 +2426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2456,7 +2450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2482,7 +2476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2508,7 +2502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2534,7 +2528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2560,7 +2554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2586,7 +2580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2612,7 +2606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2638,7 +2632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2664,7 +2658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2690,7 +2684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2716,7 +2710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2742,7 +2736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2768,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2794,7 +2788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2820,7 +2814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2846,7 +2840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2872,7 +2866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2898,7 +2892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2924,7 +2918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -2950,7 +2944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3002,7 +2996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3028,7 +3022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3054,7 +3048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3080,7 +3074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3106,7 +3100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3132,7 +3126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3158,7 +3152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3184,7 +3178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3210,7 +3204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3236,7 +3230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3262,7 +3256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3288,7 +3282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3314,7 +3308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3340,7 +3334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3366,7 +3360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3392,7 +3386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3418,7 +3412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3444,7 +3438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3470,7 +3464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3496,7 +3490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3522,7 +3516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3546,7 +3540,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3572,7 +3566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3598,7 +3592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3624,7 +3618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3650,7 +3644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3676,7 +3670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3702,7 +3696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3728,7 +3722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3754,7 +3748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3780,7 +3774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3806,7 +3800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3832,7 +3826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3858,7 +3852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3884,7 +3878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3910,7 +3904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -3936,7 +3930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -3962,7 +3956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -3988,7 +3982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4014,7 +4008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4040,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4066,7 +4060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4092,7 +4086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4118,7 +4112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4144,7 +4138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4170,7 +4164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4196,7 +4190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4222,7 +4216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4241,12 +4235,14 @@
       <c r="L118" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="M118" s="4"/>
+      <c r="M118" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N118" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4272,7 +4268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4298,7 +4294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4324,7 +4320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4350,7 +4346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4376,7 +4372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4402,7 +4398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4428,7 +4424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4454,7 +4450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4480,7 +4476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4506,7 +4502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4532,7 +4528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4558,7 +4554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4584,7 +4580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4610,7 +4606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4636,7 +4632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4662,7 +4658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4688,7 +4684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4714,7 +4710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4740,7 +4736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4766,7 +4762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4792,7 +4788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4816,7 +4812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4842,7 +4838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4866,7 +4862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45904</v>
       </c>
@@ -4892,7 +4888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -4918,7 +4914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -4944,7 +4940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -4970,7 +4966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -4996,7 +4992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5022,7 +5018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5048,7 +5044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5074,7 +5070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5100,7 +5096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45908</v>
       </c>
@@ -5126,7 +5122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5152,7 +5148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5178,7 +5174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5204,7 +5200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45909</v>
       </c>
@@ -5230,7 +5226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5256,7 +5252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5282,7 +5278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5308,7 +5304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5334,7 +5330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5360,7 +5356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45910</v>
       </c>
@@ -5386,7 +5382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5406,7 +5402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5432,7 +5428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5458,7 +5454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5484,7 +5480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5510,7 +5506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5536,7 +5532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45911</v>
       </c>
@@ -5556,7 +5552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5582,7 +5578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5608,7 +5604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5634,7 +5630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5649,12 +5645,14 @@
       </c>
       <c r="K173" s="9"/>
       <c r="L173" s="4"/>
-      <c r="M173" s="4"/>
+      <c r="M173" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N173" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5680,7 +5678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5706,7 +5704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5732,7 +5730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5758,7 +5756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5784,7 +5782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5810,7 +5808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5836,7 +5834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5862,7 +5860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45915</v>
       </c>
@@ -5888,7 +5886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -5914,7 +5912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -5940,7 +5938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -5966,7 +5964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -5992,7 +5990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6018,7 +6016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6044,7 +6042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45916</v>
       </c>
@@ -6070,7 +6068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6096,7 +6094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6122,7 +6120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6148,7 +6146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6174,7 +6172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45917</v>
       </c>
@@ -6200,7 +6198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6226,7 +6224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6252,7 +6250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6278,7 +6276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6304,7 +6302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6330,7 +6328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6356,7 +6354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45918</v>
       </c>
@@ -6382,7 +6380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6408,7 +6406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6434,7 +6432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6460,7 +6458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6486,7 +6484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6512,7 +6510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6538,7 +6536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6555,7 +6553,7 @@
         <v>230</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M208" s="4" t="s">
         <v>8</v>
@@ -6564,7 +6562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6590,7 +6588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6616,7 +6614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6629,12 +6627,14 @@
       <c r="J211" s="4"/>
       <c r="K211" s="9"/>
       <c r="L211" s="4"/>
-      <c r="M211" s="4"/>
+      <c r="M211" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N211" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45922</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45923</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45924</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45925</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45929</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45930</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45931</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>210</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M261" s="4" t="s">
         <v>8</v>
@@ -7932,7 +7932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8062,7 +8062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45932</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>151</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K270" s="9">
         <v>235</v>
@@ -8166,7 +8166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8191,11 +8191,8 @@
       <c r="N271" s="6">
         <v>2</v>
       </c>
-      <c r="O271" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="272" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8212,7 +8209,7 @@
         <v>240</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M272" s="4" t="s">
         <v>8</v>
@@ -8221,7 +8218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8246,11 +8243,9 @@
       <c r="N273" s="6">
         <v>2</v>
       </c>
-      <c r="O273" s="19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O273" s="19"/>
+    </row>
+    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8276,7 +8271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8302,7 +8297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8328,7 +8323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8354,7 +8349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45903</v>
       </c>
@@ -8380,7 +8375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8406,7 +8401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8432,7 +8427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8458,12 +8453,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>215</v>
@@ -8484,7 +8479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8510,7 +8505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8536,7 +8531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8562,7 +8557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8588,15 +8583,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
       <c r="H287" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I287" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="I287" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>27</v>
@@ -8614,7 +8609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8631,7 +8626,7 @@
         <v>140</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>8</v>
@@ -8640,7 +8635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8666,7 +8661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8683,7 +8678,7 @@
         <v>179.9</v>
       </c>
       <c r="L290" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M290" s="4" t="s">
         <v>8</v>
@@ -8692,7 +8687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8718,7 +8713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8744,7 +8739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8770,7 +8765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8797,156 +8792,84 @@
       </c>
     </row>
     <row r="295" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G295" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H295" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="I295" s="6" t="s">
-        <v>155</v>
-      </c>
+      <c r="G295" s="3"/>
+      <c r="H295" s="4"/>
+      <c r="I295" s="6"/>
       <c r="J295" s="4"/>
       <c r="K295" s="9"/>
       <c r="L295" s="4"/>
       <c r="M295" s="4"/>
-      <c r="N295" s="6">
-        <v>2</v>
-      </c>
+      <c r="N295" s="6"/>
     </row>
     <row r="296" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G296" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H296" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I296" s="6" t="s">
-        <v>147</v>
-      </c>
+      <c r="G296" s="3"/>
+      <c r="H296" s="4"/>
+      <c r="I296" s="6"/>
       <c r="J296" s="4"/>
       <c r="K296" s="4"/>
       <c r="L296" s="4"/>
       <c r="M296" s="4"/>
-      <c r="N296" s="6">
-        <v>3</v>
-      </c>
+      <c r="N296" s="6"/>
     </row>
     <row r="297" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G297" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H297" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I297" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J297" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="K297" s="4">
-        <v>160</v>
-      </c>
-      <c r="L297" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="M297" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N297" s="4">
-        <v>3</v>
-      </c>
+      <c r="G297" s="3"/>
+      <c r="H297" s="4"/>
+      <c r="I297" s="6"/>
+      <c r="J297" s="4"/>
+      <c r="K297" s="4"/>
+      <c r="L297" s="4"/>
+      <c r="M297" s="4"/>
+      <c r="N297" s="4"/>
     </row>
     <row r="298" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G298" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H298" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I298" s="6" t="s">
-        <v>154</v>
-      </c>
+      <c r="G298" s="3"/>
+      <c r="H298" s="4"/>
+      <c r="I298" s="6"/>
       <c r="J298" s="4"/>
       <c r="K298" s="9"/>
       <c r="L298" s="4"/>
       <c r="M298" s="4"/>
-      <c r="N298" s="6">
-        <v>3</v>
-      </c>
+      <c r="N298" s="6"/>
     </row>
     <row r="299" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G299" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H299" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I299" s="6" t="s">
-        <v>144</v>
-      </c>
+      <c r="G299" s="3"/>
+      <c r="H299" s="4"/>
+      <c r="I299" s="6"/>
       <c r="J299" s="4"/>
       <c r="K299" s="9"/>
       <c r="L299" s="4"/>
       <c r="M299" s="4"/>
-      <c r="N299" s="6">
-        <v>3</v>
-      </c>
+      <c r="N299" s="6"/>
     </row>
     <row r="300" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G300" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H300" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I300" s="6" t="s">
-        <v>145</v>
-      </c>
+      <c r="G300" s="3"/>
+      <c r="H300" s="4"/>
+      <c r="I300" s="6"/>
       <c r="J300" s="4"/>
       <c r="K300" s="9"/>
       <c r="L300" s="4"/>
       <c r="M300" s="4"/>
-      <c r="N300" s="6">
-        <v>3</v>
-      </c>
+      <c r="N300" s="6"/>
     </row>
     <row r="301" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G301" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H301" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I301" s="6" t="s">
-        <v>151</v>
-      </c>
+      <c r="G301" s="3"/>
+      <c r="H301" s="4"/>
+      <c r="I301" s="6"/>
       <c r="J301" s="4"/>
       <c r="K301" s="9"/>
       <c r="L301" s="4"/>
       <c r="M301" s="4"/>
-      <c r="N301" s="6">
-        <v>3</v>
-      </c>
+      <c r="N301" s="6"/>
     </row>
     <row r="302" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G302" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H302" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="I302" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="G302" s="3"/>
+      <c r="H302" s="4"/>
+      <c r="I302" s="6"/>
       <c r="J302" s="4"/>
       <c r="K302" s="9"/>
       <c r="L302" s="4"/>
       <c r="M302" s="20"/>
-      <c r="N302" s="6">
-        <v>2</v>
-      </c>
+      <c r="N302" s="6"/>
     </row>
     <row r="303" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G303" s="4"/>
@@ -9079,13 +9002,7 @@
       <c r="N315" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N302" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" month="10" day="8" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="G5:N302" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1364" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5F85806-09B3-4E24-9BDF-4AB0900C819A}"/>
+  <xr:revisionPtr revIDLastSave="1428" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCBFF874-08D1-4740-B44F-BB1ACAAFA21F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$309</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="248">
   <si>
     <t>DATA</t>
   </si>
@@ -637,9 +637,6 @@
     <t>HOTEL LAGO DOS ENCANTOS</t>
   </si>
   <si>
-    <t>HOTEL CAMPEAO</t>
-  </si>
-  <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
@@ -776,6 +773,15 @@
   </si>
   <si>
     <t>HOTEL MARIO ARMANDO</t>
+  </si>
+  <si>
+    <t>HOTEL CAMPEÃO</t>
+  </si>
+  <si>
+    <t>HOTEL COSTA E FILHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POUSADA AMERICA </t>
   </si>
 </sst>
 </file>
@@ -4331,7 +4337,7 @@
         <v>148</v>
       </c>
       <c r="J122" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K122" s="9">
         <v>110</v>
@@ -5445,7 +5451,7 @@
         <v>170</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>8</v>
@@ -5471,7 +5477,7 @@
         <v>170</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="M166" s="4" t="s">
         <v>8</v>
@@ -5663,13 +5669,13 @@
         <v>152</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K174" s="9">
         <v>250</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M174" s="4" t="s">
         <v>8</v>
@@ -5686,7 +5692,7 @@
         <v>171</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>73</v>
@@ -5695,7 +5701,7 @@
         <v>220</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>8</v>
@@ -5877,7 +5883,7 @@
         <v>140</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M182" s="4" t="s">
         <v>7</v>
@@ -5894,7 +5900,7 @@
         <v>167</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>59</v>
@@ -5981,7 +5987,7 @@
         <v>220</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M186" s="4" t="s">
         <v>8</v>
@@ -6183,7 +6189,7 @@
         <v>148</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K194" s="9">
         <v>150</v>
@@ -6215,7 +6221,7 @@
         <v>240</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M195" s="4" t="s">
         <v>8</v>
@@ -6293,7 +6299,7 @@
         <v>230</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M198" s="4" t="s">
         <v>8</v>
@@ -6365,7 +6371,7 @@
         <v>148</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K201" s="9">
         <v>180</v>
@@ -6501,7 +6507,7 @@
         <v>200</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M206" s="4" t="s">
         <v>8</v>
@@ -6547,13 +6553,13 @@
         <v>152</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K208" s="9">
         <v>230</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M208" s="4" t="s">
         <v>8</v>
@@ -6692,16 +6698,16 @@
         <v>176</v>
       </c>
       <c r="I214" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K214" s="9">
         <v>170</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M214" s="4" t="s">
         <v>8</v>
@@ -6805,7 +6811,7 @@
         <v>250</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M218" s="4" t="s">
         <v>8</v>
@@ -6857,7 +6863,7 @@
         <v>275</v>
       </c>
       <c r="L220" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M220" s="4" t="s">
         <v>8</v>
@@ -6935,7 +6941,7 @@
         <v>220</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M223" s="4" t="s">
         <v>8</v>
@@ -7033,13 +7039,13 @@
         <v>148</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K227" s="9">
         <v>110</v>
       </c>
       <c r="L227" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M227" s="4" t="s">
         <v>8</v>
@@ -7082,7 +7088,7 @@
         <v>160</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>51</v>
@@ -7134,7 +7140,7 @@
         <v>164</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>22</v>
@@ -7221,7 +7227,7 @@
         <v>170</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M234" s="4" t="s">
         <v>8</v>
@@ -7247,7 +7253,7 @@
         <v>250</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M235" s="4" t="s">
         <v>8</v>
@@ -7290,16 +7296,16 @@
         <v>160</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K237" s="9">
         <v>180</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M237" s="4" t="s">
         <v>8</v>
@@ -7342,7 +7348,7 @@
         <v>164</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>37</v>
@@ -7368,10 +7374,10 @@
         <v>175</v>
       </c>
       <c r="I240" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="J240" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="J240" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="K240" s="9">
         <v>209</v>
@@ -7423,13 +7429,13 @@
         <v>152</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K242" s="9">
         <v>200</v>
       </c>
       <c r="L242" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M242" s="4" t="s">
         <v>8</v>
@@ -7495,7 +7501,7 @@
         <v>45929</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I245" s="6" t="s">
         <v>197</v>
@@ -7507,7 +7513,7 @@
         <v>220</v>
       </c>
       <c r="L245" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M245" s="4" t="s">
         <v>8</v>
@@ -7527,13 +7533,13 @@
         <v>147</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K246" s="9">
         <v>240</v>
       </c>
       <c r="L246" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M246" s="4" t="s">
         <v>8</v>
@@ -7550,10 +7556,10 @@
         <v>175</v>
       </c>
       <c r="I247" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K247" s="9">
         <v>209</v>
@@ -7637,7 +7643,7 @@
         <v>250</v>
       </c>
       <c r="L250" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M250" s="4" t="s">
         <v>8</v>
@@ -7651,10 +7657,10 @@
         <v>45929</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>27</v>
@@ -7663,7 +7669,7 @@
         <v>265</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M251" s="4" t="s">
         <v>8</v>
@@ -7859,7 +7865,7 @@
         <v>45931</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I259" s="6" t="s">
         <v>149</v>
@@ -7923,7 +7929,7 @@
         <v>210</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M261" s="4" t="s">
         <v>8</v>
@@ -7943,7 +7949,7 @@
         <v>148</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K262" s="9">
         <v>110</v>
@@ -8015,7 +8021,7 @@
         <v>45931</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I265" s="6" t="s">
         <v>145</v>
@@ -8041,7 +8047,7 @@
         <v>45931</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I266" s="6" t="s">
         <v>151</v>
@@ -8119,7 +8125,7 @@
         <v>45932</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I269" s="6" t="s">
         <v>145</v>
@@ -8145,13 +8151,13 @@
         <v>45932</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I270" s="6" t="s">
         <v>151</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K270" s="9">
         <v>235</v>
@@ -8174,10 +8180,10 @@
         <v>175</v>
       </c>
       <c r="I271" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K271" s="9">
         <v>259</v>
@@ -8203,13 +8209,13 @@
         <v>141</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K272" s="9">
         <v>240</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M272" s="4" t="s">
         <v>8</v>
@@ -8226,16 +8232,16 @@
         <v>170</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K273" s="9">
         <v>200</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M273" s="4" t="s">
         <v>8</v>
@@ -8256,13 +8262,13 @@
         <v>152</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K274" s="9">
         <v>250</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M274" s="4" t="s">
         <v>8</v>
@@ -8340,7 +8346,7 @@
         <v>250</v>
       </c>
       <c r="L277" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M277" s="4" t="s">
         <v>8</v>
@@ -8366,7 +8372,7 @@
         <v>240</v>
       </c>
       <c r="L278" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M278" s="4" t="s">
         <v>8</v>
@@ -8432,7 +8438,7 @@
         <v>45936</v>
       </c>
       <c r="H281" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>197</v>
@@ -8444,7 +8450,7 @@
         <v>220</v>
       </c>
       <c r="L281" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M281" s="4" t="s">
         <v>8</v>
@@ -8458,13 +8464,13 @@
         <v>45936</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K282" s="9">
         <v>259</v>
@@ -8574,7 +8580,7 @@
         <v>250</v>
       </c>
       <c r="L286" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M286" s="4" t="s">
         <v>8</v>
@@ -8588,10 +8594,10 @@
         <v>45936</v>
       </c>
       <c r="H287" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I287" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="I287" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>27</v>
@@ -8600,7 +8606,7 @@
         <v>265</v>
       </c>
       <c r="L287" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M287" s="4" t="s">
         <v>8</v>
@@ -8626,7 +8632,7 @@
         <v>140</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>8</v>
@@ -8678,7 +8684,7 @@
         <v>179.9</v>
       </c>
       <c r="L290" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M290" s="4" t="s">
         <v>8</v>
@@ -8770,7 +8776,7 @@
         <v>45937</v>
       </c>
       <c r="H294" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I294" s="6" t="s">
         <v>197</v>
@@ -8782,7 +8788,7 @@
         <v>220</v>
       </c>
       <c r="L294" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M294" s="4" t="s">
         <v>8</v>
@@ -8872,74 +8878,186 @@
       <c r="N302" s="6"/>
     </row>
     <row r="303" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G303" s="4"/>
-      <c r="H303" s="4"/>
-      <c r="I303" s="6"/>
-      <c r="J303" s="4"/>
-      <c r="K303" s="9"/>
-      <c r="L303" s="4"/>
-      <c r="M303" s="4"/>
-      <c r="N303" s="6"/>
+      <c r="G303" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H303" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J303" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K303" s="9">
+        <v>200</v>
+      </c>
+      <c r="L303" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M303" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N303" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="304" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G304" s="4"/>
-      <c r="H304" s="4"/>
-      <c r="I304" s="6"/>
-      <c r="J304" s="4"/>
-      <c r="K304" s="9"/>
-      <c r="L304" s="4"/>
-      <c r="M304" s="4"/>
-      <c r="N304" s="6"/>
+      <c r="G304" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H304" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I304" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J304" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K304" s="9">
+        <v>280</v>
+      </c>
+      <c r="L304" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M304" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N304" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="305" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G305" s="4"/>
-      <c r="H305" s="4"/>
-      <c r="I305" s="6"/>
-      <c r="J305" s="4"/>
-      <c r="K305" s="9"/>
-      <c r="L305" s="4"/>
-      <c r="M305" s="4"/>
-      <c r="N305" s="6"/>
+      <c r="G305" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H305" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J305" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="K305" s="9">
+        <v>160</v>
+      </c>
+      <c r="L305" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="M305" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N305" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="306" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G306" s="4"/>
-      <c r="H306" s="4"/>
-      <c r="I306" s="6"/>
-      <c r="J306" s="4"/>
-      <c r="K306" s="9"/>
-      <c r="L306" s="4"/>
-      <c r="M306" s="4"/>
-      <c r="N306" s="6"/>
+      <c r="G306" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H306" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I306" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J306" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K306" s="9">
+        <v>170</v>
+      </c>
+      <c r="L306" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="M306" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N306" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="307" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G307" s="4"/>
-      <c r="H307" s="4"/>
-      <c r="I307" s="6"/>
-      <c r="J307" s="4"/>
-      <c r="K307" s="9"/>
-      <c r="L307" s="4"/>
-      <c r="M307" s="4"/>
-      <c r="N307" s="6"/>
+      <c r="G307" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J307" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K307" s="9">
+        <v>200</v>
+      </c>
+      <c r="L307" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="M307" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N307" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="308" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G308" s="4"/>
-      <c r="H308" s="4"/>
-      <c r="I308" s="6"/>
-      <c r="J308" s="4"/>
-      <c r="K308" s="9"/>
-      <c r="L308" s="4"/>
-      <c r="M308" s="4"/>
-      <c r="N308" s="6"/>
+      <c r="G308" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I308" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J308" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K308" s="9">
+        <v>170</v>
+      </c>
+      <c r="L308" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="M308" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N308" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="309" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G309" s="4"/>
-      <c r="H309" s="4"/>
-      <c r="I309" s="6"/>
-      <c r="J309" s="4"/>
-      <c r="K309" s="9"/>
-      <c r="L309" s="4"/>
-      <c r="M309" s="4"/>
-      <c r="N309" s="6"/>
+      <c r="G309" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I309" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J309" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K309" s="9">
+        <v>230</v>
+      </c>
+      <c r="L309" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M309" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N309" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="310" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G310" s="4"/>
@@ -9002,7 +9120,7 @@
       <c r="N315" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N302" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N309" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1428" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCBFF874-08D1-4740-B44F-BB1ACAAFA21F}"/>
+  <xr:revisionPtr revIDLastSave="1579" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C01DA02-E3E2-463E-A5AC-4FB97D537685}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$323</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="262">
   <si>
     <t>DATA</t>
   </si>
@@ -136,9 +136,6 @@
     <t>KAA HOUSE</t>
   </si>
   <si>
-    <t>VIÇOSA</t>
-  </si>
-  <si>
     <t>HOTEL COLIBRI</t>
   </si>
   <si>
@@ -322,9 +319,6 @@
     <t>HOTEL DALLAS</t>
   </si>
   <si>
-    <t>COLIBRI</t>
-  </si>
-  <si>
     <t>HOTEL PRIMAVERA</t>
   </si>
   <si>
@@ -673,9 +667,6 @@
     <t>JOSE ALDEONIS</t>
   </si>
   <si>
-    <t>ESPAÇO COLIBRI</t>
-  </si>
-  <si>
     <t>HOTEL SONO BOM</t>
   </si>
   <si>
@@ -706,9 +697,6 @@
     <t>HOTEL GOIA</t>
   </si>
   <si>
-    <t>TRES CORAÇOES</t>
-  </si>
-  <si>
     <t>HOTEL MEDIEVAL 2</t>
   </si>
   <si>
@@ -782,6 +770,60 @@
   </si>
   <si>
     <t xml:space="preserve">POUSADA AMERICA </t>
+  </si>
+  <si>
+    <t>BRUNO MENDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELSO </t>
+  </si>
+  <si>
+    <t>LUCAS GABRIEL</t>
+  </si>
+  <si>
+    <t>JOSÉ ARLINDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MAYCOLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME </t>
+  </si>
+  <si>
+    <t>ERASMO</t>
+  </si>
+  <si>
+    <t>JOAO MONLEVADE</t>
+  </si>
+  <si>
+    <t>BELLA POUSADA</t>
+  </si>
+  <si>
+    <t>POUSADA CAMPO VERDE</t>
+  </si>
+  <si>
+    <t>ENTRE RIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOTEL VITORIA </t>
+  </si>
+  <si>
+    <t>POUSADA ESPERANÇA</t>
+  </si>
+  <si>
+    <t>HOTEL MEDIEVAL 1</t>
+  </si>
+  <si>
+    <t>POUSADA IBIÁ</t>
+  </si>
+  <si>
+    <t>MATOZINHOS</t>
+  </si>
+  <si>
+    <t>PONTE NOVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOTEL PARAISO </t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1318,7 @@
   <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O315"/>
+  <dimension ref="G5:O326"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1295,10 +1337,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>1</v>
@@ -1321,10 +1363,10 @@
         <v>45873</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>24</v>
@@ -1347,19 +1389,19 @@
         <v>45873</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K7" s="9">
         <v>74.900000000000006</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>7</v>
@@ -1373,10 +1415,10 @@
         <v>45873</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J8" s="17" t="s">
         <v>27</v>
@@ -1385,7 +1427,7 @@
         <v>80</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>7</v>
@@ -1399,19 +1441,19 @@
         <v>45873</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K9" s="9">
         <v>110</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>7</v>
@@ -1425,19 +1467,19 @@
         <v>45875</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K10" s="9">
         <v>170</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>7</v>
@@ -1451,19 +1493,19 @@
         <v>45875</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K11" s="9">
         <v>150</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>7</v>
@@ -1477,19 +1519,19 @@
         <v>45875</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K12" s="9">
         <v>85</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>7</v>
@@ -1503,19 +1545,19 @@
         <v>45875</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K13" s="9">
         <v>135</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>7</v>
@@ -1529,19 +1571,19 @@
         <v>45875</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K14" s="9">
         <v>100</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>7</v>
@@ -1555,13 +1597,13 @@
         <v>45875</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K15" s="9">
         <v>178</v>
@@ -1581,19 +1623,19 @@
         <v>45875</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K16" s="5">
         <v>80</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>7</v>
@@ -1607,10 +1649,10 @@
         <v>45875</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>5</v>
@@ -1633,13 +1675,13 @@
         <v>45876</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K18" s="10">
         <v>74.900000000000006</v>
@@ -1659,19 +1701,19 @@
         <v>45876</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K19" s="10">
         <v>120</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>7</v>
@@ -1685,19 +1727,19 @@
         <v>45876</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K20" s="10">
         <v>170</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>7</v>
@@ -1711,19 +1753,19 @@
         <v>45876</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K21" s="10">
         <v>150</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>7</v>
@@ -1737,19 +1779,19 @@
         <v>45876</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K22" s="10">
         <v>150</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>7</v>
@@ -1763,19 +1805,19 @@
         <v>45876</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K23" s="10">
         <v>110</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>7</v>
@@ -1789,19 +1831,19 @@
         <v>45876</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K24" s="10">
         <v>130</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>7</v>
@@ -1815,19 +1857,19 @@
         <v>45876</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K25" s="10">
         <v>75</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>7</v>
@@ -1841,10 +1883,10 @@
         <v>45876</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>22</v>
@@ -1853,7 +1895,7 @@
         <v>85</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>7</v>
@@ -1867,19 +1909,19 @@
         <v>45876</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K27" s="10">
         <v>100</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>7</v>
@@ -1893,19 +1935,19 @@
         <v>45876</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K28" s="10">
         <v>100</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>7</v>
@@ -1919,19 +1961,19 @@
         <v>45880</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K29" s="5">
         <v>100</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>7</v>
@@ -1945,13 +1987,13 @@
         <v>45880</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K30" s="5">
         <v>74.900000000000006</v>
@@ -1971,10 +2013,10 @@
         <v>45880</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>27</v>
@@ -1997,10 +2039,10 @@
         <v>45880</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>29</v>
@@ -2009,7 +2051,7 @@
         <v>95</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>7</v>
@@ -2023,19 +2065,19 @@
         <v>45880</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>32</v>
+        <v>141</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="K33" s="5">
         <v>160</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>7</v>
@@ -2049,19 +2091,19 @@
         <v>45881</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K34" s="5">
         <v>150</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>7</v>
@@ -2075,19 +2117,19 @@
         <v>45881</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K35" s="5">
         <v>160</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>7</v>
@@ -2101,19 +2143,19 @@
         <v>45881</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K36" s="5">
         <v>140</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>7</v>
@@ -2127,19 +2169,19 @@
         <v>45881</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K37" s="5">
         <v>150</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>7</v>
@@ -2153,10 +2195,10 @@
         <v>45881</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>10</v>
@@ -2179,10 +2221,10 @@
         <v>45881</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>5</v>
@@ -2205,19 +2247,19 @@
         <v>45881</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K40" s="5">
         <v>105</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>7</v>
@@ -2231,19 +2273,19 @@
         <v>45882</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K41" s="5">
         <v>220</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M41" s="4" t="s">
         <v>7</v>
@@ -2257,19 +2299,19 @@
         <v>45882</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K42" s="5">
         <v>175</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>7</v>
@@ -2283,19 +2325,19 @@
         <v>45882</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K43" s="5">
         <v>180</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>7</v>
@@ -2309,19 +2351,19 @@
         <v>45882</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J44" s="17" t="s">
-        <v>32</v>
+        <v>148</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="K44" s="5">
         <v>160</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>7</v>
@@ -2335,19 +2377,19 @@
         <v>45882</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K45" s="5">
         <v>115</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>7</v>
@@ -2361,10 +2403,10 @@
         <v>45882</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J46" s="17" t="s">
         <v>15</v>
@@ -2372,7 +2414,9 @@
       <c r="K46" s="5">
         <v>100</v>
       </c>
-      <c r="L46" s="4"/>
+      <c r="L46" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="M46" s="4" t="s">
         <v>7</v>
       </c>
@@ -2385,10 +2429,10 @@
         <v>45883</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J47" s="17" t="s">
         <v>5</v>
@@ -2411,10 +2455,10 @@
         <v>45883</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J48" s="17" t="s">
         <v>16</v>
@@ -2423,7 +2467,7 @@
         <v>140</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>7</v>
@@ -2437,18 +2481,20 @@
         <v>45883</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K49" s="5">
         <v>200</v>
       </c>
-      <c r="L49" s="4"/>
+      <c r="L49" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="M49" s="4" t="s">
         <v>8</v>
       </c>
@@ -2461,13 +2507,13 @@
         <v>45883</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K50" s="5">
         <v>129</v>
@@ -2487,13 +2533,13 @@
         <v>45883</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K51" s="5">
         <v>149</v>
@@ -2513,19 +2559,19 @@
         <v>45883</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K52" s="5">
         <v>160</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M52" s="4" t="s">
         <v>7</v>
@@ -2539,19 +2585,19 @@
         <v>45883</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J53" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K53" s="5">
         <v>150</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>7</v>
@@ -2565,10 +2611,10 @@
         <v>45883</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J54" s="17" t="s">
         <v>5</v>
@@ -2591,19 +2637,19 @@
         <v>45883</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K55" s="5">
         <v>140</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>7</v>
@@ -2617,19 +2663,19 @@
         <v>45883</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J56" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K56" s="5">
         <v>188</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M56" s="4" t="s">
         <v>7</v>
@@ -2643,19 +2689,19 @@
         <v>45883</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J57" s="17" t="s">
-        <v>100</v>
+        <v>148</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="K57" s="5">
         <v>99</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M57" s="4" t="s">
         <v>7</v>
@@ -2669,19 +2715,19 @@
         <v>45883</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J58" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K58" s="5">
         <v>75</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>7</v>
@@ -2695,19 +2741,19 @@
         <v>45883</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K59" s="5">
         <v>75</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>7</v>
@@ -2721,19 +2767,19 @@
         <v>45883</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J60" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K60" s="5">
         <v>150</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>7</v>
@@ -2747,19 +2793,19 @@
         <v>45883</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J61" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K61" s="5">
         <v>100</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>7</v>
@@ -2773,10 +2819,10 @@
         <v>45883</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J62" s="17" t="s">
         <v>15</v>
@@ -2799,19 +2845,19 @@
         <v>45887</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J63" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K63" s="5">
         <v>150</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>7</v>
@@ -2825,19 +2871,19 @@
         <v>45887</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K64" s="5">
         <v>149</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>7</v>
@@ -2851,10 +2897,10 @@
         <v>45887</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J65" s="17" t="s">
         <v>22</v>
@@ -2877,10 +2923,10 @@
         <v>45887</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J66" s="17" t="s">
         <v>27</v>
@@ -2889,7 +2935,7 @@
         <v>140</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M66" s="4" t="s">
         <v>7</v>
@@ -2903,10 +2949,10 @@
         <v>45887</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J67" s="17" t="s">
         <v>29</v>
@@ -2915,7 +2961,7 @@
         <v>175</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M67" s="4" t="s">
         <v>7</v>
@@ -2929,19 +2975,19 @@
         <v>45887</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K68" s="5">
         <v>90</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M68" s="4" t="s">
         <v>7</v>
@@ -2955,19 +3001,19 @@
         <v>45887</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K69" s="5">
         <v>135</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M69" s="4" t="s">
         <v>7</v>
@@ -2981,19 +3027,19 @@
         <v>45888</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K70" s="5">
         <v>220</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>8</v>
@@ -3007,19 +3053,19 @@
         <v>45888</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J71" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K71" s="5">
         <v>170</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>8</v>
@@ -3033,19 +3079,19 @@
         <v>45888</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K72" s="5">
         <v>110</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>7</v>
@@ -3059,10 +3105,10 @@
         <v>45888</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J73" s="17" t="s">
         <v>10</v>
@@ -3085,19 +3131,19 @@
         <v>45888</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J74" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K74" s="5">
         <v>175</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M74" s="4" t="s">
         <v>7</v>
@@ -3111,19 +3157,19 @@
         <v>45889</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K75" s="5">
         <v>130</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>7</v>
@@ -3137,10 +3183,10 @@
         <v>45889</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J76" s="17" t="s">
         <v>15</v>
@@ -3163,19 +3209,19 @@
         <v>45889</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J77" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K77" s="5">
         <v>155</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>8</v>
@@ -3189,19 +3235,19 @@
         <v>45889</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K78" s="5">
         <v>150</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>7</v>
@@ -3215,19 +3261,19 @@
         <v>45889</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K79" s="5">
         <v>170</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>8</v>
@@ -3241,19 +3287,19 @@
         <v>45889</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K80" s="5">
         <v>80</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>7</v>
@@ -3267,10 +3313,10 @@
         <v>45889</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J81" s="17" t="s">
         <v>22</v>
@@ -3293,19 +3339,19 @@
         <v>45890</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K82" s="5">
         <v>200</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>8</v>
@@ -3319,19 +3365,19 @@
         <v>45890</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="J83" s="17" t="s">
-        <v>32</v>
+        <v>141</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="K83" s="5">
         <v>130</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>7</v>
@@ -3345,19 +3391,19 @@
         <v>45890</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K84" s="5">
         <v>120</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>7</v>
@@ -3371,19 +3417,19 @@
         <v>45890</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K85" s="5">
         <v>100</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>7</v>
@@ -3397,19 +3443,19 @@
         <v>45890</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K86" s="5">
         <v>220</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>8</v>
@@ -3423,10 +3469,10 @@
         <v>45890</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J87" s="17" t="s">
         <v>26</v>
@@ -3435,7 +3481,7 @@
         <v>159</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>7</v>
@@ -3449,19 +3495,19 @@
         <v>45890</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K88" s="5">
         <v>200</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>8</v>
@@ -3475,10 +3521,10 @@
         <v>45890</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J89" s="17" t="s">
         <v>10</v>
@@ -3501,10 +3547,10 @@
         <v>45890</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J90" s="17" t="s">
         <v>5</v>
@@ -3513,7 +3559,7 @@
         <v>140</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>7</v>
@@ -3527,19 +3573,19 @@
         <v>45890</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K91" s="5">
         <v>120</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>7</v>
@@ -3551,19 +3597,19 @@
         <v>45890</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K92" s="5">
         <v>75</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M92" s="4" t="s">
         <v>7</v>
@@ -3577,10 +3623,10 @@
         <v>45894</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J93" s="17" t="s">
         <v>24</v>
@@ -3603,10 +3649,10 @@
         <v>45894</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>26</v>
@@ -3629,10 +3675,10 @@
         <v>45894</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J95" s="17" t="s">
         <v>27</v>
@@ -3655,10 +3701,10 @@
         <v>45894</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J96" s="17" t="s">
         <v>29</v>
@@ -3681,10 +3727,10 @@
         <v>45895</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J97" s="17" t="s">
         <v>11</v>
@@ -3707,10 +3753,10 @@
         <v>45895</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J98" s="17" t="s">
         <v>13</v>
@@ -3733,10 +3779,10 @@
         <v>45895</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J99" s="17" t="s">
         <v>14</v>
@@ -3759,10 +3805,10 @@
         <v>45895</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J100" s="17" t="s">
         <v>16</v>
@@ -3785,10 +3831,10 @@
         <v>45895</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J101" s="17" t="s">
         <v>10</v>
@@ -3811,10 +3857,10 @@
         <v>45895</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J102" s="17" t="s">
         <v>15</v>
@@ -3837,10 +3883,10 @@
         <v>45895</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J103" s="17" t="s">
         <v>5</v>
@@ -3863,19 +3909,19 @@
         <v>45896</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K104" s="5">
         <v>55</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M104" s="4" t="s">
         <v>7</v>
@@ -3889,19 +3935,19 @@
         <v>45896</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K105" s="5">
         <v>155</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>8</v>
@@ -3915,19 +3961,19 @@
         <v>45896</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J106" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K106" s="5">
         <v>140</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>7</v>
@@ -3941,19 +3987,19 @@
         <v>45896</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J107" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K107" s="5">
         <v>85</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>7</v>
@@ -3967,10 +4013,10 @@
         <v>45896</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J108" s="17" t="s">
         <v>22</v>
@@ -3993,19 +4039,19 @@
         <v>45896</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J109" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K109" s="5">
         <v>120</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M109" s="4" t="s">
         <v>7</v>
@@ -4019,19 +4065,19 @@
         <v>45896</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K110" s="5">
         <v>230</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M110" s="4" t="s">
         <v>8</v>
@@ -4045,19 +4091,19 @@
         <v>45896</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K111" s="5">
         <v>150</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M111" s="4" t="s">
         <v>7</v>
@@ -4071,19 +4117,19 @@
         <v>45897</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="J112" s="17" t="s">
-        <v>32</v>
+        <v>141</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="K112" s="9">
         <v>69</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M112" s="4" t="s">
         <v>7</v>
@@ -4097,19 +4143,19 @@
         <v>45897</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J113" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K113" s="9">
         <v>200</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M113" s="4" t="s">
         <v>8</v>
@@ -4123,19 +4169,19 @@
         <v>45897</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J114" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K114" s="9">
         <v>140</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M114" s="4" t="s">
         <v>8</v>
@@ -4149,19 +4195,19 @@
         <v>45897</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K115" s="9">
         <v>115</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M115" s="4" t="s">
         <v>7</v>
@@ -4175,10 +4221,10 @@
         <v>45897</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J116" s="17" t="s">
         <v>26</v>
@@ -4201,19 +4247,19 @@
         <v>45897</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K117" s="9">
         <v>200</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>8</v>
@@ -4227,19 +4273,19 @@
         <v>45897</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J118" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K118" s="9">
         <v>160</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M118" s="4" t="s">
         <v>8</v>
@@ -4253,10 +4299,10 @@
         <v>45897</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J119" s="17" t="s">
         <v>10</v>
@@ -4279,10 +4325,10 @@
         <v>45897</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J120" s="17" t="s">
         <v>5</v>
@@ -4305,10 +4351,10 @@
         <v>45897</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J121" s="17" t="s">
         <v>29</v>
@@ -4317,7 +4363,7 @@
         <v>115</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>7</v>
@@ -4331,19 +4377,19 @@
         <v>45897</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J122" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K122" s="9">
         <v>110</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M122" s="4" t="s">
         <v>7</v>
@@ -4357,10 +4403,10 @@
         <v>45901</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J123" s="17" t="s">
         <v>24</v>
@@ -4369,7 +4415,7 @@
         <v>220</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M123" s="4" t="s">
         <v>8</v>
@@ -4383,13 +4429,13 @@
         <v>45901</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J124" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K124" s="9">
         <v>209</v>
@@ -4409,10 +4455,10 @@
         <v>45901</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J125" s="17" t="s">
         <v>27</v>
@@ -4435,10 +4481,10 @@
         <v>45901</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J126" s="17" t="s">
         <v>29</v>
@@ -4447,7 +4493,7 @@
         <v>175</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M126" s="4" t="s">
         <v>8</v>
@@ -4461,19 +4507,19 @@
         <v>45902</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J127" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K127" s="9">
         <v>175</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M127" s="4" t="s">
         <v>7</v>
@@ -4487,19 +4533,19 @@
         <v>45902</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J128" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K128" s="9">
         <v>240</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M128" s="4" t="s">
         <v>8</v>
@@ -4513,19 +4559,19 @@
         <v>45902</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J129" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K129" s="9">
         <v>160</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M129" s="4" t="s">
         <v>8</v>
@@ -4539,10 +4585,10 @@
         <v>45902</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J130" s="17" t="s">
         <v>10</v>
@@ -4565,19 +4611,19 @@
         <v>45902</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J131" s="17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K131" s="9">
         <v>150</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>8</v>
@@ -4591,19 +4637,19 @@
         <v>45902</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J132" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K132" s="9">
         <v>220</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M132" s="4" t="s">
         <v>8</v>
@@ -4617,19 +4663,19 @@
         <v>45902</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K133" s="9">
         <v>220</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>8</v>
@@ -4643,19 +4689,19 @@
         <v>45903</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K134" s="9">
         <v>140</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>8</v>
@@ -4669,19 +4715,19 @@
         <v>45903</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K135" s="9">
         <v>240</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M135" s="4" t="s">
         <v>8</v>
@@ -4695,19 +4741,19 @@
         <v>45903</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K136" s="9">
         <v>200</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M136" s="4" t="s">
         <v>8</v>
@@ -4721,19 +4767,19 @@
         <v>45903</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K137" s="9">
         <v>170</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M137" s="4" t="s">
         <v>8</v>
@@ -4747,19 +4793,19 @@
         <v>45903</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K138" s="9">
         <v>170</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M138" s="4" t="s">
         <v>8</v>
@@ -4773,19 +4819,19 @@
         <v>45903</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K139" s="9">
         <v>200</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M139" s="4" t="s">
         <v>8</v>
@@ -4799,13 +4845,13 @@
         <v>45903</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K140" s="9">
         <v>200</v>
@@ -4823,19 +4869,19 @@
         <v>45903</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K141" s="9">
         <v>120</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>8</v>
@@ -4849,13 +4895,13 @@
         <v>45903</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K142" s="9">
         <v>200</v>
@@ -4873,19 +4919,19 @@
         <v>45904</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K143" s="9">
         <v>185</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>8</v>
@@ -4899,19 +4945,19 @@
         <v>45904</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="K144" s="9">
         <v>198</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="M144" s="4" t="s">
         <v>8</v>
@@ -4925,19 +4971,19 @@
         <v>45904</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K145" s="9">
         <v>230</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M145" s="4" t="s">
         <v>8</v>
@@ -4951,19 +4997,19 @@
         <v>45904</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K146" s="9">
         <v>190</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M146" s="4" t="s">
         <v>8</v>
@@ -4977,19 +5023,19 @@
         <v>45904</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K147" s="9">
         <v>200</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M147" s="4" t="s">
         <v>8</v>
@@ -5003,13 +5049,13 @@
         <v>45904</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K148" s="9">
         <v>209</v>
@@ -5029,10 +5075,10 @@
         <v>45904</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>5</v>
@@ -5041,7 +5087,7 @@
         <v>220</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M149" s="4" t="s">
         <v>8</v>
@@ -5055,19 +5101,19 @@
         <v>45904</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K150" s="9">
         <v>160</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M150" s="4" t="s">
         <v>8</v>
@@ -5081,19 +5127,19 @@
         <v>45904</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K151" s="9">
         <v>230</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M151" s="4" t="s">
         <v>8</v>
@@ -5107,10 +5153,10 @@
         <v>45908</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>24</v>
@@ -5119,7 +5165,7 @@
         <v>220</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M152" s="4" t="s">
         <v>8</v>
@@ -5133,13 +5179,13 @@
         <v>45908</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K153" s="9">
         <v>159</v>
@@ -5159,10 +5205,10 @@
         <v>45908</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>27</v>
@@ -5185,10 +5231,10 @@
         <v>45908</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J155" s="4" t="s">
         <v>29</v>
@@ -5197,7 +5243,7 @@
         <v>175</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M155" s="4" t="s">
         <v>8</v>
@@ -5211,19 +5257,19 @@
         <v>45909</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K156" s="9">
         <v>200</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M156" s="4" t="s">
         <v>8</v>
@@ -5237,19 +5283,19 @@
         <v>45909</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K157" s="9">
         <v>240</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M157" s="4" t="s">
         <v>8</v>
@@ -5263,10 +5309,10 @@
         <v>45909</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>10</v>
@@ -5289,19 +5335,19 @@
         <v>45909</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K159" s="9">
         <v>220</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M159" s="4" t="s">
         <v>8</v>
@@ -5315,19 +5361,19 @@
         <v>45909</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J160" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K160" s="9">
         <v>175</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M160" s="4" t="s">
         <v>7</v>
@@ -5341,19 +5387,19 @@
         <v>45909</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K161" s="9">
         <v>200</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M161" s="4" t="s">
         <v>8</v>
@@ -5367,10 +5413,10 @@
         <v>45910</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>15</v>
@@ -5393,10 +5439,10 @@
         <v>45910</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J163" s="4"/>
       <c r="K163" s="9"/>
@@ -5413,19 +5459,19 @@
         <v>45910</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K164" s="9">
         <v>200</v>
       </c>
       <c r="L164" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M164" s="4" t="s">
         <v>8</v>
@@ -5439,19 +5485,19 @@
         <v>45910</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K165" s="9">
         <v>170</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>8</v>
@@ -5465,19 +5511,19 @@
         <v>45910</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K166" s="9">
         <v>170</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="M166" s="4" t="s">
         <v>8</v>
@@ -5491,10 +5537,10 @@
         <v>45910</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>22</v>
@@ -5517,19 +5563,19 @@
         <v>45910</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K168" s="9">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M168" s="4" t="s">
         <v>8</v>
@@ -5543,10 +5589,10 @@
         <v>45911</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J169" s="4"/>
       <c r="K169" s="9"/>
@@ -5563,19 +5609,19 @@
         <v>45911</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K170" s="9">
         <v>170</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M170" s="4" t="s">
         <v>8</v>
@@ -5589,19 +5635,19 @@
         <v>45911</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J171" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K171" s="9">
+        <v>198</v>
+      </c>
+      <c r="L171" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="K171" s="9">
-        <v>200</v>
-      </c>
-      <c r="L171" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="M171" s="4" t="s">
         <v>8</v>
@@ -5615,19 +5661,19 @@
         <v>45911</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K172" s="9">
         <v>170</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M172" s="4" t="s">
         <v>8</v>
@@ -5641,16 +5687,20 @@
         <v>45911</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J173" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="K173" s="9"/>
-      <c r="L173" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="K173" s="9">
+        <v>235</v>
+      </c>
+      <c r="L173" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="M173" s="4" t="s">
         <v>8</v>
       </c>
@@ -5663,19 +5713,19 @@
         <v>45911</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K174" s="9">
         <v>250</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M174" s="4" t="s">
         <v>8</v>
@@ -5689,19 +5739,19 @@
         <v>45911</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K175" s="9">
         <v>220</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>8</v>
@@ -5715,19 +5765,19 @@
         <v>45911</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K176" s="9">
         <v>200</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M176" s="4" t="s">
         <v>8</v>
@@ -5741,13 +5791,13 @@
         <v>45911</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K177" s="9">
         <v>209</v>
@@ -5767,19 +5817,19 @@
         <v>45911</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K178" s="9">
         <v>220</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M178" s="4" t="s">
         <v>8</v>
@@ -5793,19 +5843,19 @@
         <v>45911</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K179" s="9">
         <v>260</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M179" s="4" t="s">
         <v>8</v>
@@ -5819,19 +5869,19 @@
         <v>45911</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K180" s="9">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M180" s="4" t="s">
         <v>8</v>
@@ -5845,10 +5895,10 @@
         <v>45911</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>27</v>
@@ -5871,10 +5921,10 @@
         <v>45915</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>27</v>
@@ -5883,7 +5933,7 @@
         <v>140</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M182" s="4" t="s">
         <v>7</v>
@@ -5897,19 +5947,19 @@
         <v>45915</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K183" s="9">
         <v>220</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M183" s="4" t="s">
         <v>8</v>
@@ -5923,13 +5973,13 @@
         <v>45915</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K184" s="9">
         <v>209</v>
@@ -5949,10 +5999,10 @@
         <v>45915</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>29</v>
@@ -5961,7 +6011,7 @@
         <v>175</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M185" s="4" t="s">
         <v>8</v>
@@ -5975,10 +6025,10 @@
         <v>45915</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>24</v>
@@ -5987,7 +6037,7 @@
         <v>220</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M186" s="4" t="s">
         <v>8</v>
@@ -6001,19 +6051,19 @@
         <v>45915</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K187" s="9">
         <v>200</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M187" s="4" t="s">
         <v>8</v>
@@ -6027,13 +6077,13 @@
         <v>45915</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K188" s="9">
         <v>259</v>
@@ -6053,10 +6103,10 @@
         <v>45916</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>11</v>
@@ -6079,19 +6129,19 @@
         <v>45916</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K190" s="9">
         <v>200</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M190" s="4" t="s">
         <v>8</v>
@@ -6105,19 +6155,19 @@
         <v>45916</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K191" s="9">
         <v>200</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M191" s="4" t="s">
         <v>8</v>
@@ -6131,19 +6181,19 @@
         <v>45916</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K192" s="9">
         <v>170</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M192" s="4" t="s">
         <v>8</v>
@@ -6157,10 +6207,10 @@
         <v>45916</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>10</v>
@@ -6183,19 +6233,19 @@
         <v>45917</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K194" s="9">
         <v>150</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M194" s="4" t="s">
         <v>8</v>
@@ -6209,19 +6259,19 @@
         <v>45917</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K195" s="9">
         <v>240</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M195" s="4" t="s">
         <v>8</v>
@@ -6235,19 +6285,19 @@
         <v>45917</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K196" s="9">
         <v>220</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M196" s="4" t="s">
         <v>8</v>
@@ -6261,19 +6311,19 @@
         <v>45917</v>
       </c>
       <c r="H197" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K197" s="9">
         <v>280</v>
       </c>
       <c r="L197" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M197" s="4" t="s">
         <v>8</v>
@@ -6287,19 +6337,19 @@
         <v>45917</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K198" s="9">
         <v>230</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M198" s="4" t="s">
         <v>8</v>
@@ -6313,19 +6363,19 @@
         <v>45917</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K199" s="9">
         <v>230</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M199" s="4" t="s">
         <v>8</v>
@@ -6339,10 +6389,10 @@
         <v>45917</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>22</v>
@@ -6365,19 +6415,19 @@
         <v>45918</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K201" s="9">
         <v>180</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M201" s="4" t="s">
         <v>8</v>
@@ -6391,19 +6441,19 @@
         <v>45918</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J202" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K202" s="9">
+        <v>198</v>
+      </c>
+      <c r="L202" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="K202" s="9">
-        <v>200</v>
-      </c>
-      <c r="L202" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="M202" s="4" t="s">
         <v>8</v>
@@ -6417,19 +6467,19 @@
         <v>45918</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K203" s="9">
         <v>170</v>
       </c>
       <c r="L203" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M203" s="4" t="s">
         <v>8</v>
@@ -6443,19 +6493,19 @@
         <v>45918</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K204" s="9">
         <v>200</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M204" s="4" t="s">
         <v>8</v>
@@ -6469,19 +6519,19 @@
         <v>45918</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K205" s="9">
         <v>150</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M205" s="4" t="s">
         <v>8</v>
@@ -6495,10 +6545,10 @@
         <v>45918</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>13</v>
@@ -6507,7 +6557,7 @@
         <v>200</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M206" s="4" t="s">
         <v>8</v>
@@ -6521,19 +6571,19 @@
         <v>45918</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K207" s="9">
         <v>159</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M207" s="4" t="s">
         <v>8</v>
@@ -6547,19 +6597,19 @@
         <v>45918</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K208" s="9">
         <v>230</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M208" s="4" t="s">
         <v>8</v>
@@ -6573,10 +6623,10 @@
         <v>45918</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I209" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J209" s="4" t="s">
         <v>29</v>
@@ -6585,7 +6635,7 @@
         <v>175</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M209" s="4" t="s">
         <v>8</v>
@@ -6599,19 +6649,19 @@
         <v>45918</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I210" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K210" s="9">
         <v>260</v>
       </c>
       <c r="L210" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M210" s="4" t="s">
         <v>8</v>
@@ -6625,10 +6675,10 @@
         <v>45918</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I211" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J211" s="4"/>
       <c r="K211" s="9"/>
@@ -6645,19 +6695,19 @@
         <v>45918</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K212" s="9">
         <v>185</v>
       </c>
       <c r="L212" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M212" s="4" t="s">
         <v>8</v>
@@ -6671,17 +6721,19 @@
         <v>45918</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I213" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J213" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K213" s="9">
+        <v>240</v>
+      </c>
+      <c r="L213" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="K213" s="9"/>
-      <c r="L213" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="M213" s="4" t="s">
         <v>8</v>
@@ -6695,19 +6747,19 @@
         <v>45922</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I214" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J214" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="J214" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="K214" s="9">
         <v>170</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M214" s="4" t="s">
         <v>8</v>
@@ -6721,19 +6773,19 @@
         <v>45922</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K215" s="9">
         <v>209</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M215" s="4" t="s">
         <v>8</v>
@@ -6747,19 +6799,19 @@
         <v>45922</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K216" s="9">
         <v>200</v>
       </c>
       <c r="L216" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M216" s="4" t="s">
         <v>8</v>
@@ -6773,19 +6825,19 @@
         <v>45922</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K217" s="9">
         <v>220</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M217" s="4" t="s">
         <v>8</v>
@@ -6799,10 +6851,10 @@
         <v>45922</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J218" s="4" t="s">
         <v>27</v>
@@ -6811,7 +6863,7 @@
         <v>250</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M218" s="4" t="s">
         <v>8</v>
@@ -6825,10 +6877,10 @@
         <v>45922</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J219" s="4" t="s">
         <v>29</v>
@@ -6837,7 +6889,7 @@
         <v>175</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M219" s="4" t="s">
         <v>8</v>
@@ -6851,10 +6903,10 @@
         <v>45922</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I220" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J220" s="4" t="s">
         <v>27</v>
@@ -6863,7 +6915,7 @@
         <v>275</v>
       </c>
       <c r="L220" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M220" s="4" t="s">
         <v>8</v>
@@ -6877,19 +6929,19 @@
         <v>45923</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I221" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K221" s="9">
         <v>200</v>
       </c>
       <c r="L221" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M221" s="4" t="s">
         <v>8</v>
@@ -6903,19 +6955,19 @@
         <v>45923</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I222" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K222" s="9">
         <v>200</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M222" s="4" t="s">
         <v>8</v>
@@ -6929,10 +6981,10 @@
         <v>45923</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>24</v>
@@ -6941,7 +6993,7 @@
         <v>220</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M223" s="4" t="s">
         <v>8</v>
@@ -6955,19 +7007,19 @@
         <v>45923</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K224" s="9">
         <v>280</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M224" s="4" t="s">
         <v>8</v>
@@ -6981,10 +7033,10 @@
         <v>45923</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J225" s="4" t="s">
         <v>15</v>
@@ -7007,10 +7059,10 @@
         <v>45923</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I226" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>11</v>
@@ -7033,19 +7085,19 @@
         <v>45924</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K227" s="9">
         <v>110</v>
       </c>
       <c r="L227" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M227" s="4" t="s">
         <v>8</v>
@@ -7059,19 +7111,19 @@
         <v>45924</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K228" s="9">
         <v>205</v>
       </c>
       <c r="L228" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M228" s="4" t="s">
         <v>8</v>
@@ -7085,19 +7137,19 @@
         <v>45924</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K229" s="9">
         <v>200</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M229" s="4" t="s">
         <v>8</v>
@@ -7111,19 +7163,19 @@
         <v>45924</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K230" s="9">
         <v>170</v>
       </c>
       <c r="L230" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M230" s="4" t="s">
         <v>8</v>
@@ -7137,10 +7189,10 @@
         <v>45924</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>22</v>
@@ -7163,19 +7215,19 @@
         <v>45924</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K232" s="9">
         <v>220</v>
       </c>
       <c r="L232" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M232" s="4" t="s">
         <v>8</v>
@@ -7189,19 +7241,19 @@
         <v>45924</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K233" s="9">
         <v>175</v>
       </c>
       <c r="L233" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M233" s="4" t="s">
         <v>7</v>
@@ -7215,19 +7267,19 @@
         <v>45924</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K234" s="9">
         <v>170</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M234" s="4" t="s">
         <v>8</v>
@@ -7241,10 +7293,10 @@
         <v>45925</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J235" s="4" t="s">
         <v>27</v>
@@ -7253,7 +7305,7 @@
         <v>250</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M235" s="4" t="s">
         <v>8</v>
@@ -7267,19 +7319,19 @@
         <v>45925</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J236" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K236" s="9">
+        <v>198</v>
+      </c>
+      <c r="L236" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="K236" s="9">
-        <v>200</v>
-      </c>
-      <c r="L236" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="M236" s="4" t="s">
         <v>8</v>
@@ -7293,19 +7345,19 @@
         <v>45925</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K237" s="9">
         <v>180</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M237" s="4" t="s">
         <v>8</v>
@@ -7319,19 +7371,19 @@
         <v>45925</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I238" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K238" s="9">
         <v>150</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M238" s="4" t="s">
         <v>8</v>
@@ -7345,19 +7397,19 @@
         <v>45925</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K239" s="9">
         <v>220</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M239" s="4" t="s">
         <v>8</v>
@@ -7371,13 +7423,13 @@
         <v>45925</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I240" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K240" s="9">
         <v>209</v>
@@ -7397,19 +7449,19 @@
         <v>45925</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K241" s="9">
         <v>200</v>
       </c>
       <c r="L241" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M241" s="4" t="s">
         <v>8</v>
@@ -7423,19 +7475,19 @@
         <v>45925</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K242" s="9">
         <v>200</v>
       </c>
       <c r="L242" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M242" s="4" t="s">
         <v>8</v>
@@ -7449,19 +7501,19 @@
         <v>45925</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K243" s="9">
         <v>280</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M243" s="4" t="s">
         <v>8</v>
@@ -7475,19 +7527,19 @@
         <v>45925</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I244" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K244" s="9">
         <v>200</v>
       </c>
       <c r="L244" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M244" s="4" t="s">
         <v>8</v>
@@ -7501,10 +7553,10 @@
         <v>45929</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I245" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>24</v>
@@ -7513,7 +7565,7 @@
         <v>220</v>
       </c>
       <c r="L245" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M245" s="4" t="s">
         <v>8</v>
@@ -7527,19 +7579,19 @@
         <v>45925</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I246" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="K246" s="9">
         <v>240</v>
       </c>
       <c r="L246" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M246" s="4" t="s">
         <v>8</v>
@@ -7553,13 +7605,13 @@
         <v>45929</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I247" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K247" s="9">
         <v>209</v>
@@ -7579,19 +7631,19 @@
         <v>45929</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I248" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K248" s="9">
         <v>200</v>
       </c>
       <c r="L248" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M248" s="4" t="s">
         <v>8</v>
@@ -7605,19 +7657,19 @@
         <v>45929</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K249" s="9">
         <v>220</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M249" s="4" t="s">
         <v>8</v>
@@ -7631,10 +7683,10 @@
         <v>45929</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I250" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J250" s="4" t="s">
         <v>27</v>
@@ -7643,7 +7695,7 @@
         <v>250</v>
       </c>
       <c r="L250" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M250" s="4" t="s">
         <v>8</v>
@@ -7657,10 +7709,10 @@
         <v>45929</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>27</v>
@@ -7669,7 +7721,7 @@
         <v>265</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M251" s="4" t="s">
         <v>8</v>
@@ -7683,10 +7735,10 @@
         <v>45929</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I252" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J252" s="4" t="s">
         <v>29</v>
@@ -7695,7 +7747,7 @@
         <v>175</v>
       </c>
       <c r="L252" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M252" s="4" t="s">
         <v>8</v>
@@ -7709,19 +7761,19 @@
         <v>45930</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K253" s="9">
         <v>200</v>
       </c>
       <c r="L253" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M253" s="4" t="s">
         <v>8</v>
@@ -7735,19 +7787,19 @@
         <v>45930</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K254" s="9">
         <v>200</v>
       </c>
       <c r="L254" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M254" s="4" t="s">
         <v>8</v>
@@ -7761,19 +7813,19 @@
         <v>45930</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I255" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K255" s="9">
         <v>200</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M255" s="4" t="s">
         <v>8</v>
@@ -7787,19 +7839,19 @@
         <v>45930</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I256" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K256" s="9">
         <v>280</v>
       </c>
       <c r="L256" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M256" s="4" t="s">
         <v>8</v>
@@ -7813,10 +7865,10 @@
         <v>45930</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I257" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J257" s="4" t="s">
         <v>15</v>
@@ -7839,10 +7891,10 @@
         <v>45930</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I258" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J258" s="4" t="s">
         <v>11</v>
@@ -7865,19 +7917,19 @@
         <v>45931</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K259" s="9">
         <v>240</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M259" s="4" t="s">
         <v>8</v>
@@ -7891,19 +7943,19 @@
         <v>45931</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K260" s="9">
         <v>280</v>
       </c>
       <c r="L260" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M260" s="4" t="s">
         <v>8</v>
@@ -7917,19 +7969,19 @@
         <v>45931</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I261" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K261" s="9">
         <v>210</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M261" s="4" t="s">
         <v>8</v>
@@ -7943,19 +7995,19 @@
         <v>45931</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I262" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K262" s="9">
         <v>110</v>
       </c>
       <c r="L262" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M262" s="4" t="s">
         <v>8</v>
@@ -7969,19 +8021,19 @@
         <v>45931</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I263" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K263" s="9">
         <v>212</v>
       </c>
       <c r="L263" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M263" s="4" t="s">
         <v>8</v>
@@ -7995,19 +8047,19 @@
         <v>45931</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K264" s="9">
         <v>200</v>
       </c>
       <c r="L264" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M264" s="4" t="s">
         <v>8</v>
@@ -8021,19 +8073,19 @@
         <v>45931</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I265" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K265" s="9">
         <v>190</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M265" s="4" t="s">
         <v>8</v>
@@ -8047,10 +8099,10 @@
         <v>45931</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J266" s="4" t="s">
         <v>22</v>
@@ -8073,19 +8125,19 @@
         <v>45932</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J267" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K267" s="9">
+        <v>198</v>
+      </c>
+      <c r="L267" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="K267" s="9">
-        <v>200</v>
-      </c>
-      <c r="L267" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="M267" s="4" t="s">
         <v>8</v>
@@ -8099,19 +8151,19 @@
         <v>45932</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K268" s="9">
         <v>200</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M268" s="4" t="s">
         <v>8</v>
@@ -8125,19 +8177,19 @@
         <v>45932</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I269" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K269" s="9">
         <v>150</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M269" s="4" t="s">
         <v>8</v>
@@ -8151,19 +8203,19 @@
         <v>45932</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I270" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K270" s="9">
         <v>235</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M270" s="4" t="s">
         <v>8</v>
@@ -8177,13 +8229,13 @@
         <v>45932</v>
       </c>
       <c r="H271" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I271" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K271" s="9">
         <v>259</v>
@@ -8203,19 +8255,19 @@
         <v>45932</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I272" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K272" s="9">
         <v>240</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M272" s="4" t="s">
         <v>8</v>
@@ -8229,19 +8281,19 @@
         <v>45932</v>
       </c>
       <c r="H273" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K273" s="9">
         <v>200</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M273" s="4" t="s">
         <v>8</v>
@@ -8256,19 +8308,19 @@
         <v>45932</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K274" s="9">
         <v>250</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M274" s="4" t="s">
         <v>8</v>
@@ -8282,19 +8334,19 @@
         <v>45932</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K275" s="9">
         <v>280</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M275" s="4" t="s">
         <v>8</v>
@@ -8308,10 +8360,10 @@
         <v>45932</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J276" s="4" t="s">
         <v>29</v>
@@ -8320,7 +8372,7 @@
         <v>175</v>
       </c>
       <c r="L276" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M276" s="4" t="s">
         <v>8</v>
@@ -8334,10 +8386,10 @@
         <v>45932</v>
       </c>
       <c r="H277" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J277" s="4" t="s">
         <v>27</v>
@@ -8346,7 +8398,7 @@
         <v>250</v>
       </c>
       <c r="L277" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M277" s="4" t="s">
         <v>8</v>
@@ -8360,19 +8412,19 @@
         <v>45903</v>
       </c>
       <c r="H278" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K278" s="9">
         <v>240</v>
       </c>
       <c r="L278" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M278" s="4" t="s">
         <v>8</v>
@@ -8386,19 +8438,19 @@
         <v>45933</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K279" s="9">
         <v>230</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M279" s="4" t="s">
         <v>8</v>
@@ -8412,10 +8464,10 @@
         <v>45933</v>
       </c>
       <c r="H280" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>10</v>
@@ -8438,10 +8490,10 @@
         <v>45936</v>
       </c>
       <c r="H281" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J281" s="4" t="s">
         <v>24</v>
@@ -8450,7 +8502,7 @@
         <v>220</v>
       </c>
       <c r="L281" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M281" s="4" t="s">
         <v>8</v>
@@ -8464,13 +8516,13 @@
         <v>45936</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K282" s="9">
         <v>259</v>
@@ -8490,19 +8542,19 @@
         <v>45936</v>
       </c>
       <c r="H283" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K283" s="9">
         <v>200</v>
       </c>
       <c r="L283" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M283" s="4" t="s">
         <v>8</v>
@@ -8516,19 +8568,19 @@
         <v>45936</v>
       </c>
       <c r="H284" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K284" s="9">
         <v>240</v>
       </c>
       <c r="L284" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M284" s="4" t="s">
         <v>8</v>
@@ -8542,10 +8594,10 @@
         <v>45936</v>
       </c>
       <c r="H285" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J285" s="4" t="s">
         <v>29</v>
@@ -8554,7 +8606,7 @@
         <v>175</v>
       </c>
       <c r="L285" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M285" s="4" t="s">
         <v>8</v>
@@ -8568,10 +8620,10 @@
         <v>45936</v>
       </c>
       <c r="H286" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J286" s="4" t="s">
         <v>27</v>
@@ -8580,7 +8632,7 @@
         <v>250</v>
       </c>
       <c r="L286" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M286" s="4" t="s">
         <v>8</v>
@@ -8594,10 +8646,10 @@
         <v>45936</v>
       </c>
       <c r="H287" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I287" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>27</v>
@@ -8606,7 +8658,7 @@
         <v>265</v>
       </c>
       <c r="L287" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M287" s="4" t="s">
         <v>8</v>
@@ -8620,19 +8672,19 @@
         <v>45937</v>
       </c>
       <c r="H288" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I288" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K288" s="9">
         <v>140</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>8</v>
@@ -8646,19 +8698,19 @@
         <v>45937</v>
       </c>
       <c r="H289" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I289" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K289" s="9">
         <v>200</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M289" s="4" t="s">
         <v>8</v>
@@ -8672,19 +8724,19 @@
         <v>45937</v>
       </c>
       <c r="H290" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I290" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K290" s="9">
         <v>179.9</v>
       </c>
       <c r="L290" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M290" s="4" t="s">
         <v>8</v>
@@ -8698,19 +8750,19 @@
         <v>45937</v>
       </c>
       <c r="H291" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K291" s="9">
         <v>200</v>
       </c>
       <c r="L291" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>8</v>
@@ -8724,19 +8776,19 @@
         <v>45937</v>
       </c>
       <c r="H292" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I292" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K292" s="9">
         <v>280</v>
       </c>
       <c r="L292" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M292" s="4" t="s">
         <v>8</v>
@@ -8750,10 +8802,10 @@
         <v>45937</v>
       </c>
       <c r="H293" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J293" s="4" t="s">
         <v>15</v>
@@ -8776,10 +8828,10 @@
         <v>45937</v>
       </c>
       <c r="H294" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J294" s="4" t="s">
         <v>24</v>
@@ -8788,7 +8840,7 @@
         <v>220</v>
       </c>
       <c r="L294" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M294" s="4" t="s">
         <v>8</v>
@@ -8798,74 +8850,186 @@
       </c>
     </row>
     <row r="295" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G295" s="3"/>
-      <c r="H295" s="4"/>
-      <c r="I295" s="6"/>
-      <c r="J295" s="4"/>
-      <c r="K295" s="9"/>
-      <c r="L295" s="4"/>
-      <c r="M295" s="4"/>
-      <c r="N295" s="6"/>
+      <c r="G295" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H295" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I295" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J295" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K295" s="9">
+        <v>200</v>
+      </c>
+      <c r="L295" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M295" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N295" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="296" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G296" s="3"/>
-      <c r="H296" s="4"/>
-      <c r="I296" s="6"/>
-      <c r="J296" s="4"/>
-      <c r="K296" s="4"/>
-      <c r="L296" s="4"/>
-      <c r="M296" s="4"/>
-      <c r="N296" s="6"/>
+      <c r="G296" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I296" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J296" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K296" s="9">
+        <v>280</v>
+      </c>
+      <c r="L296" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M296" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N296" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="297" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G297" s="3"/>
-      <c r="H297" s="4"/>
-      <c r="I297" s="6"/>
-      <c r="J297" s="4"/>
-      <c r="K297" s="4"/>
-      <c r="L297" s="4"/>
-      <c r="M297" s="4"/>
-      <c r="N297" s="4"/>
+      <c r="G297" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H297" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I297" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J297" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K297" s="9">
+        <v>160</v>
+      </c>
+      <c r="L297" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="M297" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N297" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="298" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G298" s="3"/>
-      <c r="H298" s="4"/>
-      <c r="I298" s="6"/>
-      <c r="J298" s="4"/>
-      <c r="K298" s="9"/>
-      <c r="L298" s="4"/>
-      <c r="M298" s="4"/>
-      <c r="N298" s="6"/>
+      <c r="G298" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H298" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I298" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J298" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K298" s="9">
+        <v>170</v>
+      </c>
+      <c r="L298" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M298" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N298" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="299" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G299" s="3"/>
-      <c r="H299" s="4"/>
-      <c r="I299" s="6"/>
-      <c r="J299" s="4"/>
-      <c r="K299" s="9"/>
-      <c r="L299" s="4"/>
-      <c r="M299" s="4"/>
-      <c r="N299" s="6"/>
+      <c r="G299" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H299" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I299" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J299" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K299" s="9">
+        <v>200</v>
+      </c>
+      <c r="L299" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="M299" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N299" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="300" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G300" s="3"/>
-      <c r="H300" s="4"/>
-      <c r="I300" s="6"/>
-      <c r="J300" s="4"/>
-      <c r="K300" s="9"/>
-      <c r="L300" s="4"/>
-      <c r="M300" s="4"/>
-      <c r="N300" s="6"/>
+      <c r="G300" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H300" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I300" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="J300" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K300" s="9">
+        <v>170</v>
+      </c>
+      <c r="L300" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M300" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N300" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="301" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G301" s="3"/>
-      <c r="H301" s="4"/>
-      <c r="I301" s="6"/>
-      <c r="J301" s="4"/>
-      <c r="K301" s="9"/>
-      <c r="L301" s="4"/>
-      <c r="M301" s="4"/>
-      <c r="N301" s="6"/>
+      <c r="G301" s="3">
+        <v>45938</v>
+      </c>
+      <c r="H301" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I301" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J301" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K301" s="9">
+        <v>230</v>
+      </c>
+      <c r="L301" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M301" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N301" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="302" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G302" s="3"/>
@@ -8878,249 +9042,471 @@
       <c r="N302" s="6"/>
     </row>
     <row r="303" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G303" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H303" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="I303" s="6" t="s">
+      <c r="G303" s="4"/>
+      <c r="H303" s="4"/>
+      <c r="I303" s="6"/>
+      <c r="J303" s="4"/>
+      <c r="K303" s="9"/>
+      <c r="L303" s="4"/>
+      <c r="M303" s="4"/>
+      <c r="N303" s="6"/>
+    </row>
+    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G304" s="4"/>
+      <c r="H304" s="4"/>
+      <c r="I304" s="6"/>
+      <c r="J304" s="4"/>
+      <c r="K304" s="9"/>
+      <c r="L304" s="4"/>
+      <c r="M304" s="4"/>
+      <c r="N304" s="6"/>
+    </row>
+    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G305" s="4"/>
+      <c r="H305" s="4"/>
+      <c r="I305" s="6"/>
+      <c r="J305" s="4"/>
+      <c r="K305" s="9"/>
+      <c r="L305" s="4"/>
+      <c r="M305" s="4"/>
+      <c r="N305" s="6"/>
+    </row>
+    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G306" s="4"/>
+      <c r="H306" s="4"/>
+      <c r="I306" s="6"/>
+      <c r="J306" s="4"/>
+      <c r="K306" s="9"/>
+      <c r="L306" s="4"/>
+      <c r="M306" s="4"/>
+      <c r="N306" s="6"/>
+    </row>
+    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G307" s="4"/>
+      <c r="H307" s="4"/>
+      <c r="I307" s="6"/>
+      <c r="J307" s="4"/>
+      <c r="K307" s="9"/>
+      <c r="L307" s="4"/>
+      <c r="M307" s="4"/>
+      <c r="N307" s="6"/>
+    </row>
+    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G308" s="4"/>
+      <c r="H308" s="4"/>
+      <c r="I308" s="6"/>
+      <c r="J308" s="4"/>
+      <c r="K308" s="9"/>
+      <c r="L308" s="4"/>
+      <c r="M308" s="4"/>
+      <c r="N308" s="6"/>
+    </row>
+    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G309" s="4"/>
+      <c r="H309" s="4"/>
+      <c r="I309" s="6"/>
+      <c r="J309" s="4"/>
+      <c r="K309" s="9"/>
+      <c r="L309" s="4"/>
+      <c r="M309" s="4"/>
+      <c r="N309" s="6"/>
+    </row>
+    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G310" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H310" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I310" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J310" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K310" s="9">
+        <v>230</v>
+      </c>
+      <c r="L310" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="M310" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N310" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G311" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I311" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J311" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K311" s="9">
+        <v>180</v>
+      </c>
+      <c r="L311" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="M311" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N311" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G312" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H312" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="J303" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K303" s="9">
+      <c r="I312" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J312" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K312" s="9">
+        <v>198</v>
+      </c>
+      <c r="L312" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M312" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N312" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G313" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H313" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I313" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J313" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K313" s="9">
+        <v>180</v>
+      </c>
+      <c r="L313" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="M313" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N313" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G314" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H314" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I314" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="J314" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K314" s="9">
+        <v>150</v>
+      </c>
+      <c r="L314" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="M314" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N314" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G315" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H315" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I315" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J315" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K315" s="9">
+        <v>140</v>
+      </c>
+      <c r="L315" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="M315" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N315" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G316" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I316" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J316" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K316" s="9">
+        <v>140</v>
+      </c>
+      <c r="L316" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="M316" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N316" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G317" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I317" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="J317" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K317" s="9">
         <v>200</v>
       </c>
-      <c r="L303" s="4" t="s">
+      <c r="L317" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="M317" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N317" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G318" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I318" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="J318" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K318" s="9">
+        <v>220</v>
+      </c>
+      <c r="L318" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="M318" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N318" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G319" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H319" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M303" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N303" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G304" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H304" s="4" t="s">
+      <c r="I319" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="J319" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K319" s="9">
+        <v>200</v>
+      </c>
+      <c r="L319" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="M319" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N319" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G320" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H320" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I320" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J320" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="K320" s="9">
+        <v>280</v>
+      </c>
+      <c r="L320" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M320" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N320" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G321" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H321" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I321" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="J321" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="K321" s="9">
+        <v>180</v>
+      </c>
+      <c r="L321" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="M321" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N321" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G322" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H322" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I322" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="J322" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K322" s="9">
+        <v>200</v>
+      </c>
+      <c r="L322" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M322" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N322" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G323" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H323" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="I304" s="6" t="s">
+      <c r="I323" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="J304" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="K304" s="9">
-        <v>280</v>
-      </c>
-      <c r="L304" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M304" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N304" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G305" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H305" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I305" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J305" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="K305" s="9">
-        <v>160</v>
-      </c>
-      <c r="L305" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="M305" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N305" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G306" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H306" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I306" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J306" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K306" s="9">
-        <v>170</v>
-      </c>
-      <c r="L306" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M306" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N306" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G307" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H307" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I307" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J307" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K307" s="9">
-        <v>200</v>
-      </c>
-      <c r="L307" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="M307" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N307" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G308" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H308" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I308" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J308" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K308" s="9">
-        <v>170</v>
-      </c>
-      <c r="L308" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M308" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N308" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G309" s="3">
-        <v>45938</v>
-      </c>
-      <c r="H309" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I309" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J309" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K309" s="9">
-        <v>230</v>
-      </c>
-      <c r="L309" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M309" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N309" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G310" s="4"/>
-      <c r="H310" s="4"/>
-      <c r="I310" s="6"/>
-      <c r="J310" s="4"/>
-      <c r="K310" s="9"/>
-      <c r="L310" s="4"/>
-      <c r="M310" s="4"/>
-      <c r="N310" s="6"/>
-    </row>
-    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G311" s="4"/>
-      <c r="H311" s="4"/>
-      <c r="I311" s="6"/>
-      <c r="J311" s="4"/>
-      <c r="K311" s="9"/>
-      <c r="L311" s="4"/>
-      <c r="M311" s="4"/>
-      <c r="N311" s="6"/>
-    </row>
-    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G312" s="4"/>
-      <c r="H312" s="4"/>
-      <c r="I312" s="6"/>
-      <c r="J312" s="4"/>
-      <c r="K312" s="9"/>
-      <c r="L312" s="4"/>
-      <c r="M312" s="4"/>
-      <c r="N312" s="6"/>
-    </row>
-    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G313" s="4"/>
-      <c r="H313" s="4"/>
-      <c r="I313" s="6"/>
-      <c r="J313" s="4"/>
-      <c r="K313" s="9"/>
-      <c r="L313" s="4"/>
-      <c r="M313" s="4"/>
-      <c r="N313" s="6"/>
-    </row>
-    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G314" s="4"/>
-      <c r="H314" s="4"/>
-      <c r="I314" s="6"/>
-      <c r="J314" s="4"/>
-      <c r="K314" s="9"/>
-      <c r="L314" s="4"/>
-      <c r="M314" s="4"/>
-      <c r="N314" s="6"/>
-    </row>
-    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G315" s="4"/>
-      <c r="H315" s="4"/>
-      <c r="I315" s="6"/>
-      <c r="J315" s="4"/>
-      <c r="K315" s="9"/>
-      <c r="L315" s="4"/>
-      <c r="M315" s="4"/>
-      <c r="N315" s="6"/>
+      <c r="J323" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="K323" s="9">
+        <v>220</v>
+      </c>
+      <c r="L323" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M323" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N323" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G324" s="4"/>
+      <c r="H324" s="4"/>
+      <c r="I324" s="6"/>
+      <c r="J324" s="4"/>
+      <c r="K324" s="9"/>
+      <c r="L324" s="4"/>
+      <c r="M324" s="4"/>
+      <c r="N324" s="6"/>
+    </row>
+    <row r="325" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G325" s="4"/>
+      <c r="H325" s="4"/>
+      <c r="I325" s="6"/>
+      <c r="J325" s="4"/>
+      <c r="K325" s="9"/>
+      <c r="L325" s="4"/>
+      <c r="M325" s="4"/>
+      <c r="N325" s="6"/>
+    </row>
+    <row r="326" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G326" s="4"/>
+      <c r="H326" s="4"/>
+      <c r="I326" s="6"/>
+      <c r="J326" s="4"/>
+      <c r="K326" s="9"/>
+      <c r="L326" s="4"/>
+      <c r="M326" s="4"/>
+      <c r="N326" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N309" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N323" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1579" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C01DA02-E3E2-463E-A5AC-4FB97D537685}"/>
+  <xr:revisionPtr revIDLastSave="1640" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C544A0D2-D567-4BF9-B006-FE026D3C524F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$324</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="264">
   <si>
     <t>DATA</t>
   </si>
@@ -824,6 +824,12 @@
   </si>
   <si>
     <t xml:space="preserve">HOTEL PARAISO </t>
+  </si>
+  <si>
+    <t>BARBACENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRA DAS VERTENTES </t>
   </si>
 </sst>
 </file>
@@ -834,7 +840,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -843,14 +849,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -977,7 +975,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9032,64 +9030,160 @@
       </c>
     </row>
     <row r="302" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G302" s="3"/>
-      <c r="H302" s="4"/>
-      <c r="I302" s="6"/>
-      <c r="J302" s="4"/>
-      <c r="K302" s="9"/>
-      <c r="L302" s="4"/>
-      <c r="M302" s="20"/>
-      <c r="N302" s="6"/>
+      <c r="G302" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H302" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I302" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J302" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K302" s="9">
+        <v>220</v>
+      </c>
+      <c r="L302" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="M302" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="N302" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="303" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G303" s="4"/>
-      <c r="H303" s="4"/>
-      <c r="I303" s="6"/>
-      <c r="J303" s="4"/>
-      <c r="K303" s="9"/>
-      <c r="L303" s="4"/>
-      <c r="M303" s="4"/>
-      <c r="N303" s="6"/>
+      <c r="G303" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H303" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="J303" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K303" s="9">
+        <v>140</v>
+      </c>
+      <c r="L303" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="M303" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N303" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="304" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G304" s="4"/>
-      <c r="H304" s="4"/>
-      <c r="I304" s="6"/>
-      <c r="J304" s="4"/>
-      <c r="K304" s="9"/>
-      <c r="L304" s="4"/>
-      <c r="M304" s="4"/>
-      <c r="N304" s="6"/>
+      <c r="G304" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H304" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I304" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J304" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K304" s="9">
+        <v>200</v>
+      </c>
+      <c r="L304" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="M304" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N304" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="305" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G305" s="4"/>
-      <c r="H305" s="4"/>
-      <c r="I305" s="6"/>
-      <c r="J305" s="4"/>
-      <c r="K305" s="9"/>
-      <c r="L305" s="4"/>
-      <c r="M305" s="4"/>
-      <c r="N305" s="6"/>
+      <c r="G305" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H305" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="J305" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K305" s="9">
+        <v>220</v>
+      </c>
+      <c r="L305" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M305" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N305" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="306" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G306" s="4"/>
-      <c r="H306" s="4"/>
-      <c r="I306" s="6"/>
-      <c r="J306" s="4"/>
-      <c r="K306" s="9"/>
-      <c r="L306" s="4"/>
-      <c r="M306" s="4"/>
-      <c r="N306" s="6"/>
+      <c r="G306" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H306" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I306" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J306" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K306" s="9">
+        <v>180</v>
+      </c>
+      <c r="L306" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="M306" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N306" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="307" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G307" s="4"/>
-      <c r="H307" s="4"/>
-      <c r="I307" s="6"/>
-      <c r="J307" s="4"/>
-      <c r="K307" s="9"/>
-      <c r="L307" s="4"/>
-      <c r="M307" s="4"/>
-      <c r="N307" s="6"/>
+      <c r="G307" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="J307" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K307" s="9">
+        <v>220</v>
+      </c>
+      <c r="L307" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="M307" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N307" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="308" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G308" s="4"/>
@@ -9476,14 +9570,30 @@
       </c>
     </row>
     <row r="324" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G324" s="4"/>
-      <c r="H324" s="4"/>
-      <c r="I324" s="6"/>
-      <c r="J324" s="4"/>
-      <c r="K324" s="9"/>
-      <c r="L324" s="4"/>
-      <c r="M324" s="4"/>
-      <c r="N324" s="6"/>
+      <c r="G324" s="3">
+        <v>45940</v>
+      </c>
+      <c r="H324" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I324" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J324" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="K324" s="9">
+        <v>220</v>
+      </c>
+      <c r="L324" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="M324" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N324" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="325" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G325" s="4"/>
@@ -9506,7 +9616,7 @@
       <c r="N326" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N323" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N324" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1640" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C544A0D2-D567-4BF9-B006-FE026D3C524F}"/>
+  <xr:revisionPtr revIDLastSave="1667" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32307686-C7AB-4D8B-B730-86601E647A46}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="266">
   <si>
     <t>DATA</t>
   </si>
@@ -830,6 +830,12 @@
   </si>
   <si>
     <t xml:space="preserve">SERRA DAS VERTENTES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUANHAES </t>
+  </si>
+  <si>
+    <t>HOTEL JOAZINHO</t>
   </si>
 </sst>
 </file>
@@ -922,7 +928,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -973,9 +979,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1313,10 +1316,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1">
+  <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O326"/>
+  <dimension ref="G5:O337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1356,7 +1359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1382,7 +1385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1434,7 +1437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1460,7 +1463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1486,7 +1489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1512,7 +1515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1538,7 +1541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1564,7 +1567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1590,7 +1593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1642,7 +1645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1694,7 +1697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1746,7 +1749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1772,7 +1775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1798,7 +1801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1824,7 +1827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1850,7 +1853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1876,7 +1879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1902,7 +1905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -1980,7 +1983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -2006,7 +2009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -2032,7 +2035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2058,7 +2061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2084,7 +2087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2110,7 +2113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2136,7 +2139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2188,7 +2191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2214,7 +2217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2240,7 +2243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2266,7 +2269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2292,7 +2295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2318,7 +2321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2344,7 +2347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2370,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2396,7 +2399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2422,7 +2425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2474,7 +2477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2500,7 +2503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2526,7 +2529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2552,7 +2555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2578,7 +2581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2604,7 +2607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2630,7 +2633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2682,7 +2685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2708,7 +2711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2734,7 +2737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2760,7 +2763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2786,7 +2789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2812,7 +2815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2838,7 +2841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2890,7 +2893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2916,7 +2919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2942,7 +2945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2968,7 +2971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -2994,7 +2997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -3020,7 +3023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3046,7 +3049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3072,7 +3075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3098,7 +3101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3124,7 +3127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3176,7 +3179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3202,7 +3205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3254,7 +3257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3280,7 +3283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3306,7 +3309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3332,7 +3335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3358,7 +3361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3384,7 +3387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3410,7 +3413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3436,7 +3439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3462,7 +3465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3488,7 +3491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3514,7 +3517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3540,7 +3543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3566,7 +3569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3590,7 +3593,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3616,7 +3619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3642,7 +3645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3694,7 +3697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3720,7 +3723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3746,7 +3749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3772,7 +3775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3798,7 +3801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3824,7 +3827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3850,7 +3853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3876,7 +3879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3902,7 +3905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3954,7 +3957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -3980,7 +3983,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -4006,7 +4009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -4032,7 +4035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4058,7 +4061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4084,7 +4087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4110,7 +4113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4136,7 +4139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4162,7 +4165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4188,7 +4191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4214,7 +4217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4240,7 +4243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4266,7 +4269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4292,7 +4295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4318,7 +4321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4344,7 +4347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4370,7 +4373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4396,7 +4399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4448,7 +4451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4474,7 +4477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4500,7 +4503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4526,7 +4529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4552,7 +4555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4578,7 +4581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4604,7 +4607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4630,7 +4633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4656,7 +4659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4682,7 +4685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4708,7 +4711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4734,7 +4737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4760,7 +4763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4786,7 +4789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4812,7 +4815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4838,7 +4841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4862,7 +4865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4912,7 +4915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45904</v>
       </c>
@@ -4938,7 +4941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -4964,7 +4967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -4990,7 +4993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -5016,7 +5019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -5042,7 +5045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5068,7 +5071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5094,7 +5097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5120,7 +5123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5146,7 +5149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45908</v>
       </c>
@@ -5172,7 +5175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5198,7 +5201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5224,7 +5227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5250,7 +5253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45909</v>
       </c>
@@ -5276,7 +5279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5302,7 +5305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5328,7 +5331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5354,7 +5357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5380,7 +5383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5406,7 +5409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45910</v>
       </c>
@@ -5432,7 +5435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5452,7 +5455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5478,7 +5481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5504,7 +5507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5530,7 +5533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5556,7 +5559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5582,7 +5585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45911</v>
       </c>
@@ -5602,7 +5605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5628,7 +5631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5654,7 +5657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5680,7 +5683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5706,7 +5709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5732,7 +5735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5758,7 +5761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5784,7 +5787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5810,7 +5813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5836,7 +5839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5862,7 +5865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5888,7 +5891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5914,7 +5917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45915</v>
       </c>
@@ -5940,7 +5943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -5966,7 +5969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -5992,7 +5995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -6018,7 +6021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -6044,7 +6047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6070,7 +6073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6096,7 +6099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45916</v>
       </c>
@@ -6122,7 +6125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6148,7 +6151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6174,7 +6177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6200,7 +6203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6226,7 +6229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45917</v>
       </c>
@@ -6252,7 +6255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6278,7 +6281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6304,7 +6307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6330,7 +6333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6356,7 +6359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6382,7 +6385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6408,7 +6411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45918</v>
       </c>
@@ -6434,7 +6437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6460,7 +6463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6486,7 +6489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6512,7 +6515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6538,7 +6541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6564,7 +6567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6590,7 +6593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6616,7 +6619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6642,7 +6645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6668,7 +6671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6688,7 +6691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6714,7 +6717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6740,7 +6743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45922</v>
       </c>
@@ -6766,7 +6769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6792,7 +6795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6818,7 +6821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6844,7 +6847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6870,7 +6873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6896,7 +6899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6922,7 +6925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45923</v>
       </c>
@@ -6948,7 +6951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -6974,7 +6977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -7000,7 +7003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -7026,7 +7029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -7052,7 +7055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7078,7 +7081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45924</v>
       </c>
@@ -7104,7 +7107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7130,7 +7133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7156,7 +7159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7182,7 +7185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7208,7 +7211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7234,7 +7237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7260,7 +7263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7286,7 +7289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45925</v>
       </c>
@@ -7312,7 +7315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7338,7 +7341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7364,7 +7367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7390,7 +7393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7416,7 +7419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7442,7 +7445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7468,7 +7471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7494,7 +7497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7520,7 +7523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7546,7 +7549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45929</v>
       </c>
@@ -7572,7 +7575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7598,7 +7601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7624,7 +7627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7650,7 +7653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7676,7 +7679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7728,7 +7731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7754,7 +7757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45930</v>
       </c>
@@ -7780,7 +7783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7806,7 +7809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7832,7 +7835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7858,7 +7861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7884,7 +7887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7910,7 +7913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45931</v>
       </c>
@@ -7936,7 +7939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -7962,7 +7965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -7988,7 +7991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -8014,7 +8017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8040,7 +8043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8066,7 +8069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8092,7 +8095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8118,7 +8121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45932</v>
       </c>
@@ -8144,7 +8147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8170,7 +8173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8196,7 +8199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8222,7 +8225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8248,7 +8251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8274,7 +8277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8301,7 +8304,7 @@
       </c>
       <c r="O273" s="19"/>
     </row>
-    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8327,7 +8330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8353,7 +8356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8379,7 +8382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8405,7 +8408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45903</v>
       </c>
@@ -8431,7 +8434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8457,7 +8460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8483,7 +8486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8509,7 +8512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8535,7 +8538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8561,7 +8564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8587,7 +8590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8613,7 +8616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8639,7 +8642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8665,7 +8668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8691,7 +8694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8717,7 +8720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8743,7 +8746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8769,7 +8772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8795,7 +8798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8821,7 +8824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8847,7 +8850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8873,7 +8876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8899,7 +8902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -8925,7 +8928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -8951,7 +8954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -8977,7 +8980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -9003,7 +9006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9048,7 +9051,7 @@
       <c r="L302" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="M302" s="20" t="s">
+      <c r="M302" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N302" s="6">
@@ -9185,7 +9188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G308" s="4"/>
       <c r="H308" s="4"/>
       <c r="I308" s="6"/>
@@ -9195,7 +9198,7 @@
       <c r="M308" s="4"/>
       <c r="N308" s="6"/>
     </row>
-    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G309" s="4"/>
       <c r="H309" s="4"/>
       <c r="I309" s="6"/>
@@ -9205,7 +9208,7 @@
       <c r="M309" s="4"/>
       <c r="N309" s="6"/>
     </row>
-    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9231,7 +9234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9257,7 +9260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9283,7 +9286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9309,7 +9312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9335,7 +9338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9361,7 +9364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45939</v>
       </c>
@@ -9387,7 +9390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45939</v>
       </c>
@@ -9413,7 +9416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45939</v>
       </c>
@@ -9439,7 +9442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45939</v>
       </c>
@@ -9465,7 +9468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45939</v>
       </c>
@@ -9491,7 +9494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45939</v>
       </c>
@@ -9517,7 +9520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45939</v>
       </c>
@@ -9543,7 +9546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45939</v>
       </c>
@@ -9569,7 +9572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45940</v>
       </c>
@@ -9596,27 +9599,209 @@
       </c>
     </row>
     <row r="325" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G325" s="4"/>
-      <c r="H325" s="4"/>
-      <c r="I325" s="6"/>
+      <c r="G325" s="3">
+        <v>45944</v>
+      </c>
+      <c r="H325" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I325" s="6" t="s">
+        <v>153</v>
+      </c>
       <c r="J325" s="4"/>
       <c r="K325" s="9"/>
       <c r="L325" s="4"/>
-      <c r="M325" s="4"/>
-      <c r="N325" s="6"/>
+      <c r="M325" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N325" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="326" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G326" s="4"/>
-      <c r="H326" s="4"/>
-      <c r="I326" s="6"/>
+      <c r="G326" s="3">
+        <v>45944</v>
+      </c>
+      <c r="H326" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I326" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="J326" s="4"/>
       <c r="K326" s="9"/>
       <c r="L326" s="4"/>
-      <c r="M326" s="4"/>
-      <c r="N326" s="6"/>
+      <c r="M326" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N326" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G327" s="3">
+        <v>45944</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I327" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J327" s="4"/>
+      <c r="K327" s="9"/>
+      <c r="L327" s="4"/>
+      <c r="M327" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N327" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G328" s="3">
+        <v>45944</v>
+      </c>
+      <c r="H328" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I328" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J328" s="4"/>
+      <c r="K328" s="9"/>
+      <c r="L328" s="4"/>
+      <c r="M328" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N328" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G329" s="3">
+        <v>45944</v>
+      </c>
+      <c r="H329" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="I329" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J329" s="4"/>
+      <c r="K329" s="9"/>
+      <c r="L329" s="4"/>
+      <c r="M329" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N329" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G330" s="3">
+        <v>45944</v>
+      </c>
+      <c r="H330" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I330" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J330" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K330" s="9">
+        <v>160</v>
+      </c>
+      <c r="L330" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="M330" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N330" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="331" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G331" s="4"/>
+      <c r="H331" s="4"/>
+      <c r="I331" s="6"/>
+      <c r="J331" s="4"/>
+      <c r="K331" s="9"/>
+      <c r="L331" s="4"/>
+      <c r="M331" s="4"/>
+      <c r="N331" s="6"/>
+    </row>
+    <row r="332" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G332" s="4"/>
+      <c r="H332" s="4"/>
+      <c r="I332" s="6"/>
+      <c r="J332" s="4"/>
+      <c r="K332" s="9"/>
+      <c r="L332" s="4"/>
+      <c r="M332" s="4"/>
+      <c r="N332" s="6"/>
+    </row>
+    <row r="333" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G333" s="4"/>
+      <c r="H333" s="4"/>
+      <c r="I333" s="6"/>
+      <c r="J333" s="4"/>
+      <c r="K333" s="9"/>
+      <c r="L333" s="4"/>
+      <c r="M333" s="4"/>
+      <c r="N333" s="6"/>
+    </row>
+    <row r="334" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G334" s="4"/>
+      <c r="H334" s="4"/>
+      <c r="I334" s="6"/>
+      <c r="J334" s="4"/>
+      <c r="K334" s="9"/>
+      <c r="L334" s="4"/>
+      <c r="M334" s="4"/>
+      <c r="N334" s="6"/>
+    </row>
+    <row r="335" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G335" s="4"/>
+      <c r="H335" s="4"/>
+      <c r="I335" s="6"/>
+      <c r="J335" s="4"/>
+      <c r="K335" s="9"/>
+      <c r="L335" s="4"/>
+      <c r="M335" s="4"/>
+      <c r="N335" s="6"/>
+    </row>
+    <row r="336" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G336" s="4"/>
+      <c r="H336" s="4"/>
+      <c r="I336" s="6"/>
+      <c r="J336" s="4"/>
+      <c r="K336" s="9"/>
+      <c r="L336" s="4"/>
+      <c r="M336" s="4"/>
+      <c r="N336" s="6"/>
+    </row>
+    <row r="337" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G337" s="4"/>
+      <c r="H337" s="4"/>
+      <c r="I337" s="6"/>
+      <c r="J337" s="4"/>
+      <c r="K337" s="9"/>
+      <c r="L337" s="4"/>
+      <c r="M337" s="4"/>
+      <c r="N337" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N324" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N324" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2025" month="10" day="13" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1667" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32307686-C7AB-4D8B-B730-86601E647A46}"/>
+  <xr:revisionPtr revIDLastSave="1684" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4B9F7C8-F597-4CFA-A8C0-F273239E8880}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$330</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="267">
   <si>
     <t>DATA</t>
   </si>
@@ -82,9 +82,6 @@
     <t>SANTO ANTONIO DO AMPARO</t>
   </si>
   <si>
-    <t>TRES PONTAS</t>
-  </si>
-  <si>
     <t>GUANHAES</t>
   </si>
   <si>
@@ -836,6 +833,12 @@
   </si>
   <si>
     <t>HOTEL JOAZINHO</t>
+  </si>
+  <si>
+    <t>HOTEL SANTOS DUMMONT</t>
+  </si>
+  <si>
+    <t>TRÊS PONTAS</t>
   </si>
 </sst>
 </file>
@@ -1338,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>1</v>
@@ -1356,7 +1359,7 @@
         <v>3</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
@@ -1364,19 +1367,19 @@
         <v>45873</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6" s="9">
         <v>170</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>7</v>
@@ -1390,19 +1393,19 @@
         <v>45873</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K7" s="9">
         <v>74.900000000000006</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>7</v>
@@ -1416,19 +1419,19 @@
         <v>45873</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K8" s="9">
         <v>80</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>7</v>
@@ -1442,19 +1445,19 @@
         <v>45873</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K9" s="9">
         <v>110</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>7</v>
@@ -1468,19 +1471,19 @@
         <v>45875</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K10" s="9">
         <v>170</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>7</v>
@@ -1494,19 +1497,19 @@
         <v>45875</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K11" s="9">
         <v>150</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>7</v>
@@ -1520,19 +1523,19 @@
         <v>45875</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K12" s="9">
         <v>85</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>7</v>
@@ -1546,19 +1549,19 @@
         <v>45875</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K13" s="9">
         <v>135</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>7</v>
@@ -1572,19 +1575,19 @@
         <v>45875</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K14" s="9">
         <v>100</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>7</v>
@@ -1598,19 +1601,19 @@
         <v>45875</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K15" s="9">
         <v>178</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>7</v>
@@ -1624,19 +1627,19 @@
         <v>45875</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K16" s="5">
         <v>80</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>7</v>
@@ -1650,10 +1653,10 @@
         <v>45875</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>5</v>
@@ -1676,19 +1679,19 @@
         <v>45876</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K18" s="10">
         <v>74.900000000000006</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>7</v>
@@ -1702,19 +1705,19 @@
         <v>45876</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K19" s="10">
         <v>120</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>7</v>
@@ -1728,19 +1731,19 @@
         <v>45876</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K20" s="10">
         <v>170</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>7</v>
@@ -1754,19 +1757,19 @@
         <v>45876</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K21" s="10">
         <v>150</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>7</v>
@@ -1780,19 +1783,19 @@
         <v>45876</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K22" s="10">
         <v>150</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>7</v>
@@ -1806,19 +1809,19 @@
         <v>45876</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K23" s="10">
         <v>110</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>7</v>
@@ -1832,19 +1835,19 @@
         <v>45876</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K24" s="10">
         <v>130</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>7</v>
@@ -1858,19 +1861,19 @@
         <v>45876</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K25" s="10">
         <v>75</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>7</v>
@@ -1884,19 +1887,19 @@
         <v>45876</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K26" s="10">
         <v>85</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>7</v>
@@ -1910,19 +1913,19 @@
         <v>45876</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K27" s="10">
         <v>100</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>7</v>
@@ -1936,19 +1939,19 @@
         <v>45876</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K28" s="10">
         <v>100</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>7</v>
@@ -1962,19 +1965,19 @@
         <v>45880</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K29" s="5">
         <v>100</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>7</v>
@@ -1988,19 +1991,19 @@
         <v>45880</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K30" s="5">
         <v>74.900000000000006</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>7</v>
@@ -2014,19 +2017,19 @@
         <v>45880</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K31" s="5">
         <v>140</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>7</v>
@@ -2040,19 +2043,19 @@
         <v>45880</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K32" s="5">
         <v>95</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>7</v>
@@ -2066,19 +2069,19 @@
         <v>45880</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K33" s="5">
         <v>160</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>7</v>
@@ -2092,19 +2095,19 @@
         <v>45881</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K34" s="5">
         <v>150</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>7</v>
@@ -2118,19 +2121,19 @@
         <v>45881</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K35" s="5">
         <v>160</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>7</v>
@@ -2144,19 +2147,19 @@
         <v>45881</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K36" s="5">
         <v>140</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>7</v>
@@ -2170,19 +2173,19 @@
         <v>45881</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K37" s="5">
         <v>150</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>7</v>
@@ -2196,10 +2199,10 @@
         <v>45881</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>10</v>
@@ -2222,10 +2225,10 @@
         <v>45881</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>5</v>
@@ -2248,19 +2251,19 @@
         <v>45881</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K40" s="5">
         <v>105</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>7</v>
@@ -2274,19 +2277,19 @@
         <v>45882</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K41" s="5">
         <v>220</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M41" s="4" t="s">
         <v>7</v>
@@ -2300,19 +2303,19 @@
         <v>45882</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K42" s="5">
         <v>175</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>7</v>
@@ -2326,19 +2329,19 @@
         <v>45882</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K43" s="5">
         <v>180</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>7</v>
@@ -2352,19 +2355,19 @@
         <v>45882</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K44" s="5">
         <v>160</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>7</v>
@@ -2378,19 +2381,19 @@
         <v>45882</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K45" s="5">
         <v>115</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>7</v>
@@ -2404,19 +2407,19 @@
         <v>45882</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K46" s="5">
         <v>100</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>7</v>
@@ -2430,10 +2433,10 @@
         <v>45883</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J47" s="17" t="s">
         <v>5</v>
@@ -2456,19 +2459,19 @@
         <v>45883</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K48" s="5">
         <v>140</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>7</v>
@@ -2482,19 +2485,19 @@
         <v>45883</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K49" s="5">
         <v>200</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>8</v>
@@ -2508,19 +2511,19 @@
         <v>45883</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K50" s="5">
         <v>129</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>7</v>
@@ -2534,19 +2537,19 @@
         <v>45883</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K51" s="5">
         <v>149</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>8</v>
@@ -2560,19 +2563,19 @@
         <v>45883</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K52" s="5">
         <v>160</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M52" s="4" t="s">
         <v>7</v>
@@ -2586,19 +2589,19 @@
         <v>45883</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J53" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K53" s="5">
         <v>150</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>7</v>
@@ -2612,10 +2615,10 @@
         <v>45883</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J54" s="17" t="s">
         <v>5</v>
@@ -2638,19 +2641,19 @@
         <v>45883</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K55" s="5">
         <v>140</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>7</v>
@@ -2664,19 +2667,19 @@
         <v>45883</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J56" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K56" s="5">
         <v>188</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M56" s="4" t="s">
         <v>7</v>
@@ -2690,19 +2693,19 @@
         <v>45883</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K57" s="5">
         <v>99</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M57" s="4" t="s">
         <v>7</v>
@@ -2716,19 +2719,19 @@
         <v>45883</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J58" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K58" s="5">
         <v>75</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>7</v>
@@ -2742,19 +2745,19 @@
         <v>45883</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K59" s="5">
         <v>75</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>7</v>
@@ -2768,19 +2771,19 @@
         <v>45883</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J60" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K60" s="5">
         <v>150</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>7</v>
@@ -2794,19 +2797,19 @@
         <v>45883</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J61" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K61" s="5">
         <v>100</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>7</v>
@@ -2820,19 +2823,19 @@
         <v>45883</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J62" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K62" s="5">
         <v>80</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M62" s="4" t="s">
         <v>7</v>
@@ -2846,19 +2849,19 @@
         <v>45887</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J63" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K63" s="5">
         <v>150</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>7</v>
@@ -2872,19 +2875,19 @@
         <v>45887</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K64" s="5">
         <v>149</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>7</v>
@@ -2898,19 +2901,19 @@
         <v>45887</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J65" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K65" s="5">
         <v>110</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M65" s="4" t="s">
         <v>7</v>
@@ -2924,19 +2927,19 @@
         <v>45887</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J66" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K66" s="5">
         <v>140</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M66" s="4" t="s">
         <v>7</v>
@@ -2950,19 +2953,19 @@
         <v>45887</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K67" s="5">
         <v>175</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M67" s="4" t="s">
         <v>7</v>
@@ -2976,19 +2979,19 @@
         <v>45887</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K68" s="5">
         <v>90</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M68" s="4" t="s">
         <v>7</v>
@@ -3002,19 +3005,19 @@
         <v>45887</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K69" s="5">
         <v>135</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M69" s="4" t="s">
         <v>7</v>
@@ -3028,19 +3031,19 @@
         <v>45888</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K70" s="5">
         <v>220</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>8</v>
@@ -3054,19 +3057,19 @@
         <v>45888</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J71" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K71" s="5">
         <v>170</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>8</v>
@@ -3080,19 +3083,19 @@
         <v>45888</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K72" s="5">
         <v>110</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>7</v>
@@ -3106,10 +3109,10 @@
         <v>45888</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J73" s="17" t="s">
         <v>10</v>
@@ -3132,19 +3135,19 @@
         <v>45888</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J74" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K74" s="5">
         <v>175</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M74" s="4" t="s">
         <v>7</v>
@@ -3158,19 +3161,19 @@
         <v>45889</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K75" s="5">
         <v>130</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>7</v>
@@ -3184,19 +3187,19 @@
         <v>45889</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K76" s="5">
         <v>80</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M76" s="4" t="s">
         <v>7</v>
@@ -3210,19 +3213,19 @@
         <v>45889</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J77" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K77" s="5">
         <v>155</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>8</v>
@@ -3236,19 +3239,19 @@
         <v>45889</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K78" s="5">
         <v>150</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>7</v>
@@ -3262,19 +3265,19 @@
         <v>45889</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K79" s="5">
         <v>170</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>8</v>
@@ -3288,19 +3291,19 @@
         <v>45889</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K80" s="5">
         <v>80</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>7</v>
@@ -3314,19 +3317,19 @@
         <v>45889</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K81" s="5">
         <v>190</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M81" s="4" t="s">
         <v>8</v>
@@ -3340,19 +3343,19 @@
         <v>45890</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K82" s="5">
         <v>200</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>8</v>
@@ -3366,19 +3369,19 @@
         <v>45890</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K83" s="5">
         <v>130</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>7</v>
@@ -3392,19 +3395,19 @@
         <v>45890</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K84" s="5">
         <v>120</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>7</v>
@@ -3418,19 +3421,19 @@
         <v>45890</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K85" s="5">
         <v>100</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>7</v>
@@ -3444,19 +3447,19 @@
         <v>45890</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K86" s="5">
         <v>220</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>8</v>
@@ -3470,19 +3473,19 @@
         <v>45890</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K87" s="5">
         <v>159</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>7</v>
@@ -3496,19 +3499,19 @@
         <v>45890</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K88" s="5">
         <v>200</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>8</v>
@@ -3522,10 +3525,10 @@
         <v>45890</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J89" s="17" t="s">
         <v>10</v>
@@ -3548,10 +3551,10 @@
         <v>45890</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J90" s="17" t="s">
         <v>5</v>
@@ -3560,7 +3563,7 @@
         <v>140</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>7</v>
@@ -3574,19 +3577,19 @@
         <v>45890</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K91" s="5">
         <v>120</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>7</v>
@@ -3598,19 +3601,19 @@
         <v>45890</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K92" s="5">
         <v>75</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M92" s="4" t="s">
         <v>7</v>
@@ -3624,19 +3627,19 @@
         <v>45894</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K93" s="5">
         <v>180</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M93" s="4" t="s">
         <v>7</v>
@@ -3650,19 +3653,19 @@
         <v>45894</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K94" s="5">
         <v>149</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M94" s="4" t="s">
         <v>8</v>
@@ -3676,19 +3679,19 @@
         <v>45894</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J95" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K95" s="5">
         <v>140</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M95" s="4" t="s">
         <v>7</v>
@@ -3702,19 +3705,19 @@
         <v>45894</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K96" s="5">
         <v>175</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M96" s="4" t="s">
         <v>8</v>
@@ -3728,10 +3731,10 @@
         <v>45895</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J97" s="17" t="s">
         <v>11</v>
@@ -3740,7 +3743,7 @@
         <v>120</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M97" s="4" t="s">
         <v>7</v>
@@ -3754,10 +3757,10 @@
         <v>45895</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J98" s="17" t="s">
         <v>13</v>
@@ -3780,19 +3783,19 @@
         <v>45895</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J99" s="17" t="s">
-        <v>14</v>
+        <v>144</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="K99" s="5">
         <v>178</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M99" s="4" t="s">
         <v>7</v>
@@ -3806,19 +3809,19 @@
         <v>45895</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K100" s="5">
         <v>150</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M100" s="4" t="s">
         <v>7</v>
@@ -3832,10 +3835,10 @@
         <v>45895</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J101" s="17" t="s">
         <v>10</v>
@@ -3858,19 +3861,19 @@
         <v>45895</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K102" s="5">
         <v>80</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M102" s="4" t="s">
         <v>7</v>
@@ -3884,10 +3887,10 @@
         <v>45895</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J103" s="17" t="s">
         <v>5</v>
@@ -3910,19 +3913,19 @@
         <v>45896</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K104" s="5">
         <v>55</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M104" s="4" t="s">
         <v>7</v>
@@ -3936,19 +3939,19 @@
         <v>45896</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K105" s="5">
         <v>155</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>8</v>
@@ -3962,19 +3965,19 @@
         <v>45896</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J106" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K106" s="5">
         <v>140</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>7</v>
@@ -3988,19 +3991,19 @@
         <v>45896</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J107" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K107" s="5">
         <v>85</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>7</v>
@@ -4014,19 +4017,19 @@
         <v>45896</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J108" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K108" s="5">
         <v>110</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M108" s="4" t="s">
         <v>7</v>
@@ -4040,19 +4043,19 @@
         <v>45896</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J109" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K109" s="5">
         <v>120</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M109" s="4" t="s">
         <v>7</v>
@@ -4066,19 +4069,19 @@
         <v>45896</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K110" s="5">
         <v>230</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M110" s="4" t="s">
         <v>8</v>
@@ -4092,19 +4095,19 @@
         <v>45896</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K111" s="5">
         <v>150</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M111" s="4" t="s">
         <v>7</v>
@@ -4118,19 +4121,19 @@
         <v>45897</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K112" s="9">
         <v>69</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M112" s="4" t="s">
         <v>7</v>
@@ -4144,19 +4147,19 @@
         <v>45897</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J113" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K113" s="9">
         <v>200</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M113" s="4" t="s">
         <v>8</v>
@@ -4170,19 +4173,19 @@
         <v>45897</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J114" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K114" s="9">
         <v>140</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M114" s="4" t="s">
         <v>8</v>
@@ -4196,19 +4199,19 @@
         <v>45897</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K115" s="9">
         <v>115</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M115" s="4" t="s">
         <v>7</v>
@@ -4222,19 +4225,19 @@
         <v>45897</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K116" s="9">
         <v>209</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M116" s="4" t="s">
         <v>8</v>
@@ -4248,19 +4251,19 @@
         <v>45897</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K117" s="9">
         <v>200</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>8</v>
@@ -4274,19 +4277,19 @@
         <v>45897</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J118" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K118" s="9">
         <v>160</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M118" s="4" t="s">
         <v>8</v>
@@ -4300,10 +4303,10 @@
         <v>45897</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J119" s="17" t="s">
         <v>10</v>
@@ -4326,10 +4329,10 @@
         <v>45897</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J120" s="17" t="s">
         <v>5</v>
@@ -4352,19 +4355,19 @@
         <v>45897</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J121" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K121" s="9">
         <v>115</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>7</v>
@@ -4378,19 +4381,19 @@
         <v>45897</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J122" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K122" s="9">
         <v>110</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M122" s="4" t="s">
         <v>7</v>
@@ -4404,19 +4407,19 @@
         <v>45901</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J123" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K123" s="9">
         <v>220</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M123" s="4" t="s">
         <v>8</v>
@@ -4430,19 +4433,19 @@
         <v>45901</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J124" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K124" s="9">
         <v>209</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M124" s="4" t="s">
         <v>8</v>
@@ -4456,19 +4459,19 @@
         <v>45901</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J125" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K125" s="9">
         <v>140</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M125" s="4" t="s">
         <v>7</v>
@@ -4482,19 +4485,19 @@
         <v>45901</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J126" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K126" s="9">
         <v>175</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M126" s="4" t="s">
         <v>8</v>
@@ -4508,19 +4511,19 @@
         <v>45902</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J127" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K127" s="9">
         <v>175</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M127" s="4" t="s">
         <v>7</v>
@@ -4534,19 +4537,19 @@
         <v>45902</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J128" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K128" s="9">
         <v>240</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M128" s="4" t="s">
         <v>8</v>
@@ -4560,19 +4563,19 @@
         <v>45902</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J129" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K129" s="9">
         <v>160</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M129" s="4" t="s">
         <v>8</v>
@@ -4586,10 +4589,10 @@
         <v>45902</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J130" s="17" t="s">
         <v>10</v>
@@ -4612,19 +4615,19 @@
         <v>45902</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J131" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K131" s="9">
         <v>150</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>8</v>
@@ -4638,19 +4641,19 @@
         <v>45902</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J132" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K132" s="9">
         <v>220</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M132" s="4" t="s">
         <v>8</v>
@@ -4664,19 +4667,19 @@
         <v>45902</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K133" s="9">
         <v>220</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>8</v>
@@ -4690,19 +4693,19 @@
         <v>45903</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K134" s="9">
         <v>140</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>8</v>
@@ -4716,19 +4719,19 @@
         <v>45903</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K135" s="9">
         <v>240</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M135" s="4" t="s">
         <v>8</v>
@@ -4742,19 +4745,19 @@
         <v>45903</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K136" s="9">
         <v>200</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M136" s="4" t="s">
         <v>8</v>
@@ -4768,19 +4771,19 @@
         <v>45903</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K137" s="9">
         <v>170</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M137" s="4" t="s">
         <v>8</v>
@@ -4794,19 +4797,19 @@
         <v>45903</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K138" s="9">
         <v>170</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M138" s="4" t="s">
         <v>8</v>
@@ -4820,19 +4823,19 @@
         <v>45903</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K139" s="9">
         <v>200</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M139" s="4" t="s">
         <v>8</v>
@@ -4846,13 +4849,13 @@
         <v>45903</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K140" s="9">
         <v>200</v>
@@ -4870,19 +4873,19 @@
         <v>45903</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K141" s="9">
         <v>120</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>8</v>
@@ -4896,13 +4899,13 @@
         <v>45903</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K142" s="9">
         <v>200</v>
@@ -4920,19 +4923,19 @@
         <v>45904</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K143" s="9">
         <v>185</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>8</v>
@@ -4946,19 +4949,19 @@
         <v>45904</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K144" s="9">
         <v>198</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M144" s="4" t="s">
         <v>8</v>
@@ -4972,19 +4975,19 @@
         <v>45904</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K145" s="9">
         <v>230</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M145" s="4" t="s">
         <v>8</v>
@@ -4998,19 +5001,19 @@
         <v>45904</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K146" s="9">
         <v>190</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M146" s="4" t="s">
         <v>8</v>
@@ -5024,19 +5027,19 @@
         <v>45904</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K147" s="9">
         <v>200</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M147" s="4" t="s">
         <v>8</v>
@@ -5050,19 +5053,19 @@
         <v>45904</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K148" s="9">
         <v>209</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M148" s="4" t="s">
         <v>8</v>
@@ -5076,10 +5079,10 @@
         <v>45904</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>5</v>
@@ -5088,7 +5091,7 @@
         <v>220</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M149" s="4" t="s">
         <v>8</v>
@@ -5102,19 +5105,19 @@
         <v>45904</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K150" s="9">
         <v>160</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M150" s="4" t="s">
         <v>8</v>
@@ -5128,19 +5131,19 @@
         <v>45904</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K151" s="9">
         <v>230</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M151" s="4" t="s">
         <v>8</v>
@@ -5154,19 +5157,19 @@
         <v>45908</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K152" s="9">
         <v>220</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M152" s="4" t="s">
         <v>8</v>
@@ -5180,19 +5183,19 @@
         <v>45908</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K153" s="9">
         <v>159</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M153" s="4" t="s">
         <v>8</v>
@@ -5206,19 +5209,19 @@
         <v>45908</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K154" s="9">
         <v>240</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M154" s="4" t="s">
         <v>8</v>
@@ -5232,19 +5235,19 @@
         <v>45908</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K155" s="9">
         <v>175</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M155" s="4" t="s">
         <v>8</v>
@@ -5258,19 +5261,19 @@
         <v>45909</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K156" s="9">
         <v>200</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M156" s="4" t="s">
         <v>8</v>
@@ -5284,19 +5287,19 @@
         <v>45909</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K157" s="9">
         <v>240</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M157" s="4" t="s">
         <v>8</v>
@@ -5310,10 +5313,10 @@
         <v>45909</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>10</v>
@@ -5336,19 +5339,19 @@
         <v>45909</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K159" s="9">
         <v>220</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M159" s="4" t="s">
         <v>8</v>
@@ -5362,19 +5365,19 @@
         <v>45909</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J160" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K160" s="9">
         <v>175</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M160" s="4" t="s">
         <v>7</v>
@@ -5388,19 +5391,19 @@
         <v>45909</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K161" s="9">
         <v>200</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M161" s="4" t="s">
         <v>8</v>
@@ -5414,19 +5417,19 @@
         <v>45910</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K162" s="9">
         <v>160</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M162" s="4" t="s">
         <v>8</v>
@@ -5440,10 +5443,10 @@
         <v>45910</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J163" s="4"/>
       <c r="K163" s="9"/>
@@ -5460,19 +5463,19 @@
         <v>45910</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K164" s="9">
         <v>200</v>
       </c>
       <c r="L164" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M164" s="4" t="s">
         <v>8</v>
@@ -5486,19 +5489,19 @@
         <v>45910</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K165" s="9">
         <v>170</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>8</v>
@@ -5512,19 +5515,19 @@
         <v>45910</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K166" s="9">
         <v>170</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M166" s="4" t="s">
         <v>8</v>
@@ -5538,19 +5541,19 @@
         <v>45910</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K167" s="9">
         <v>190</v>
       </c>
       <c r="L167" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M167" s="4" t="s">
         <v>8</v>
@@ -5564,19 +5567,19 @@
         <v>45910</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K168" s="9">
         <v>198</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M168" s="4" t="s">
         <v>8</v>
@@ -5590,10 +5593,10 @@
         <v>45911</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J169" s="4"/>
       <c r="K169" s="9"/>
@@ -5610,19 +5613,19 @@
         <v>45911</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K170" s="9">
         <v>170</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M170" s="4" t="s">
         <v>8</v>
@@ -5636,19 +5639,19 @@
         <v>45911</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K171" s="9">
         <v>198</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M171" s="4" t="s">
         <v>8</v>
@@ -5662,19 +5665,19 @@
         <v>45911</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K172" s="9">
         <v>170</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M172" s="4" t="s">
         <v>8</v>
@@ -5688,19 +5691,19 @@
         <v>45911</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J173" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K173" s="9">
         <v>235</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M173" s="4" t="s">
         <v>8</v>
@@ -5714,19 +5717,19 @@
         <v>45911</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K174" s="9">
         <v>250</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M174" s="4" t="s">
         <v>8</v>
@@ -5740,19 +5743,19 @@
         <v>45911</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K175" s="9">
         <v>220</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>8</v>
@@ -5766,19 +5769,19 @@
         <v>45911</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K176" s="9">
         <v>200</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M176" s="4" t="s">
         <v>8</v>
@@ -5792,19 +5795,19 @@
         <v>45911</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K177" s="9">
         <v>209</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M177" s="4" t="s">
         <v>8</v>
@@ -5818,19 +5821,19 @@
         <v>45911</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K178" s="9">
         <v>220</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M178" s="4" t="s">
         <v>8</v>
@@ -5844,19 +5847,19 @@
         <v>45911</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K179" s="9">
         <v>260</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M179" s="4" t="s">
         <v>8</v>
@@ -5870,19 +5873,19 @@
         <v>45911</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K180" s="9">
         <v>198</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M180" s="4" t="s">
         <v>8</v>
@@ -5896,19 +5899,19 @@
         <v>45911</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K181" s="9">
         <v>280</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M181" s="4" t="s">
         <v>8</v>
@@ -5922,19 +5925,19 @@
         <v>45915</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K182" s="9">
         <v>140</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M182" s="4" t="s">
         <v>7</v>
@@ -5948,19 +5951,19 @@
         <v>45915</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K183" s="9">
         <v>220</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M183" s="4" t="s">
         <v>8</v>
@@ -5974,19 +5977,19 @@
         <v>45915</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K184" s="9">
         <v>209</v>
       </c>
       <c r="L184" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M184" s="4" t="s">
         <v>8</v>
@@ -6000,19 +6003,19 @@
         <v>45915</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K185" s="9">
         <v>175</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M185" s="4" t="s">
         <v>8</v>
@@ -6026,19 +6029,19 @@
         <v>45915</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K186" s="9">
         <v>220</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M186" s="4" t="s">
         <v>8</v>
@@ -6052,19 +6055,19 @@
         <v>45915</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K187" s="9">
         <v>200</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M187" s="4" t="s">
         <v>8</v>
@@ -6078,19 +6081,19 @@
         <v>45915</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K188" s="9">
         <v>259</v>
       </c>
       <c r="L188" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M188" s="4" t="s">
         <v>8</v>
@@ -6104,10 +6107,10 @@
         <v>45916</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>11</v>
@@ -6116,7 +6119,7 @@
         <v>120</v>
       </c>
       <c r="L189" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M189" s="4" t="s">
         <v>7</v>
@@ -6130,19 +6133,19 @@
         <v>45916</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K190" s="9">
         <v>200</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M190" s="4" t="s">
         <v>8</v>
@@ -6156,19 +6159,19 @@
         <v>45916</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K191" s="9">
         <v>200</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M191" s="4" t="s">
         <v>8</v>
@@ -6182,19 +6185,19 @@
         <v>45916</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K192" s="9">
         <v>170</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M192" s="4" t="s">
         <v>8</v>
@@ -6208,10 +6211,10 @@
         <v>45916</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>10</v>
@@ -6234,19 +6237,19 @@
         <v>45917</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K194" s="9">
         <v>150</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M194" s="4" t="s">
         <v>8</v>
@@ -6260,19 +6263,19 @@
         <v>45917</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K195" s="9">
         <v>240</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M195" s="4" t="s">
         <v>8</v>
@@ -6286,19 +6289,19 @@
         <v>45917</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K196" s="9">
         <v>220</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M196" s="4" t="s">
         <v>8</v>
@@ -6312,19 +6315,19 @@
         <v>45917</v>
       </c>
       <c r="H197" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K197" s="9">
         <v>280</v>
       </c>
       <c r="L197" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M197" s="4" t="s">
         <v>8</v>
@@ -6338,19 +6341,19 @@
         <v>45917</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K198" s="9">
         <v>230</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M198" s="4" t="s">
         <v>8</v>
@@ -6364,19 +6367,19 @@
         <v>45917</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K199" s="9">
         <v>230</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M199" s="4" t="s">
         <v>8</v>
@@ -6390,19 +6393,19 @@
         <v>45917</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K200" s="9">
         <v>190</v>
       </c>
       <c r="L200" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M200" s="4" t="s">
         <v>8</v>
@@ -6416,19 +6419,19 @@
         <v>45918</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K201" s="9">
         <v>180</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M201" s="4" t="s">
         <v>8</v>
@@ -6442,19 +6445,19 @@
         <v>45918</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K202" s="9">
         <v>198</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M202" s="4" t="s">
         <v>8</v>
@@ -6468,19 +6471,19 @@
         <v>45918</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K203" s="9">
         <v>170</v>
       </c>
       <c r="L203" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M203" s="4" t="s">
         <v>8</v>
@@ -6494,19 +6497,19 @@
         <v>45918</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K204" s="9">
         <v>200</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M204" s="4" t="s">
         <v>8</v>
@@ -6520,19 +6523,19 @@
         <v>45918</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K205" s="9">
         <v>150</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M205" s="4" t="s">
         <v>8</v>
@@ -6546,10 +6549,10 @@
         <v>45918</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>13</v>
@@ -6558,7 +6561,7 @@
         <v>200</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M206" s="4" t="s">
         <v>8</v>
@@ -6572,19 +6575,19 @@
         <v>45918</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K207" s="9">
         <v>159</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M207" s="4" t="s">
         <v>8</v>
@@ -6598,19 +6601,19 @@
         <v>45918</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K208" s="9">
         <v>230</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M208" s="4" t="s">
         <v>8</v>
@@ -6624,19 +6627,19 @@
         <v>45918</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I209" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K209" s="9">
         <v>175</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M209" s="4" t="s">
         <v>8</v>
@@ -6650,19 +6653,19 @@
         <v>45918</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I210" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K210" s="9">
         <v>260</v>
       </c>
       <c r="L210" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M210" s="4" t="s">
         <v>8</v>
@@ -6676,10 +6679,10 @@
         <v>45918</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I211" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J211" s="4"/>
       <c r="K211" s="9"/>
@@ -6696,19 +6699,19 @@
         <v>45918</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K212" s="9">
         <v>185</v>
       </c>
       <c r="L212" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M212" s="4" t="s">
         <v>8</v>
@@ -6722,19 +6725,19 @@
         <v>45918</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I213" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K213" s="9">
         <v>240</v>
       </c>
       <c r="L213" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M213" s="4" t="s">
         <v>8</v>
@@ -6748,19 +6751,19 @@
         <v>45922</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I214" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K214" s="9">
         <v>170</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M214" s="4" t="s">
         <v>8</v>
@@ -6774,19 +6777,19 @@
         <v>45922</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K215" s="9">
         <v>209</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M215" s="4" t="s">
         <v>8</v>
@@ -6800,19 +6803,19 @@
         <v>45922</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K216" s="9">
         <v>200</v>
       </c>
       <c r="L216" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M216" s="4" t="s">
         <v>8</v>
@@ -6826,19 +6829,19 @@
         <v>45922</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K217" s="9">
         <v>220</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M217" s="4" t="s">
         <v>8</v>
@@ -6852,19 +6855,19 @@
         <v>45922</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K218" s="9">
         <v>250</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M218" s="4" t="s">
         <v>8</v>
@@ -6878,19 +6881,19 @@
         <v>45922</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K219" s="9">
         <v>175</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M219" s="4" t="s">
         <v>8</v>
@@ -6904,19 +6907,19 @@
         <v>45922</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I220" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K220" s="9">
         <v>275</v>
       </c>
       <c r="L220" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M220" s="4" t="s">
         <v>8</v>
@@ -6930,19 +6933,19 @@
         <v>45923</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I221" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K221" s="9">
         <v>200</v>
       </c>
       <c r="L221" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M221" s="4" t="s">
         <v>8</v>
@@ -6956,19 +6959,19 @@
         <v>45923</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I222" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K222" s="9">
         <v>200</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M222" s="4" t="s">
         <v>8</v>
@@ -6982,19 +6985,19 @@
         <v>45923</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K223" s="9">
         <v>220</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M223" s="4" t="s">
         <v>8</v>
@@ -7008,19 +7011,19 @@
         <v>45923</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K224" s="9">
         <v>280</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M224" s="4" t="s">
         <v>8</v>
@@ -7034,19 +7037,19 @@
         <v>45923</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K225" s="9">
         <v>160</v>
       </c>
       <c r="L225" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M225" s="4" t="s">
         <v>8</v>
@@ -7060,10 +7063,10 @@
         <v>45923</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I226" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>11</v>
@@ -7072,7 +7075,7 @@
         <v>120</v>
       </c>
       <c r="L226" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M226" s="4" t="s">
         <v>7</v>
@@ -7086,19 +7089,19 @@
         <v>45924</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K227" s="9">
         <v>110</v>
       </c>
       <c r="L227" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M227" s="4" t="s">
         <v>8</v>
@@ -7112,19 +7115,19 @@
         <v>45924</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K228" s="9">
         <v>205</v>
       </c>
       <c r="L228" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M228" s="4" t="s">
         <v>8</v>
@@ -7138,19 +7141,19 @@
         <v>45924</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K229" s="9">
         <v>200</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M229" s="4" t="s">
         <v>8</v>
@@ -7164,19 +7167,19 @@
         <v>45924</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K230" s="9">
         <v>170</v>
       </c>
       <c r="L230" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M230" s="4" t="s">
         <v>8</v>
@@ -7190,19 +7193,19 @@
         <v>45924</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K231" s="9">
         <v>190</v>
       </c>
       <c r="L231" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M231" s="4" t="s">
         <v>8</v>
@@ -7216,19 +7219,19 @@
         <v>45924</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K232" s="9">
         <v>220</v>
       </c>
       <c r="L232" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M232" s="4" t="s">
         <v>8</v>
@@ -7242,19 +7245,19 @@
         <v>45924</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K233" s="9">
         <v>175</v>
       </c>
       <c r="L233" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M233" s="4" t="s">
         <v>7</v>
@@ -7268,19 +7271,19 @@
         <v>45924</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K234" s="9">
         <v>170</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M234" s="4" t="s">
         <v>8</v>
@@ -7294,19 +7297,19 @@
         <v>45925</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K235" s="9">
         <v>250</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M235" s="4" t="s">
         <v>8</v>
@@ -7320,19 +7323,19 @@
         <v>45925</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K236" s="9">
         <v>198</v>
       </c>
       <c r="L236" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M236" s="4" t="s">
         <v>8</v>
@@ -7346,19 +7349,19 @@
         <v>45925</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K237" s="9">
         <v>180</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M237" s="4" t="s">
         <v>8</v>
@@ -7372,19 +7375,19 @@
         <v>45925</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I238" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K238" s="9">
         <v>150</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M238" s="4" t="s">
         <v>8</v>
@@ -7398,19 +7401,19 @@
         <v>45925</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K239" s="9">
         <v>220</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M239" s="4" t="s">
         <v>8</v>
@@ -7424,19 +7427,19 @@
         <v>45925</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I240" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="J240" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="J240" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="K240" s="9">
         <v>209</v>
       </c>
       <c r="L240" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M240" s="4" t="s">
         <v>8</v>
@@ -7450,19 +7453,19 @@
         <v>45925</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K241" s="9">
         <v>200</v>
       </c>
       <c r="L241" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M241" s="4" t="s">
         <v>8</v>
@@ -7476,19 +7479,19 @@
         <v>45925</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K242" s="9">
         <v>200</v>
       </c>
       <c r="L242" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M242" s="4" t="s">
         <v>8</v>
@@ -7502,19 +7505,19 @@
         <v>45925</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K243" s="9">
         <v>280</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M243" s="4" t="s">
         <v>8</v>
@@ -7528,19 +7531,19 @@
         <v>45925</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I244" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K244" s="9">
         <v>200</v>
       </c>
       <c r="L244" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M244" s="4" t="s">
         <v>8</v>
@@ -7554,19 +7557,19 @@
         <v>45929</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I245" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J245" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K245" s="9">
         <v>220</v>
       </c>
       <c r="L245" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M245" s="4" t="s">
         <v>8</v>
@@ -7580,19 +7583,19 @@
         <v>45925</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I246" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K246" s="9">
         <v>240</v>
       </c>
       <c r="L246" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M246" s="4" t="s">
         <v>8</v>
@@ -7606,19 +7609,19 @@
         <v>45929</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I247" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K247" s="9">
         <v>209</v>
       </c>
       <c r="L247" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M247" s="4" t="s">
         <v>8</v>
@@ -7632,19 +7635,19 @@
         <v>45929</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I248" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K248" s="9">
         <v>200</v>
       </c>
       <c r="L248" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M248" s="4" t="s">
         <v>8</v>
@@ -7658,19 +7661,19 @@
         <v>45929</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K249" s="9">
         <v>220</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M249" s="4" t="s">
         <v>8</v>
@@ -7684,19 +7687,19 @@
         <v>45929</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I250" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K250" s="9">
         <v>250</v>
       </c>
       <c r="L250" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M250" s="4" t="s">
         <v>8</v>
@@ -7710,19 +7713,19 @@
         <v>45929</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K251" s="9">
         <v>265</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M251" s="4" t="s">
         <v>8</v>
@@ -7736,19 +7739,19 @@
         <v>45929</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I252" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K252" s="9">
         <v>175</v>
       </c>
       <c r="L252" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M252" s="4" t="s">
         <v>8</v>
@@ -7762,19 +7765,19 @@
         <v>45930</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K253" s="9">
         <v>200</v>
       </c>
       <c r="L253" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M253" s="4" t="s">
         <v>8</v>
@@ -7788,19 +7791,19 @@
         <v>45930</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K254" s="9">
         <v>200</v>
       </c>
       <c r="L254" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M254" s="4" t="s">
         <v>8</v>
@@ -7814,19 +7817,19 @@
         <v>45930</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I255" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K255" s="9">
         <v>200</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M255" s="4" t="s">
         <v>8</v>
@@ -7840,19 +7843,19 @@
         <v>45930</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I256" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K256" s="9">
         <v>280</v>
       </c>
       <c r="L256" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M256" s="4" t="s">
         <v>8</v>
@@ -7866,19 +7869,19 @@
         <v>45930</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I257" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J257" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K257" s="9">
         <v>160</v>
       </c>
       <c r="L257" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M257" s="4" t="s">
         <v>8</v>
@@ -7892,10 +7895,10 @@
         <v>45930</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I258" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J258" s="4" t="s">
         <v>11</v>
@@ -7904,7 +7907,7 @@
         <v>200</v>
       </c>
       <c r="L258" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M258" s="4" t="s">
         <v>8</v>
@@ -7918,19 +7921,19 @@
         <v>45931</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K259" s="9">
         <v>240</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M259" s="4" t="s">
         <v>8</v>
@@ -7944,19 +7947,19 @@
         <v>45931</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K260" s="9">
         <v>280</v>
       </c>
       <c r="L260" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M260" s="4" t="s">
         <v>8</v>
@@ -7970,19 +7973,19 @@
         <v>45931</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I261" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K261" s="9">
         <v>210</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M261" s="4" t="s">
         <v>8</v>
@@ -7996,19 +7999,19 @@
         <v>45931</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I262" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K262" s="9">
         <v>110</v>
       </c>
       <c r="L262" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M262" s="4" t="s">
         <v>8</v>
@@ -8022,19 +8025,19 @@
         <v>45931</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I263" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K263" s="9">
         <v>212</v>
       </c>
       <c r="L263" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M263" s="4" t="s">
         <v>8</v>
@@ -8048,19 +8051,19 @@
         <v>45931</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K264" s="9">
         <v>200</v>
       </c>
       <c r="L264" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M264" s="4" t="s">
         <v>8</v>
@@ -8074,19 +8077,19 @@
         <v>45931</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I265" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K265" s="9">
         <v>190</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M265" s="4" t="s">
         <v>8</v>
@@ -8100,19 +8103,19 @@
         <v>45931</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K266" s="9">
         <v>190</v>
       </c>
       <c r="L266" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M266" s="4" t="s">
         <v>8</v>
@@ -8126,19 +8129,19 @@
         <v>45932</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K267" s="9">
         <v>198</v>
       </c>
       <c r="L267" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M267" s="4" t="s">
         <v>8</v>
@@ -8152,19 +8155,19 @@
         <v>45932</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K268" s="9">
         <v>200</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M268" s="4" t="s">
         <v>8</v>
@@ -8178,19 +8181,19 @@
         <v>45932</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I269" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K269" s="9">
         <v>150</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M269" s="4" t="s">
         <v>8</v>
@@ -8204,19 +8207,19 @@
         <v>45932</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I270" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K270" s="9">
         <v>235</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M270" s="4" t="s">
         <v>8</v>
@@ -8230,19 +8233,19 @@
         <v>45932</v>
       </c>
       <c r="H271" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I271" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K271" s="9">
         <v>259</v>
       </c>
       <c r="L271" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M271" s="4" t="s">
         <v>8</v>
@@ -8256,19 +8259,19 @@
         <v>45932</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I272" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K272" s="9">
         <v>240</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M272" s="4" t="s">
         <v>8</v>
@@ -8282,19 +8285,19 @@
         <v>45932</v>
       </c>
       <c r="H273" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K273" s="9">
         <v>200</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M273" s="4" t="s">
         <v>8</v>
@@ -8309,19 +8312,19 @@
         <v>45932</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K274" s="9">
         <v>250</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M274" s="4" t="s">
         <v>8</v>
@@ -8335,19 +8338,19 @@
         <v>45932</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K275" s="9">
         <v>280</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M275" s="4" t="s">
         <v>8</v>
@@ -8361,19 +8364,19 @@
         <v>45932</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K276" s="9">
         <v>175</v>
       </c>
       <c r="L276" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M276" s="4" t="s">
         <v>8</v>
@@ -8387,19 +8390,19 @@
         <v>45932</v>
       </c>
       <c r="H277" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K277" s="9">
         <v>250</v>
       </c>
       <c r="L277" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M277" s="4" t="s">
         <v>8</v>
@@ -8413,19 +8416,19 @@
         <v>45903</v>
       </c>
       <c r="H278" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K278" s="9">
         <v>240</v>
       </c>
       <c r="L278" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M278" s="4" t="s">
         <v>8</v>
@@ -8439,19 +8442,19 @@
         <v>45933</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K279" s="9">
         <v>230</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M279" s="4" t="s">
         <v>8</v>
@@ -8465,10 +8468,10 @@
         <v>45933</v>
       </c>
       <c r="H280" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>10</v>
@@ -8491,19 +8494,19 @@
         <v>45936</v>
       </c>
       <c r="H281" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K281" s="9">
         <v>220</v>
       </c>
       <c r="L281" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M281" s="4" t="s">
         <v>8</v>
@@ -8517,19 +8520,19 @@
         <v>45936</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K282" s="9">
         <v>259</v>
       </c>
       <c r="L282" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M282" s="4" t="s">
         <v>8</v>
@@ -8543,19 +8546,19 @@
         <v>45936</v>
       </c>
       <c r="H283" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K283" s="9">
         <v>200</v>
       </c>
       <c r="L283" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M283" s="4" t="s">
         <v>8</v>
@@ -8569,19 +8572,19 @@
         <v>45936</v>
       </c>
       <c r="H284" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K284" s="9">
         <v>240</v>
       </c>
       <c r="L284" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M284" s="4" t="s">
         <v>8</v>
@@ -8595,19 +8598,19 @@
         <v>45936</v>
       </c>
       <c r="H285" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K285" s="9">
         <v>175</v>
       </c>
       <c r="L285" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M285" s="4" t="s">
         <v>8</v>
@@ -8621,19 +8624,19 @@
         <v>45936</v>
       </c>
       <c r="H286" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K286" s="9">
         <v>250</v>
       </c>
       <c r="L286" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M286" s="4" t="s">
         <v>8</v>
@@ -8647,19 +8650,19 @@
         <v>45936</v>
       </c>
       <c r="H287" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I287" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="I287" s="6" t="s">
-        <v>236</v>
-      </c>
       <c r="J287" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K287" s="9">
         <v>265</v>
       </c>
       <c r="L287" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M287" s="4" t="s">
         <v>8</v>
@@ -8673,19 +8676,19 @@
         <v>45937</v>
       </c>
       <c r="H288" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I288" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K288" s="9">
         <v>140</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>8</v>
@@ -8699,19 +8702,19 @@
         <v>45937</v>
       </c>
       <c r="H289" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I289" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K289" s="9">
         <v>200</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M289" s="4" t="s">
         <v>8</v>
@@ -8725,19 +8728,19 @@
         <v>45937</v>
       </c>
       <c r="H290" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I290" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K290" s="9">
         <v>179.9</v>
       </c>
       <c r="L290" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M290" s="4" t="s">
         <v>8</v>
@@ -8751,19 +8754,19 @@
         <v>45937</v>
       </c>
       <c r="H291" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K291" s="9">
         <v>200</v>
       </c>
       <c r="L291" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>8</v>
@@ -8777,19 +8780,19 @@
         <v>45937</v>
       </c>
       <c r="H292" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I292" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K292" s="9">
         <v>280</v>
       </c>
       <c r="L292" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M292" s="4" t="s">
         <v>8</v>
@@ -8803,19 +8806,19 @@
         <v>45937</v>
       </c>
       <c r="H293" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K293" s="9">
         <v>160</v>
       </c>
       <c r="L293" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M293" s="4" t="s">
         <v>8</v>
@@ -8829,19 +8832,19 @@
         <v>45937</v>
       </c>
       <c r="H294" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K294" s="9">
         <v>220</v>
       </c>
       <c r="L294" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M294" s="4" t="s">
         <v>8</v>
@@ -8855,19 +8858,19 @@
         <v>45938</v>
       </c>
       <c r="H295" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K295" s="9">
         <v>200</v>
       </c>
       <c r="L295" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M295" s="4" t="s">
         <v>8</v>
@@ -8881,19 +8884,19 @@
         <v>45938</v>
       </c>
       <c r="H296" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K296" s="9">
         <v>280</v>
       </c>
       <c r="L296" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M296" s="4" t="s">
         <v>8</v>
@@ -8907,19 +8910,19 @@
         <v>45938</v>
       </c>
       <c r="H297" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I297" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K297" s="9">
         <v>160</v>
       </c>
       <c r="L297" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M297" s="4" t="s">
         <v>8</v>
@@ -8933,19 +8936,19 @@
         <v>45938</v>
       </c>
       <c r="H298" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K298" s="9">
         <v>170</v>
       </c>
       <c r="L298" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M298" s="4" t="s">
         <v>8</v>
@@ -8959,19 +8962,19 @@
         <v>45938</v>
       </c>
       <c r="H299" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K299" s="9">
         <v>200</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M299" s="4" t="s">
         <v>8</v>
@@ -8985,19 +8988,19 @@
         <v>45938</v>
       </c>
       <c r="H300" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I300" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K300" s="9">
         <v>170</v>
       </c>
       <c r="L300" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M300" s="4" t="s">
         <v>8</v>
@@ -9011,19 +9014,19 @@
         <v>45938</v>
       </c>
       <c r="H301" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K301" s="9">
         <v>230</v>
       </c>
       <c r="L301" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M301" s="4" t="s">
         <v>8</v>
@@ -9032,24 +9035,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45943</v>
       </c>
       <c r="H302" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K302" s="9">
         <v>220</v>
       </c>
       <c r="L302" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M302" s="4" t="s">
         <v>8</v>
@@ -9058,24 +9061,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45943</v>
       </c>
       <c r="H303" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K303" s="9">
         <v>140</v>
       </c>
       <c r="L303" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M303" s="4" t="s">
         <v>8</v>
@@ -9084,24 +9087,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45943</v>
       </c>
       <c r="H304" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I304" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K304" s="9">
         <v>200</v>
       </c>
       <c r="L304" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M304" s="4" t="s">
         <v>8</v>
@@ -9110,24 +9113,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45943</v>
       </c>
       <c r="H305" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K305" s="9">
         <v>220</v>
       </c>
       <c r="L305" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M305" s="4" t="s">
         <v>8</v>
@@ -9136,24 +9139,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45943</v>
       </c>
       <c r="H306" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K306" s="9">
         <v>180</v>
       </c>
       <c r="L306" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M306" s="4" t="s">
         <v>8</v>
@@ -9162,24 +9165,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45943</v>
       </c>
       <c r="H307" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K307" s="9">
         <v>220</v>
       </c>
       <c r="L307" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M307" s="4" t="s">
         <v>8</v>
@@ -9213,19 +9216,19 @@
         <v>45939</v>
       </c>
       <c r="H310" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K310" s="9">
         <v>230</v>
       </c>
       <c r="L310" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M310" s="4" t="s">
         <v>8</v>
@@ -9239,19 +9242,19 @@
         <v>45939</v>
       </c>
       <c r="H311" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K311" s="9">
         <v>180</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M311" s="4" t="s">
         <v>8</v>
@@ -9265,19 +9268,19 @@
         <v>45939</v>
       </c>
       <c r="H312" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K312" s="9">
         <v>198</v>
       </c>
       <c r="L312" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M312" s="4" t="s">
         <v>8</v>
@@ -9291,19 +9294,19 @@
         <v>45939</v>
       </c>
       <c r="H313" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I313" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K313" s="9">
         <v>180</v>
       </c>
       <c r="L313" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M313" s="4" t="s">
         <v>8</v>
@@ -9317,19 +9320,19 @@
         <v>45939</v>
       </c>
       <c r="H314" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I314" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K314" s="9">
         <v>150</v>
       </c>
       <c r="L314" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M314" s="4" t="s">
         <v>8</v>
@@ -9343,19 +9346,19 @@
         <v>45939</v>
       </c>
       <c r="H315" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I315" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K315" s="9">
         <v>140</v>
       </c>
       <c r="L315" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M315" s="4" t="s">
         <v>8</v>
@@ -9369,19 +9372,19 @@
         <v>45939</v>
       </c>
       <c r="H316" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I316" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K316" s="9">
         <v>140</v>
       </c>
       <c r="L316" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M316" s="4" t="s">
         <v>8</v>
@@ -9395,19 +9398,19 @@
         <v>45939</v>
       </c>
       <c r="H317" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I317" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K317" s="9">
         <v>200</v>
       </c>
       <c r="L317" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M317" s="4" t="s">
         <v>8</v>
@@ -9421,19 +9424,19 @@
         <v>45939</v>
       </c>
       <c r="H318" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I318" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I318" s="6" t="s">
-        <v>246</v>
-      </c>
       <c r="J318" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K318" s="9">
         <v>220</v>
       </c>
       <c r="L318" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M318" s="4" t="s">
         <v>8</v>
@@ -9447,19 +9450,19 @@
         <v>45939</v>
       </c>
       <c r="H319" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I319" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I319" s="6" t="s">
-        <v>248</v>
-      </c>
       <c r="J319" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K319" s="9">
         <v>200</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M319" s="4" t="s">
         <v>8</v>
@@ -9473,19 +9476,19 @@
         <v>45939</v>
       </c>
       <c r="H320" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I320" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K320" s="9">
         <v>280</v>
       </c>
       <c r="L320" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M320" s="4" t="s">
         <v>8</v>
@@ -9499,19 +9502,19 @@
         <v>45939</v>
       </c>
       <c r="H321" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I321" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K321" s="9">
         <v>180</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M321" s="4" t="s">
         <v>8</v>
@@ -9525,19 +9528,19 @@
         <v>45939</v>
       </c>
       <c r="H322" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I322" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K322" s="9">
         <v>200</v>
       </c>
       <c r="L322" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M322" s="4" t="s">
         <v>8</v>
@@ -9551,19 +9554,19 @@
         <v>45939</v>
       </c>
       <c r="H323" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K323" s="9">
         <v>220</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M323" s="4" t="s">
         <v>8</v>
@@ -9577,19 +9580,19 @@
         <v>45940</v>
       </c>
       <c r="H324" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K324" s="9">
         <v>220</v>
       </c>
       <c r="L324" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M324" s="4" t="s">
         <v>8</v>
@@ -9603,14 +9606,20 @@
         <v>45944</v>
       </c>
       <c r="H325" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I325" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J325" s="4"/>
-      <c r="K325" s="9"/>
-      <c r="L325" s="4"/>
+        <v>152</v>
+      </c>
+      <c r="J325" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K325" s="9">
+        <v>160</v>
+      </c>
+      <c r="L325" s="4" t="s">
+        <v>265</v>
+      </c>
       <c r="M325" s="4" t="s">
         <v>8</v>
       </c>
@@ -9623,10 +9632,10 @@
         <v>45944</v>
       </c>
       <c r="H326" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I326" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J326" s="4"/>
       <c r="K326" s="9"/>
@@ -9643,12 +9652,14 @@
         <v>45944</v>
       </c>
       <c r="H327" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J327" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="J327" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="K327" s="9"/>
       <c r="L327" s="4"/>
       <c r="M327" s="4" t="s">
@@ -9663,10 +9674,10 @@
         <v>45944</v>
       </c>
       <c r="H328" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I328" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J328" s="4"/>
       <c r="K328" s="9"/>
@@ -9683,10 +9694,10 @@
         <v>45944</v>
       </c>
       <c r="H329" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I329" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J329" s="4"/>
       <c r="K329" s="9"/>
@@ -9703,19 +9714,19 @@
         <v>45944</v>
       </c>
       <c r="H330" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I330" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K330" s="9">
         <v>160</v>
       </c>
       <c r="L330" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M330" s="4" t="s">
         <v>8</v>
@@ -9795,10 +9806,10 @@
       <c r="N337" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N324" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:N330" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="10" day="13" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="14" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1684" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4B9F7C8-F597-4CFA-A8C0-F273239E8880}"/>
+  <xr:revisionPtr revIDLastSave="1710" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA89788C-838E-4EE9-9E19-77759EC6BC1B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="268">
   <si>
     <t>DATA</t>
   </si>
@@ -839,6 +839,9 @@
   </si>
   <si>
     <t>TRÊS PONTAS</t>
+  </si>
+  <si>
+    <t>HOTEL CAFÉ</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1" filterMode="1">
+  <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="G5:O337"/>
@@ -1362,7 +1365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1388,7 +1391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1440,7 +1443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1466,7 +1469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1492,7 +1495,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1518,7 +1521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1544,7 +1547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1570,7 +1573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1674,7 +1677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1700,7 +1703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1726,7 +1729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1752,7 +1755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1804,7 +1807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1830,7 +1833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1882,7 +1885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1908,7 +1911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1934,7 +1937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1960,7 +1963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -1986,7 +1989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -2012,7 +2015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -2038,7 +2041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2064,7 +2067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2090,7 +2093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2116,7 +2119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2142,7 +2145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2168,7 +2171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2194,7 +2197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2220,7 +2223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2246,7 +2249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2272,7 +2275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2324,7 +2327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2350,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2376,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2402,7 +2405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2428,7 +2431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2454,7 +2457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2480,7 +2483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2506,7 +2509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2532,7 +2535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2558,7 +2561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2584,7 +2587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2610,7 +2613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2636,7 +2639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2662,7 +2665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2688,7 +2691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2714,7 +2717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2740,7 +2743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2792,7 +2795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2818,7 +2821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2844,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2870,7 +2873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2896,7 +2899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2922,7 +2925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2948,7 +2951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2974,7 +2977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -3000,7 +3003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -3026,7 +3029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3052,7 +3055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3078,7 +3081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3104,7 +3107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3130,7 +3133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3156,7 +3159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3182,7 +3185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3208,7 +3211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3234,7 +3237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3260,7 +3263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3286,7 +3289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3312,7 +3315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3338,7 +3341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3364,7 +3367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3390,7 +3393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3416,7 +3419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3442,7 +3445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3468,7 +3471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3494,7 +3497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3520,7 +3523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3546,7 +3549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3572,7 +3575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3596,7 +3599,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3622,7 +3625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3648,7 +3651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3674,7 +3677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3700,7 +3703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3726,7 +3729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3778,7 +3781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3804,7 +3807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3830,7 +3833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3856,7 +3859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3882,7 +3885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3908,7 +3911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3960,7 +3963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -3986,7 +3989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -4012,7 +4015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -4038,7 +4041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4064,7 +4067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4090,7 +4093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4116,7 +4119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4142,7 +4145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4168,7 +4171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4194,7 +4197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4220,7 +4223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4246,7 +4249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4272,7 +4275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4298,7 +4301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4324,7 +4327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4350,7 +4353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4402,7 +4405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4428,7 +4431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4454,7 +4457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4480,7 +4483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4506,7 +4509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4532,7 +4535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4558,7 +4561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4584,7 +4587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4610,7 +4613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4636,7 +4639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4662,7 +4665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4688,7 +4691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4714,7 +4717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4740,7 +4743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4766,7 +4769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4792,7 +4795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4818,7 +4821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4844,7 +4847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4868,7 +4871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4894,7 +4897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4918,7 +4921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45904</v>
       </c>
@@ -4944,7 +4947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -4970,7 +4973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -4996,7 +4999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -5022,7 +5025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -5048,7 +5051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5074,7 +5077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5100,7 +5103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5126,7 +5129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5152,7 +5155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45908</v>
       </c>
@@ -5178,7 +5181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5204,7 +5207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5230,7 +5233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5256,7 +5259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45909</v>
       </c>
@@ -5282,7 +5285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5308,7 +5311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5334,7 +5337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5360,7 +5363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5386,7 +5389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5412,7 +5415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45910</v>
       </c>
@@ -5438,7 +5441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5458,7 +5461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5484,7 +5487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5510,7 +5513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5536,7 +5539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5562,7 +5565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5588,7 +5591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45911</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5634,7 +5637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5660,7 +5663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5686,7 +5689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5712,7 +5715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5738,7 +5741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5764,7 +5767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5790,7 +5793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5816,7 +5819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5842,7 +5845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5868,7 +5871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5894,7 +5897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5920,7 +5923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45915</v>
       </c>
@@ -5946,7 +5949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -5972,7 +5975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -5998,7 +6001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -6024,7 +6027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -6050,7 +6053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6076,7 +6079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6102,7 +6105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45916</v>
       </c>
@@ -6128,7 +6131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6154,7 +6157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6180,7 +6183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6206,7 +6209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6232,7 +6235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45917</v>
       </c>
@@ -6258,7 +6261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6284,7 +6287,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6310,7 +6313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6336,7 +6339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6362,7 +6365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6388,7 +6391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6414,7 +6417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45918</v>
       </c>
@@ -6440,7 +6443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6466,7 +6469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6492,7 +6495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6518,7 +6521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6544,7 +6547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6570,7 +6573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6596,7 +6599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6622,7 +6625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6648,7 +6651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6674,7 +6677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6694,7 +6697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6720,7 +6723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6746,7 +6749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45922</v>
       </c>
@@ -6772,7 +6775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6798,7 +6801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6824,7 +6827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6850,7 +6853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6876,7 +6879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6902,7 +6905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6928,7 +6931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45923</v>
       </c>
@@ -6954,7 +6957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -6980,7 +6983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -7006,7 +7009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -7032,7 +7035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -7058,7 +7061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7084,7 +7087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45924</v>
       </c>
@@ -7110,7 +7113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7136,7 +7139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7162,7 +7165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7188,7 +7191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7214,7 +7217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7240,7 +7243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7266,7 +7269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7292,7 +7295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45925</v>
       </c>
@@ -7318,7 +7321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7344,7 +7347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7370,7 +7373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7396,7 +7399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7422,7 +7425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7448,7 +7451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7474,7 +7477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7500,7 +7503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7526,7 +7529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7552,7 +7555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45929</v>
       </c>
@@ -7578,7 +7581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7604,7 +7607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7630,7 +7633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7656,7 +7659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7682,7 +7685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7708,7 +7711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7734,7 +7737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7760,7 +7763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45930</v>
       </c>
@@ -7786,7 +7789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7812,7 +7815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7838,7 +7841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7864,7 +7867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7890,7 +7893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7916,7 +7919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45931</v>
       </c>
@@ -7942,7 +7945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -7968,7 +7971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -7994,7 +7997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -8020,7 +8023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8046,7 +8049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8072,7 +8075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8098,7 +8101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8124,7 +8127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45932</v>
       </c>
@@ -8150,7 +8153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8176,7 +8179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8202,7 +8205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8228,7 +8231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8254,7 +8257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8280,7 +8283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8307,7 +8310,7 @@
       </c>
       <c r="O273" s="19"/>
     </row>
-    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8333,7 +8336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8359,7 +8362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8385,7 +8388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8411,7 +8414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45903</v>
       </c>
@@ -8437,7 +8440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8463,7 +8466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8489,7 +8492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8515,7 +8518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8541,7 +8544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8567,7 +8570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8593,7 +8596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8619,7 +8622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8645,7 +8648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8671,7 +8674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8697,7 +8700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8723,7 +8726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8749,7 +8752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8775,7 +8778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8801,7 +8804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8827,7 +8830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8853,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8879,7 +8882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8905,7 +8908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -8931,7 +8934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -8957,7 +8960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -8983,7 +8986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -9009,7 +9012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9035,7 +9038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45943</v>
       </c>
@@ -9061,7 +9064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45943</v>
       </c>
@@ -9075,7 +9078,7 @@
         <v>25</v>
       </c>
       <c r="K303" s="9">
-        <v>140</v>
+        <v>259</v>
       </c>
       <c r="L303" s="4" t="s">
         <v>252</v>
@@ -9087,7 +9090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45943</v>
       </c>
@@ -9113,7 +9116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45943</v>
       </c>
@@ -9139,7 +9142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45943</v>
       </c>
@@ -9165,7 +9168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45943</v>
       </c>
@@ -9191,7 +9194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G308" s="4"/>
       <c r="H308" s="4"/>
       <c r="I308" s="6"/>
@@ -9201,7 +9204,7 @@
       <c r="M308" s="4"/>
       <c r="N308" s="6"/>
     </row>
-    <row r="309" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G309" s="4"/>
       <c r="H309" s="4"/>
       <c r="I309" s="6"/>
@@ -9211,7 +9214,7 @@
       <c r="M309" s="4"/>
       <c r="N309" s="6"/>
     </row>
-    <row r="310" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9237,7 +9240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9263,7 +9266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9289,7 +9292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9315,7 +9318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9341,7 +9344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9367,7 +9370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45939</v>
       </c>
@@ -9393,7 +9396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45939</v>
       </c>
@@ -9419,7 +9422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45939</v>
       </c>
@@ -9445,7 +9448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45939</v>
       </c>
@@ -9471,7 +9474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45939</v>
       </c>
@@ -9497,7 +9500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45939</v>
       </c>
@@ -9523,7 +9526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45939</v>
       </c>
@@ -9549,7 +9552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45939</v>
       </c>
@@ -9575,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45940</v>
       </c>
@@ -9637,9 +9640,15 @@
       <c r="I326" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="J326" s="4"/>
-      <c r="K326" s="9"/>
-      <c r="L326" s="4"/>
+      <c r="J326" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K326" s="9">
+        <v>200</v>
+      </c>
+      <c r="L326" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="M326" s="4" t="s">
         <v>8</v>
       </c>
@@ -9660,8 +9669,12 @@
       <c r="J327" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="K327" s="9"/>
-      <c r="L327" s="4"/>
+      <c r="K327" s="9">
+        <v>270</v>
+      </c>
+      <c r="L327" s="4" t="s">
+        <v>267</v>
+      </c>
       <c r="M327" s="4" t="s">
         <v>8</v>
       </c>
@@ -9679,9 +9692,15 @@
       <c r="I328" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J328" s="4"/>
-      <c r="K328" s="9"/>
-      <c r="L328" s="4"/>
+      <c r="J328" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K328" s="9">
+        <v>200</v>
+      </c>
+      <c r="L328" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="M328" s="4" t="s">
         <v>8</v>
       </c>
@@ -9699,9 +9718,15 @@
       <c r="I329" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="J329" s="4"/>
-      <c r="K329" s="9"/>
-      <c r="L329" s="4"/>
+      <c r="J329" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="K329" s="9">
+        <v>280</v>
+      </c>
+      <c r="L329" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="M329" s="4" t="s">
         <v>8</v>
       </c>
@@ -9806,13 +9831,7 @@
       <c r="N337" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N330" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" month="10" day="14" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="G5:N330" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1710" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA89788C-838E-4EE9-9E19-77759EC6BC1B}"/>
+  <xr:revisionPtr revIDLastSave="1712" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94976382-B703-4F43-AE60-93DBF68FB97A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1712" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94976382-B703-4F43-AE60-93DBF68FB97A}"/>
+  <xr:revisionPtr revIDLastSave="1854" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B66D996-7FB7-4922-95F2-8E802807062B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$330</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$339</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="248">
   <si>
     <t>DATA</t>
   </si>
@@ -112,9 +112,6 @@
     <t>CARMOPOLIS DE MINAS</t>
   </si>
   <si>
-    <t>POUSADA DA TRILHA</t>
-  </si>
-  <si>
     <t>SÃO JOÃO DEL REY</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
     <t>HOTEL SOLAR</t>
   </si>
   <si>
-    <t>HOTEL POUSADA DA TRILHA</t>
-  </si>
-  <si>
     <t>HOTEL PLANALTO</t>
   </si>
   <si>
@@ -172,9 +166,6 @@
     <t>LAVRAS</t>
   </si>
   <si>
-    <t>GANHAES</t>
-  </si>
-  <si>
     <t>BAR DO JOÃOZINHO</t>
   </si>
   <si>
@@ -193,9 +184,6 @@
     <t>RIO CASCA</t>
   </si>
   <si>
-    <t>TRES PONTAS MG</t>
-  </si>
-  <si>
     <t xml:space="preserve"> GIRA SOL</t>
   </si>
   <si>
@@ -211,9 +199,6 @@
     <t>HOTEL MATOZINHO</t>
   </si>
   <si>
-    <t>MATOZINHO</t>
-  </si>
-  <si>
     <t xml:space="preserve">HOTEL IPÊ </t>
   </si>
   <si>
@@ -232,21 +217,12 @@
     <t>HOSTEL ROTOR</t>
   </si>
   <si>
-    <t>HOTEL VITORIA</t>
-  </si>
-  <si>
     <t>HOTEL PARADISE</t>
   </si>
   <si>
     <t>HOTEL PICPO</t>
   </si>
   <si>
-    <t>SÃO JÕAO DEL REY MG</t>
-  </si>
-  <si>
-    <t>ARCOS MG</t>
-  </si>
-  <si>
     <t>JOÃO MONLEVADE MG</t>
   </si>
   <si>
@@ -274,12 +250,6 @@
     <t>ABAETÉ PALACE</t>
   </si>
   <si>
-    <t>TRES CORAÇÕES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOTEL MEDIEVAL </t>
-  </si>
-  <si>
     <t>POUSADA PÉ DA SERRA</t>
   </si>
   <si>
@@ -379,15 +349,9 @@
     <t>POUSADA RENASCER</t>
   </si>
   <si>
-    <t>SÃO JOÃO MG</t>
-  </si>
-  <si>
     <t>POMPEU MG</t>
   </si>
   <si>
-    <t>POUSADA TRILHA</t>
-  </si>
-  <si>
     <t>POUSADA RESIDENCIAL</t>
   </si>
   <si>
@@ -565,9 +529,6 @@
     <t>ALDEMIR</t>
   </si>
   <si>
-    <t xml:space="preserve">SAO JOÃO DEL REY </t>
-  </si>
-  <si>
     <t>REQUINTE DO PEIXE</t>
   </si>
   <si>
@@ -580,9 +541,6 @@
     <t>HOTEL RABELO</t>
   </si>
   <si>
-    <t>GONZADA</t>
-  </si>
-  <si>
     <t>POUSADA OASIS</t>
   </si>
   <si>
@@ -601,9 +559,6 @@
     <t>HOTEL SANTO ANTONIO</t>
   </si>
   <si>
-    <t>HOTEL AGUAS CLARAS</t>
-  </si>
-  <si>
     <t>HOTEL CASARÃO</t>
   </si>
   <si>
@@ -652,9 +607,6 @@
     <t>INDEFINIDO</t>
   </si>
   <si>
-    <t>MARIO ARMANDO HOTEL</t>
-  </si>
-  <si>
     <t>GOUVEIA</t>
   </si>
   <si>
@@ -673,9 +625,6 @@
     <t>RICHARD</t>
   </si>
   <si>
-    <t>SAO JOAO EVANGELISTA</t>
-  </si>
-  <si>
     <t>HOTEL CASA BLANCA</t>
   </si>
   <si>
@@ -685,9 +634,6 @@
     <t xml:space="preserve">DOUGLAS RODRIGUES </t>
   </si>
   <si>
-    <t>SAO JOAO DEL REY</t>
-  </si>
-  <si>
     <t>PASSA TEMPO</t>
   </si>
   <si>
@@ -709,18 +655,12 @@
     <t>VALDECI</t>
   </si>
   <si>
-    <t>SÃO JOAO DEL REY</t>
-  </si>
-  <si>
     <t>wesley.a</t>
   </si>
   <si>
     <t>wesley.l</t>
   </si>
   <si>
-    <t>SÃO JOAO EVANGELISTA</t>
-  </si>
-  <si>
     <t>PERDÕES</t>
   </si>
   <si>
@@ -733,9 +673,6 @@
     <t>HOTEL PLAZARO</t>
   </si>
   <si>
-    <t>IBIA</t>
-  </si>
-  <si>
     <t>HOTEL VILA HELMAR</t>
   </si>
   <si>
@@ -790,9 +727,6 @@
     <t>ERASMO</t>
   </si>
   <si>
-    <t>JOAO MONLEVADE</t>
-  </si>
-  <si>
     <t>BELLA POUSADA</t>
   </si>
   <si>
@@ -802,9 +736,6 @@
     <t>ENTRE RIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">HOTEL VITORIA </t>
-  </si>
-  <si>
     <t>POUSADA ESPERANÇA</t>
   </si>
   <si>
@@ -829,12 +760,6 @@
     <t xml:space="preserve">SERRA DAS VERTENTES </t>
   </si>
   <si>
-    <t xml:space="preserve">GUANHAES </t>
-  </si>
-  <si>
-    <t>HOTEL JOAZINHO</t>
-  </si>
-  <si>
     <t>HOTEL SANTOS DUMMONT</t>
   </si>
   <si>
@@ -842,6 +767,21 @@
   </si>
   <si>
     <t>HOTEL CAFÉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS SILVA </t>
+  </si>
+  <si>
+    <t>HOTEL ÁGUAS CLARAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAGO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREDER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOTEL COSTA E FILHO </t>
   </si>
 </sst>
 </file>
@@ -868,7 +808,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -878,6 +818,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -934,7 +880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -985,6 +931,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1322,10 +1278,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1">
+  <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O337"/>
+  <dimension ref="G5:O342"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1344,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>1</v>
@@ -1365,15 +1321,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>23</v>
@@ -1382,7 +1338,7 @@
         <v>170</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>7</v>
@@ -1391,24 +1347,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>113</v>
+        <v>125</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K7" s="9">
         <v>74.900000000000006</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>7</v>
@@ -1417,24 +1373,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="9">
         <v>80</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>7</v>
@@ -1443,24 +1399,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="K9" s="9">
         <v>110</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>7</v>
@@ -1469,24 +1425,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K10" s="9">
         <v>170</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>7</v>
@@ -1495,24 +1451,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K11" s="9">
         <v>150</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>7</v>
@@ -1521,24 +1477,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K12" s="9">
         <v>85</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>7</v>
@@ -1547,24 +1503,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K13" s="9">
         <v>135</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>7</v>
@@ -1573,24 +1529,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K14" s="9">
         <v>100</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>7</v>
@@ -1599,18 +1555,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>51</v>
+        <v>132</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="K15" s="9">
         <v>178</v>
@@ -1625,24 +1581,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>57</v>
+        <v>133</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="K16" s="5">
         <v>80</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>7</v>
@@ -1651,15 +1607,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>5</v>
@@ -1677,24 +1633,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>67</v>
+        <v>135</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K18" s="10">
         <v>74.900000000000006</v>
       </c>
-      <c r="L18" s="7" t="s">
-        <v>24</v>
+      <c r="L18" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>7</v>
@@ -1703,24 +1659,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K19" s="10">
         <v>120</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>7</v>
@@ -1729,24 +1685,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>68</v>
+        <v>137</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="K20" s="10">
         <v>170</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>7</v>
@@ -1755,24 +1711,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K21" s="10">
         <v>150</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>7</v>
@@ -1781,24 +1737,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K22" s="10">
         <v>150</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>7</v>
@@ -1807,24 +1763,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="K23" s="10">
         <v>110</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>7</v>
@@ -1833,24 +1789,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K24" s="10">
         <v>130</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>7</v>
@@ -1859,24 +1815,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K25" s="10">
         <v>75</v>
       </c>
-      <c r="L25" s="7" t="s">
-        <v>64</v>
+      <c r="L25" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>7</v>
@@ -1885,15 +1841,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>21</v>
@@ -1902,7 +1858,7 @@
         <v>85</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>7</v>
@@ -1911,24 +1867,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K27" s="10">
         <v>100</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>7</v>
@@ -1937,24 +1893,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K28" s="10">
         <v>100</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>7</v>
@@ -1963,24 +1919,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K29" s="5">
         <v>100</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>7</v>
@@ -1989,24 +1945,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K30" s="5">
         <v>74.900000000000006</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>7</v>
@@ -2015,24 +1971,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K31" s="5">
         <v>140</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>7</v>
@@ -2041,24 +1997,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K32" s="5">
         <v>95</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>7</v>
@@ -2067,24 +2023,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K33" s="5">
         <v>160</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>7</v>
@@ -2093,24 +2049,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="K34" s="5">
         <v>150</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>7</v>
@@ -2119,24 +2075,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="K35" s="5">
         <v>160</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>7</v>
@@ -2145,24 +2101,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="K36" s="5">
         <v>140</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>7</v>
@@ -2171,24 +2127,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K37" s="5">
         <v>150</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>7</v>
@@ -2197,15 +2153,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>10</v>
@@ -2223,15 +2179,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>5</v>
@@ -2249,24 +2205,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K40" s="5">
         <v>105</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>7</v>
@@ -2275,24 +2231,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K41" s="5">
         <v>220</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M41" s="4" t="s">
         <v>7</v>
@@ -2301,24 +2257,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K42" s="5">
         <v>175</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>7</v>
@@ -2327,24 +2283,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K43" s="5">
         <v>180</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>7</v>
@@ -2353,24 +2309,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K44" s="5">
         <v>160</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>7</v>
@@ -2379,24 +2335,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K45" s="5">
         <v>115</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>7</v>
@@ -2405,15 +2361,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J46" s="17" t="s">
         <v>14</v>
@@ -2431,15 +2387,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J47" s="17" t="s">
         <v>5</v>
@@ -2457,15 +2413,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J48" s="17" t="s">
         <v>15</v>
@@ -2474,7 +2430,7 @@
         <v>140</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>7</v>
@@ -2483,24 +2439,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K49" s="5">
         <v>200</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>8</v>
@@ -2509,24 +2465,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K50" s="5">
         <v>129</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>7</v>
@@ -2535,24 +2491,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K51" s="5">
         <v>149</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>8</v>
@@ -2561,24 +2517,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="K52" s="5">
         <v>160</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="M52" s="4" t="s">
         <v>7</v>
@@ -2587,24 +2543,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J53" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K53" s="5">
         <v>150</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>7</v>
@@ -2613,15 +2569,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J54" s="17" t="s">
         <v>5</v>
@@ -2639,24 +2595,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K55" s="5">
         <v>140</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>7</v>
@@ -2665,24 +2621,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J56" s="17" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K56" s="5">
         <v>188</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="M56" s="4" t="s">
         <v>7</v>
@@ -2691,24 +2647,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K57" s="5">
         <v>99</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M57" s="4" t="s">
         <v>7</v>
@@ -2717,24 +2673,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J58" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K58" s="5">
         <v>75</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>7</v>
@@ -2743,24 +2699,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K59" s="5">
         <v>75</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>7</v>
@@ -2769,24 +2725,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J60" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K60" s="5">
         <v>150</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>7</v>
@@ -2795,24 +2751,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J61" s="17" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K61" s="5">
         <v>100</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>7</v>
@@ -2821,15 +2777,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J62" s="17" t="s">
         <v>14</v>
@@ -2847,24 +2803,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="J63" s="17" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K63" s="5">
         <v>150</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>7</v>
@@ -2873,24 +2829,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K64" s="5">
         <v>149</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>7</v>
@@ -2899,15 +2855,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J65" s="17" t="s">
         <v>21</v>
@@ -2925,24 +2881,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J66" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K66" s="5">
         <v>140</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="M66" s="4" t="s">
         <v>7</v>
@@ -2951,24 +2907,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K67" s="5">
         <v>175</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M67" s="4" t="s">
         <v>7</v>
@@ -2977,24 +2933,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K68" s="5">
         <v>90</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M68" s="4" t="s">
         <v>7</v>
@@ -3003,24 +2959,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K69" s="5">
         <v>135</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="M69" s="4" t="s">
         <v>7</v>
@@ -3029,24 +2985,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J70" s="17" t="s">
-        <v>57</v>
+        <v>134</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="K70" s="5">
         <v>220</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M70" s="4" t="s">
         <v>8</v>
@@ -3055,24 +3011,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J71" s="17" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="K71" s="5">
         <v>170</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="M71" s="4" t="s">
         <v>8</v>
@@ -3081,24 +3037,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K72" s="5">
         <v>110</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>7</v>
@@ -3107,15 +3063,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J73" s="17" t="s">
         <v>10</v>
@@ -3133,24 +3089,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J74" s="17" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K74" s="5">
         <v>175</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M74" s="4" t="s">
         <v>7</v>
@@ -3159,24 +3115,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="K75" s="5">
         <v>130</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>7</v>
@@ -3185,15 +3141,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J76" s="17" t="s">
         <v>14</v>
@@ -3211,24 +3167,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J77" s="17" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K77" s="5">
         <v>155</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>8</v>
@@ -3237,24 +3193,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K78" s="5">
         <v>150</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>7</v>
@@ -3263,24 +3219,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K79" s="5">
         <v>170</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>8</v>
@@ -3289,24 +3245,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="K80" s="5">
         <v>80</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>7</v>
@@ -3315,15 +3271,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J81" s="17" t="s">
         <v>21</v>
@@ -3341,24 +3297,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="K82" s="5">
         <v>200</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>8</v>
@@ -3367,24 +3323,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K83" s="5">
         <v>130</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>7</v>
@@ -3393,24 +3349,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K84" s="5">
         <v>120</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>7</v>
@@ -3419,24 +3375,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K85" s="5">
         <v>100</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>7</v>
@@ -3445,24 +3401,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K86" s="5">
         <v>220</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>8</v>
@@ -3471,24 +3427,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K87" s="5">
         <v>159</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>7</v>
@@ -3497,24 +3453,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K88" s="5">
         <v>200</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>8</v>
@@ -3523,15 +3479,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J89" s="17" t="s">
         <v>10</v>
@@ -3549,15 +3505,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J90" s="17" t="s">
         <v>5</v>
@@ -3566,7 +3522,7 @@
         <v>140</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>7</v>
@@ -3575,48 +3531,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K91" s="5">
         <v>120</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>7</v>
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K92" s="5">
         <v>75</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M92" s="4" t="s">
         <v>7</v>
@@ -3625,15 +3581,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J93" s="17" t="s">
         <v>23</v>
@@ -3642,7 +3598,7 @@
         <v>180</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M93" s="4" t="s">
         <v>7</v>
@@ -3651,24 +3607,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>25</v>
+        <v>125</v>
+      </c>
+      <c r="J94" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K94" s="5">
         <v>149</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M94" s="4" t="s">
         <v>8</v>
@@ -3677,24 +3633,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J95" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K95" s="5">
         <v>140</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M95" s="4" t="s">
         <v>7</v>
@@ -3703,24 +3659,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K96" s="5">
         <v>175</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M96" s="4" t="s">
         <v>8</v>
@@ -3729,15 +3685,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J97" s="17" t="s">
         <v>11</v>
@@ -3755,15 +3711,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J98" s="17" t="s">
         <v>13</v>
@@ -3781,18 +3737,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J99" s="15" t="s">
-        <v>51</v>
+        <v>132</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="K99" s="5">
         <v>178</v>
@@ -3807,15 +3763,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J100" s="17" t="s">
         <v>15</v>
@@ -3833,15 +3789,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J101" s="17" t="s">
         <v>10</v>
@@ -3859,15 +3815,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J102" s="17" t="s">
         <v>14</v>
@@ -3885,15 +3841,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J103" s="17" t="s">
         <v>5</v>
@@ -3911,24 +3867,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="K104" s="5">
         <v>55</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="M104" s="4" t="s">
         <v>7</v>
@@ -3937,24 +3893,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K105" s="5">
         <v>155</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>8</v>
@@ -3963,24 +3919,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J106" s="17" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K106" s="5">
         <v>140</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>7</v>
@@ -3989,24 +3945,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J107" s="17" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K107" s="5">
         <v>85</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>7</v>
@@ -4015,15 +3971,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J108" s="17" t="s">
         <v>21</v>
@@ -4041,24 +3997,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J109" s="17" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="K109" s="5">
         <v>120</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="M109" s="4" t="s">
         <v>7</v>
@@ -4067,24 +4023,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="K110" s="5">
         <v>230</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="M110" s="4" t="s">
         <v>8</v>
@@ -4093,24 +4049,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="K111" s="5">
         <v>150</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="M111" s="4" t="s">
         <v>7</v>
@@ -4119,24 +4075,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K112" s="9">
         <v>69</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M112" s="4" t="s">
         <v>7</v>
@@ -4145,24 +4101,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J113" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K113" s="9">
         <v>200</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M113" s="4" t="s">
         <v>8</v>
@@ -4171,24 +4127,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J114" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K114" s="9">
         <v>140</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="M114" s="4" t="s">
         <v>8</v>
@@ -4197,24 +4153,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="K115" s="9">
         <v>115</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="M115" s="4" t="s">
         <v>7</v>
@@ -4223,24 +4179,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K116" s="9">
         <v>209</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M116" s="4" t="s">
         <v>8</v>
@@ -4249,24 +4205,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K117" s="9">
         <v>200</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>8</v>
@@ -4275,24 +4231,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J118" s="17" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="K118" s="9">
         <v>160</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="M118" s="4" t="s">
         <v>8</v>
@@ -4301,15 +4257,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J119" s="17" t="s">
         <v>10</v>
@@ -4327,15 +4283,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J120" s="17" t="s">
         <v>5</v>
@@ -4353,24 +4309,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J121" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K121" s="9">
         <v>115</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>7</v>
@@ -4379,24 +4335,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J122" s="17" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="K122" s="9">
         <v>110</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="M122" s="4" t="s">
         <v>7</v>
@@ -4405,15 +4361,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J123" s="17" t="s">
         <v>23</v>
@@ -4422,7 +4378,7 @@
         <v>220</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="M123" s="4" t="s">
         <v>8</v>
@@ -4431,24 +4387,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J124" s="17" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="K124" s="9">
         <v>209</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M124" s="4" t="s">
         <v>8</v>
@@ -4457,24 +4413,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J125" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K125" s="9">
         <v>140</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M125" s="4" t="s">
         <v>7</v>
@@ -4483,24 +4439,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J126" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K126" s="9">
         <v>175</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M126" s="4" t="s">
         <v>8</v>
@@ -4509,24 +4465,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J127" s="17" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K127" s="9">
         <v>175</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M127" s="4" t="s">
         <v>7</v>
@@ -4535,24 +4491,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J128" s="17" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="K128" s="9">
         <v>240</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="M128" s="4" t="s">
         <v>8</v>
@@ -4561,24 +4517,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J129" s="17" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="K129" s="9">
         <v>160</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="M129" s="4" t="s">
         <v>8</v>
@@ -4587,15 +4543,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J130" s="17" t="s">
         <v>10</v>
@@ -4613,24 +4569,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J131" s="17" t="s">
-        <v>180</v>
+        <v>133</v>
+      </c>
+      <c r="J131" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="K131" s="9">
         <v>150</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>8</v>
@@ -4639,24 +4595,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J132" s="17" t="s">
-        <v>57</v>
+        <v>134</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="K132" s="9">
         <v>220</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M132" s="4" t="s">
         <v>8</v>
@@ -4665,24 +4621,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K133" s="9">
         <v>220</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>8</v>
@@ -4691,24 +4647,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="K134" s="9">
         <v>140</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>8</v>
@@ -4717,24 +4673,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J135" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
+      </c>
+      <c r="J135" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="K135" s="9">
         <v>240</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="M135" s="4" t="s">
         <v>8</v>
@@ -4743,24 +4699,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K136" s="9">
         <v>200</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="M136" s="4" t="s">
         <v>8</v>
@@ -4769,24 +4725,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K137" s="9">
         <v>170</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M137" s="4" t="s">
         <v>8</v>
@@ -4795,24 +4751,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K138" s="9">
         <v>170</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M138" s="4" t="s">
         <v>8</v>
@@ -4821,24 +4777,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K139" s="9">
         <v>200</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M139" s="4" t="s">
         <v>8</v>
@@ -4847,18 +4803,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="K140" s="9">
         <v>200</v>
@@ -4871,24 +4827,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="K141" s="9">
         <v>120</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>8</v>
@@ -4897,18 +4853,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K142" s="9">
         <v>200</v>
@@ -4921,24 +4877,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45904</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K143" s="9">
         <v>185</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>8</v>
@@ -4947,24 +4903,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K144" s="9">
         <v>198</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M144" s="4" t="s">
         <v>8</v>
@@ -4973,24 +4929,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K145" s="9">
         <v>230</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="M145" s="4" t="s">
         <v>8</v>
@@ -4999,24 +4955,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K146" s="9">
         <v>190</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M146" s="4" t="s">
         <v>8</v>
@@ -5025,24 +4981,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K147" s="9">
         <v>200</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M147" s="4" t="s">
         <v>8</v>
@@ -5051,24 +5007,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="J148" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
+      </c>
+      <c r="J148" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K148" s="9">
         <v>209</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M148" s="4" t="s">
         <v>8</v>
@@ -5077,15 +5033,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>5</v>
@@ -5094,7 +5050,7 @@
         <v>220</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M149" s="4" t="s">
         <v>8</v>
@@ -5103,24 +5059,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="K150" s="9">
         <v>160</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="M150" s="4" t="s">
         <v>8</v>
@@ -5129,24 +5085,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K151" s="9">
         <v>230</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="M151" s="4" t="s">
         <v>8</v>
@@ -5155,15 +5111,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45908</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>23</v>
@@ -5172,7 +5128,7 @@
         <v>220</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="M152" s="4" t="s">
         <v>8</v>
@@ -5181,24 +5137,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J153" s="4" t="s">
-        <v>175</v>
+        <v>125</v>
+      </c>
+      <c r="J153" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K153" s="9">
         <v>159</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M153" s="4" t="s">
         <v>8</v>
@@ -5207,24 +5163,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K154" s="9">
         <v>240</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M154" s="4" t="s">
         <v>8</v>
@@ -5233,24 +5189,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K155" s="9">
         <v>175</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M155" s="4" t="s">
         <v>8</v>
@@ -5259,24 +5215,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45909</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="K156" s="9">
         <v>200</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="M156" s="4" t="s">
         <v>8</v>
@@ -5285,24 +5241,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="K157" s="9">
         <v>240</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="M157" s="4" t="s">
         <v>8</v>
@@ -5311,15 +5267,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>10</v>
@@ -5337,24 +5293,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K159" s="9">
         <v>220</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M159" s="4" t="s">
         <v>8</v>
@@ -5363,24 +5319,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J160" s="17" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K160" s="9">
         <v>175</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M160" s="4" t="s">
         <v>7</v>
@@ -5389,24 +5345,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K161" s="9">
         <v>200</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M161" s="4" t="s">
         <v>8</v>
@@ -5415,17 +5371,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45910</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J162" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J162" s="17" t="s">
         <v>14</v>
       </c>
       <c r="K162" s="9">
@@ -5441,15 +5397,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J163" s="4"/>
       <c r="K163" s="9"/>
@@ -5461,24 +5417,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K164" s="9">
         <v>200</v>
       </c>
       <c r="L164" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M164" s="4" t="s">
         <v>8</v>
@@ -5487,24 +5443,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K165" s="9">
         <v>170</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>8</v>
@@ -5513,24 +5469,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K166" s="9">
         <v>170</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="M166" s="4" t="s">
         <v>8</v>
@@ -5539,15 +5495,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>21</v>
@@ -5565,24 +5521,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K168" s="9">
         <v>198</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M168" s="4" t="s">
         <v>8</v>
@@ -5591,15 +5547,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45911</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J169" s="4"/>
       <c r="K169" s="9"/>
@@ -5611,24 +5567,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K170" s="9">
         <v>170</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M170" s="4" t="s">
         <v>8</v>
@@ -5637,24 +5593,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K171" s="9">
         <v>198</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M171" s="4" t="s">
         <v>8</v>
@@ -5663,24 +5619,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K172" s="9">
         <v>170</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="M172" s="4" t="s">
         <v>8</v>
@@ -5689,24 +5645,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J173" s="15" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K173" s="9">
         <v>235</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M173" s="4" t="s">
         <v>8</v>
@@ -5715,24 +5671,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="K174" s="9">
         <v>250</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="M174" s="4" t="s">
         <v>8</v>
@@ -5741,24 +5697,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="K175" s="9">
         <v>220</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>8</v>
@@ -5767,24 +5723,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K176" s="9">
         <v>200</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M176" s="4" t="s">
         <v>8</v>
@@ -5793,24 +5749,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J177" s="4" t="s">
-        <v>175</v>
+        <v>125</v>
+      </c>
+      <c r="J177" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K177" s="9">
         <v>209</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M177" s="4" t="s">
         <v>8</v>
@@ -5819,24 +5775,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K178" s="9">
         <v>220</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M178" s="4" t="s">
         <v>8</v>
@@ -5845,24 +5801,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K179" s="9">
         <v>260</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M179" s="4" t="s">
         <v>8</v>
@@ -5871,24 +5827,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K180" s="9">
         <v>198</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M180" s="4" t="s">
         <v>8</v>
@@ -5897,24 +5853,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K181" s="9">
         <v>280</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M181" s="4" t="s">
         <v>8</v>
@@ -5923,24 +5879,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45915</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K182" s="9">
         <v>140</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="M182" s="4" t="s">
         <v>7</v>
@@ -5949,24 +5905,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K183" s="9">
         <v>220</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M183" s="4" t="s">
         <v>8</v>
@@ -5975,24 +5931,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J184" s="4" t="s">
-        <v>175</v>
+        <v>125</v>
+      </c>
+      <c r="J184" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K184" s="9">
         <v>209</v>
       </c>
       <c r="L184" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M184" s="4" t="s">
         <v>8</v>
@@ -6001,24 +5957,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K185" s="9">
         <v>175</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M185" s="4" t="s">
         <v>8</v>
@@ -6027,15 +5983,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>23</v>
@@ -6044,7 +6000,7 @@
         <v>220</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M186" s="4" t="s">
         <v>8</v>
@@ -6053,24 +6009,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K187" s="9">
         <v>200</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M187" s="4" t="s">
         <v>8</v>
@@ -6079,24 +6035,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J188" s="4" t="s">
-        <v>175</v>
+        <v>132</v>
+      </c>
+      <c r="J188" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K188" s="9">
         <v>259</v>
       </c>
       <c r="L188" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M188" s="4" t="s">
         <v>8</v>
@@ -6105,15 +6061,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45916</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>11</v>
@@ -6131,24 +6087,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K190" s="9">
         <v>200</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M190" s="4" t="s">
         <v>8</v>
@@ -6157,24 +6113,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K191" s="9">
         <v>200</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M191" s="4" t="s">
         <v>8</v>
@@ -6183,24 +6139,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K192" s="9">
         <v>170</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="M192" s="4" t="s">
         <v>8</v>
@@ -6209,15 +6165,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>10</v>
@@ -6235,24 +6191,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45917</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="K194" s="9">
         <v>150</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="M194" s="4" t="s">
         <v>8</v>
@@ -6261,24 +6217,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="K195" s="9">
         <v>240</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="M195" s="4" t="s">
         <v>8</v>
@@ -6287,24 +6243,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K196" s="9">
         <v>220</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M196" s="4" t="s">
         <v>8</v>
@@ -6313,24 +6269,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
       <c r="H197" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K197" s="9">
         <v>280</v>
       </c>
       <c r="L197" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M197" s="4" t="s">
         <v>8</v>
@@ -6339,24 +6295,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K198" s="9">
         <v>230</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="M198" s="4" t="s">
         <v>8</v>
@@ -6365,24 +6321,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K199" s="9">
         <v>230</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="M199" s="4" t="s">
         <v>8</v>
@@ -6391,15 +6347,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>21</v>
@@ -6417,24 +6373,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45918</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="K201" s="9">
         <v>180</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="M201" s="4" t="s">
         <v>8</v>
@@ -6443,24 +6399,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K202" s="9">
         <v>198</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M202" s="4" t="s">
         <v>8</v>
@@ -6469,24 +6425,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K203" s="9">
         <v>170</v>
       </c>
       <c r="L203" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M203" s="4" t="s">
         <v>8</v>
@@ -6495,24 +6451,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K204" s="9">
         <v>200</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="M204" s="4" t="s">
         <v>8</v>
@@ -6521,24 +6477,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K205" s="9">
         <v>150</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="M205" s="4" t="s">
         <v>8</v>
@@ -6547,15 +6503,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>13</v>
@@ -6564,7 +6520,7 @@
         <v>200</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M206" s="4" t="s">
         <v>8</v>
@@ -6573,24 +6529,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J207" s="4" t="s">
-        <v>175</v>
+        <v>125</v>
+      </c>
+      <c r="J207" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K207" s="9">
         <v>159</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M207" s="4" t="s">
         <v>8</v>
@@ -6599,24 +6555,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="K208" s="9">
         <v>230</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="M208" s="4" t="s">
         <v>8</v>
@@ -6625,24 +6581,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I209" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K209" s="9">
         <v>175</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M209" s="4" t="s">
         <v>8</v>
@@ -6651,24 +6607,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I210" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K210" s="9">
         <v>260</v>
       </c>
       <c r="L210" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M210" s="4" t="s">
         <v>8</v>
@@ -6677,15 +6633,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I211" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J211" s="4"/>
       <c r="K211" s="9"/>
@@ -6697,24 +6653,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K212" s="9">
         <v>185</v>
       </c>
       <c r="L212" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M212" s="4" t="s">
         <v>8</v>
@@ -6723,24 +6679,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I213" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J213" s="4" t="s">
-        <v>78</v>
+        <v>132</v>
+      </c>
+      <c r="J213" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="K213" s="9">
         <v>240</v>
       </c>
       <c r="L213" s="4" t="s">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="M213" s="4" t="s">
         <v>8</v>
@@ -6749,24 +6705,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45922</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I214" s="6" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="K214" s="9">
         <v>170</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="M214" s="4" t="s">
         <v>8</v>
@@ -6775,24 +6731,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J215" s="4" t="s">
-        <v>175</v>
+        <v>125</v>
+      </c>
+      <c r="J215" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K215" s="9">
         <v>209</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M215" s="4" t="s">
         <v>8</v>
@@ -6801,24 +6757,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K216" s="9">
         <v>200</v>
       </c>
       <c r="L216" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M216" s="4" t="s">
         <v>8</v>
@@ -6827,24 +6783,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K217" s="9">
         <v>220</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M217" s="4" t="s">
         <v>8</v>
@@ -6853,24 +6809,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K218" s="9">
         <v>250</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M218" s="4" t="s">
         <v>8</v>
@@ -6879,24 +6835,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K219" s="9">
         <v>175</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M219" s="4" t="s">
         <v>8</v>
@@ -6905,24 +6861,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I220" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K220" s="9">
         <v>275</v>
       </c>
       <c r="L220" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M220" s="4" t="s">
         <v>8</v>
@@ -6931,24 +6887,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45923</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I221" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K221" s="9">
         <v>200</v>
       </c>
       <c r="L221" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M221" s="4" t="s">
         <v>8</v>
@@ -6957,24 +6913,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I222" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="K222" s="9">
         <v>200</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="M222" s="4" t="s">
         <v>8</v>
@@ -6983,15 +6939,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>23</v>
@@ -7000,7 +6956,7 @@
         <v>220</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M223" s="4" t="s">
         <v>8</v>
@@ -7009,24 +6965,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K224" s="9">
         <v>280</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M224" s="4" t="s">
         <v>8</v>
@@ -7035,17 +6991,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J225" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J225" s="17" t="s">
         <v>14</v>
       </c>
       <c r="K225" s="9">
@@ -7061,15 +7017,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I226" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>11</v>
@@ -7087,24 +7043,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45924</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="K227" s="9">
         <v>110</v>
       </c>
       <c r="L227" s="4" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="M227" s="4" t="s">
         <v>8</v>
@@ -7113,24 +7069,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K228" s="9">
         <v>205</v>
       </c>
       <c r="L228" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M228" s="4" t="s">
         <v>8</v>
@@ -7139,24 +7095,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K229" s="9">
         <v>200</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M229" s="4" t="s">
         <v>8</v>
@@ -7165,24 +7121,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K230" s="9">
         <v>170</v>
       </c>
       <c r="L230" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M230" s="4" t="s">
         <v>8</v>
@@ -7191,15 +7147,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>21</v>
@@ -7217,24 +7173,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K232" s="9">
         <v>220</v>
       </c>
       <c r="L232" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M232" s="4" t="s">
         <v>8</v>
@@ -7243,24 +7199,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K233" s="9">
         <v>175</v>
       </c>
       <c r="L233" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M233" s="4" t="s">
         <v>7</v>
@@ -7269,24 +7225,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="K234" s="9">
         <v>170</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="M234" s="4" t="s">
         <v>8</v>
@@ -7295,24 +7251,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45925</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K235" s="9">
         <v>250</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M235" s="4" t="s">
         <v>8</v>
@@ -7321,24 +7277,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K236" s="9">
         <v>198</v>
       </c>
       <c r="L236" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M236" s="4" t="s">
         <v>8</v>
@@ -7347,24 +7303,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="K237" s="9">
         <v>180</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="M237" s="4" t="s">
         <v>8</v>
@@ -7373,24 +7329,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I238" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K238" s="9">
         <v>150</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="M238" s="4" t="s">
         <v>8</v>
@@ -7399,24 +7355,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K239" s="9">
         <v>220</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M239" s="4" t="s">
         <v>8</v>
@@ -7425,24 +7381,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I240" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="J240" s="4" t="s">
-        <v>215</v>
+        <v>197</v>
+      </c>
+      <c r="J240" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K240" s="9">
         <v>209</v>
       </c>
       <c r="L240" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M240" s="4" t="s">
         <v>8</v>
@@ -7451,24 +7407,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K241" s="9">
         <v>200</v>
       </c>
       <c r="L241" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M241" s="4" t="s">
         <v>8</v>
@@ -7477,24 +7433,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="K242" s="9">
         <v>200</v>
       </c>
       <c r="L242" s="4" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="M242" s="4" t="s">
         <v>8</v>
@@ -7503,24 +7459,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K243" s="9">
         <v>280</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M243" s="4" t="s">
         <v>8</v>
@@ -7529,24 +7485,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I244" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K244" s="9">
         <v>200</v>
       </c>
       <c r="L244" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M244" s="4" t="s">
         <v>8</v>
@@ -7555,15 +7511,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45929</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I245" s="6" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>23</v>
@@ -7572,7 +7528,7 @@
         <v>220</v>
       </c>
       <c r="L245" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M245" s="4" t="s">
         <v>8</v>
@@ -7581,24 +7537,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I246" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J246" s="4" t="s">
-        <v>78</v>
+        <v>132</v>
+      </c>
+      <c r="J246" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="K246" s="9">
         <v>240</v>
       </c>
       <c r="L246" s="4" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="M246" s="4" t="s">
         <v>8</v>
@@ -7607,24 +7563,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I247" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="J247" s="4" t="s">
-        <v>223</v>
+        <v>197</v>
+      </c>
+      <c r="J247" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K247" s="9">
         <v>209</v>
       </c>
       <c r="L247" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M247" s="4" t="s">
         <v>8</v>
@@ -7633,24 +7589,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I248" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K248" s="9">
         <v>200</v>
       </c>
       <c r="L248" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M248" s="4" t="s">
         <v>8</v>
@@ -7659,24 +7615,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K249" s="9">
         <v>220</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M249" s="4" t="s">
         <v>8</v>
@@ -7685,24 +7641,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I250" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K250" s="9">
         <v>250</v>
       </c>
       <c r="L250" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M250" s="4" t="s">
         <v>8</v>
@@ -7711,24 +7667,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K251" s="9">
         <v>265</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M251" s="4" t="s">
         <v>8</v>
@@ -7737,24 +7693,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I252" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K252" s="9">
         <v>175</v>
       </c>
       <c r="L252" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M252" s="4" t="s">
         <v>8</v>
@@ -7763,24 +7719,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45930</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K253" s="9">
         <v>200</v>
       </c>
       <c r="L253" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M253" s="4" t="s">
         <v>8</v>
@@ -7789,24 +7745,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="K254" s="9">
         <v>200</v>
       </c>
       <c r="L254" s="4" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="M254" s="4" t="s">
         <v>8</v>
@@ -7815,24 +7771,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I255" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K255" s="9">
         <v>200</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M255" s="4" t="s">
         <v>8</v>
@@ -7841,24 +7797,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I256" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K256" s="9">
         <v>280</v>
       </c>
       <c r="L256" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M256" s="4" t="s">
         <v>8</v>
@@ -7867,17 +7823,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I257" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J257" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J257" s="17" t="s">
         <v>14</v>
       </c>
       <c r="K257" s="9">
@@ -7893,15 +7849,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I258" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J258" s="4" t="s">
         <v>11</v>
@@ -7919,24 +7875,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45931</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K259" s="9">
         <v>240</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M259" s="4" t="s">
         <v>8</v>
@@ -7945,24 +7901,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K260" s="9">
         <v>280</v>
       </c>
       <c r="L260" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M260" s="4" t="s">
         <v>8</v>
@@ -7971,24 +7927,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I261" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="K261" s="9">
         <v>210</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="M261" s="4" t="s">
         <v>8</v>
@@ -7997,24 +7953,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I262" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J262" s="4" t="s">
-        <v>226</v>
+        <v>133</v>
+      </c>
+      <c r="J262" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="K262" s="9">
         <v>110</v>
       </c>
       <c r="L262" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="M262" s="4" t="s">
         <v>8</v>
@@ -8023,24 +7979,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I263" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K263" s="9">
         <v>212</v>
       </c>
       <c r="L263" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M263" s="4" t="s">
         <v>8</v>
@@ -8049,24 +8005,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K264" s="9">
         <v>200</v>
       </c>
       <c r="L264" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M264" s="4" t="s">
         <v>8</v>
@@ -8075,24 +8031,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="I265" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K265" s="9">
         <v>190</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="M265" s="4" t="s">
         <v>8</v>
@@ -8101,15 +8057,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J266" s="4" t="s">
         <v>21</v>
@@ -8127,24 +8083,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45932</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K267" s="9">
         <v>198</v>
       </c>
       <c r="L267" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M267" s="4" t="s">
         <v>8</v>
@@ -8153,24 +8109,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K268" s="9">
         <v>200</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M268" s="4" t="s">
         <v>8</v>
@@ -8179,24 +8135,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="I269" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K269" s="9">
         <v>150</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="M269" s="4" t="s">
         <v>8</v>
@@ -8205,24 +8161,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="I270" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J270" s="4" t="s">
-        <v>231</v>
+        <v>136</v>
+      </c>
+      <c r="J270" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="K270" s="9">
         <v>235</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M270" s="4" t="s">
         <v>8</v>
@@ -8231,24 +8187,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
       <c r="H271" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I271" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J271" s="4" t="s">
-        <v>223</v>
+        <v>194</v>
+      </c>
+      <c r="J271" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K271" s="9">
         <v>259</v>
       </c>
       <c r="L271" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M271" s="4" t="s">
         <v>8</v>
@@ -8257,24 +8213,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I272" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="K272" s="9">
         <v>240</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="M272" s="4" t="s">
         <v>8</v>
@@ -8283,24 +8239,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
       <c r="H273" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="K273" s="9">
         <v>200</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="M273" s="4" t="s">
         <v>8</v>
@@ -8310,24 +8266,24 @@
       </c>
       <c r="O273" s="19"/>
     </row>
-    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="K274" s="9">
         <v>250</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="M274" s="4" t="s">
         <v>8</v>
@@ -8336,24 +8292,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K275" s="9">
         <v>280</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M275" s="4" t="s">
         <v>8</v>
@@ -8362,24 +8318,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K276" s="9">
         <v>175</v>
       </c>
       <c r="L276" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M276" s="4" t="s">
         <v>8</v>
@@ -8388,24 +8344,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
       <c r="H277" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K277" s="9">
         <v>250</v>
       </c>
       <c r="L277" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M277" s="4" t="s">
         <v>8</v>
@@ -8414,24 +8370,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45903</v>
       </c>
       <c r="H278" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J278" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
+      </c>
+      <c r="J278" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="K278" s="9">
         <v>240</v>
       </c>
       <c r="L278" s="4" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="M278" s="4" t="s">
         <v>8</v>
@@ -8440,24 +8396,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K279" s="9">
         <v>230</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="M279" s="4" t="s">
         <v>8</v>
@@ -8466,15 +8422,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
       <c r="H280" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>10</v>
@@ -8492,15 +8448,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
       <c r="H281" s="4" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J281" s="4" t="s">
         <v>23</v>
@@ -8509,7 +8465,7 @@
         <v>220</v>
       </c>
       <c r="L281" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M281" s="4" t="s">
         <v>8</v>
@@ -8518,24 +8474,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J282" s="4" t="s">
-        <v>223</v>
+        <v>194</v>
+      </c>
+      <c r="J282" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="K282" s="9">
         <v>259</v>
       </c>
       <c r="L282" s="4" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="M282" s="4" t="s">
         <v>8</v>
@@ -8544,24 +8500,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
       <c r="H283" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K283" s="9">
         <v>200</v>
       </c>
       <c r="L283" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M283" s="4" t="s">
         <v>8</v>
@@ -8570,24 +8526,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
       <c r="H284" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K284" s="9">
         <v>240</v>
       </c>
       <c r="L284" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M284" s="4" t="s">
         <v>8</v>
@@ -8596,24 +8552,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
       <c r="H285" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K285" s="9">
         <v>175</v>
       </c>
       <c r="L285" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M285" s="4" t="s">
         <v>8</v>
@@ -8622,24 +8578,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
       <c r="H286" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K286" s="9">
         <v>250</v>
       </c>
       <c r="L286" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M286" s="4" t="s">
         <v>8</v>
@@ -8648,24 +8604,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
       <c r="H287" s="4" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="I287" s="6" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K287" s="9">
         <v>265</v>
       </c>
       <c r="L287" s="4" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M287" s="4" t="s">
         <v>8</v>
@@ -8674,24 +8630,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
       <c r="H288" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I288" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K288" s="9">
         <v>140</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>8</v>
@@ -8700,24 +8656,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
       <c r="H289" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I289" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K289" s="9">
         <v>200</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M289" s="4" t="s">
         <v>8</v>
@@ -8726,24 +8682,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
       <c r="H290" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I290" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="K290" s="9">
         <v>179.9</v>
       </c>
       <c r="L290" s="4" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="M290" s="4" t="s">
         <v>8</v>
@@ -8752,24 +8708,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
       <c r="H291" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K291" s="9">
         <v>200</v>
       </c>
       <c r="L291" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>8</v>
@@ -8778,24 +8734,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
       <c r="H292" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I292" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K292" s="9">
         <v>280</v>
       </c>
       <c r="L292" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M292" s="4" t="s">
         <v>8</v>
@@ -8804,17 +8760,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
       <c r="H293" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J293" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J293" s="17" t="s">
         <v>14</v>
       </c>
       <c r="K293" s="9">
@@ -8830,15 +8786,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
       <c r="H294" s="4" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J294" s="4" t="s">
         <v>23</v>
@@ -8847,7 +8803,7 @@
         <v>220</v>
       </c>
       <c r="L294" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M294" s="4" t="s">
         <v>8</v>
@@ -8856,24 +8812,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
       <c r="H295" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K295" s="9">
         <v>200</v>
       </c>
       <c r="L295" s="4" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="M295" s="4" t="s">
         <v>8</v>
@@ -8882,24 +8838,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
       <c r="H296" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K296" s="9">
         <v>280</v>
       </c>
       <c r="L296" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M296" s="4" t="s">
         <v>8</v>
@@ -8908,24 +8864,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
       <c r="H297" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I297" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J297" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
+      </c>
+      <c r="J297" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="K297" s="9">
         <v>160</v>
       </c>
       <c r="L297" s="4" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="M297" s="4" t="s">
         <v>8</v>
@@ -8934,24 +8890,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
       <c r="H298" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K298" s="9">
         <v>170</v>
       </c>
       <c r="L298" s="4" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="M298" s="4" t="s">
         <v>8</v>
@@ -8960,24 +8916,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
       <c r="H299" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K299" s="9">
         <v>200</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M299" s="4" t="s">
         <v>8</v>
@@ -8986,24 +8942,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
       <c r="H300" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I300" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K300" s="9">
         <v>170</v>
       </c>
       <c r="L300" s="4" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="M300" s="4" t="s">
         <v>8</v>
@@ -9012,15 +8968,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
       <c r="H301" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J301" s="4" t="s">
         <v>21</v>
@@ -9038,15 +8994,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45943</v>
       </c>
       <c r="H302" s="4" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J302" s="4" t="s">
         <v>23</v>
@@ -9055,7 +9011,7 @@
         <v>220</v>
       </c>
       <c r="L302" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M302" s="4" t="s">
         <v>8</v>
@@ -9064,24 +9020,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45943</v>
       </c>
       <c r="H303" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K303" s="9">
         <v>259</v>
       </c>
       <c r="L303" s="4" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="M303" s="4" t="s">
         <v>8</v>
@@ -9090,24 +9046,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45943</v>
       </c>
       <c r="H304" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I304" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K304" s="9">
         <v>200</v>
       </c>
       <c r="L304" s="4" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="M304" s="4" t="s">
         <v>8</v>
@@ -9116,24 +9072,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45943</v>
       </c>
       <c r="H305" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="K305" s="9">
         <v>220</v>
       </c>
       <c r="L305" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M305" s="4" t="s">
         <v>8</v>
@@ -9142,24 +9098,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45943</v>
       </c>
       <c r="H306" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K306" s="9">
         <v>180</v>
       </c>
       <c r="L306" s="4" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="M306" s="4" t="s">
         <v>8</v>
@@ -9168,24 +9124,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45943</v>
       </c>
       <c r="H307" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="K307" s="9">
         <v>220</v>
       </c>
       <c r="L307" s="4" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="M307" s="4" t="s">
         <v>8</v>
@@ -9194,7 +9150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G308" s="4"/>
       <c r="H308" s="4"/>
       <c r="I308" s="6"/>
@@ -9204,7 +9160,7 @@
       <c r="M308" s="4"/>
       <c r="N308" s="6"/>
     </row>
-    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G309" s="4"/>
       <c r="H309" s="4"/>
       <c r="I309" s="6"/>
@@ -9214,24 +9170,24 @@
       <c r="M309" s="4"/>
       <c r="N309" s="6"/>
     </row>
-    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
       <c r="H310" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J310" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
+      </c>
+      <c r="J310" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="K310" s="9">
         <v>230</v>
       </c>
       <c r="L310" s="4" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="M310" s="4" t="s">
         <v>8</v>
@@ -9240,24 +9196,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
       <c r="H311" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K311" s="9">
         <v>180</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="M311" s="4" t="s">
         <v>8</v>
@@ -9266,24 +9222,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
       <c r="H312" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K312" s="9">
         <v>198</v>
       </c>
       <c r="L312" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M312" s="4" t="s">
         <v>8</v>
@@ -9292,24 +9248,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
       <c r="H313" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I313" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="K313" s="9">
         <v>180</v>
       </c>
       <c r="L313" s="4" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="M313" s="4" t="s">
         <v>8</v>
@@ -9318,24 +9274,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
       <c r="H314" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I314" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K314" s="9">
         <v>150</v>
       </c>
       <c r="L314" s="4" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="M314" s="4" t="s">
         <v>8</v>
@@ -9344,24 +9300,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
       <c r="H315" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I315" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J315" s="4" t="s">
-        <v>74</v>
+        <v>136</v>
+      </c>
+      <c r="J315" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="K315" s="9">
         <v>140</v>
       </c>
       <c r="L315" s="4" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="M315" s="4" t="s">
         <v>8</v>
@@ -9370,24 +9326,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45939</v>
       </c>
       <c r="H316" s="4" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="I316" s="6" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K316" s="9">
         <v>140</v>
       </c>
       <c r="L316" s="4" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="M316" s="4" t="s">
         <v>8</v>
@@ -9396,24 +9352,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45939</v>
       </c>
       <c r="H317" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I317" s="6" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K317" s="9">
         <v>200</v>
       </c>
       <c r="L317" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M317" s="4" t="s">
         <v>8</v>
@@ -9422,24 +9378,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45939</v>
       </c>
       <c r="H318" s="4" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="I318" s="6" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="K318" s="9">
         <v>220</v>
       </c>
       <c r="L318" s="4" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="M318" s="4" t="s">
         <v>8</v>
@@ -9448,24 +9404,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45939</v>
       </c>
       <c r="H319" s="4" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="I319" s="6" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K319" s="9">
         <v>200</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M319" s="4" t="s">
         <v>8</v>
@@ -9474,24 +9430,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45939</v>
       </c>
       <c r="H320" s="4" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="I320" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="K320" s="9">
         <v>280</v>
       </c>
       <c r="L320" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M320" s="4" t="s">
         <v>8</v>
@@ -9500,24 +9456,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45939</v>
       </c>
       <c r="H321" s="4" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="I321" s="6" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="K321" s="9">
         <v>180</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="M321" s="4" t="s">
         <v>8</v>
@@ -9526,24 +9482,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45939</v>
       </c>
       <c r="H322" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I322" s="6" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K322" s="9">
         <v>200</v>
       </c>
       <c r="L322" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M322" s="4" t="s">
         <v>8</v>
@@ -9552,24 +9508,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45939</v>
       </c>
       <c r="H323" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="K323" s="9">
         <v>220</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M323" s="4" t="s">
         <v>8</v>
@@ -9578,24 +9534,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45940</v>
       </c>
       <c r="H324" s="4" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="K324" s="9">
         <v>220</v>
       </c>
       <c r="L324" s="4" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="M324" s="4" t="s">
         <v>8</v>
@@ -9604,15 +9560,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
       <c r="H325" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I325" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J325" s="4" t="s">
         <v>11</v>
@@ -9621,7 +9577,7 @@
         <v>160</v>
       </c>
       <c r="L325" s="4" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="M325" s="4" t="s">
         <v>8</v>
@@ -9630,24 +9586,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
       <c r="H326" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I326" s="6" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K326" s="9">
         <v>200</v>
       </c>
       <c r="L326" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M326" s="4" t="s">
         <v>8</v>
@@ -9656,24 +9612,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
       <c r="H327" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="K327" s="9">
         <v>270</v>
       </c>
       <c r="L327" s="4" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="M327" s="4" t="s">
         <v>8</v>
@@ -9682,24 +9638,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
       <c r="H328" s="4" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="I328" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="K328" s="9">
         <v>200</v>
       </c>
       <c r="L328" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="M328" s="4" t="s">
         <v>8</v>
@@ -9708,24 +9664,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G329" s="3">
         <v>45944</v>
       </c>
       <c r="H329" s="4" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="I329" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="K329" s="9">
         <v>280</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M329" s="4" t="s">
         <v>8</v>
@@ -9734,24 +9690,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45944</v>
       </c>
       <c r="H330" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I330" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J330" s="4" t="s">
-        <v>263</v>
+        <v>133</v>
+      </c>
+      <c r="J330" s="17" t="s">
+        <v>14</v>
       </c>
       <c r="K330" s="9">
         <v>160</v>
       </c>
       <c r="L330" s="4" t="s">
-        <v>264</v>
+        <v>16</v>
       </c>
       <c r="M330" s="4" t="s">
         <v>8</v>
@@ -9760,78 +9716,248 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G331" s="4"/>
-      <c r="H331" s="4"/>
-      <c r="I331" s="6"/>
-      <c r="J331" s="4"/>
-      <c r="K331" s="9"/>
-      <c r="L331" s="4"/>
-      <c r="M331" s="4"/>
-      <c r="N331" s="6"/>
+    <row r="331" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G331" s="20">
+        <v>45944</v>
+      </c>
+      <c r="H331" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="I331" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J331" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="K331" s="23">
+        <v>180</v>
+      </c>
+      <c r="L331" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="M331" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="N331" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="332" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G332" s="4"/>
-      <c r="H332" s="4"/>
-      <c r="I332" s="6"/>
-      <c r="J332" s="4"/>
-      <c r="K332" s="9"/>
-      <c r="L332" s="4"/>
-      <c r="M332" s="4"/>
-      <c r="N332" s="6"/>
+      <c r="G332" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H332" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I332" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J332" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="K332" s="9">
+        <v>220</v>
+      </c>
+      <c r="L332" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M332" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N332" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="333" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G333" s="4"/>
-      <c r="H333" s="4"/>
-      <c r="I333" s="6"/>
-      <c r="J333" s="4"/>
-      <c r="K333" s="9"/>
-      <c r="L333" s="4"/>
-      <c r="M333" s="4"/>
-      <c r="N333" s="6"/>
+      <c r="G333" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H333" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I333" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J333" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K333" s="9">
+        <v>230</v>
+      </c>
+      <c r="L333" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="M333" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N333" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="334" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G334" s="4"/>
-      <c r="H334" s="4"/>
-      <c r="I334" s="6"/>
-      <c r="J334" s="4"/>
-      <c r="K334" s="9"/>
-      <c r="L334" s="4"/>
-      <c r="M334" s="4"/>
-      <c r="N334" s="6"/>
+      <c r="G334" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H334" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="I334" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="J334" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K334" s="9">
+        <v>200</v>
+      </c>
+      <c r="L334" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M334" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N334" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="335" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G335" s="4"/>
-      <c r="H335" s="4"/>
-      <c r="I335" s="6"/>
+      <c r="G335" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H335" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I335" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="J335" s="4"/>
       <c r="K335" s="9"/>
       <c r="L335" s="4"/>
       <c r="M335" s="4"/>
-      <c r="N335" s="6"/>
+      <c r="N335" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="336" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G336" s="4"/>
-      <c r="H336" s="4"/>
-      <c r="I336" s="6"/>
+      <c r="G336" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H336" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I336" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="J336" s="4"/>
       <c r="K336" s="9"/>
       <c r="L336" s="4"/>
       <c r="M336" s="4"/>
-      <c r="N336" s="6"/>
-    </row>
-    <row r="337" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G337" s="4"/>
+      <c r="N336" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G337" s="3"/>
       <c r="H337" s="4"/>
       <c r="I337" s="6"/>
       <c r="J337" s="4"/>
       <c r="K337" s="9"/>
       <c r="L337" s="4"/>
       <c r="M337" s="4"/>
-      <c r="N337" s="6"/>
+      <c r="N337" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="338" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G338" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H338" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I338" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J338" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="K338" s="9">
+        <v>160</v>
+      </c>
+      <c r="L338" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M338" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N338" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G339" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H339" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I339" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J339" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K339" s="9">
+        <v>218.9</v>
+      </c>
+      <c r="L339" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="M339" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N339" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="340" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G340" s="4"/>
+      <c r="H340" s="4"/>
+      <c r="I340" s="6"/>
+      <c r="J340" s="4"/>
+      <c r="K340" s="9"/>
+      <c r="L340" s="4"/>
+      <c r="M340" s="4"/>
+      <c r="N340" s="6"/>
+    </row>
+    <row r="341" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G341" s="4"/>
+      <c r="H341" s="4"/>
+      <c r="I341" s="6"/>
+      <c r="J341" s="4"/>
+      <c r="K341" s="9"/>
+      <c r="L341" s="4"/>
+      <c r="M341" s="4"/>
+      <c r="N341" s="6"/>
+    </row>
+    <row r="342" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G342" s="4"/>
+      <c r="H342" s="4"/>
+      <c r="I342" s="6"/>
+      <c r="J342" s="4"/>
+      <c r="K342" s="9"/>
+      <c r="L342" s="4"/>
+      <c r="M342" s="4"/>
+      <c r="N342" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N330" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N339" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2025" month="10" day="15" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1854" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B66D996-7FB7-4922-95F2-8E802807062B}"/>
+  <xr:revisionPtr revIDLastSave="1872" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5397E018-A14D-4149-ACB6-22BB0DB23259}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="248">
   <si>
     <t>DATA</t>
   </si>
@@ -880,7 +880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -942,6 +942,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1278,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1" filterMode="1">
+  <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="G5:O342"/>
@@ -1321,7 +1327,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1347,7 +1353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1373,7 +1379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1399,7 +1405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1425,7 +1431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1451,7 +1457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1477,7 +1483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1529,7 +1535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1555,7 +1561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1581,7 +1587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1607,7 +1613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1633,7 +1639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1659,7 +1665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1685,7 +1691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1711,7 +1717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1737,7 +1743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1763,7 +1769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1789,7 +1795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1815,7 +1821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1841,7 +1847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1867,7 +1873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1893,7 +1899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1919,7 +1925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -1945,7 +1951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -1971,7 +1977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -1997,7 +2003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2023,7 +2029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2049,7 +2055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2075,7 +2081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2101,7 +2107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2127,7 +2133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2153,7 +2159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2179,7 +2185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2205,7 +2211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2231,7 +2237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2257,7 +2263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2283,7 +2289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2309,7 +2315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2335,7 +2341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2361,7 +2367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2387,7 +2393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2413,7 +2419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2439,7 +2445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2465,7 +2471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2491,7 +2497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2517,7 +2523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2543,7 +2549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2569,7 +2575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2595,7 +2601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2621,7 +2627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2647,7 +2653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2673,7 +2679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2699,7 +2705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2725,7 +2731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2751,7 +2757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2777,7 +2783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2803,7 +2809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2829,7 +2835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2855,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2881,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2907,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2933,7 +2939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -2959,7 +2965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -2985,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3011,7 +3017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3037,7 +3043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3063,7 +3069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3089,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3115,7 +3121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3141,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3167,7 +3173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3193,7 +3199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3219,7 +3225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3245,7 +3251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3271,7 +3277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3297,7 +3303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3323,7 +3329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3349,7 +3355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3375,7 +3381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3401,7 +3407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3427,7 +3433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3453,7 +3459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3479,7 +3485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3505,7 +3511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3531,7 +3537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3555,7 +3561,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3581,7 +3587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3607,7 +3613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3633,7 +3639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3659,7 +3665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3685,7 +3691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3711,7 +3717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3737,7 +3743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3763,7 +3769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3789,7 +3795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3815,7 +3821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3841,7 +3847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3867,7 +3873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3893,7 +3899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3919,7 +3925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -3945,7 +3951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -3971,7 +3977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -3997,7 +4003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4023,7 +4029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4049,7 +4055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4075,7 +4081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4101,7 +4107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4127,7 +4133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4153,7 +4159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4179,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4205,7 +4211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4231,7 +4237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4257,7 +4263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4283,7 +4289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4309,7 +4315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4335,7 +4341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4361,7 +4367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4387,7 +4393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4413,7 +4419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4439,7 +4445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4465,7 +4471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4491,7 +4497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4517,7 +4523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4543,7 +4549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4569,7 +4575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4595,7 +4601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4621,7 +4627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4647,7 +4653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4673,7 +4679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4699,7 +4705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4725,7 +4731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4751,7 +4757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4777,7 +4783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4803,7 +4809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4827,7 +4833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4853,7 +4859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4877,50 +4883,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
-        <v>45904</v>
+        <v>45903</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="K143" s="9">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N143" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="144" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="K144" s="9">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M144" s="4" t="s">
         <v>8</v>
@@ -4929,24 +4935,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="K145" s="9">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="M145" s="4" t="s">
         <v>8</v>
@@ -4955,24 +4961,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="K146" s="9">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="M146" s="4" t="s">
         <v>8</v>
@@ -4981,24 +4987,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K147" s="9">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="M147" s="4" t="s">
         <v>8</v>
@@ -5007,24 +5013,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="J148" s="17" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K148" s="9">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="M148" s="4" t="s">
         <v>8</v>
@@ -5033,24 +5039,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K149" s="9">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M149" s="4" t="s">
         <v>8</v>
@@ -5059,24 +5065,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="K150" s="9">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="M150" s="4" t="s">
         <v>8</v>
@@ -5085,51 +5091,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
       <c r="H151" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J151" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K151" s="9">
+        <v>160</v>
+      </c>
+      <c r="L151" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M151" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N151" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G152" s="3">
+        <v>45904</v>
+      </c>
+      <c r="H152" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="I151" s="6" t="s">
+      <c r="I152" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J151" s="4" t="s">
+      <c r="J152" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K151" s="9">
+      <c r="K152" s="9">
         <v>230</v>
       </c>
-      <c r="L151" s="4" t="s">
+      <c r="L152" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="M151" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N151" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="152" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G152" s="3">
-        <v>45908</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="I152" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J152" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K152" s="9">
-        <v>220</v>
-      </c>
-      <c r="L152" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="M152" s="4" t="s">
         <v>8</v>
       </c>
@@ -5137,330 +5143,330 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I153" s="4" t="s">
-        <v>125</v>
+        <v>141</v>
+      </c>
+      <c r="I153" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="J153" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K153" s="9">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="M153" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N153" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="N153" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I154" s="6" t="s">
-        <v>140</v>
+        <v>160</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K154" s="9">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="M154" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N154" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="155" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="N154" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
       <c r="H155" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I155" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J155" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K155" s="9">
+        <v>240</v>
+      </c>
+      <c r="L155" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M155" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N155" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G156" s="3">
+        <v>45908</v>
+      </c>
+      <c r="H156" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I155" s="6" t="s">
+      <c r="I156" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="J155" s="4" t="s">
+      <c r="J156" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K155" s="9">
+      <c r="K156" s="9">
         <v>175</v>
       </c>
-      <c r="L155" s="4" t="s">
+      <c r="L156" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="M155" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N155" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="156" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G156" s="3">
-        <v>45909</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="I156" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J156" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K156" s="9">
-        <v>200</v>
-      </c>
-      <c r="L156" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="M156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N156" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="K157" s="9">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="M157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N157" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="158" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="K158" s="9">
-        <v>200</v>
-      </c>
-      <c r="L158" s="1" t="s">
-        <v>9</v>
+        <v>240</v>
+      </c>
+      <c r="L158" s="24" t="s">
+        <v>180</v>
       </c>
       <c r="M158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N158" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="159" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>235</v>
+        <v>10</v>
       </c>
       <c r="K159" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="M159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N159" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="160" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J160" s="17" t="s">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="K160" s="9">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N160" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
       <c r="H161" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I161" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J161" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K161" s="9">
+        <v>175</v>
+      </c>
+      <c r="L161" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M161" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N161" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G162" s="3">
+        <v>45909</v>
+      </c>
+      <c r="H162" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="I161" s="6" t="s">
+      <c r="I162" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="J161" s="4" t="s">
+      <c r="J162" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="K161" s="9">
+      <c r="K162" s="9">
         <v>200</v>
       </c>
-      <c r="L161" s="4" t="s">
+      <c r="L162" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M161" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N161" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G162" s="3">
-        <v>45910</v>
-      </c>
-      <c r="H162" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="I162" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J162" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="K162" s="9">
-        <v>160</v>
-      </c>
-      <c r="L162" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="M162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N162" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="163" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J163" s="4"/>
-      <c r="K163" s="9"/>
-      <c r="L163" s="4"/>
+        <v>133</v>
+      </c>
+      <c r="J163" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K163" s="9">
+        <v>160</v>
+      </c>
+      <c r="L163" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="M163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N163" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K164" s="9">
-        <v>200</v>
-      </c>
-      <c r="L164" s="4" t="s">
-        <v>244</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="J164" s="24"/>
+      <c r="K164" s="9"/>
+      <c r="L164" s="4"/>
       <c r="M164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N164" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K165" s="9">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>8</v>
@@ -5469,15 +5475,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>47</v>
@@ -5495,24 +5501,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="K167" s="9">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="L167" s="4" t="s">
-        <v>22</v>
+        <v>219</v>
       </c>
       <c r="M167" s="4" t="s">
         <v>8</v>
@@ -5521,45 +5527,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
       <c r="H168" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I168" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J168" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K168" s="9">
+        <v>190</v>
+      </c>
+      <c r="L168" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M168" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N168" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G169" s="3">
+        <v>45910</v>
+      </c>
+      <c r="H169" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I168" s="6" t="s">
+      <c r="I169" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="J168" s="4" t="s">
+      <c r="J169" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K168" s="9">
+      <c r="K169" s="9">
         <v>198</v>
       </c>
-      <c r="L168" s="4" t="s">
+      <c r="L169" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M168" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N168" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="169" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G169" s="3">
-        <v>45911</v>
-      </c>
-      <c r="H169" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="I169" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J169" s="4"/>
-      <c r="K169" s="9"/>
-      <c r="L169" s="4"/>
       <c r="M169" s="4" t="s">
         <v>8</v>
       </c>
@@ -5567,25 +5579,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J170" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K170" s="9">
-        <v>170</v>
-      </c>
-      <c r="L170" s="4" t="s">
-        <v>32</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="J170" s="4"/>
+      <c r="K170" s="9"/>
+      <c r="L170" s="4"/>
       <c r="M170" s="4" t="s">
         <v>8</v>
       </c>
@@ -5593,24 +5599,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="K171" s="9">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M171" s="4" t="s">
         <v>8</v>
@@ -5619,24 +5625,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="K172" s="9">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="M172" s="4" t="s">
         <v>8</v>
@@ -5645,24 +5651,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="J173" s="15" t="s">
-        <v>66</v>
+        <v>130</v>
+      </c>
+      <c r="J173" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="K173" s="9">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="M173" s="4" t="s">
         <v>8</v>
@@ -5671,24 +5677,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J174" s="4" t="s">
-        <v>183</v>
+        <v>131</v>
+      </c>
+      <c r="J174" s="25" t="s">
+        <v>66</v>
       </c>
       <c r="K174" s="9">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>184</v>
+        <v>51</v>
       </c>
       <c r="M174" s="4" t="s">
         <v>8</v>
@@ -5697,24 +5703,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="K175" s="9">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>8</v>
@@ -5723,24 +5729,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="K176" s="9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="M176" s="4" t="s">
         <v>8</v>
@@ -5749,24 +5755,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J177" s="17" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K177" s="9">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="M177" s="4" t="s">
         <v>8</v>
@@ -5775,24 +5781,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>235</v>
+        <v>24</v>
       </c>
       <c r="K178" s="9">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M178" s="4" t="s">
         <v>8</v>
@@ -5801,24 +5807,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
       <c r="K179" s="9">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="M179" s="4" t="s">
         <v>8</v>
@@ -5827,50 +5833,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K180" s="9">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="M180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N180" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="K181" s="9">
-        <v>280</v>
+        <v>198</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M181" s="4" t="s">
         <v>8</v>
@@ -5879,9 +5885,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
-        <v>45915</v>
+        <v>45911</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>144</v>
@@ -5893,62 +5899,62 @@
         <v>25</v>
       </c>
       <c r="K182" s="9">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="M182" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N182" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="183" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>235</v>
+        <v>25</v>
       </c>
       <c r="K183" s="9">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>94</v>
+        <v>185</v>
       </c>
       <c r="M183" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N183" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="J184" s="17" t="s">
-        <v>24</v>
+        <v>235</v>
       </c>
       <c r="K184" s="9">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L184" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M184" s="4" t="s">
         <v>8</v>
@@ -5957,24 +5963,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K185" s="9">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="M185" s="4" t="s">
         <v>8</v>
@@ -5983,24 +5989,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K186" s="9">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>186</v>
+        <v>56</v>
       </c>
       <c r="M186" s="4" t="s">
         <v>8</v>
@@ -6009,24 +6015,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="K187" s="9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="M187" s="4" t="s">
         <v>8</v>
@@ -6035,102 +6041,102 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
       <c r="H188" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I188" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J188" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="K188" s="9">
+        <v>200</v>
+      </c>
+      <c r="L188" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M188" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N188" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G189" s="3">
+        <v>45915</v>
+      </c>
+      <c r="H189" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="I188" s="6" t="s">
+      <c r="I189" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J188" s="17" t="s">
+      <c r="J189" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K188" s="9">
+      <c r="K189" s="9">
         <v>259</v>
       </c>
-      <c r="L188" s="4" t="s">
+      <c r="L189" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="M188" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N188" s="6">
+      <c r="M189" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N189" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G189" s="3">
-        <v>45916</v>
-      </c>
-      <c r="H189" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I189" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J189" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K189" s="9">
-        <v>120</v>
-      </c>
-      <c r="L189" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M189" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N189" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="K190" s="9">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="M190" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N190" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="K191" s="9">
         <v>200</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="M191" s="4" t="s">
         <v>8</v>
@@ -6139,61 +6145,61 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="K192" s="9">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="M192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N192" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="193" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="K193" s="9">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="L193" s="4" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="M193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N193" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
-        <v>45917</v>
+        <v>45916</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>147</v>
@@ -6202,65 +6208,65 @@
         <v>133</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>187</v>
+        <v>10</v>
       </c>
       <c r="K194" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>166</v>
+        <v>9</v>
       </c>
       <c r="M194" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N194" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="195" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
       <c r="H195" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I195" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J195" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="K195" s="9">
         <v>150</v>
       </c>
-      <c r="I195" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J195" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K195" s="9">
-        <v>240</v>
-      </c>
       <c r="L195" s="4" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="M195" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N195" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="196" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
       <c r="K196" s="9">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="M196" s="4" t="s">
         <v>8</v>
@@ -6269,50 +6275,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
       <c r="H197" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>65</v>
+        <v>235</v>
       </c>
       <c r="K197" s="9">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="L197" s="4" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="M197" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N197" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="198" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="K198" s="9">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="M198" s="4" t="s">
         <v>8</v>
@@ -6321,24 +6327,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="K199" s="9">
         <v>230</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="M199" s="4" t="s">
         <v>8</v>
@@ -6347,24 +6353,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="K200" s="9">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="L200" s="4" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="M200" s="4" t="s">
         <v>8</v>
@@ -6373,50 +6379,50 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="K201" s="9">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="M201" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N201" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="202" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="K202" s="9">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="M202" s="4" t="s">
         <v>8</v>
@@ -6425,24 +6431,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="K203" s="9">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="L203" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M203" s="4" t="s">
         <v>8</v>
@@ -6451,24 +6457,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="K204" s="9">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="M204" s="4" t="s">
         <v>8</v>
@@ -6477,24 +6483,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="K205" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>44</v>
+        <v>173</v>
       </c>
       <c r="M205" s="4" t="s">
         <v>8</v>
@@ -6503,24 +6509,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="K206" s="9">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="M206" s="4" t="s">
         <v>8</v>
@@ -6529,24 +6535,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J207" s="17" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K207" s="9">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="M207" s="4" t="s">
         <v>8</v>
@@ -6555,24 +6561,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="K208" s="9">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="M208" s="4" t="s">
         <v>8</v>
@@ -6581,24 +6587,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I209" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="K209" s="9">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="M209" s="4" t="s">
         <v>8</v>
@@ -6607,24 +6613,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="I210" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="K210" s="9">
-        <v>260</v>
+        <v>175</v>
       </c>
       <c r="L210" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M210" s="4" t="s">
         <v>8</v>
@@ -6633,19 +6639,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I211" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J211" s="4"/>
-      <c r="K211" s="9"/>
-      <c r="L211" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="J211" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K211" s="9">
+        <v>260</v>
+      </c>
+      <c r="L211" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="M211" s="4" t="s">
         <v>8</v>
       </c>
@@ -6653,25 +6665,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J212" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K212" s="9">
-        <v>185</v>
-      </c>
-      <c r="L212" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="J212" s="4"/>
+      <c r="K212" s="9"/>
+      <c r="L212" s="4"/>
       <c r="M212" s="4" t="s">
         <v>8</v>
       </c>
@@ -6679,76 +6685,76 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
       <c r="H213" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I213" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J213" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K213" s="9">
+        <v>185</v>
+      </c>
+      <c r="L213" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M213" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N213" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G214" s="3">
+        <v>45918</v>
+      </c>
+      <c r="H214" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="I213" s="6" t="s">
+      <c r="I214" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J213" s="17" t="s">
+      <c r="J214" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="K213" s="9">
+      <c r="K214" s="9">
         <v>240</v>
       </c>
-      <c r="L213" s="4" t="s">
+      <c r="L214" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="M213" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N213" s="6">
+      <c r="M214" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N214" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G214" s="3">
-        <v>45922</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="I214" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="J214" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="K214" s="9">
-        <v>170</v>
-      </c>
-      <c r="L214" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="M214" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N214" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="215" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="J215" s="17" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="K215" s="9">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="M215" s="4" t="s">
         <v>8</v>
@@ -6757,24 +6763,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="K216" s="9">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="L216" s="4" t="s">
-        <v>244</v>
+        <v>90</v>
       </c>
       <c r="M216" s="4" t="s">
         <v>8</v>
@@ -6783,24 +6789,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>235</v>
+        <v>46</v>
       </c>
       <c r="K217" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="M217" s="4" t="s">
         <v>8</v>
@@ -6809,24 +6815,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="K218" s="9">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="M218" s="4" t="s">
         <v>8</v>
@@ -6835,102 +6841,102 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K219" s="9">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>56</v>
+        <v>229</v>
       </c>
       <c r="M219" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N219" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="220" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
       <c r="H220" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I220" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J220" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K220" s="9">
+        <v>175</v>
+      </c>
+      <c r="L220" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M220" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N220" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G221" s="3">
+        <v>45922</v>
+      </c>
+      <c r="H221" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="I220" s="6" t="s">
+      <c r="I221" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J220" s="4" t="s">
+      <c r="J221" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K220" s="9">
+      <c r="K221" s="9">
         <v>275</v>
       </c>
-      <c r="L220" s="4" t="s">
+      <c r="L221" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M220" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N220" s="6">
+      <c r="M221" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N221" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G221" s="3">
-        <v>45923</v>
-      </c>
-      <c r="H221" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I221" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J221" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K221" s="9">
-        <v>200</v>
-      </c>
-      <c r="L221" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="M221" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N221" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="222" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I222" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="K222" s="9">
         <v>200</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="M222" s="4" t="s">
         <v>8</v>
@@ -6939,24 +6945,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="K223" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="M223" s="4" t="s">
         <v>8</v>
@@ -6965,24 +6971,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="K224" s="9">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>55</v>
+        <v>186</v>
       </c>
       <c r="M224" s="4" t="s">
         <v>8</v>
@@ -6991,102 +6997,102 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J225" s="17" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="K225" s="9">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="L225" s="4" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="M225" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N225" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
       <c r="H226" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I226" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J226" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K226" s="9">
+        <v>160</v>
+      </c>
+      <c r="L226" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M226" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N226" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G227" s="3">
+        <v>45923</v>
+      </c>
+      <c r="H227" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="I226" s="6" t="s">
+      <c r="I227" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J226" s="4" t="s">
+      <c r="J227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K226" s="9">
+      <c r="K227" s="9">
         <v>120</v>
       </c>
-      <c r="L226" s="4" t="s">
+      <c r="L227" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M226" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N226" s="18">
+      <c r="M227" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N227" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G227" s="3">
-        <v>45924</v>
-      </c>
-      <c r="H227" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="I227" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J227" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K227" s="9">
-        <v>110</v>
-      </c>
-      <c r="L227" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="M227" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N227" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="228" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="K228" s="9">
-        <v>205</v>
+        <v>110</v>
       </c>
       <c r="L228" s="4" t="s">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="M228" s="4" t="s">
         <v>8</v>
@@ -7095,24 +7101,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="K229" s="9">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="M229" s="4" t="s">
         <v>8</v>
@@ -7121,24 +7127,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K230" s="9">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="L230" s="4" t="s">
-        <v>49</v>
+        <v>244</v>
       </c>
       <c r="M230" s="4" t="s">
         <v>8</v>
@@ -7147,24 +7153,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="K231" s="9">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="L231" s="4" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M231" s="4" t="s">
         <v>8</v>
@@ -7173,128 +7179,128 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="K232" s="9">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="L232" s="4" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="M232" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N232" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="233" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="K233" s="9">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="L233" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="M233" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N233" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="K234" s="9">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="M234" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N234" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
-        <v>45925</v>
+        <v>45924</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="K235" s="9">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="M235" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N235" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="236" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="K236" s="9">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="L236" s="4" t="s">
-        <v>30</v>
+        <v>229</v>
       </c>
       <c r="M236" s="4" t="s">
         <v>8</v>
@@ -7303,24 +7309,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="J237" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K237" s="9">
         <v>198</v>
       </c>
-      <c r="K237" s="9">
-        <v>180</v>
-      </c>
       <c r="L237" s="4" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="M237" s="4" t="s">
         <v>8</v>
@@ -7329,24 +7335,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I238" s="6" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="K238" s="9">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="M238" s="4" t="s">
         <v>8</v>
@@ -7355,24 +7361,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K239" s="9">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M239" s="4" t="s">
         <v>8</v>
@@ -7381,24 +7387,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="I240" s="6" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="J240" s="17" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K240" s="9">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L240" s="4" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="M240" s="4" t="s">
         <v>8</v>
@@ -7407,24 +7413,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="K241" s="9">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="L241" s="4" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="M241" s="4" t="s">
         <v>8</v>
@@ -7433,24 +7439,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="K242" s="9">
         <v>200</v>
       </c>
       <c r="L242" s="4" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="M242" s="4" t="s">
         <v>8</v>
@@ -7459,24 +7465,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="K243" s="9">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>55</v>
+        <v>201</v>
       </c>
       <c r="M243" s="4" t="s">
         <v>8</v>
@@ -7485,51 +7491,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
       <c r="H244" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I244" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J244" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K244" s="9">
+        <v>280</v>
+      </c>
+      <c r="L244" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M244" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N244" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G245" s="3">
+        <v>45925</v>
+      </c>
+      <c r="H245" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I244" s="6" t="s">
+      <c r="I245" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="J244" s="4" t="s">
+      <c r="J245" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K244" s="9">
+      <c r="K245" s="9">
         <v>200</v>
       </c>
-      <c r="L244" s="4" t="s">
+      <c r="L245" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="M244" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N244" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="245" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G245" s="3">
-        <v>45929</v>
-      </c>
-      <c r="H245" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="I245" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="J245" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K245" s="9">
-        <v>220</v>
-      </c>
-      <c r="L245" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="M245" s="4" t="s">
         <v>8</v>
       </c>
@@ -7537,7 +7543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7563,24 +7569,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="I247" s="6" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="J247" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K247" s="9">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L247" s="4" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="M247" s="4" t="s">
         <v>8</v>
@@ -7589,24 +7595,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I248" s="6" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="K248" s="9">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="L248" s="4" t="s">
-        <v>244</v>
+        <v>90</v>
       </c>
       <c r="M248" s="4" t="s">
         <v>8</v>
@@ -7615,24 +7621,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>235</v>
+        <v>46</v>
       </c>
       <c r="K249" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="M249" s="4" t="s">
         <v>8</v>
@@ -7641,47 +7647,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I250" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="K250" s="9">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="L250" s="4" t="s">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="M250" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N250" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="251" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K251" s="9">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="L251" s="4" t="s">
         <v>229</v>
@@ -7690,54 +7696,54 @@
         <v>8</v>
       </c>
       <c r="N251" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="252" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
       <c r="H252" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="I252" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="J252" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K252" s="9">
+        <v>265</v>
+      </c>
+      <c r="L252" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="M252" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N252" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G253" s="3">
+        <v>45929</v>
+      </c>
+      <c r="H253" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I252" s="6" t="s">
+      <c r="I253" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J252" s="4" t="s">
+      <c r="J253" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K252" s="9">
+      <c r="K253" s="9">
         <v>175</v>
       </c>
-      <c r="L252" s="4" t="s">
+      <c r="L253" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="M252" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N252" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="253" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G253" s="3">
-        <v>45930</v>
-      </c>
-      <c r="H253" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I253" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J253" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K253" s="9">
-        <v>200</v>
-      </c>
-      <c r="L253" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="M253" s="4" t="s">
         <v>8</v>
       </c>
@@ -7745,76 +7751,76 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="K254" s="9">
         <v>200</v>
       </c>
       <c r="L254" s="4" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="M254" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N254" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="255" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I255" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="K255" s="9">
         <v>200</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M255" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N255" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="256" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="I256" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="K256" s="9">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="L256" s="4" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="M256" s="4" t="s">
         <v>8</v>
@@ -7823,77 +7829,77 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I257" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J257" s="17" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="K257" s="9">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="L257" s="4" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="M257" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N257" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="258" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
       <c r="H258" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I258" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J258" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K258" s="9">
+        <v>160</v>
+      </c>
+      <c r="L258" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M258" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N258" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G259" s="3">
+        <v>45930</v>
+      </c>
+      <c r="H259" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="I258" s="6" t="s">
+      <c r="I259" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J258" s="4" t="s">
+      <c r="J259" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K258" s="9">
+      <c r="K259" s="9">
         <v>200</v>
       </c>
-      <c r="L258" s="4" t="s">
+      <c r="L259" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M258" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N258" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="259" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G259" s="3">
-        <v>45931</v>
-      </c>
-      <c r="H259" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="I259" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="J259" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="K259" s="9">
-        <v>240</v>
-      </c>
-      <c r="L259" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="M259" s="4" t="s">
         <v>8</v>
       </c>
@@ -7901,24 +7907,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="K260" s="9">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="L260" s="4" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="M260" s="4" t="s">
         <v>8</v>
@@ -7927,24 +7933,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I261" s="6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="K261" s="9">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="M261" s="4" t="s">
         <v>8</v>
@@ -7953,24 +7959,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I262" s="6" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J262" s="17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K262" s="9">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="L262" s="4" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="M262" s="4" t="s">
         <v>8</v>
@@ -7979,50 +7985,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I263" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="K263" s="9">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="L263" s="4" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="M263" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N263" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="264" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="K264" s="9">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="L264" s="4" t="s">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="M264" s="4" t="s">
         <v>8</v>
@@ -8031,24 +8037,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="I265" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="K265" s="9">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="M265" s="4" t="s">
         <v>8</v>
@@ -8057,24 +8063,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="K266" s="9">
         <v>190</v>
       </c>
       <c r="L266" s="4" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="M266" s="4" t="s">
         <v>8</v>
@@ -8083,50 +8089,50 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
-        <v>45932</v>
+        <v>45931</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="K267" s="9">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="L267" s="4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M267" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N267" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="268" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="K268" s="9">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M268" s="4" t="s">
         <v>8</v>
@@ -8135,24 +8141,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="I269" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="K269" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="M269" s="4" t="s">
         <v>8</v>
@@ -8161,24 +8167,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I270" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J270" s="15" t="s">
-        <v>66</v>
+        <v>130</v>
+      </c>
+      <c r="J270" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="K270" s="9">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M270" s="4" t="s">
         <v>8</v>
@@ -8187,24 +8193,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
       <c r="H271" s="4" t="s">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="I271" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="J271" s="17" t="s">
-        <v>24</v>
+        <v>136</v>
+      </c>
+      <c r="J271" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="K271" s="9">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="L271" s="4" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="M271" s="4" t="s">
         <v>8</v>
@@ -8213,24 +8219,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I272" s="6" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="K272" s="9">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>211</v>
+        <v>90</v>
       </c>
       <c r="M272" s="4" t="s">
         <v>8</v>
@@ -8239,24 +8245,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
       <c r="H273" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K273" s="9">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M273" s="4" t="s">
         <v>8</v>
@@ -8266,24 +8272,24 @@
       </c>
       <c r="O273" s="19"/>
     </row>
-    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="K274" s="9">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="M274" s="4" t="s">
         <v>8</v>
@@ -8292,24 +8298,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J275" s="1" t="s">
-        <v>61</v>
+        <v>137</v>
+      </c>
+      <c r="J275" s="24" t="s">
+        <v>183</v>
       </c>
       <c r="K275" s="9">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="M275" s="4" t="s">
         <v>8</v>
@@ -8318,24 +8324,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="K276" s="9">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="L276" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M276" s="4" t="s">
         <v>8</v>
@@ -8344,50 +8350,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
       <c r="H277" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I277" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J277" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K277" s="9">
+        <v>175</v>
+      </c>
+      <c r="L277" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M277" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N277" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G278" s="3">
+        <v>45932</v>
+      </c>
+      <c r="H278" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="I277" s="6" t="s">
+      <c r="I278" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J277" s="4" t="s">
+      <c r="J278" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K277" s="9">
+      <c r="K278" s="9">
         <v>250</v>
       </c>
-      <c r="L277" s="4" t="s">
+      <c r="L278" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="M277" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N277" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G278" s="3">
-        <v>45903</v>
-      </c>
-      <c r="H278" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="I278" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J278" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="K278" s="9">
-        <v>240</v>
-      </c>
-      <c r="L278" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="M278" s="4" t="s">
         <v>8</v>
@@ -8396,7 +8402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8422,7 +8428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8448,7 +8454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8474,7 +8480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8500,7 +8506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8526,7 +8532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8552,7 +8558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8578,7 +8584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8604,7 +8610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8630,7 +8636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8656,7 +8662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8682,7 +8688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8708,7 +8714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8734,7 +8740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8760,7 +8766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8786,7 +8792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8812,7 +8818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8838,7 +8844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8864,7 +8870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -8890,7 +8896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -8916,7 +8922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -8942,7 +8948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -8968,7 +8974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -8994,24 +9000,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
-        <v>45943</v>
+        <v>45939</v>
       </c>
       <c r="H302" s="4" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="K302" s="9">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="L302" s="4" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="M302" s="4" t="s">
         <v>8</v>
@@ -9020,174 +9026,206 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
-        <v>45943</v>
+        <v>45939</v>
       </c>
       <c r="H303" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J303" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K303" s="9">
+        <v>180</v>
+      </c>
+      <c r="L303" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M303" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N303" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G304" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H304" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I303" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="J303" s="4" t="s">
+      <c r="I304" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J304" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K304" s="9">
+        <v>198</v>
+      </c>
+      <c r="L304" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M304" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N304" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G305" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H305" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J305" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K305" s="9">
+        <v>180</v>
+      </c>
+      <c r="L305" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="M305" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N305" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G306" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H306" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I306" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J306" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K306" s="9">
+        <v>150</v>
+      </c>
+      <c r="L306" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M306" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N306" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G307" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J307" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="K307" s="9">
+        <v>140</v>
+      </c>
+      <c r="L307" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M307" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N307" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G308" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="I308" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J308" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K303" s="9">
-        <v>259</v>
-      </c>
-      <c r="L303" s="4" t="s">
+      <c r="K308" s="9">
+        <v>140</v>
+      </c>
+      <c r="L308" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="M303" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N303" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="304" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G304" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H304" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="I304" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J304" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K304" s="9">
+      <c r="M308" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N308" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G309" s="3">
+        <v>45939</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I309" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="J309" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K309" s="9">
         <v>200</v>
       </c>
-      <c r="L304" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="M304" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N304" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="305" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G305" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H305" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I305" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="J305" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="K305" s="9">
-        <v>220</v>
-      </c>
-      <c r="L305" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M305" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N305" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="306" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G306" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H306" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I306" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J306" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K306" s="9">
-        <v>180</v>
-      </c>
-      <c r="L306" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M306" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N306" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="307" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G307" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H307" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="I307" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="J307" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="K307" s="9">
-        <v>220</v>
-      </c>
-      <c r="L307" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="M307" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N307" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="308" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G308" s="4"/>
-      <c r="H308" s="4"/>
-      <c r="I308" s="6"/>
-      <c r="J308" s="4"/>
-      <c r="K308" s="9"/>
-      <c r="L308" s="4"/>
-      <c r="M308" s="4"/>
-      <c r="N308" s="6"/>
-    </row>
-    <row r="309" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G309" s="4"/>
-      <c r="H309" s="4"/>
-      <c r="I309" s="6"/>
-      <c r="J309" s="4"/>
-      <c r="K309" s="9"/>
-      <c r="L309" s="4"/>
-      <c r="M309" s="4"/>
-      <c r="N309" s="6"/>
-    </row>
-    <row r="310" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L309" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M309" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N309" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
       <c r="H310" s="4" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="J310" s="17" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="K310" s="9">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="L310" s="4" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="M310" s="4" t="s">
         <v>8</v>
@@ -9196,24 +9234,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
       <c r="H311" s="4" t="s">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>133</v>
+        <v>226</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="K311" s="9">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="M311" s="4" t="s">
         <v>8</v>
@@ -9222,24 +9260,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
       <c r="H312" s="4" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K312" s="9">
-        <v>198</v>
+        <v>280</v>
       </c>
       <c r="L312" s="4" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="M312" s="4" t="s">
         <v>8</v>
@@ -9248,24 +9286,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
       <c r="H313" s="4" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="I313" s="6" t="s">
-        <v>129</v>
+        <v>214</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K313" s="9">
         <v>180</v>
       </c>
       <c r="L313" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="M313" s="4" t="s">
         <v>8</v>
@@ -9274,24 +9312,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
       <c r="H314" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I314" s="6" t="s">
-        <v>130</v>
+        <v>228</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K314" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L314" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M314" s="4" t="s">
         <v>8</v>
@@ -9300,35 +9338,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
       <c r="H315" s="4" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I315" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J315" s="15" t="s">
-        <v>66</v>
+        <v>134</v>
+      </c>
+      <c r="J315" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="K315" s="9">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="L315" s="4" t="s">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="M315" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N315" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="316" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H316" s="4" t="s">
         <v>212</v>
@@ -9337,66 +9375,66 @@
         <v>194</v>
       </c>
       <c r="J316" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="K316" s="9">
+        <v>220</v>
+      </c>
+      <c r="L316" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="M316" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N316" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G317" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I317" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="J317" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K317" s="9">
+        <v>220</v>
+      </c>
+      <c r="L317" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M317" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N317" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G318" s="3">
+        <v>45943</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I318" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="J318" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K316" s="9">
-        <v>140</v>
-      </c>
-      <c r="L316" s="4" t="s">
+      <c r="K318" s="9">
+        <v>259</v>
+      </c>
+      <c r="L318" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="M316" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N316" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="317" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G317" s="3">
-        <v>45939</v>
-      </c>
-      <c r="H317" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I317" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="J317" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K317" s="9">
-        <v>200</v>
-      </c>
-      <c r="L317" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="M317" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N317" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="318" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G318" s="3">
-        <v>45939</v>
-      </c>
-      <c r="H318" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="I318" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="J318" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="K318" s="9">
-        <v>220</v>
-      </c>
-      <c r="L318" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="M318" s="4" t="s">
         <v>8</v>
       </c>
@@ -9404,24 +9442,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="H319" s="4" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="I319" s="6" t="s">
-        <v>226</v>
+        <v>129</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="K319" s="9">
         <v>200</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>167</v>
+        <v>244</v>
       </c>
       <c r="M319" s="4" t="s">
         <v>8</v>
@@ -9430,24 +9468,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="H320" s="4" t="s">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="I320" s="6" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
       <c r="K320" s="9">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="L320" s="4" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="M320" s="4" t="s">
         <v>8</v>
@@ -9456,50 +9494,50 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="H321" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I321" s="6" t="s">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>236</v>
+        <v>25</v>
       </c>
       <c r="K321" s="9">
         <v>180</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="M321" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N321" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="322" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="H322" s="4" t="s">
         <v>156</v>
       </c>
       <c r="I322" s="6" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K322" s="9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="L322" s="4" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="M322" s="4" t="s">
         <v>8</v>
@@ -9508,102 +9546,102 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
-        <v>45939</v>
+        <v>45944</v>
       </c>
       <c r="H323" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>235</v>
+        <v>11</v>
       </c>
       <c r="K323" s="9">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>39</v>
+        <v>240</v>
       </c>
       <c r="M323" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N323" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="324" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="H324" s="4" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="I324" s="6" t="s">
         <v>194</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>238</v>
+        <v>41</v>
       </c>
       <c r="K324" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L324" s="4" t="s">
-        <v>239</v>
+        <v>120</v>
       </c>
       <c r="M324" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N324" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="325" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
       <c r="H325" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I325" s="6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>11</v>
+        <v>241</v>
       </c>
       <c r="K325" s="9">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="L325" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M325" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N325" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="326" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
       <c r="H326" s="4" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="I326" s="6" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="K326" s="9">
         <v>200</v>
       </c>
       <c r="L326" s="4" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="M326" s="4" t="s">
         <v>8</v>
@@ -9612,134 +9650,134 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
       <c r="H327" s="4" t="s">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>241</v>
+        <v>61</v>
       </c>
       <c r="K327" s="9">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="L327" s="4" t="s">
-        <v>242</v>
+        <v>55</v>
       </c>
       <c r="M327" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N327" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="328" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
       <c r="H328" s="4" t="s">
-        <v>223</v>
+        <v>147</v>
       </c>
       <c r="I328" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="K328" s="9">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L328" s="4" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="M328" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N328" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="329" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G329" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="329" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G329" s="20">
         <v>45944</v>
       </c>
-      <c r="H329" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="I329" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J329" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K329" s="9">
-        <v>280</v>
-      </c>
-      <c r="L329" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M329" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N329" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="330" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H329" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="I329" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J329" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="K329" s="23">
+        <v>180</v>
+      </c>
+      <c r="L329" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="M329" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="N329" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="H330" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I330" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J330" s="17" t="s">
-        <v>14</v>
+        <v>235</v>
       </c>
       <c r="K330" s="9">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L330" s="4" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="M330" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N330" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G331" s="3">
+        <v>45945</v>
+      </c>
+      <c r="H331" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I331" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J331" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K331" s="9">
+        <v>230</v>
+      </c>
+      <c r="L331" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="M331" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N331" s="6">
         <v>3</v>
-      </c>
-    </row>
-    <row r="331" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G331" s="20">
-        <v>45944</v>
-      </c>
-      <c r="H331" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="I331" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="J331" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="K331" s="23">
-        <v>180</v>
-      </c>
-      <c r="L331" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="M331" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="N331" s="22">
-        <v>1</v>
       </c>
     </row>
     <row r="332" spans="7:14" x14ac:dyDescent="0.25">
@@ -9747,25 +9785,25 @@
         <v>45945</v>
       </c>
       <c r="H332" s="4" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="I332" s="6" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>235</v>
+        <v>46</v>
       </c>
       <c r="K332" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L332" s="4" t="s">
-        <v>39</v>
+        <v>244</v>
       </c>
       <c r="M332" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N332" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="7:14" x14ac:dyDescent="0.25">
@@ -9773,10 +9811,10 @@
         <v>45945</v>
       </c>
       <c r="H333" s="4" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="I333" s="6" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="J333" s="4" t="s">
         <v>47</v>
@@ -9799,19 +9837,19 @@
         <v>45945</v>
       </c>
       <c r="H334" s="4" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="I334" s="6" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="K334" s="9">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="L334" s="4" t="s">
-        <v>244</v>
+        <v>22</v>
       </c>
       <c r="M334" s="4" t="s">
         <v>8</v>
@@ -9825,17 +9863,25 @@
         <v>45945</v>
       </c>
       <c r="H335" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I335" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J335" s="4"/>
-      <c r="K335" s="9"/>
-      <c r="L335" s="4"/>
-      <c r="M335" s="4"/>
+        <v>133</v>
+      </c>
+      <c r="J335" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K335" s="9">
+        <v>160</v>
+      </c>
+      <c r="L335" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M335" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N335" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="7:14" x14ac:dyDescent="0.25">
@@ -9843,79 +9889,55 @@
         <v>45945</v>
       </c>
       <c r="H336" s="4" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="I336" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J336" s="4"/>
-      <c r="K336" s="9"/>
-      <c r="L336" s="4"/>
-      <c r="M336" s="4"/>
+        <v>132</v>
+      </c>
+      <c r="J336" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K336" s="9">
+        <v>218.9</v>
+      </c>
+      <c r="L336" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="M336" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N336" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="337" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G337" s="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G337" s="4"/>
       <c r="H337" s="4"/>
       <c r="I337" s="6"/>
       <c r="J337" s="4"/>
       <c r="K337" s="9"/>
       <c r="L337" s="4"/>
       <c r="M337" s="4"/>
-      <c r="N337" s="6">
-        <v>2</v>
-      </c>
+      <c r="N337" s="6"/>
     </row>
     <row r="338" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G338" s="3">
-        <v>45945</v>
-      </c>
-      <c r="H338" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="I338" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J338" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="K338" s="9">
-        <v>160</v>
-      </c>
-      <c r="L338" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="M338" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N338" s="6">
-        <v>2</v>
-      </c>
+      <c r="G338" s="4"/>
+      <c r="H338" s="4"/>
+      <c r="I338" s="6"/>
+      <c r="J338" s="17"/>
+      <c r="K338" s="9"/>
+      <c r="L338" s="4"/>
+      <c r="M338" s="4"/>
+      <c r="N338" s="6"/>
     </row>
     <row r="339" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G339" s="3">
-        <v>45945</v>
-      </c>
-      <c r="H339" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="I339" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J339" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K339" s="9">
-        <v>218.9</v>
-      </c>
-      <c r="L339" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="M339" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="G339" s="3"/>
+      <c r="H339" s="4"/>
+      <c r="I339" s="6"/>
+      <c r="J339" s="4"/>
+      <c r="K339" s="9"/>
+      <c r="L339" s="4"/>
+      <c r="M339" s="4"/>
       <c r="N339" s="6">
         <v>2</v>
       </c>
@@ -9951,13 +9973,10 @@
       <c r="N342" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N339" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" month="10" day="15" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="G5:N339" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
+    <sortCondition ref="G6:G339"/>
+  </sortState>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1872" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5397E018-A14D-4149-ACB6-22BB0DB23259}"/>
+  <xr:revisionPtr revIDLastSave="1916" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1881563-2C13-41C2-929F-4DF6F0932D55}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$342</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="249">
   <si>
     <t>DATA</t>
   </si>
@@ -782,6 +782,9 @@
   </si>
   <si>
     <t xml:space="preserve">HOTEL COSTA E FILHO </t>
+  </si>
+  <si>
+    <t>DOUGLAS RODRIGUES</t>
   </si>
 </sst>
 </file>
@@ -880,7 +883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -941,9 +944,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1284,10 +1284,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1">
+  <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O342"/>
+  <dimension ref="G5:O356"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1327,7 +1327,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45903</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45904</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45908</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5289,7 +5289,7 @@
       <c r="K158" s="9">
         <v>240</v>
       </c>
-      <c r="L158" s="24" t="s">
+      <c r="L158" s="1" t="s">
         <v>180</v>
       </c>
       <c r="M158" s="4" t="s">
@@ -5299,7 +5299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45909</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5439,7 +5439,6 @@
       <c r="I164" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J164" s="24"/>
       <c r="K164" s="9"/>
       <c r="L164" s="4"/>
       <c r="M164" s="4" t="s">
@@ -5449,7 +5448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5475,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5501,7 +5500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5527,7 +5526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5553,7 +5552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45910</v>
       </c>
@@ -5579,7 +5578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5599,7 +5598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5625,7 +5624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5651,7 +5650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5677,7 +5676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5687,7 +5686,7 @@
       <c r="I174" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J174" s="25" t="s">
+      <c r="J174" s="24" t="s">
         <v>66</v>
       </c>
       <c r="K174" s="9">
@@ -5703,7 +5702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5729,7 +5728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5755,7 +5754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5781,7 +5780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5807,7 +5806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5833,7 +5832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5859,7 +5858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5885,7 +5884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45911</v>
       </c>
@@ -5911,7 +5910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -5937,7 +5936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -5963,7 +5962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -5989,7 +5988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -6015,7 +6014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6041,7 +6040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6067,7 +6066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45915</v>
       </c>
@@ -6093,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6119,7 +6118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6145,7 +6144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6171,7 +6170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6197,7 +6196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45916</v>
       </c>
@@ -6223,7 +6222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6249,7 +6248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6275,7 +6274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6301,7 +6300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6327,7 +6326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6353,7 +6352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6379,7 +6378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45917</v>
       </c>
@@ -6405,7 +6404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6431,7 +6430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6457,7 +6456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6483,7 +6482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6509,7 +6508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6535,7 +6534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6561,7 +6560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6587,7 +6586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6613,7 +6612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6639,7 +6638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6665,7 +6664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6685,7 +6684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6711,7 +6710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45918</v>
       </c>
@@ -6737,7 +6736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6763,7 +6762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6789,7 +6788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6815,7 +6814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6841,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6867,7 +6866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6893,7 +6892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45922</v>
       </c>
@@ -6919,7 +6918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -6945,7 +6944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -6971,7 +6970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -6997,7 +6996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -7023,7 +7022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7049,7 +7048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45923</v>
       </c>
@@ -7075,7 +7074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7101,7 +7100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7127,7 +7126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7153,7 +7152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7179,7 +7178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7205,7 +7204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7231,7 +7230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7257,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45924</v>
       </c>
@@ -7283,7 +7282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7309,7 +7308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7335,7 +7334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7361,7 +7360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7387,7 +7386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7413,7 +7412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7439,7 +7438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7465,7 +7464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7491,7 +7490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7517,7 +7516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45925</v>
       </c>
@@ -7543,7 +7542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7569,7 +7568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7595,7 +7594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7621,7 +7620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7647,7 +7646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7673,7 +7672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7699,7 +7698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7725,7 +7724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45929</v>
       </c>
@@ -7751,7 +7750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7777,7 +7776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7803,7 +7802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7829,7 +7828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7855,7 +7854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7881,7 +7880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45930</v>
       </c>
@@ -7907,7 +7906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -7933,7 +7932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -7959,7 +7958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -7985,7 +7984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8011,7 +8010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8037,7 +8036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8063,7 +8062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8089,7 +8088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
@@ -8115,7 +8114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8141,7 +8140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8167,7 +8166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8193,7 +8192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8219,7 +8218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8245,7 +8244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8272,7 +8271,7 @@
       </c>
       <c r="O273" s="19"/>
     </row>
-    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8298,7 +8297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8308,7 +8307,7 @@
       <c r="I275" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="J275" s="24" t="s">
+      <c r="J275" s="1" t="s">
         <v>183</v>
       </c>
       <c r="K275" s="9">
@@ -8324,7 +8323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8350,7 +8349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8376,7 +8375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
@@ -8402,7 +8401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8428,7 +8427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8454,7 +8453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8480,7 +8479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8506,7 +8505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8532,7 +8531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8558,7 +8557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8584,7 +8583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8610,7 +8609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8636,7 +8635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8662,7 +8661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8688,7 +8687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8714,7 +8713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8740,7 +8739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8766,7 +8765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8792,7 +8791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8818,7 +8817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8844,7 +8843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8870,7 +8869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -8896,7 +8895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -8922,7 +8921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -8948,7 +8947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -8974,7 +8973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9000,7 +8999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
@@ -9026,7 +9025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
@@ -9052,7 +9051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
@@ -9078,7 +9077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
@@ -9104,7 +9103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
@@ -9130,7 +9129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
@@ -9140,7 +9139,7 @@
       <c r="I307" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J307" s="25" t="s">
+      <c r="J307" s="24" t="s">
         <v>66</v>
       </c>
       <c r="K307" s="9">
@@ -9156,7 +9155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
@@ -9182,7 +9181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
@@ -9208,7 +9207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9234,7 +9233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9260,7 +9259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9286,7 +9285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9312,7 +9311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9338,7 +9337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9364,7 +9363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45940</v>
       </c>
@@ -9390,7 +9389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
@@ -9416,7 +9415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
@@ -9442,7 +9441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
@@ -9468,7 +9467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
@@ -9494,7 +9493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
@@ -9520,7 +9519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45943</v>
       </c>
@@ -9546,7 +9545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
@@ -9572,7 +9571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
@@ -9598,7 +9597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
@@ -9624,7 +9623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
@@ -9650,7 +9649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
@@ -9676,7 +9675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
@@ -9702,7 +9701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G329" s="20">
         <v>45944</v>
       </c>
@@ -9728,7 +9727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
@@ -9754,7 +9753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
@@ -9780,7 +9779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
@@ -9806,7 +9805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
@@ -9832,7 +9831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
@@ -9858,7 +9857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
@@ -9884,7 +9883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
@@ -9911,69 +9910,329 @@
       </c>
     </row>
     <row r="337" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G337" s="4"/>
-      <c r="H337" s="4"/>
-      <c r="I337" s="6"/>
-      <c r="J337" s="4"/>
-      <c r="K337" s="9"/>
-      <c r="L337" s="4"/>
-      <c r="M337" s="4"/>
-      <c r="N337" s="6"/>
+      <c r="G337" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H337" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I337" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J337" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K337" s="9">
+        <v>198</v>
+      </c>
+      <c r="L337" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M337" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N337" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="338" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G338" s="4"/>
-      <c r="H338" s="4"/>
-      <c r="I338" s="6"/>
+      <c r="G338" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H338" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="I338" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="J338" s="17"/>
       <c r="K338" s="9"/>
       <c r="L338" s="4"/>
-      <c r="M338" s="4"/>
-      <c r="N338" s="6"/>
+      <c r="M338" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N338" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="339" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G339" s="3"/>
-      <c r="H339" s="4"/>
-      <c r="I339" s="6"/>
+      <c r="G339" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H339" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I339" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="J339" s="4"/>
       <c r="K339" s="9"/>
       <c r="L339" s="4"/>
-      <c r="M339" s="4"/>
+      <c r="M339" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N339" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="340" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G340" s="4"/>
-      <c r="H340" s="4"/>
-      <c r="I340" s="6"/>
+      <c r="G340" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H340" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I340" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="J340" s="4"/>
       <c r="K340" s="9"/>
       <c r="L340" s="4"/>
-      <c r="M340" s="4"/>
-      <c r="N340" s="6"/>
+      <c r="M340" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N340" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="341" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G341" s="4"/>
-      <c r="H341" s="4"/>
-      <c r="I341" s="6"/>
+      <c r="G341" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H341" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="I341" s="6" t="s">
+        <v>194</v>
+      </c>
       <c r="J341" s="4"/>
       <c r="K341" s="9"/>
       <c r="L341" s="4"/>
-      <c r="M341" s="4"/>
-      <c r="N341" s="6"/>
+      <c r="M341" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N341" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="342" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G342" s="4"/>
-      <c r="H342" s="4"/>
-      <c r="I342" s="6"/>
+      <c r="G342" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H342" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I342" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="J342" s="4"/>
       <c r="K342" s="9"/>
       <c r="L342" s="4"/>
-      <c r="M342" s="4"/>
-      <c r="N342" s="6"/>
+      <c r="M342" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N342" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="343" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G343" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H343" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I343" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="J343" s="4"/>
+      <c r="K343" s="9"/>
+      <c r="L343" s="4"/>
+      <c r="M343" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N343" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="344" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G344" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H344" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I344" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J344" s="4"/>
+      <c r="K344" s="9"/>
+      <c r="L344" s="4"/>
+      <c r="M344" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N344" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="345" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G345" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H345" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="I345" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J345" s="4"/>
+      <c r="K345" s="9"/>
+      <c r="L345" s="4"/>
+      <c r="M345" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N345" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="346" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G346" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H346" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I346" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="J346" s="4"/>
+      <c r="K346" s="9"/>
+      <c r="L346" s="4"/>
+      <c r="M346" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N346" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="347" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G347" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H347" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I347" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J347" s="4"/>
+      <c r="K347" s="9"/>
+      <c r="L347" s="4"/>
+      <c r="M347" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N347" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="348" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G348" s="4"/>
+      <c r="H348" s="4"/>
+      <c r="I348" s="6"/>
+      <c r="J348" s="4"/>
+      <c r="K348" s="9"/>
+      <c r="L348" s="4"/>
+      <c r="M348" s="4"/>
+      <c r="N348" s="6"/>
+    </row>
+    <row r="349" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G349" s="4"/>
+      <c r="H349" s="4"/>
+      <c r="I349" s="6"/>
+      <c r="J349" s="4"/>
+      <c r="K349" s="9"/>
+      <c r="L349" s="4"/>
+      <c r="M349" s="4"/>
+      <c r="N349" s="6"/>
+    </row>
+    <row r="350" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G350" s="4"/>
+      <c r="H350" s="4"/>
+      <c r="I350" s="6"/>
+      <c r="J350" s="4"/>
+      <c r="K350" s="9"/>
+      <c r="L350" s="4"/>
+      <c r="M350" s="4"/>
+      <c r="N350" s="6"/>
+    </row>
+    <row r="351" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G351" s="4"/>
+      <c r="H351" s="4"/>
+      <c r="I351" s="6"/>
+      <c r="J351" s="4"/>
+      <c r="K351" s="9"/>
+      <c r="L351" s="4"/>
+      <c r="M351" s="4"/>
+      <c r="N351" s="6"/>
+    </row>
+    <row r="352" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G352" s="4"/>
+      <c r="H352" s="4"/>
+      <c r="I352" s="6"/>
+      <c r="J352" s="4"/>
+      <c r="K352" s="9"/>
+      <c r="L352" s="4"/>
+      <c r="M352" s="4"/>
+      <c r="N352" s="6"/>
+    </row>
+    <row r="353" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G353" s="4"/>
+      <c r="H353" s="4"/>
+      <c r="I353" s="6"/>
+      <c r="J353" s="4"/>
+      <c r="K353" s="9"/>
+      <c r="L353" s="4"/>
+      <c r="M353" s="4"/>
+      <c r="N353" s="6"/>
+    </row>
+    <row r="354" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G354" s="4"/>
+      <c r="H354" s="4"/>
+      <c r="I354" s="6"/>
+      <c r="J354" s="4"/>
+      <c r="K354" s="9"/>
+      <c r="L354" s="4"/>
+      <c r="M354" s="4"/>
+      <c r="N354" s="6"/>
+    </row>
+    <row r="355" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G355" s="4"/>
+      <c r="H355" s="4"/>
+      <c r="I355" s="6"/>
+      <c r="J355" s="4"/>
+      <c r="K355" s="9"/>
+      <c r="L355" s="4"/>
+      <c r="M355" s="4"/>
+      <c r="N355" s="6"/>
+    </row>
+    <row r="356" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G356" s="4"/>
+      <c r="H356" s="4"/>
+      <c r="I356" s="6"/>
+      <c r="J356" s="4"/>
+      <c r="K356" s="9"/>
+      <c r="L356" s="4"/>
+      <c r="M356" s="4"/>
+      <c r="N356" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N339" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N342" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2025" month="10" day="16" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
     <sortCondition ref="G6:G339"/>
   </sortState>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1916" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1881563-2C13-41C2-929F-4DF6F0932D55}"/>
+  <xr:revisionPtr revIDLastSave="1921" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A04E4BE9-DF24-4B82-95D4-AC891A319130}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$347</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10226,7 +10226,7 @@
       <c r="N356" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N342" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:N347" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
         <dateGroupItem year="2025" month="10" day="16" dateTimeGrouping="day"/>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1921" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A04E4BE9-DF24-4B82-95D4-AC891A319130}"/>
+  <xr:revisionPtr revIDLastSave="1922" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA276C02-4A19-485B-9432-C42A3D9B47E4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1" filterMode="1">
+  <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="G5:O356"/>
@@ -1327,7 +1327,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45903</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45904</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45908</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45909</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45910</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45911</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45915</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45916</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45917</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6586,7 +6586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45918</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45922</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45923</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45924</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45925</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45929</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45930</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8062,7 +8062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="O273" s="19"/>
     </row>
-    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8531,7 +8531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8609,7 +8609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8661,7 +8661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
@@ -9025,7 +9025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
@@ -9077,7 +9077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45940</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
@@ -9519,7 +9519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45943</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
@@ -9649,7 +9649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G329" s="20">
         <v>45944</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
@@ -9779,7 +9779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
@@ -9831,7 +9831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
@@ -9857,7 +9857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
@@ -10226,13 +10226,7 @@
       <c r="N356" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N347" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" month="10" day="16" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="G5:N347" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
     <sortCondition ref="G6:G339"/>
   </sortState>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1922" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA276C02-4A19-485B-9432-C42A3D9B47E4}"/>
+  <xr:revisionPtr revIDLastSave="2158" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C511DE0-C4CA-4B4D-9DF8-A873E18EE2FB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$364</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="255">
   <si>
     <t>DATA</t>
   </si>
@@ -334,9 +334,6 @@
     <t>CARMO DO RIO CLARO</t>
   </si>
   <si>
-    <t>SÃO LORENÇO</t>
-  </si>
-  <si>
     <t xml:space="preserve">HOTEL REAL </t>
   </si>
   <si>
@@ -785,6 +782,27 @@
   </si>
   <si>
     <t>DOUGLAS RODRIGUES</t>
+  </si>
+  <si>
+    <t>SÃO LOURENÇO</t>
+  </si>
+  <si>
+    <t>HOTEL THALITA</t>
+  </si>
+  <si>
+    <t>CARATINGA</t>
+  </si>
+  <si>
+    <t>HOTEL CARATINGA</t>
+  </si>
+  <si>
+    <t>HOTEL REAL MARIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WELINGTON</t>
+  </si>
+  <si>
+    <t>JOSE ARILDO</t>
   </si>
 </sst>
 </file>
@@ -883,7 +901,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -948,6 +966,10 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1287,7 +1309,7 @@
   <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O356"/>
+  <dimension ref="G5:O369"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1298,18 +1320,18 @@
     <col min="12" max="12" width="28.28515625" style="1" customWidth="1"/>
     <col min="13" max="13" width="14.28515625" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="15" max="15" width="20.140625" style="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>1</v>
@@ -1327,15 +1349,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>23</v>
@@ -1352,16 +1374,17 @@
       <c r="N6" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O6"/>
+    </row>
+    <row r="7" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>24</v>
@@ -1378,16 +1401,17 @@
       <c r="N7" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O7"/>
+    </row>
+    <row r="8" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J8" s="17" t="s">
         <v>25</v>
@@ -1396,7 +1420,7 @@
         <v>80</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>7</v>
@@ -1404,19 +1428,20 @@
       <c r="N8" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O8"/>
+    </row>
+    <row r="9" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K9" s="9">
         <v>110</v>
@@ -1430,16 +1455,17 @@
       <c r="N9" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O9"/>
+    </row>
+    <row r="10" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J10" s="15" t="s">
         <v>45</v>
@@ -1456,16 +1482,17 @@
       <c r="N10" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O10"/>
+    </row>
+    <row r="11" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>46</v>
@@ -1474,7 +1501,7 @@
         <v>150</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>7</v>
@@ -1482,16 +1509,17 @@
       <c r="N11" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O11"/>
+    </row>
+    <row r="12" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>47</v>
@@ -1508,16 +1536,17 @@
       <c r="N12" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O12"/>
+    </row>
+    <row r="13" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>66</v>
@@ -1534,16 +1563,17 @@
       <c r="N13" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O13"/>
+    </row>
+    <row r="14" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J14" s="15" t="s">
         <v>66</v>
@@ -1560,19 +1590,20 @@
       <c r="N14" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O14"/>
+    </row>
+    <row r="15" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K15" s="9">
         <v>178</v>
@@ -1586,19 +1617,20 @@
       <c r="N15" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O15"/>
+    </row>
+    <row r="16" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K16" s="5">
         <v>80</v>
@@ -1612,16 +1644,17 @@
       <c r="N16" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O16"/>
+    </row>
+    <row r="17" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>5</v>
@@ -1639,15 +1672,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>24</v>
@@ -1665,15 +1698,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J19" s="17" t="s">
         <v>41</v>
@@ -1691,15 +1724,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>35</v>
@@ -1717,15 +1750,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J21" s="15" t="s">
         <v>61</v>
@@ -1743,15 +1776,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>62</v>
@@ -1769,15 +1802,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>63</v>
@@ -1795,15 +1828,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>64</v>
@@ -1821,15 +1854,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>43</v>
@@ -1847,15 +1880,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>21</v>
@@ -1873,15 +1906,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>65</v>
@@ -1899,15 +1932,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>66</v>
@@ -1925,15 +1958,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J29" s="17" t="s">
         <v>67</v>
@@ -1951,15 +1984,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J30" s="17" t="s">
         <v>24</v>
@@ -1977,15 +2010,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>25</v>
@@ -2003,15 +2036,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>27</v>
@@ -2029,15 +2062,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>87</v>
@@ -2055,24 +2088,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K34" s="5">
         <v>150</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>7</v>
@@ -2081,15 +2114,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J35" s="17" t="s">
         <v>71</v>
@@ -2107,15 +2140,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>72</v>
@@ -2133,15 +2166,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J37" s="17" t="s">
         <v>61</v>
@@ -2150,7 +2183,7 @@
         <v>150</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>7</v>
@@ -2159,15 +2192,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>10</v>
@@ -2185,15 +2218,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>5</v>
@@ -2211,15 +2244,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J40" s="17" t="s">
         <v>74</v>
@@ -2237,15 +2270,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J41" s="17" t="s">
         <v>76</v>
@@ -2263,15 +2296,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J42" s="17" t="s">
         <v>78</v>
@@ -2289,15 +2322,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J43" s="17" t="s">
         <v>80</v>
@@ -2315,15 +2348,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>87</v>
@@ -2341,15 +2374,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J45" s="17" t="s">
         <v>45</v>
@@ -2367,15 +2400,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J46" s="17" t="s">
         <v>14</v>
@@ -2393,15 +2426,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J47" s="17" t="s">
         <v>5</v>
@@ -2419,15 +2452,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J48" s="17" t="s">
         <v>15</v>
@@ -2445,15 +2478,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J49" s="17" t="s">
         <v>41</v>
@@ -2462,7 +2495,7 @@
         <v>200</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>8</v>
@@ -2471,15 +2504,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J50" s="17" t="s">
         <v>24</v>
@@ -2497,15 +2530,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J51" s="17" t="s">
         <v>24</v>
@@ -2523,15 +2556,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J52" s="17" t="s">
         <v>35</v>
@@ -2549,15 +2582,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J53" s="17" t="s">
         <v>61</v>
@@ -2575,15 +2608,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J54" s="17" t="s">
         <v>5</v>
@@ -2601,15 +2634,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J55" s="17" t="s">
         <v>84</v>
@@ -2627,15 +2660,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J56" s="17" t="s">
         <v>85</v>
@@ -2653,15 +2686,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>87</v>
@@ -2679,15 +2712,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J58" s="17" t="s">
         <v>43</v>
@@ -2705,15 +2738,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J59" s="17" t="s">
         <v>43</v>
@@ -2731,15 +2764,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J60" s="17" t="s">
         <v>46</v>
@@ -2748,7 +2781,7 @@
         <v>150</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>7</v>
@@ -2757,15 +2790,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J61" s="17" t="s">
         <v>65</v>
@@ -2783,15 +2816,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J62" s="17" t="s">
         <v>14</v>
@@ -2809,15 +2842,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J63" s="17" t="s">
         <v>67</v>
@@ -2835,15 +2868,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J64" s="17" t="s">
         <v>24</v>
@@ -2861,15 +2894,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J65" s="17" t="s">
         <v>21</v>
@@ -2887,15 +2920,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J66" s="17" t="s">
         <v>25</v>
@@ -2913,15 +2946,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J67" s="17" t="s">
         <v>27</v>
@@ -2939,15 +2972,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J68" s="17" t="s">
         <v>31</v>
@@ -2965,15 +2998,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J69" s="17" t="s">
         <v>92</v>
@@ -2991,18 +3024,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K70" s="5">
         <v>220</v>
@@ -3017,15 +3050,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J71" s="17" t="s">
         <v>95</v>
@@ -3043,15 +3076,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J72" s="17" t="s">
         <v>97</v>
@@ -3069,15 +3102,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J73" s="17" t="s">
         <v>10</v>
@@ -3095,15 +3128,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J74" s="17" t="s">
         <v>78</v>
@@ -3121,24 +3154,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J75" s="17" t="s">
-        <v>98</v>
+        <v>131</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>248</v>
       </c>
       <c r="K75" s="5">
         <v>130</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>7</v>
@@ -3147,15 +3180,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J76" s="17" t="s">
         <v>14</v>
@@ -3173,15 +3206,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J77" s="17" t="s">
         <v>65</v>
@@ -3190,7 +3223,7 @@
         <v>155</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>8</v>
@@ -3199,15 +3232,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J78" s="17" t="s">
         <v>46</v>
@@ -3216,7 +3249,7 @@
         <v>150</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>7</v>
@@ -3225,15 +3258,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J79" s="17" t="s">
         <v>47</v>
@@ -3251,24 +3284,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K80" s="5">
         <v>80</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>7</v>
@@ -3277,15 +3310,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J81" s="17" t="s">
         <v>21</v>
@@ -3303,15 +3336,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J82" s="17" t="s">
         <v>14</v>
@@ -3329,15 +3362,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>87</v>
@@ -3355,15 +3388,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J84" s="17" t="s">
         <v>31</v>
@@ -3381,15 +3414,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>34</v>
@@ -3407,15 +3440,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J86" s="17" t="s">
         <v>35</v>
@@ -3433,15 +3466,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J87" s="17" t="s">
         <v>24</v>
@@ -3459,15 +3492,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J88" s="17" t="s">
         <v>38</v>
@@ -3485,15 +3518,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J89" s="17" t="s">
         <v>10</v>
@@ -3511,15 +3544,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J90" s="17" t="s">
         <v>5</v>
@@ -3537,15 +3570,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J91" s="17" t="s">
         <v>41</v>
@@ -3561,15 +3594,15 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J92" s="17" t="s">
         <v>43</v>
@@ -3587,15 +3620,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J93" s="17" t="s">
         <v>23</v>
@@ -3613,15 +3646,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J94" s="17" t="s">
         <v>24</v>
@@ -3639,15 +3672,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J95" s="17" t="s">
         <v>25</v>
@@ -3665,15 +3698,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J96" s="17" t="s">
         <v>27</v>
@@ -3691,15 +3724,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J97" s="17" t="s">
         <v>11</v>
@@ -3717,15 +3750,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J98" s="17" t="s">
         <v>13</v>
@@ -3743,18 +3776,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K99" s="5">
         <v>178</v>
@@ -3769,15 +3802,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J100" s="17" t="s">
         <v>15</v>
@@ -3795,15 +3828,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J101" s="17" t="s">
         <v>10</v>
@@ -3821,15 +3854,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J102" s="17" t="s">
         <v>14</v>
@@ -3847,15 +3880,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J103" s="17" t="s">
         <v>5</v>
@@ -3873,24 +3906,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K104" s="5">
         <v>55</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M104" s="4" t="s">
         <v>7</v>
@@ -3899,15 +3932,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J105" s="17" t="s">
         <v>65</v>
@@ -3916,7 +3949,7 @@
         <v>155</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>8</v>
@@ -3925,15 +3958,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J106" s="17" t="s">
         <v>80</v>
@@ -3942,7 +3975,7 @@
         <v>140</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>7</v>
@@ -3951,24 +3984,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J107" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K107" s="5">
         <v>85</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>7</v>
@@ -3977,15 +4010,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J108" s="17" t="s">
         <v>21</v>
@@ -4003,24 +4036,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J109" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K109" s="5">
         <v>120</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M109" s="4" t="s">
         <v>7</v>
@@ -4029,24 +4062,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K110" s="5">
         <v>230</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M110" s="4" t="s">
         <v>8</v>
@@ -4055,24 +4088,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K111" s="5">
         <v>150</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M111" s="4" t="s">
         <v>7</v>
@@ -4081,15 +4114,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>87</v>
@@ -4107,15 +4140,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J113" s="17" t="s">
         <v>46</v>
@@ -4124,7 +4157,7 @@
         <v>200</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M113" s="4" t="s">
         <v>8</v>
@@ -4133,15 +4166,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J114" s="17" t="s">
         <v>43</v>
@@ -4159,24 +4192,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K115" s="9">
         <v>115</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M115" s="4" t="s">
         <v>7</v>
@@ -4185,15 +4218,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J116" s="17" t="s">
         <v>24</v>
@@ -4211,15 +4244,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J117" s="17" t="s">
         <v>41</v>
@@ -4228,7 +4261,7 @@
         <v>200</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>8</v>
@@ -4237,24 +4270,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J118" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K118" s="9">
         <v>160</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M118" s="4" t="s">
         <v>8</v>
@@ -4263,15 +4296,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J119" s="17" t="s">
         <v>10</v>
@@ -4289,15 +4322,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J120" s="17" t="s">
         <v>5</v>
@@ -4315,15 +4348,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J121" s="17" t="s">
         <v>27</v>
@@ -4341,24 +4374,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J122" s="17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K122" s="9">
         <v>110</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M122" s="4" t="s">
         <v>7</v>
@@ -4367,15 +4400,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J123" s="17" t="s">
         <v>23</v>
@@ -4384,7 +4417,7 @@
         <v>220</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M123" s="4" t="s">
         <v>8</v>
@@ -4393,15 +4426,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J124" s="17" t="s">
         <v>24</v>
@@ -4419,15 +4452,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J125" s="17" t="s">
         <v>25</v>
@@ -4445,15 +4478,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J126" s="17" t="s">
         <v>27</v>
@@ -4471,15 +4504,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J127" s="17" t="s">
         <v>78</v>
@@ -4497,24 +4530,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J128" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K128" s="9">
         <v>240</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M128" s="4" t="s">
         <v>8</v>
@@ -4523,24 +4556,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J129" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K129" s="9">
         <v>160</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M129" s="4" t="s">
         <v>8</v>
@@ -4549,15 +4582,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J130" s="17" t="s">
         <v>10</v>
@@ -4575,24 +4608,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K131" s="9">
         <v>150</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M131" s="4" t="s">
         <v>8</v>
@@ -4601,18 +4634,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J132" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K132" s="9">
         <v>220</v>
@@ -4627,15 +4660,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>97</v>
@@ -4644,7 +4677,7 @@
         <v>220</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>8</v>
@@ -4653,24 +4686,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K134" s="9">
         <v>140</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>8</v>
@@ -4679,24 +4712,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J135" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K135" s="9">
         <v>240</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M135" s="4" t="s">
         <v>8</v>
@@ -4705,15 +4738,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J136" s="4" t="s">
         <v>85</v>
@@ -4722,7 +4755,7 @@
         <v>200</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M136" s="4" t="s">
         <v>8</v>
@@ -4731,15 +4764,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>47</v>
@@ -4757,15 +4790,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>47</v>
@@ -4783,15 +4816,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J139" s="4" t="s">
         <v>46</v>
@@ -4800,7 +4833,7 @@
         <v>200</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M139" s="4" t="s">
         <v>8</v>
@@ -4809,18 +4842,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K140" s="9">
         <v>200</v>
@@ -4833,24 +4866,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K141" s="9">
         <v>120</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M141" s="4" t="s">
         <v>8</v>
@@ -4859,15 +4892,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J142" s="4" t="s">
         <v>61</v>
@@ -4883,24 +4916,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45903</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K143" s="9">
         <v>240</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M143" s="4" t="s">
         <v>8</v>
@@ -4909,15 +4942,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>34</v>
@@ -4935,15 +4968,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>87</v>
@@ -4961,24 +4994,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K146" s="9">
         <v>230</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M146" s="4" t="s">
         <v>8</v>
@@ -4987,15 +5020,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>31</v>
@@ -5013,15 +5046,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J148" s="17" t="s">
         <v>41</v>
@@ -5030,7 +5063,7 @@
         <v>200</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M148" s="4" t="s">
         <v>8</v>
@@ -5039,15 +5072,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>24</v>
@@ -5065,15 +5098,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>5</v>
@@ -5091,24 +5124,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K151" s="9">
         <v>160</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M151" s="4" t="s">
         <v>8</v>
@@ -5117,15 +5150,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45904</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>61</v>
@@ -5134,7 +5167,7 @@
         <v>230</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M152" s="4" t="s">
         <v>8</v>
@@ -5143,15 +5176,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J153" s="17" t="s">
         <v>23</v>
@@ -5160,7 +5193,7 @@
         <v>220</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M153" s="4" t="s">
         <v>8</v>
@@ -5169,15 +5202,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>24</v>
@@ -5195,15 +5228,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J155" s="4" t="s">
         <v>25</v>
@@ -5221,15 +5254,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45908</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J156" s="4" t="s">
         <v>27</v>
@@ -5247,24 +5280,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K157" s="9">
         <v>200</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M157" s="4" t="s">
         <v>8</v>
@@ -5273,15 +5306,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>95</v>
@@ -5290,7 +5323,7 @@
         <v>240</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M158" s="4" t="s">
         <v>8</v>
@@ -5299,15 +5332,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>10</v>
@@ -5325,18 +5358,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J160" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K160" s="9">
         <v>220</v>
@@ -5351,15 +5384,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J161" s="4" t="s">
         <v>78</v>
@@ -5377,15 +5410,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45909</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J162" s="17" t="s">
         <v>97</v>
@@ -5394,7 +5427,7 @@
         <v>200</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M162" s="4" t="s">
         <v>8</v>
@@ -5403,15 +5436,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>14</v>
@@ -5429,16 +5462,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>132</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="J164" s="1"/>
       <c r="K164" s="9"/>
       <c r="L164" s="4"/>
       <c r="M164" s="4" t="s">
@@ -5448,15 +5482,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J165" s="4" t="s">
         <v>46</v>
@@ -5465,7 +5499,7 @@
         <v>200</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M165" s="4" t="s">
         <v>8</v>
@@ -5474,15 +5508,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>47</v>
@@ -5491,7 +5525,7 @@
         <v>170</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M166" s="4" t="s">
         <v>8</v>
@@ -5500,15 +5534,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>47</v>
@@ -5517,7 +5551,7 @@
         <v>170</v>
       </c>
       <c r="L167" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M167" s="4" t="s">
         <v>8</v>
@@ -5526,15 +5560,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>21</v>
@@ -5552,15 +5586,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45910</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>87</v>
@@ -5578,15 +5612,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J170" s="4"/>
       <c r="K170" s="9"/>
@@ -5598,15 +5632,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>31</v>
@@ -5624,15 +5658,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J172" s="4" t="s">
         <v>87</v>
@@ -5650,24 +5684,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J173" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K173" s="9">
         <v>170</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M173" s="4" t="s">
         <v>8</v>
@@ -5676,15 +5710,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J174" s="24" t="s">
         <v>66</v>
@@ -5702,24 +5736,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K175" s="9">
         <v>250</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M175" s="4" t="s">
         <v>8</v>
@@ -5728,15 +5762,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>63</v>
@@ -5745,7 +5779,7 @@
         <v>220</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M176" s="4" t="s">
         <v>8</v>
@@ -5754,15 +5788,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J177" s="17" t="s">
         <v>41</v>
@@ -5771,7 +5805,7 @@
         <v>200</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M177" s="4" t="s">
         <v>8</v>
@@ -5780,15 +5814,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J178" s="4" t="s">
         <v>24</v>
@@ -5806,18 +5840,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K179" s="9">
         <v>220</v>
@@ -5832,15 +5866,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J180" s="4" t="s">
         <v>61</v>
@@ -5858,15 +5892,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>87</v>
@@ -5884,15 +5918,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45911</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>25</v>
@@ -5910,15 +5944,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>25</v>
@@ -5927,7 +5961,7 @@
         <v>140</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M183" s="4" t="s">
         <v>7</v>
@@ -5936,18 +5970,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J184" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K184" s="9">
         <v>220</v>
@@ -5962,15 +5996,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>24</v>
@@ -5988,15 +6022,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>27</v>
@@ -6014,15 +6048,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>23</v>
@@ -6031,7 +6065,7 @@
         <v>220</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M187" s="4" t="s">
         <v>8</v>
@@ -6040,15 +6074,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J188" s="17" t="s">
         <v>46</v>
@@ -6057,7 +6091,7 @@
         <v>200</v>
       </c>
       <c r="L188" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M188" s="4" t="s">
         <v>8</v>
@@ -6066,15 +6100,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45915</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>24</v>
@@ -6092,15 +6126,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>11</v>
@@ -6118,15 +6152,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>97</v>
@@ -6135,7 +6169,7 @@
         <v>200</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M191" s="4" t="s">
         <v>8</v>
@@ -6144,15 +6178,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>41</v>
@@ -6161,7 +6195,7 @@
         <v>200</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M192" s="4" t="s">
         <v>8</v>
@@ -6170,24 +6204,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K193" s="9">
         <v>170</v>
       </c>
       <c r="L193" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M193" s="4" t="s">
         <v>8</v>
@@ -6196,15 +6230,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45916</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>10</v>
@@ -6222,24 +6256,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K195" s="9">
         <v>150</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M195" s="4" t="s">
         <v>8</v>
@@ -6248,24 +6282,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K196" s="9">
         <v>240</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M196" s="4" t="s">
         <v>8</v>
@@ -6274,18 +6308,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
       <c r="H197" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K197" s="9">
         <v>220</v>
@@ -6300,15 +6334,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>65</v>
@@ -6317,7 +6351,7 @@
         <v>280</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M198" s="4" t="s">
         <v>8</v>
@@ -6326,15 +6360,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>46</v>
@@ -6343,7 +6377,7 @@
         <v>230</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M199" s="4" t="s">
         <v>8</v>
@@ -6352,24 +6386,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K200" s="9">
         <v>230</v>
       </c>
       <c r="L200" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M200" s="4" t="s">
         <v>8</v>
@@ -6378,15 +6412,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45917</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>21</v>
@@ -6404,24 +6438,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K202" s="9">
         <v>180</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M202" s="4" t="s">
         <v>8</v>
@@ -6430,15 +6464,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>87</v>
@@ -6456,15 +6490,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>31</v>
@@ -6482,15 +6516,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>85</v>
@@ -6499,7 +6533,7 @@
         <v>200</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M205" s="4" t="s">
         <v>8</v>
@@ -6508,15 +6542,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I206" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>43</v>
@@ -6534,15 +6568,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J207" s="17" t="s">
         <v>13</v>
@@ -6551,7 +6585,7 @@
         <v>200</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M207" s="4" t="s">
         <v>8</v>
@@ -6560,15 +6594,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I208" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>24</v>
@@ -6586,24 +6620,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I209" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K209" s="9">
         <v>230</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M209" s="4" t="s">
         <v>8</v>
@@ -6612,15 +6646,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I210" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J210" s="4" t="s">
         <v>27</v>
@@ -6638,15 +6672,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I211" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>61</v>
@@ -6664,15 +6698,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J212" s="4"/>
       <c r="K212" s="9"/>
@@ -6684,15 +6718,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I213" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J213" s="17" t="s">
         <v>34</v>
@@ -6710,24 +6744,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45918</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I214" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K214" s="9">
         <v>240</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M214" s="4" t="s">
         <v>8</v>
@@ -6736,24 +6770,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I215" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J215" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K215" s="9">
         <v>170</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M215" s="4" t="s">
         <v>8</v>
@@ -6762,15 +6796,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I216" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>24</v>
@@ -6788,15 +6822,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J217" s="4" t="s">
         <v>46</v>
@@ -6805,7 +6839,7 @@
         <v>200</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M217" s="4" t="s">
         <v>8</v>
@@ -6814,18 +6848,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I218" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K218" s="9">
         <v>220</v>
@@ -6840,15 +6874,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J219" s="4" t="s">
         <v>25</v>
@@ -6857,7 +6891,7 @@
         <v>250</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M219" s="4" t="s">
         <v>8</v>
@@ -6866,15 +6900,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I220" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J220" s="4" t="s">
         <v>27</v>
@@ -6892,15 +6926,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45922</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I221" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J221" s="4" t="s">
         <v>25</v>
@@ -6909,7 +6943,7 @@
         <v>275</v>
       </c>
       <c r="L221" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M221" s="4" t="s">
         <v>8</v>
@@ -6918,15 +6952,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I222" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J222" s="4" t="s">
         <v>41</v>
@@ -6935,7 +6969,7 @@
         <v>200</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M222" s="4" t="s">
         <v>8</v>
@@ -6944,24 +6978,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K223" s="9">
         <v>200</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M223" s="4" t="s">
         <v>8</v>
@@ -6970,15 +7004,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>23</v>
@@ -6987,7 +7021,7 @@
         <v>220</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M224" s="4" t="s">
         <v>8</v>
@@ -6996,15 +7030,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J225" s="17" t="s">
         <v>61</v>
@@ -7022,15 +7056,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I226" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>14</v>
@@ -7048,15 +7082,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45923</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J227" s="4" t="s">
         <v>11</v>
@@ -7074,24 +7108,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K228" s="9">
         <v>110</v>
       </c>
       <c r="L228" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M228" s="4" t="s">
         <v>8</v>
@@ -7100,15 +7134,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>65</v>
@@ -7117,7 +7151,7 @@
         <v>205</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M229" s="4" t="s">
         <v>8</v>
@@ -7126,15 +7160,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>46</v>
@@ -7143,7 +7177,7 @@
         <v>200</v>
       </c>
       <c r="L230" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M230" s="4" t="s">
         <v>8</v>
@@ -7152,15 +7186,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I231" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>47</v>
@@ -7178,15 +7212,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>21</v>
@@ -7204,18 +7238,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K233" s="9">
         <v>220</v>
@@ -7230,15 +7264,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>78</v>
@@ -7256,24 +7290,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45924</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>98</v>
+        <v>248</v>
       </c>
       <c r="K235" s="9">
         <v>170</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M235" s="4" t="s">
         <v>8</v>
@@ -7282,15 +7316,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J236" s="4" t="s">
         <v>25</v>
@@ -7299,7 +7333,7 @@
         <v>250</v>
       </c>
       <c r="L236" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M236" s="4" t="s">
         <v>8</v>
@@ -7308,15 +7342,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I237" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J237" s="4" t="s">
         <v>87</v>
@@ -7334,24 +7368,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I238" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K238" s="9">
         <v>180</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M238" s="4" t="s">
         <v>8</v>
@@ -7360,15 +7394,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>43</v>
@@ -7386,15 +7420,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I240" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J240" s="17" t="s">
         <v>34</v>
@@ -7412,15 +7446,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J241" s="4" t="s">
         <v>24</v>
@@ -7438,15 +7472,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>41</v>
@@ -7455,7 +7489,7 @@
         <v>200</v>
       </c>
       <c r="L242" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M242" s="4" t="s">
         <v>8</v>
@@ -7464,24 +7498,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K243" s="9">
         <v>200</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M243" s="4" t="s">
         <v>8</v>
@@ -7490,15 +7524,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I244" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J244" s="4" t="s">
         <v>61</v>
@@ -7516,15 +7550,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45925</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I245" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>38</v>
@@ -7542,24 +7576,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I246" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J246" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K246" s="9">
         <v>240</v>
       </c>
       <c r="L246" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M246" s="4" t="s">
         <v>8</v>
@@ -7568,15 +7602,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I247" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J247" s="17" t="s">
         <v>23</v>
@@ -7585,7 +7619,7 @@
         <v>220</v>
       </c>
       <c r="L247" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M247" s="4" t="s">
         <v>8</v>
@@ -7594,15 +7628,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I248" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J248" s="4" t="s">
         <v>24</v>
@@ -7620,15 +7654,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>46</v>
@@ -7637,7 +7671,7 @@
         <v>200</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M249" s="4" t="s">
         <v>8</v>
@@ -7646,18 +7680,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I250" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K250" s="9">
         <v>220</v>
@@ -7672,15 +7706,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>25</v>
@@ -7689,7 +7723,7 @@
         <v>250</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M251" s="4" t="s">
         <v>8</v>
@@ -7698,15 +7732,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I252" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J252" s="4" t="s">
         <v>25</v>
@@ -7715,7 +7749,7 @@
         <v>265</v>
       </c>
       <c r="L252" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M252" s="4" t="s">
         <v>8</v>
@@ -7724,15 +7758,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45929</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J253" s="4" t="s">
         <v>27</v>
@@ -7750,15 +7784,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J254" s="4" t="s">
         <v>41</v>
@@ -7767,7 +7801,7 @@
         <v>200</v>
       </c>
       <c r="L254" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M254" s="4" t="s">
         <v>8</v>
@@ -7776,24 +7810,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I255" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K255" s="9">
         <v>200</v>
       </c>
       <c r="L255" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M255" s="4" t="s">
         <v>8</v>
@@ -7802,15 +7836,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I256" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J256" s="4" t="s">
         <v>97</v>
@@ -7819,7 +7853,7 @@
         <v>200</v>
       </c>
       <c r="L256" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M256" s="4" t="s">
         <v>8</v>
@@ -7828,15 +7862,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I257" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J257" s="17" t="s">
         <v>61</v>
@@ -7854,15 +7888,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I258" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J258" s="4" t="s">
         <v>14</v>
@@ -7880,15 +7914,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45930</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J259" s="4" t="s">
         <v>11</v>
@@ -7906,18 +7940,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K260" s="9">
         <v>240</v>
@@ -7932,15 +7966,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I261" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J261" s="4" t="s">
         <v>76</v>
@@ -7958,24 +7992,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I262" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J262" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K262" s="9">
         <v>210</v>
       </c>
       <c r="L262" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M262" s="4" t="s">
         <v>8</v>
@@ -7984,24 +8018,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I263" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K263" s="9">
         <v>110</v>
       </c>
       <c r="L263" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M263" s="4" t="s">
         <v>8</v>
@@ -8010,15 +8044,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J264" s="4" t="s">
         <v>65</v>
@@ -8027,7 +8061,7 @@
         <v>212</v>
       </c>
       <c r="L264" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M264" s="4" t="s">
         <v>8</v>
@@ -8036,15 +8070,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I265" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J265" s="4" t="s">
         <v>46</v>
@@ -8053,7 +8087,7 @@
         <v>200</v>
       </c>
       <c r="L265" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M265" s="4" t="s">
         <v>8</v>
@@ -8062,24 +8096,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K266" s="9">
         <v>190</v>
       </c>
       <c r="L266" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M266" s="4" t="s">
         <v>8</v>
@@ -8088,15 +8122,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J267" s="4" t="s">
         <v>21</v>
@@ -8114,15 +8148,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J268" s="4" t="s">
         <v>87</v>
@@ -8140,15 +8174,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I269" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J269" s="4" t="s">
         <v>31</v>
@@ -8166,15 +8200,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I270" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J270" s="17" t="s">
         <v>43</v>
@@ -8192,15 +8226,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
       <c r="H271" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I271" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J271" s="15" t="s">
         <v>66</v>
@@ -8218,15 +8252,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I272" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J272" s="4" t="s">
         <v>24</v>
@@ -8249,19 +8283,19 @@
         <v>45932</v>
       </c>
       <c r="H273" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K273" s="9">
         <v>240</v>
       </c>
       <c r="L273" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M273" s="4" t="s">
         <v>8</v>
@@ -8276,19 +8310,19 @@
         <v>45932</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K274" s="9">
         <v>200</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M274" s="4" t="s">
         <v>8</v>
@@ -8296,25 +8330,26 @@
       <c r="N274" s="6">
         <v>2</v>
       </c>
+      <c r="O274"/>
     </row>
     <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K275" s="9">
         <v>250</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M275" s="4" t="s">
         <v>8</v>
@@ -8322,16 +8357,17 @@
       <c r="N275" s="6">
         <v>2</v>
       </c>
+      <c r="O275"/>
     </row>
     <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J276" s="4" t="s">
         <v>61</v>
@@ -8348,16 +8384,17 @@
       <c r="N276" s="6">
         <v>2</v>
       </c>
+      <c r="O276"/>
     </row>
     <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
       <c r="H277" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J277" s="4" t="s">
         <v>27</v>
@@ -8374,16 +8411,17 @@
       <c r="N277" s="6">
         <v>2</v>
       </c>
+      <c r="O277"/>
     </row>
     <row r="278" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
       <c r="H278" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J278" s="17" t="s">
         <v>25</v>
@@ -8392,7 +8430,7 @@
         <v>250</v>
       </c>
       <c r="L278" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M278" s="4" t="s">
         <v>8</v>
@@ -8400,25 +8438,26 @@
       <c r="N278" s="6">
         <v>1</v>
       </c>
+      <c r="O278"/>
     </row>
     <row r="279" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K279" s="9">
         <v>230</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M279" s="4" t="s">
         <v>8</v>
@@ -8426,16 +8465,17 @@
       <c r="N279" s="6">
         <v>1</v>
       </c>
+      <c r="O279"/>
     </row>
     <row r="280" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
       <c r="H280" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J280" s="4" t="s">
         <v>10</v>
@@ -8452,25 +8492,26 @@
       <c r="N280" s="6">
         <v>1</v>
       </c>
+      <c r="O280"/>
     </row>
     <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
       <c r="H281" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J281" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K281" s="9">
+      <c r="K281" s="26">
         <v>220</v>
       </c>
       <c r="L281" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M281" s="4" t="s">
         <v>8</v>
@@ -8478,16 +8519,17 @@
       <c r="N281" s="6">
         <v>2</v>
       </c>
+      <c r="O281"/>
     </row>
     <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J282" s="17" t="s">
         <v>24</v>
@@ -8504,16 +8546,17 @@
       <c r="N282" s="6">
         <v>2</v>
       </c>
+      <c r="O282"/>
     </row>
     <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
       <c r="H283" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I283" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J283" s="4" t="s">
         <v>46</v>
@@ -8522,7 +8565,7 @@
         <v>200</v>
       </c>
       <c r="L283" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M283" s="4" t="s">
         <v>8</v>
@@ -8530,19 +8573,20 @@
       <c r="N283" s="6">
         <v>2</v>
       </c>
+      <c r="O283"/>
     </row>
     <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
       <c r="H284" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K284" s="9">
         <v>240</v>
@@ -8556,16 +8600,17 @@
       <c r="N284" s="6">
         <v>2</v>
       </c>
+      <c r="O284"/>
     </row>
     <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
       <c r="H285" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J285" s="4" t="s">
         <v>27</v>
@@ -8582,16 +8627,17 @@
       <c r="N285" s="6">
         <v>2</v>
       </c>
+      <c r="O285"/>
     </row>
     <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
       <c r="H286" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J286" s="4" t="s">
         <v>25</v>
@@ -8600,7 +8646,7 @@
         <v>250</v>
       </c>
       <c r="L286" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M286" s="4" t="s">
         <v>8</v>
@@ -8608,16 +8654,17 @@
       <c r="N286" s="6">
         <v>4</v>
       </c>
+      <c r="O286"/>
     </row>
     <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
       <c r="H287" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="I287" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="I287" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="J287" s="4" t="s">
         <v>25</v>
@@ -8626,7 +8673,7 @@
         <v>265</v>
       </c>
       <c r="L287" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M287" s="4" t="s">
         <v>8</v>
@@ -8634,16 +8681,17 @@
       <c r="N287" s="6">
         <v>1</v>
       </c>
+      <c r="O287"/>
     </row>
     <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
       <c r="H288" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I288" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J288" s="4" t="s">
         <v>74</v>
@@ -8652,7 +8700,7 @@
         <v>140</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>8</v>
@@ -8660,16 +8708,17 @@
       <c r="N288" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="289" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O288"/>
+    </row>
+    <row r="289" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
       <c r="H289" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I289" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J289" s="4" t="s">
         <v>41</v>
@@ -8678,7 +8727,7 @@
         <v>200</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M289" s="4" t="s">
         <v>8</v>
@@ -8687,24 +8736,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
       <c r="H290" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I290" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K290" s="9">
         <v>179.9</v>
       </c>
       <c r="L290" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M290" s="4" t="s">
         <v>8</v>
@@ -8713,15 +8762,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
       <c r="H291" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J291" s="4" t="s">
         <v>97</v>
@@ -8730,7 +8779,7 @@
         <v>200</v>
       </c>
       <c r="L291" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>8</v>
@@ -8739,15 +8788,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
       <c r="H292" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I292" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J292" s="4" t="s">
         <v>61</v>
@@ -8765,15 +8814,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
       <c r="H293" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J293" s="17" t="s">
         <v>14</v>
@@ -8791,15 +8840,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
       <c r="H294" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J294" s="4" t="s">
         <v>23</v>
@@ -8808,7 +8857,7 @@
         <v>220</v>
       </c>
       <c r="L294" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M294" s="4" t="s">
         <v>8</v>
@@ -8817,15 +8866,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
       <c r="H295" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J295" s="4" t="s">
         <v>78</v>
@@ -8834,7 +8883,7 @@
         <v>200</v>
       </c>
       <c r="L295" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M295" s="4" t="s">
         <v>8</v>
@@ -8843,15 +8892,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
       <c r="H296" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J296" s="4" t="s">
         <v>76</v>
@@ -8869,24 +8918,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
       <c r="H297" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I297" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J297" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K297" s="9">
         <v>160</v>
       </c>
       <c r="L297" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M297" s="4" t="s">
         <v>8</v>
@@ -8895,15 +8944,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
       <c r="H298" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J298" s="4" t="s">
         <v>47</v>
@@ -8912,7 +8961,7 @@
         <v>170</v>
       </c>
       <c r="L298" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M298" s="4" t="s">
         <v>8</v>
@@ -8921,15 +8970,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
       <c r="H299" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J299" s="4" t="s">
         <v>46</v>
@@ -8938,7 +8987,7 @@
         <v>200</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M299" s="4" t="s">
         <v>8</v>
@@ -8947,15 +8996,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
       <c r="H300" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I300" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J300" s="4" t="s">
         <v>47</v>
@@ -8964,7 +9013,7 @@
         <v>170</v>
       </c>
       <c r="L300" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M300" s="4" t="s">
         <v>8</v>
@@ -8973,15 +9022,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
       <c r="H301" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J301" s="4" t="s">
         <v>21</v>
@@ -8999,24 +9048,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
       <c r="H302" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K302" s="9">
         <v>230</v>
       </c>
       <c r="L302" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M302" s="4" t="s">
         <v>8</v>
@@ -9025,15 +9074,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
       <c r="H303" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J303" s="4" t="s">
         <v>25</v>
@@ -9042,7 +9091,7 @@
         <v>180</v>
       </c>
       <c r="L303" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M303" s="4" t="s">
         <v>8</v>
@@ -9051,15 +9100,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
       <c r="H304" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I304" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J304" s="4" t="s">
         <v>87</v>
@@ -9077,24 +9126,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
       <c r="H305" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K305" s="9">
         <v>180</v>
       </c>
       <c r="L305" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M305" s="4" t="s">
         <v>8</v>
@@ -9103,15 +9152,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
       <c r="H306" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J306" s="4" t="s">
         <v>43</v>
@@ -9129,15 +9178,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
       <c r="H307" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J307" s="24" t="s">
         <v>66</v>
@@ -9146,7 +9195,7 @@
         <v>140</v>
       </c>
       <c r="L307" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M307" s="4" t="s">
         <v>8</v>
@@ -9155,15 +9204,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
       <c r="H308" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I308" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J308" s="4" t="s">
         <v>24</v>
@@ -9172,7 +9221,7 @@
         <v>140</v>
       </c>
       <c r="L308" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M308" s="4" t="s">
         <v>8</v>
@@ -9181,15 +9230,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
       <c r="H309" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I309" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J309" s="4" t="s">
         <v>41</v>
@@ -9198,7 +9247,7 @@
         <v>200</v>
       </c>
       <c r="L309" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M309" s="4" t="s">
         <v>8</v>
@@ -9207,24 +9256,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
       <c r="H310" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I310" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="I310" s="6" t="s">
-        <v>224</v>
-      </c>
       <c r="J310" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K310" s="9">
         <v>220</v>
       </c>
       <c r="L310" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M310" s="4" t="s">
         <v>8</v>
@@ -9233,15 +9282,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
       <c r="H311" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I311" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="I311" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="J311" s="4" t="s">
         <v>97</v>
@@ -9250,7 +9299,7 @@
         <v>200</v>
       </c>
       <c r="L311" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M311" s="4" t="s">
         <v>8</v>
@@ -9259,15 +9308,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
       <c r="H312" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J312" s="4" t="s">
         <v>61</v>
@@ -9285,24 +9334,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
       <c r="H313" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I313" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K313" s="9">
         <v>180</v>
       </c>
       <c r="L313" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M313" s="4" t="s">
         <v>8</v>
@@ -9311,15 +9360,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
       <c r="H314" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I314" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J314" s="4" t="s">
         <v>38</v>
@@ -9337,18 +9386,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
       <c r="H315" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I315" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J315" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K315" s="9">
         <v>220</v>
@@ -9363,24 +9412,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45940</v>
       </c>
       <c r="H316" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I316" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K316" s="9">
         <v>220</v>
       </c>
       <c r="L316" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M316" s="4" t="s">
         <v>8</v>
@@ -9389,15 +9438,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
       <c r="H317" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I317" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J317" s="4" t="s">
         <v>23</v>
@@ -9406,7 +9455,7 @@
         <v>220</v>
       </c>
       <c r="L317" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M317" s="4" t="s">
         <v>8</v>
@@ -9415,15 +9464,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
       <c r="H318" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I318" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J318" s="4" t="s">
         <v>24</v>
@@ -9432,7 +9481,7 @@
         <v>259</v>
       </c>
       <c r="L318" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M318" s="4" t="s">
         <v>8</v>
@@ -9441,15 +9490,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
       <c r="H319" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I319" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J319" s="4" t="s">
         <v>46</v>
@@ -9458,7 +9507,7 @@
         <v>200</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M319" s="4" t="s">
         <v>8</v>
@@ -9467,18 +9516,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
       <c r="H320" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I320" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K320" s="9">
         <v>220</v>
@@ -9493,15 +9542,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
       <c r="H321" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I321" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J321" s="4" t="s">
         <v>25</v>
@@ -9510,7 +9559,7 @@
         <v>180</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M321" s="4" t="s">
         <v>8</v>
@@ -9519,15 +9568,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45943</v>
       </c>
       <c r="H322" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I322" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J322" s="4" t="s">
         <v>63</v>
@@ -9536,7 +9585,7 @@
         <v>220</v>
       </c>
       <c r="L322" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M322" s="4" t="s">
         <v>8</v>
@@ -9545,15 +9594,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
       <c r="H323" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J323" s="4" t="s">
         <v>11</v>
@@ -9562,7 +9611,7 @@
         <v>160</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M323" s="4" t="s">
         <v>8</v>
@@ -9571,15 +9620,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
       <c r="H324" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J324" s="4" t="s">
         <v>41</v>
@@ -9588,7 +9637,7 @@
         <v>200</v>
       </c>
       <c r="L324" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M324" s="4" t="s">
         <v>8</v>
@@ -9597,24 +9646,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
       <c r="H325" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I325" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K325" s="9">
         <v>270</v>
       </c>
       <c r="L325" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M325" s="4" t="s">
         <v>8</v>
@@ -9623,15 +9672,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
       <c r="H326" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I326" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J326" s="4" t="s">
         <v>97</v>
@@ -9640,7 +9689,7 @@
         <v>200</v>
       </c>
       <c r="L326" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M326" s="4" t="s">
         <v>8</v>
@@ -9649,15 +9698,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
       <c r="H327" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J327" s="4" t="s">
         <v>61</v>
@@ -9675,15 +9724,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
       <c r="H328" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I328" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J328" s="4" t="s">
         <v>14</v>
@@ -9701,24 +9750,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G329" s="20">
         <v>45944</v>
       </c>
       <c r="H329" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I329" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J329" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K329" s="23">
         <v>180</v>
       </c>
       <c r="L329" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M329" s="21" t="s">
         <v>8</v>
@@ -9727,18 +9776,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
       <c r="H330" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I330" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J330" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K330" s="9">
         <v>220</v>
@@ -9753,15 +9802,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
       <c r="H331" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I331" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J331" s="4" t="s">
         <v>47</v>
@@ -9770,7 +9819,7 @@
         <v>230</v>
       </c>
       <c r="L331" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M331" s="4" t="s">
         <v>8</v>
@@ -9779,15 +9828,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
       <c r="H332" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I332" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J332" s="4" t="s">
         <v>46</v>
@@ -9796,7 +9845,7 @@
         <v>200</v>
       </c>
       <c r="L332" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M332" s="4" t="s">
         <v>8</v>
@@ -9805,15 +9854,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
       <c r="H333" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I333" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J333" s="4" t="s">
         <v>47</v>
@@ -9822,7 +9871,7 @@
         <v>230</v>
       </c>
       <c r="L333" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M333" s="4" t="s">
         <v>8</v>
@@ -9831,15 +9880,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
       <c r="H334" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I334" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J334" s="4" t="s">
         <v>21</v>
@@ -9857,24 +9906,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
       <c r="H335" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I335" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K335" s="9">
         <v>160</v>
       </c>
       <c r="L335" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M335" s="4" t="s">
         <v>8</v>
@@ -9883,24 +9932,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
       <c r="H336" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I336" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K336" s="9">
         <v>218.9</v>
       </c>
       <c r="L336" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M336" s="4" t="s">
         <v>8</v>
@@ -9909,15 +9958,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G337" s="3">
         <v>45946</v>
       </c>
       <c r="H337" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I337" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J337" s="4" t="s">
         <v>87</v>
@@ -9934,299 +9983,727 @@
       <c r="N337" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="338" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O337"/>
+    </row>
+    <row r="338" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G338" s="3">
         <v>45946</v>
       </c>
       <c r="H338" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I338" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="J338" s="17"/>
-      <c r="K338" s="9"/>
-      <c r="L338" s="4"/>
+        <v>178</v>
+      </c>
+      <c r="J338" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K338" s="9">
+        <v>170</v>
+      </c>
+      <c r="L338" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="M338" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N338" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="339" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O338"/>
+    </row>
+    <row r="339" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G339" s="3">
         <v>45946</v>
       </c>
       <c r="H339" s="4" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J339" s="4"/>
-      <c r="K339" s="9"/>
-      <c r="L339" s="4"/>
+        <v>129</v>
+      </c>
+      <c r="J339" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K339" s="9">
+        <v>150</v>
+      </c>
+      <c r="L339" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="M339" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N339" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="340" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O339"/>
+    </row>
+    <row r="340" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G340" s="3">
         <v>45946</v>
       </c>
       <c r="H340" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I340" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J340" s="4"/>
-      <c r="K340" s="9"/>
-      <c r="L340" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="J340" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K340" s="9">
+        <v>160</v>
+      </c>
+      <c r="L340" s="4" t="s">
+        <v>233</v>
+      </c>
       <c r="M340" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N340" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="341" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O340"/>
+    </row>
+    <row r="341" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G341" s="3">
         <v>45946</v>
       </c>
       <c r="H341" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I341" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="J341" s="4"/>
-      <c r="K341" s="9"/>
-      <c r="L341" s="4"/>
+        <v>193</v>
+      </c>
+      <c r="J341" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K341" s="9">
+        <v>159</v>
+      </c>
+      <c r="L341" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="M341" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N341" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="342" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O341"/>
+    </row>
+    <row r="342" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G342" s="3">
         <v>45946</v>
       </c>
       <c r="H342" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I342" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J342" s="4"/>
-      <c r="K342" s="9"/>
-      <c r="L342" s="4"/>
+        <v>125</v>
+      </c>
+      <c r="J342" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K342" s="9">
+        <v>240</v>
+      </c>
+      <c r="L342" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="M342" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N342" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="343" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O342"/>
+    </row>
+    <row r="343" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G343" s="3">
         <v>45946</v>
       </c>
       <c r="H343" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I343" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="J343" s="4"/>
-      <c r="K343" s="9"/>
-      <c r="L343" s="4"/>
+        <v>180</v>
+      </c>
+      <c r="J343" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K343" s="9">
+        <v>178.9</v>
+      </c>
+      <c r="L343" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="M343" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N343" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="344" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O343"/>
+    </row>
+    <row r="344" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G344" s="3">
         <v>45946</v>
       </c>
       <c r="H344" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J344" s="4"/>
-      <c r="K344" s="9"/>
-      <c r="L344" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="J344" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K344" s="9">
+        <v>150</v>
+      </c>
+      <c r="L344" s="4" t="s">
+        <v>249</v>
+      </c>
       <c r="M344" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N344" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="345" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O344"/>
+    </row>
+    <row r="345" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G345" s="3">
         <v>45946</v>
       </c>
       <c r="H345" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J345" s="4"/>
-      <c r="K345" s="9"/>
-      <c r="L345" s="4"/>
+        <v>137</v>
+      </c>
+      <c r="J345" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K345" s="9">
+        <v>280</v>
+      </c>
+      <c r="L345" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="M345" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N345" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="346" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O345"/>
+    </row>
+    <row r="346" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G346" s="3">
         <v>45946</v>
       </c>
       <c r="H346" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="J346" s="4"/>
-      <c r="K346" s="9"/>
-      <c r="L346" s="4"/>
+        <v>221</v>
+      </c>
+      <c r="J346" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="K346" s="9">
+        <v>220</v>
+      </c>
+      <c r="L346" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="M346" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N346" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="347" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O346"/>
+    </row>
+    <row r="347" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G347" s="3">
         <v>45946</v>
       </c>
       <c r="H347" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I347" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J347" s="4"/>
-      <c r="K347" s="9"/>
-      <c r="L347" s="4"/>
+        <v>139</v>
+      </c>
+      <c r="J347" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K347" s="9">
+        <v>175</v>
+      </c>
+      <c r="L347" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="M347" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N347" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="348" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G348" s="4"/>
-      <c r="H348" s="4"/>
-      <c r="I348" s="6"/>
-      <c r="J348" s="4"/>
-      <c r="K348" s="9"/>
-      <c r="L348" s="4"/>
-      <c r="M348" s="4"/>
-      <c r="N348" s="6"/>
-    </row>
-    <row r="349" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G349" s="4"/>
-      <c r="H349" s="4"/>
-      <c r="I349" s="6"/>
-      <c r="J349" s="4"/>
-      <c r="K349" s="9"/>
-      <c r="L349" s="4"/>
-      <c r="M349" s="4"/>
-      <c r="N349" s="6"/>
-    </row>
-    <row r="350" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G350" s="4"/>
-      <c r="H350" s="4"/>
-      <c r="I350" s="6"/>
-      <c r="J350" s="4"/>
+      <c r="O347"/>
+    </row>
+    <row r="348" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G348" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H348" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I348" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J348" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="K348" s="9">
+        <v>170</v>
+      </c>
+      <c r="L348" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M348" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N348" s="6">
+        <v>1</v>
+      </c>
+      <c r="O348"/>
+    </row>
+    <row r="349" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G349" s="3">
+        <v>45946</v>
+      </c>
+      <c r="H349" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I349" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J349" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K349" s="9">
+        <v>180</v>
+      </c>
+      <c r="L349" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M349" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N349" s="6">
+        <v>1</v>
+      </c>
+      <c r="O349"/>
+    </row>
+    <row r="350" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G350" s="3">
+        <v>45947</v>
+      </c>
+      <c r="H350" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="I350" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="J350" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="K350" s="9"/>
-      <c r="L350" s="4"/>
-      <c r="M350" s="4"/>
-      <c r="N350" s="6"/>
-    </row>
-    <row r="351" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G351" s="4"/>
-      <c r="H351" s="4"/>
-      <c r="I351" s="6"/>
-      <c r="J351" s="4"/>
-      <c r="K351" s="9"/>
-      <c r="L351" s="4"/>
-      <c r="M351" s="4"/>
-      <c r="N351" s="6"/>
-    </row>
-    <row r="352" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G352" s="4"/>
-      <c r="H352" s="4"/>
-      <c r="I352" s="6"/>
-      <c r="J352" s="4"/>
-      <c r="K352" s="9"/>
-      <c r="L352" s="4"/>
-      <c r="M352" s="4"/>
-      <c r="N352" s="6"/>
+      <c r="L350" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M350" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N350" s="6">
+        <v>1</v>
+      </c>
+      <c r="O350"/>
+    </row>
+    <row r="351" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G351" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H351" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I351" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J351" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K351" s="9">
+        <v>220</v>
+      </c>
+      <c r="L351" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="M351" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N351" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G352" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H352" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I352" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J352" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K352" s="9">
+        <v>159</v>
+      </c>
+      <c r="L352" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M352" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N352" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="353" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G353" s="4"/>
-      <c r="H353" s="4"/>
-      <c r="I353" s="6"/>
-      <c r="J353" s="4"/>
-      <c r="K353" s="9"/>
-      <c r="L353" s="4"/>
-      <c r="M353" s="4"/>
-      <c r="N353" s="6"/>
+      <c r="G353" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H353" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I353" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="J353" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="K353" s="9">
+        <v>160</v>
+      </c>
+      <c r="L353" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="M353" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N353" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="354" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G354" s="4"/>
-      <c r="H354" s="4"/>
-      <c r="I354" s="6"/>
-      <c r="J354" s="4"/>
-      <c r="K354" s="9"/>
-      <c r="L354" s="4"/>
-      <c r="M354" s="4"/>
-      <c r="N354" s="6"/>
+      <c r="G354" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H354" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I354" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J354" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K354" s="9">
+        <v>250</v>
+      </c>
+      <c r="L354" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="M354" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N354" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="355" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G355" s="4"/>
-      <c r="H355" s="4"/>
-      <c r="I355" s="6"/>
-      <c r="J355" s="4"/>
-      <c r="K355" s="9"/>
-      <c r="L355" s="4"/>
-      <c r="M355" s="4"/>
-      <c r="N355" s="6"/>
+      <c r="G355" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H355" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I355" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="J355" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K355" s="9">
+        <v>220</v>
+      </c>
+      <c r="L355" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M355" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N355" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="356" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G356" s="4"/>
-      <c r="H356" s="4"/>
-      <c r="I356" s="6"/>
-      <c r="J356" s="4"/>
-      <c r="K356" s="9"/>
-      <c r="L356" s="4"/>
-      <c r="M356" s="4"/>
-      <c r="N356" s="6"/>
+      <c r="G356" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H356" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I356" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J356" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K356" s="9">
+        <v>180</v>
+      </c>
+      <c r="L356" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M356" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N356" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="357" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G357" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H357" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I357" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="J357" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K357" s="9">
+        <v>175</v>
+      </c>
+      <c r="L357" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M357" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N357" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G358" s="3"/>
+      <c r="H358" s="4"/>
+      <c r="I358" s="6"/>
+      <c r="J358" s="4"/>
+      <c r="K358" s="9"/>
+      <c r="L358" s="4"/>
+      <c r="M358" s="4"/>
+      <c r="N358" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G359" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H359" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I359" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J359" s="4"/>
+      <c r="K359" s="9"/>
+      <c r="L359" s="4"/>
+      <c r="M359" s="4"/>
+      <c r="N359" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="360" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G360" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H360" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I360" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J360" s="4"/>
+      <c r="K360" s="9"/>
+      <c r="L360" s="4"/>
+      <c r="M360" s="4"/>
+      <c r="N360" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="361" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G361" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I361" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J361" s="4"/>
+      <c r="K361" s="9"/>
+      <c r="L361" s="4"/>
+      <c r="M361" s="4"/>
+      <c r="N361" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="362" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G362" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H362" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I362" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J362" s="4"/>
+      <c r="K362" s="9"/>
+      <c r="L362" s="4"/>
+      <c r="M362" s="4"/>
+      <c r="N362" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G363" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H363" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I363" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J363" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K363" s="9">
+        <v>160</v>
+      </c>
+      <c r="L363" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M363" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N363" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G364" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H364" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I364" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J364" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K364" s="9">
+        <v>160</v>
+      </c>
+      <c r="L364" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="M364" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N364" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G365" s="4"/>
+      <c r="H365" s="4"/>
+      <c r="I365" s="6"/>
+      <c r="J365" s="4"/>
+      <c r="K365" s="9"/>
+      <c r="L365" s="4"/>
+      <c r="M365" s="4"/>
+      <c r="N365" s="6"/>
+    </row>
+    <row r="366" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G366" s="4"/>
+      <c r="H366" s="4"/>
+      <c r="I366" s="6"/>
+      <c r="J366" s="4"/>
+      <c r="K366" s="9"/>
+      <c r="L366" s="4"/>
+      <c r="M366" s="4"/>
+      <c r="N366" s="6"/>
+    </row>
+    <row r="367" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G367" s="4"/>
+      <c r="H367" s="4"/>
+      <c r="I367" s="6"/>
+      <c r="J367" s="4"/>
+      <c r="K367" s="9"/>
+      <c r="L367" s="4"/>
+      <c r="M367" s="4"/>
+      <c r="N367" s="6"/>
+    </row>
+    <row r="368" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G368" s="4"/>
+      <c r="H368" s="4"/>
+      <c r="I368" s="6"/>
+      <c r="J368" s="4"/>
+      <c r="K368" s="9"/>
+      <c r="L368" s="4"/>
+      <c r="M368" s="4"/>
+      <c r="N368" s="6"/>
+    </row>
+    <row r="369" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G369" s="4"/>
+      <c r="H369" s="4"/>
+      <c r="I369" s="6"/>
+      <c r="J369" s="4"/>
+      <c r="K369" s="9"/>
+      <c r="L369" s="4"/>
+      <c r="M369" s="4"/>
+      <c r="N369" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N347" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N364" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
     <sortCondition ref="G6:G339"/>
   </sortState>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2158" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C511DE0-C4CA-4B4D-9DF8-A873E18EE2FB}"/>
+  <xr:revisionPtr revIDLastSave="2166" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECB91BB1-8156-4A16-82D1-4CD0A7B86BAD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="256">
   <si>
     <t>DATA</t>
   </si>
@@ -803,6 +803,9 @@
   </si>
   <si>
     <t>JOSE ARILDO</t>
+  </si>
+  <si>
+    <t>TRES PONTAS</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1">
+  <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="G5:O369"/>
@@ -1349,7 +1352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1376,7 +1379,7 @@
       </c>
       <c r="O6"/>
     </row>
-    <row r="7" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1403,7 +1406,7 @@
       </c>
       <c r="O7"/>
     </row>
-    <row r="8" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1430,7 +1433,7 @@
       </c>
       <c r="O8"/>
     </row>
-    <row r="9" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1457,7 +1460,7 @@
       </c>
       <c r="O9"/>
     </row>
-    <row r="10" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1484,7 +1487,7 @@
       </c>
       <c r="O10"/>
     </row>
-    <row r="11" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1511,7 +1514,7 @@
       </c>
       <c r="O11"/>
     </row>
-    <row r="12" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1538,7 +1541,7 @@
       </c>
       <c r="O12"/>
     </row>
-    <row r="13" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1565,7 +1568,7 @@
       </c>
       <c r="O13"/>
     </row>
-    <row r="14" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1592,7 +1595,7 @@
       </c>
       <c r="O14"/>
     </row>
-    <row r="15" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1619,7 +1622,7 @@
       </c>
       <c r="O15"/>
     </row>
-    <row r="16" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1646,7 +1649,7 @@
       </c>
       <c r="O16"/>
     </row>
-    <row r="17" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1672,7 +1675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1698,7 +1701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1724,7 +1727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1776,7 +1779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1802,7 +1805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1828,7 +1831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1854,7 +1857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1906,7 +1909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1932,7 +1935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -1984,7 +1987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -2036,7 +2039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2062,7 +2065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2088,7 +2091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2140,7 +2143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2166,7 +2169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2192,7 +2195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2218,7 +2221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2244,7 +2247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2270,7 +2273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2322,7 +2325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2348,7 +2351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2400,7 +2403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2426,7 +2429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2452,7 +2455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2478,7 +2481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2530,7 +2533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2582,7 +2585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2608,7 +2611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2634,7 +2637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2660,7 +2663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2712,7 +2715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2738,7 +2741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2764,7 +2767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2790,7 +2793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2816,7 +2819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2842,7 +2845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2868,7 +2871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2894,7 +2897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2920,7 +2923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2946,7 +2949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2972,7 +2975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -2998,7 +3001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -3024,7 +3027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3050,7 +3053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3076,7 +3079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3102,7 +3105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3128,7 +3131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3154,7 +3157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3180,7 +3183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3232,7 +3235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3258,7 +3261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3284,7 +3287,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3310,7 +3313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3336,7 +3339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3362,7 +3365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3388,7 +3391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3414,7 +3417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3440,7 +3443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3466,7 +3469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3492,7 +3495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3518,7 +3521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3544,7 +3547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3570,7 +3573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3594,7 +3597,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3620,7 +3623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3672,7 +3675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3698,7 +3701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3724,7 +3727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3750,7 +3753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3776,7 +3779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3802,7 +3805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3828,7 +3831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3854,7 +3857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3880,7 +3883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3906,7 +3909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3932,7 +3935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3958,7 +3961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -3984,7 +3987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -4010,7 +4013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -4036,7 +4039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4062,7 +4065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4088,7 +4091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4114,7 +4117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4140,7 +4143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4166,7 +4169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4192,7 +4195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4218,7 +4221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4270,7 +4273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4296,7 +4299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4322,7 +4325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4348,7 +4351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4374,7 +4377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4400,7 +4403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4426,7 +4429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4452,7 +4455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4478,7 +4481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4504,7 +4507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4530,7 +4533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4556,7 +4559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4582,7 +4585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4608,7 +4611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4634,7 +4637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4660,7 +4663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4686,7 +4689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4712,7 +4715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4738,7 +4741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4790,7 +4793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4816,7 +4819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4842,7 +4845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4866,7 +4869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4892,7 +4895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4916,7 +4919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45903</v>
       </c>
@@ -4942,7 +4945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -4968,7 +4971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -4994,7 +4997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -5020,7 +5023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -5046,7 +5049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5072,7 +5075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5098,7 +5101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5124,7 +5127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5150,7 +5153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45904</v>
       </c>
@@ -5176,7 +5179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5202,7 +5205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5228,7 +5231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5254,7 +5257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45908</v>
       </c>
@@ -5280,7 +5283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5306,7 +5309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5332,7 +5335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5358,7 +5361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5384,7 +5387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5410,7 +5413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45909</v>
       </c>
@@ -5436,7 +5439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5462,7 +5465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5482,7 +5485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5508,7 +5511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5534,7 +5537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5560,7 +5563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5586,7 +5589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45910</v>
       </c>
@@ -5612,7 +5615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5632,7 +5635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5658,7 +5661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5684,7 +5687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5710,7 +5713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5736,7 +5739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5762,7 +5765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5788,7 +5791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5814,7 +5817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5840,7 +5843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5866,7 +5869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5892,7 +5895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5918,7 +5921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45911</v>
       </c>
@@ -5944,7 +5947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -5970,7 +5973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -5996,7 +5999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -6048,7 +6051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6074,7 +6077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6100,7 +6103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45915</v>
       </c>
@@ -6126,7 +6129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6152,7 +6155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6178,7 +6181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6204,7 +6207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6230,7 +6233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45916</v>
       </c>
@@ -6256,7 +6259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6334,7 +6337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6360,7 +6363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6386,7 +6389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6412,7 +6415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45917</v>
       </c>
@@ -6438,7 +6441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6464,7 +6467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6490,7 +6493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6516,7 +6519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6542,7 +6545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6568,7 +6571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6594,7 +6597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6620,7 +6623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6646,7 +6649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6672,7 +6675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6698,7 +6701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6718,7 +6721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6744,7 +6747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45918</v>
       </c>
@@ -6770,7 +6773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6796,7 +6799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6848,7 +6851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6874,7 +6877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6900,7 +6903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6926,7 +6929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45922</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -6978,7 +6981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -7004,7 +7007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -7030,7 +7033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -7056,7 +7059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7082,7 +7085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45923</v>
       </c>
@@ -7108,7 +7111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7134,7 +7137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7160,7 +7163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7186,7 +7189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7212,7 +7215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7238,7 +7241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7264,7 +7267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7290,7 +7293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45924</v>
       </c>
@@ -7316,7 +7319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7342,7 +7345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7368,7 +7371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7394,7 +7397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7420,7 +7423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7446,7 +7449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7472,7 +7475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7498,7 +7501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7524,7 +7527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7550,7 +7553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45925</v>
       </c>
@@ -7576,7 +7579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7602,7 +7605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7628,7 +7631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7654,7 +7657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7680,7 +7683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7706,7 +7709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7732,7 +7735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7758,7 +7761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45929</v>
       </c>
@@ -7784,7 +7787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7810,7 +7813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7836,7 +7839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7862,7 +7865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7888,7 +7891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7914,7 +7917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45930</v>
       </c>
@@ -7940,7 +7943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -7966,7 +7969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -7992,7 +7995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -8018,7 +8021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8044,7 +8047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8070,7 +8073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8096,7 +8099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8122,7 +8125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
@@ -8148,7 +8151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8174,7 +8177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8200,7 +8203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8226,7 +8229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8252,7 +8255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8278,7 +8281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8305,7 +8308,7 @@
       </c>
       <c r="O273" s="19"/>
     </row>
-    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8332,7 +8335,7 @@
       </c>
       <c r="O274"/>
     </row>
-    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8359,7 +8362,7 @@
       </c>
       <c r="O275"/>
     </row>
-    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8386,7 +8389,7 @@
       </c>
       <c r="O276"/>
     </row>
-    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8413,7 +8416,7 @@
       </c>
       <c r="O277"/>
     </row>
-    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
@@ -8440,7 +8443,7 @@
       </c>
       <c r="O278"/>
     </row>
-    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8467,7 +8470,7 @@
       </c>
       <c r="O279"/>
     </row>
-    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8494,7 +8497,7 @@
       </c>
       <c r="O280"/>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8521,7 +8524,7 @@
       </c>
       <c r="O281"/>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8548,7 +8551,7 @@
       </c>
       <c r="O282"/>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8575,7 +8578,7 @@
       </c>
       <c r="O283"/>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8602,7 +8605,7 @@
       </c>
       <c r="O284"/>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8629,7 +8632,7 @@
       </c>
       <c r="O285"/>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8656,7 +8659,7 @@
       </c>
       <c r="O286"/>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8683,7 +8686,7 @@
       </c>
       <c r="O287"/>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8710,7 +8713,7 @@
       </c>
       <c r="O288"/>
     </row>
-    <row r="289" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8736,7 +8739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8762,7 +8765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8788,7 +8791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8814,7 +8817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8840,7 +8843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8866,7 +8869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8892,7 +8895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8918,7 +8921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -8944,7 +8947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -8970,7 +8973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -8996,7 +8999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -9022,7 +9025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9048,7 +9051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
@@ -9074,7 +9077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
@@ -9100,7 +9103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
@@ -9126,7 +9129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
@@ -9152,7 +9155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
@@ -9178,7 +9181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
@@ -9204,7 +9207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
@@ -9230,7 +9233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
@@ -9256,7 +9259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9282,7 +9285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9308,7 +9311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9334,7 +9337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9360,7 +9363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9386,7 +9389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9412,7 +9415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45940</v>
       </c>
@@ -9438,7 +9441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
@@ -9464,7 +9467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
@@ -9490,7 +9493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
@@ -9516,7 +9519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
@@ -9542,7 +9545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
@@ -9568,7 +9571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45943</v>
       </c>
@@ -9594,7 +9597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
@@ -9620,7 +9623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
@@ -9646,7 +9649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
@@ -9672,7 +9675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
@@ -9698,7 +9701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
@@ -9724,7 +9727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
@@ -9750,7 +9753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G329" s="20">
         <v>45944</v>
       </c>
@@ -9776,7 +9779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
@@ -9802,7 +9805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
@@ -9828,7 +9831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
@@ -9854,7 +9857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
@@ -9880,7 +9883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
@@ -9906,7 +9909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
@@ -9932,7 +9935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
@@ -9958,7 +9961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G337" s="3">
         <v>45946</v>
       </c>
@@ -9985,7 +9988,7 @@
       </c>
       <c r="O337"/>
     </row>
-    <row r="338" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G338" s="3">
         <v>45946</v>
       </c>
@@ -10012,7 +10015,7 @@
       </c>
       <c r="O338"/>
     </row>
-    <row r="339" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G339" s="3">
         <v>45946</v>
       </c>
@@ -10039,7 +10042,7 @@
       </c>
       <c r="O339"/>
     </row>
-    <row r="340" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G340" s="3">
         <v>45946</v>
       </c>
@@ -10066,7 +10069,7 @@
       </c>
       <c r="O340"/>
     </row>
-    <row r="341" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G341" s="3">
         <v>45946</v>
       </c>
@@ -10093,7 +10096,7 @@
       </c>
       <c r="O341"/>
     </row>
-    <row r="342" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G342" s="3">
         <v>45946</v>
       </c>
@@ -10120,7 +10123,7 @@
       </c>
       <c r="O342"/>
     </row>
-    <row r="343" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G343" s="3">
         <v>45946</v>
       </c>
@@ -10147,7 +10150,7 @@
       </c>
       <c r="O343"/>
     </row>
-    <row r="344" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G344" s="3">
         <v>45946</v>
       </c>
@@ -10174,7 +10177,7 @@
       </c>
       <c r="O344"/>
     </row>
-    <row r="345" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G345" s="3">
         <v>45946</v>
       </c>
@@ -10201,7 +10204,7 @@
       </c>
       <c r="O345"/>
     </row>
-    <row r="346" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G346" s="3">
         <v>45946</v>
       </c>
@@ -10228,7 +10231,7 @@
       </c>
       <c r="O346"/>
     </row>
-    <row r="347" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G347" s="3">
         <v>45946</v>
       </c>
@@ -10255,7 +10258,7 @@
       </c>
       <c r="O347"/>
     </row>
-    <row r="348" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G348" s="3">
         <v>45946</v>
       </c>
@@ -10282,7 +10285,7 @@
       </c>
       <c r="O348"/>
     </row>
-    <row r="349" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G349" s="3">
         <v>45946</v>
       </c>
@@ -10309,7 +10312,7 @@
       </c>
       <c r="O349"/>
     </row>
-    <row r="350" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G350" s="3">
         <v>45947</v>
       </c>
@@ -10334,7 +10337,7 @@
       </c>
       <c r="O350"/>
     </row>
-    <row r="351" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G351" s="3">
         <v>45950</v>
       </c>
@@ -10360,7 +10363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G352" s="3">
         <v>45950</v>
       </c>
@@ -10386,7 +10389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G353" s="3">
         <v>45950</v>
       </c>
@@ -10412,7 +10415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G354" s="3">
         <v>45950</v>
       </c>
@@ -10438,7 +10441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G355" s="3">
         <v>45950</v>
       </c>
@@ -10464,7 +10467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G356" s="3">
         <v>45950</v>
       </c>
@@ -10490,7 +10493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G357" s="3">
         <v>45950</v>
       </c>
@@ -10516,7 +10519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="358" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G358" s="3"/>
       <c r="H358" s="4"/>
       <c r="I358" s="6"/>
@@ -10556,10 +10559,18 @@
       <c r="I360" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J360" s="4"/>
-      <c r="K360" s="9"/>
-      <c r="L360" s="4"/>
-      <c r="M360" s="4"/>
+      <c r="J360" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="K360" s="9">
+        <v>270</v>
+      </c>
+      <c r="L360" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M360" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N360" s="6">
         <v>3</v>
       </c>
@@ -10653,11 +10664,15 @@
       </c>
     </row>
     <row r="365" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G365" s="4"/>
+      <c r="G365" s="3">
+        <v>45948</v>
+      </c>
       <c r="H365" s="4"/>
       <c r="I365" s="6"/>
       <c r="J365" s="4"/>
-      <c r="K365" s="9"/>
+      <c r="K365" s="9">
+        <v>1000</v>
+      </c>
       <c r="L365" s="4"/>
       <c r="M365" s="4"/>
       <c r="N365" s="6"/>
@@ -10703,7 +10718,13 @@
       <c r="N369" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N364" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N364" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2025" month="10" day="21" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
     <sortCondition ref="G6:G339"/>
   </sortState>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2166" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECB91BB1-8156-4A16-82D1-4CD0A7B86BAD}"/>
+  <xr:revisionPtr revIDLastSave="2243" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{417CC8B5-5817-4CD0-A8C7-D250162FDD8A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$372</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="256">
   <si>
     <t>DATA</t>
   </si>
@@ -1312,7 +1312,7 @@
   <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O369"/>
+  <dimension ref="G5:O375"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -10325,7 +10325,9 @@
       <c r="J350" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K350" s="9"/>
+      <c r="K350" s="9">
+        <v>259</v>
+      </c>
       <c r="L350" s="4" t="s">
         <v>90</v>
       </c>
@@ -10527,11 +10529,9 @@
       <c r="K358" s="9"/>
       <c r="L358" s="4"/>
       <c r="M358" s="4"/>
-      <c r="N358" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="359" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="N358" s="6"/>
+    </row>
+    <row r="359" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G359" s="3">
         <v>45951</v>
       </c>
@@ -10541,15 +10541,23 @@
       <c r="I359" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="J359" s="4"/>
-      <c r="K359" s="9"/>
-      <c r="L359" s="4"/>
-      <c r="M359" s="4"/>
+      <c r="J359" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K359" s="9">
+        <v>240</v>
+      </c>
+      <c r="L359" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M359" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N359" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G360" s="3">
         <v>45951</v>
       </c>
@@ -10575,7 +10583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="361" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G361" s="3">
         <v>45951</v>
       </c>
@@ -10585,15 +10593,23 @@
       <c r="I361" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J361" s="4"/>
-      <c r="K361" s="9"/>
-      <c r="L361" s="4"/>
-      <c r="M361" s="4"/>
+      <c r="J361" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K361" s="9">
+        <v>200</v>
+      </c>
+      <c r="L361" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="M361" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N361" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G362" s="3">
         <v>45951</v>
       </c>
@@ -10603,15 +10619,23 @@
       <c r="I362" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="J362" s="4"/>
-      <c r="K362" s="9"/>
-      <c r="L362" s="4"/>
-      <c r="M362" s="4"/>
+      <c r="J362" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K362" s="9">
+        <v>280</v>
+      </c>
+      <c r="L362" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M362" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N362" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G363" s="3">
         <v>45951</v>
       </c>
@@ -10637,7 +10661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="G364" s="3">
         <v>45951</v>
       </c>
@@ -10665,63 +10689,209 @@
     </row>
     <row r="365" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G365" s="3">
-        <v>45948</v>
-      </c>
-      <c r="H365" s="4"/>
-      <c r="I365" s="6"/>
+        <v>45952</v>
+      </c>
+      <c r="H365" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I365" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="J365" s="4"/>
-      <c r="K365" s="9">
-        <v>1000</v>
-      </c>
+      <c r="K365" s="9"/>
       <c r="L365" s="4"/>
       <c r="M365" s="4"/>
-      <c r="N365" s="6"/>
+      <c r="N365" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="366" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G366" s="4"/>
-      <c r="H366" s="4"/>
-      <c r="I366" s="6"/>
-      <c r="J366" s="4"/>
-      <c r="K366" s="9"/>
-      <c r="L366" s="4"/>
-      <c r="M366" s="4"/>
-      <c r="N366" s="6"/>
+      <c r="G366" s="3">
+        <v>45952</v>
+      </c>
+      <c r="H366" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I366" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J366" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K366" s="9">
+        <v>160</v>
+      </c>
+      <c r="L366" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="M366" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N366" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="367" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G367" s="4"/>
-      <c r="H367" s="4"/>
-      <c r="I367" s="6"/>
+      <c r="G367" s="3">
+        <v>45952</v>
+      </c>
+      <c r="H367" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I367" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="J367" s="4"/>
       <c r="K367" s="9"/>
       <c r="L367" s="4"/>
       <c r="M367" s="4"/>
-      <c r="N367" s="6"/>
+      <c r="N367" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="368" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G368" s="4"/>
-      <c r="H368" s="4"/>
-      <c r="I368" s="6"/>
-      <c r="J368" s="4"/>
-      <c r="K368" s="9"/>
-      <c r="L368" s="4"/>
-      <c r="M368" s="4"/>
-      <c r="N368" s="6"/>
+      <c r="G368" s="3">
+        <v>45952</v>
+      </c>
+      <c r="H368" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I368" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J368" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K368" s="9">
+        <v>170</v>
+      </c>
+      <c r="L368" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="M368" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N368" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="369" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G369" s="4"/>
-      <c r="H369" s="4"/>
-      <c r="I369" s="6"/>
+      <c r="G369" s="3">
+        <v>45952</v>
+      </c>
+      <c r="H369" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I369" s="6" t="s">
+        <v>178</v>
+      </c>
       <c r="J369" s="4"/>
       <c r="K369" s="9"/>
       <c r="L369" s="4"/>
       <c r="M369" s="4"/>
-      <c r="N369" s="6"/>
+      <c r="N369" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G370" s="3">
+        <v>45952</v>
+      </c>
+      <c r="H370" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I370" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J370" s="4"/>
+      <c r="K370" s="9"/>
+      <c r="L370" s="4"/>
+      <c r="M370" s="4"/>
+      <c r="N370" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="371" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G371" s="3">
+        <v>45952</v>
+      </c>
+      <c r="H371" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I371" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J371" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K371" s="9"/>
+      <c r="L371" s="4"/>
+      <c r="M371" s="4"/>
+      <c r="N371" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G372" s="3">
+        <v>45952</v>
+      </c>
+      <c r="H372" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I372" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="J372" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K372" s="9">
+        <v>220</v>
+      </c>
+      <c r="L372" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M372" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N372" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="373" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G373" s="4"/>
+      <c r="H373" s="4"/>
+      <c r="I373" s="6"/>
+      <c r="J373" s="4"/>
+      <c r="K373" s="9"/>
+      <c r="L373" s="4"/>
+      <c r="M373" s="4"/>
+      <c r="N373" s="6"/>
+    </row>
+    <row r="374" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G374" s="4"/>
+      <c r="H374" s="4"/>
+      <c r="I374" s="6"/>
+      <c r="J374" s="4"/>
+      <c r="K374" s="9"/>
+      <c r="L374" s="4"/>
+      <c r="M374" s="4"/>
+      <c r="N374" s="6"/>
+    </row>
+    <row r="375" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G375" s="4"/>
+      <c r="H375" s="4"/>
+      <c r="I375" s="6"/>
+      <c r="J375" s="4"/>
+      <c r="K375" s="9"/>
+      <c r="L375" s="4"/>
+      <c r="M375" s="4"/>
+      <c r="N375" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N364" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:N372" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="10" day="21" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="22" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2243" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{417CC8B5-5817-4CD0-A8C7-D250162FDD8A}"/>
+  <xr:revisionPtr revIDLastSave="2295" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A02DA4-45F1-47F9-9B61-F6E7269EF944}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="262">
   <si>
     <t>DATA</t>
   </si>
@@ -806,6 +806,24 @@
   </si>
   <si>
     <t>TRES PONTAS</t>
+  </si>
+  <si>
+    <t>HOTEL AGUAS CLARAS</t>
+  </si>
+  <si>
+    <t>RAYNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRÊS MARIAS </t>
+  </si>
+  <si>
+    <t>HOTEL MAR DE MINAS</t>
+  </si>
+  <si>
+    <t>NÃO PLANEJADA</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -896,7 +914,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -904,7 +924,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -954,9 +974,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -974,6 +991,9 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1312,7 +1332,7 @@
   <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O375"/>
+  <dimension ref="G5:O374"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1323,7 +1343,7 @@
     <col min="12" max="12" width="28.28515625" style="1" customWidth="1"/>
     <col min="13" max="13" width="14.28515625" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" customWidth="1"/>
-    <col min="15" max="15" width="20.140625" style="25" customWidth="1"/>
+    <col min="15" max="15" width="20.140625" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="7:15" x14ac:dyDescent="0.25">
@@ -1351,6 +1371,9 @@
       <c r="N5" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="O5" s="26" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="6" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
@@ -5723,7 +5746,7 @@
       <c r="I174" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J174" s="24" t="s">
+      <c r="J174" s="23" t="s">
         <v>66</v>
       </c>
       <c r="K174" s="9">
@@ -7865,7 +7888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7890,8 +7913,9 @@
       <c r="N257" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="258" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O257"/>
+    </row>
+    <row r="258" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7916,8 +7940,9 @@
       <c r="N258" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="259" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O258"/>
+    </row>
+    <row r="259" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45930</v>
       </c>
@@ -7942,8 +7967,9 @@
       <c r="N259" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="260" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O259"/>
+    </row>
+    <row r="260" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -7968,8 +7994,9 @@
       <c r="N260" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="261" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O260" s="6"/>
+    </row>
+    <row r="261" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -7994,8 +8021,9 @@
       <c r="N261" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="262" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O261" s="6"/>
+    </row>
+    <row r="262" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -8020,8 +8048,9 @@
       <c r="N262" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="263" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O262" s="6"/>
+    </row>
+    <row r="263" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8046,8 +8075,9 @@
       <c r="N263" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="264" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O263" s="6"/>
+    </row>
+    <row r="264" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8072,8 +8102,9 @@
       <c r="N264" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="265" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O264" s="6"/>
+    </row>
+    <row r="265" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8098,8 +8129,9 @@
       <c r="N265" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="266" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O265" s="6"/>
+    </row>
+    <row r="266" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8124,8 +8156,9 @@
       <c r="N266" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="267" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O266" s="6"/>
+    </row>
+    <row r="267" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
@@ -8150,8 +8183,9 @@
       <c r="N267" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="268" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O267" s="6"/>
+    </row>
+    <row r="268" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8176,8 +8210,9 @@
       <c r="N268" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="269" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O268" s="6"/>
+    </row>
+    <row r="269" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8202,8 +8237,9 @@
       <c r="N269" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="270" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O269" s="6"/>
+    </row>
+    <row r="270" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8228,8 +8264,9 @@
       <c r="N270" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="271" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O270" s="6"/>
+    </row>
+    <row r="271" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8254,8 +8291,9 @@
       <c r="N271" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="272" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O271" s="6"/>
+    </row>
+    <row r="272" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8280,8 +8318,9 @@
       <c r="N272" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O272" s="6"/>
+    </row>
+    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8306,9 +8345,9 @@
       <c r="N273" s="6">
         <v>2</v>
       </c>
-      <c r="O273" s="19"/>
-    </row>
-    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O273" s="4"/>
+    </row>
+    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8333,9 +8372,9 @@
       <c r="N274" s="6">
         <v>2</v>
       </c>
-      <c r="O274"/>
-    </row>
-    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O274" s="6"/>
+    </row>
+    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8360,9 +8399,9 @@
       <c r="N275" s="6">
         <v>2</v>
       </c>
-      <c r="O275"/>
-    </row>
-    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O275" s="6"/>
+    </row>
+    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8387,9 +8426,9 @@
       <c r="N276" s="6">
         <v>2</v>
       </c>
-      <c r="O276"/>
-    </row>
-    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O276" s="6"/>
+    </row>
+    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8414,9 +8453,9 @@
       <c r="N277" s="6">
         <v>2</v>
       </c>
-      <c r="O277"/>
-    </row>
-    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O277" s="6"/>
+    </row>
+    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
@@ -8441,9 +8480,9 @@
       <c r="N278" s="6">
         <v>1</v>
       </c>
-      <c r="O278"/>
-    </row>
-    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O278" s="6"/>
+    </row>
+    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8468,9 +8507,9 @@
       <c r="N279" s="6">
         <v>1</v>
       </c>
-      <c r="O279"/>
-    </row>
-    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O279" s="6"/>
+    </row>
+    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8495,9 +8534,9 @@
       <c r="N280" s="6">
         <v>1</v>
       </c>
-      <c r="O280"/>
-    </row>
-    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O280" s="6"/>
+    </row>
+    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8510,7 +8549,7 @@
       <c r="J281" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K281" s="26">
+      <c r="K281" s="25">
         <v>220</v>
       </c>
       <c r="L281" s="4" t="s">
@@ -8522,9 +8561,9 @@
       <c r="N281" s="6">
         <v>2</v>
       </c>
-      <c r="O281"/>
-    </row>
-    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O281" s="6"/>
+    </row>
+    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8549,9 +8588,9 @@
       <c r="N282" s="6">
         <v>2</v>
       </c>
-      <c r="O282"/>
-    </row>
-    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O282" s="6"/>
+    </row>
+    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8576,9 +8615,9 @@
       <c r="N283" s="6">
         <v>2</v>
       </c>
-      <c r="O283"/>
-    </row>
-    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O283" s="6"/>
+    </row>
+    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8603,9 +8642,9 @@
       <c r="N284" s="6">
         <v>2</v>
       </c>
-      <c r="O284"/>
-    </row>
-    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O284" s="6"/>
+    </row>
+    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8630,9 +8669,9 @@
       <c r="N285" s="6">
         <v>2</v>
       </c>
-      <c r="O285"/>
-    </row>
-    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O285" s="6"/>
+    </row>
+    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8657,9 +8696,9 @@
       <c r="N286" s="6">
         <v>4</v>
       </c>
-      <c r="O286"/>
-    </row>
-    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O286" s="6"/>
+    </row>
+    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8684,9 +8723,9 @@
       <c r="N287" s="6">
         <v>1</v>
       </c>
-      <c r="O287"/>
-    </row>
-    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O287" s="6"/>
+    </row>
+    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8711,9 +8750,9 @@
       <c r="N288" s="6">
         <v>3</v>
       </c>
-      <c r="O288"/>
-    </row>
-    <row r="289" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O288" s="6"/>
+    </row>
+    <row r="289" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8738,8 +8777,9 @@
       <c r="N289" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="290" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O289" s="6"/>
+    </row>
+    <row r="290" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8764,8 +8804,9 @@
       <c r="N290" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="291" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O290" s="6"/>
+    </row>
+    <row r="291" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8790,8 +8831,9 @@
       <c r="N291" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="292" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O291" s="6"/>
+    </row>
+    <row r="292" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8816,8 +8858,9 @@
       <c r="N292" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="293" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O292" s="6"/>
+    </row>
+    <row r="293" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8842,8 +8885,9 @@
       <c r="N293" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="294" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O293" s="6"/>
+    </row>
+    <row r="294" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8868,8 +8912,9 @@
       <c r="N294" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="295" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O294" s="6"/>
+    </row>
+    <row r="295" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8894,8 +8939,9 @@
       <c r="N295" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="296" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O295" s="6"/>
+    </row>
+    <row r="296" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8920,8 +8966,9 @@
       <c r="N296" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="297" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O296" s="6"/>
+    </row>
+    <row r="297" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -8946,8 +8993,9 @@
       <c r="N297" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="298" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O297" s="6"/>
+    </row>
+    <row r="298" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -8972,8 +9020,9 @@
       <c r="N298" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="299" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O298" s="6"/>
+    </row>
+    <row r="299" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -8998,8 +9047,9 @@
       <c r="N299" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="300" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O299" s="6"/>
+    </row>
+    <row r="300" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -9024,8 +9074,9 @@
       <c r="N300" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="301" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O300" s="6"/>
+    </row>
+    <row r="301" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9050,8 +9101,9 @@
       <c r="N301" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="302" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O301" s="6"/>
+    </row>
+    <row r="302" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
@@ -9076,8 +9128,9 @@
       <c r="N302" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="303" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O302" s="6"/>
+    </row>
+    <row r="303" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
@@ -9102,8 +9155,9 @@
       <c r="N303" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="304" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O303" s="6"/>
+    </row>
+    <row r="304" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
@@ -9128,8 +9182,9 @@
       <c r="N304" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="305" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O304" s="6"/>
+    </row>
+    <row r="305" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
@@ -9154,8 +9209,9 @@
       <c r="N305" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="306" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O305" s="6"/>
+    </row>
+    <row r="306" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
@@ -9180,8 +9236,9 @@
       <c r="N306" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="307" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O306" s="6"/>
+    </row>
+    <row r="307" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
@@ -9191,7 +9248,7 @@
       <c r="I307" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="J307" s="24" t="s">
+      <c r="J307" s="23" t="s">
         <v>66</v>
       </c>
       <c r="K307" s="9">
@@ -9206,8 +9263,9 @@
       <c r="N307" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="308" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O307" s="6"/>
+    </row>
+    <row r="308" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
@@ -9232,8 +9290,9 @@
       <c r="N308" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="309" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O308" s="6"/>
+    </row>
+    <row r="309" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
@@ -9258,8 +9317,9 @@
       <c r="N309" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="310" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O309" s="6"/>
+    </row>
+    <row r="310" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9284,8 +9344,9 @@
       <c r="N310" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="311" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O310" s="6"/>
+    </row>
+    <row r="311" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9310,8 +9371,9 @@
       <c r="N311" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="312" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O311" s="6"/>
+    </row>
+    <row r="312" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9336,8 +9398,9 @@
       <c r="N312" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="313" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O312" s="6"/>
+    </row>
+    <row r="313" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9362,8 +9425,9 @@
       <c r="N313" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="314" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O313" s="6"/>
+    </row>
+    <row r="314" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9388,8 +9452,9 @@
       <c r="N314" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="315" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O314" s="6"/>
+    </row>
+    <row r="315" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9414,8 +9479,9 @@
       <c r="N315" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="316" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O315" s="6"/>
+    </row>
+    <row r="316" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
         <v>45940</v>
       </c>
@@ -9440,8 +9506,9 @@
       <c r="N316" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="317" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O316" s="6"/>
+    </row>
+    <row r="317" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
@@ -9466,8 +9533,9 @@
       <c r="N317" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="318" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O317" s="6"/>
+    </row>
+    <row r="318" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
@@ -9492,8 +9560,9 @@
       <c r="N318" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="319" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O318" s="6"/>
+    </row>
+    <row r="319" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
@@ -9518,8 +9587,9 @@
       <c r="N319" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="320" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O319" s="6"/>
+    </row>
+    <row r="320" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
@@ -9544,8 +9614,9 @@
       <c r="N320" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="321" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O320" s="6"/>
+    </row>
+    <row r="321" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
@@ -9570,8 +9641,9 @@
       <c r="N321" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="322" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O321" s="6"/>
+    </row>
+    <row r="322" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45943</v>
       </c>
@@ -9596,8 +9668,9 @@
       <c r="N322" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="323" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O322" s="6"/>
+    </row>
+    <row r="323" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
@@ -9622,8 +9695,9 @@
       <c r="N323" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="324" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O323" s="6"/>
+    </row>
+    <row r="324" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
@@ -9648,8 +9722,9 @@
       <c r="N324" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="325" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O324" s="6"/>
+    </row>
+    <row r="325" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
@@ -9674,8 +9749,9 @@
       <c r="N325" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="326" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O325" s="6"/>
+    </row>
+    <row r="326" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
@@ -9700,8 +9776,9 @@
       <c r="N326" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="327" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O326" s="6"/>
+    </row>
+    <row r="327" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
@@ -9726,8 +9803,9 @@
       <c r="N327" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="328" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O327" s="6"/>
+    </row>
+    <row r="328" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
@@ -9752,34 +9830,38 @@
       <c r="N328" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="329" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G329" s="20">
+      <c r="O328" s="6"/>
+    </row>
+    <row r="329" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G329" s="19">
         <v>45944</v>
       </c>
-      <c r="H329" s="21" t="s">
+      <c r="H329" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="I329" s="22" t="s">
+      <c r="I329" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="J329" s="21" t="s">
+      <c r="J329" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="K329" s="23">
+      <c r="K329" s="22">
         <v>180</v>
       </c>
-      <c r="L329" s="21" t="s">
+      <c r="L329" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="M329" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="N329" s="22">
+      <c r="M329" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="N329" s="21">
         <v>1</v>
       </c>
-    </row>
-    <row r="330" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O329" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
@@ -9804,8 +9886,9 @@
       <c r="N330" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="331" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O330" s="6"/>
+    </row>
+    <row r="331" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
@@ -9830,8 +9913,9 @@
       <c r="N331" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="332" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O331" s="6"/>
+    </row>
+    <row r="332" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
@@ -9856,8 +9940,9 @@
       <c r="N332" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="333" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O332" s="6"/>
+    </row>
+    <row r="333" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
@@ -9882,8 +9967,9 @@
       <c r="N333" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="334" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O333" s="6"/>
+    </row>
+    <row r="334" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
@@ -9908,8 +9994,9 @@
       <c r="N334" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="335" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O334" s="6"/>
+    </row>
+    <row r="335" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
@@ -9934,8 +10021,9 @@
       <c r="N335" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="336" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O335" s="6"/>
+    </row>
+    <row r="336" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
@@ -9960,8 +10048,9 @@
       <c r="N336" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="337" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O336" s="6"/>
+    </row>
+    <row r="337" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G337" s="3">
         <v>45946</v>
       </c>
@@ -9986,9 +10075,9 @@
       <c r="N337" s="6">
         <v>2</v>
       </c>
-      <c r="O337"/>
-    </row>
-    <row r="338" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O337" s="6"/>
+    </row>
+    <row r="338" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G338" s="3">
         <v>45946</v>
       </c>
@@ -10013,9 +10102,9 @@
       <c r="N338" s="6">
         <v>2</v>
       </c>
-      <c r="O338"/>
-    </row>
-    <row r="339" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O338" s="6"/>
+    </row>
+    <row r="339" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G339" s="3">
         <v>45946</v>
       </c>
@@ -10040,9 +10129,9 @@
       <c r="N339" s="6">
         <v>2</v>
       </c>
-      <c r="O339"/>
-    </row>
-    <row r="340" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O339" s="6"/>
+    </row>
+    <row r="340" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G340" s="3">
         <v>45946</v>
       </c>
@@ -10067,9 +10156,9 @@
       <c r="N340" s="6">
         <v>2</v>
       </c>
-      <c r="O340"/>
-    </row>
-    <row r="341" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O340" s="6"/>
+    </row>
+    <row r="341" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G341" s="3">
         <v>45946</v>
       </c>
@@ -10094,9 +10183,9 @@
       <c r="N341" s="6">
         <v>2</v>
       </c>
-      <c r="O341"/>
-    </row>
-    <row r="342" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O341" s="6"/>
+    </row>
+    <row r="342" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G342" s="3">
         <v>45946</v>
       </c>
@@ -10121,9 +10210,9 @@
       <c r="N342" s="6">
         <v>2</v>
       </c>
-      <c r="O342"/>
-    </row>
-    <row r="343" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O342" s="6"/>
+    </row>
+    <row r="343" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G343" s="3">
         <v>45946</v>
       </c>
@@ -10148,9 +10237,9 @@
       <c r="N343" s="6">
         <v>2</v>
       </c>
-      <c r="O343"/>
-    </row>
-    <row r="344" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O343" s="6"/>
+    </row>
+    <row r="344" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G344" s="3">
         <v>45946</v>
       </c>
@@ -10175,9 +10264,9 @@
       <c r="N344" s="6">
         <v>2</v>
       </c>
-      <c r="O344"/>
-    </row>
-    <row r="345" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O344" s="6"/>
+    </row>
+    <row r="345" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G345" s="3">
         <v>45946</v>
       </c>
@@ -10202,9 +10291,9 @@
       <c r="N345" s="6">
         <v>2</v>
       </c>
-      <c r="O345"/>
-    </row>
-    <row r="346" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O345" s="6"/>
+    </row>
+    <row r="346" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G346" s="3">
         <v>45946</v>
       </c>
@@ -10229,9 +10318,9 @@
       <c r="N346" s="6">
         <v>2</v>
       </c>
-      <c r="O346"/>
-    </row>
-    <row r="347" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O346" s="6"/>
+    </row>
+    <row r="347" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G347" s="3">
         <v>45946</v>
       </c>
@@ -10256,9 +10345,9 @@
       <c r="N347" s="6">
         <v>2</v>
       </c>
-      <c r="O347"/>
-    </row>
-    <row r="348" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O347" s="6"/>
+    </row>
+    <row r="348" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G348" s="3">
         <v>45946</v>
       </c>
@@ -10283,9 +10372,9 @@
       <c r="N348" s="6">
         <v>1</v>
       </c>
-      <c r="O348"/>
-    </row>
-    <row r="349" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O348" s="6"/>
+    </row>
+    <row r="349" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G349" s="3">
         <v>45946</v>
       </c>
@@ -10310,36 +10399,38 @@
       <c r="N349" s="6">
         <v>1</v>
       </c>
-      <c r="O349"/>
-    </row>
-    <row r="350" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G350" s="3">
+      <c r="O349" s="6"/>
+    </row>
+    <row r="350" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G350" s="19">
         <v>45947</v>
       </c>
-      <c r="H350" s="4" t="s">
+      <c r="H350" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="I350" s="6" t="s">
+      <c r="I350" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="J350" s="4" t="s">
+      <c r="J350" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K350" s="9">
+      <c r="K350" s="22">
         <v>259</v>
       </c>
-      <c r="L350" s="4" t="s">
+      <c r="L350" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="M350" s="4" t="s">
+      <c r="M350" s="20" t="s">
         <v>8</v>
       </c>
       <c r="N350" s="6">
         <v>1</v>
       </c>
-      <c r="O350"/>
-    </row>
-    <row r="351" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O350" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G351" s="3">
         <v>45950</v>
       </c>
@@ -10364,8 +10455,9 @@
       <c r="N351" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="352" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O351" s="27"/>
+    </row>
+    <row r="352" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G352" s="3">
         <v>45950</v>
       </c>
@@ -10390,8 +10482,9 @@
       <c r="N352" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="353" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O352" s="27"/>
+    </row>
+    <row r="353" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G353" s="3">
         <v>45950</v>
       </c>
@@ -10416,8 +10509,9 @@
       <c r="N353" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="354" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O353" s="27"/>
+    </row>
+    <row r="354" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G354" s="3">
         <v>45950</v>
       </c>
@@ -10442,8 +10536,9 @@
       <c r="N354" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="355" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O354" s="27"/>
+    </row>
+    <row r="355" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G355" s="3">
         <v>45950</v>
       </c>
@@ -10468,8 +10563,9 @@
       <c r="N355" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="356" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O355" s="27"/>
+    </row>
+    <row r="356" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G356" s="3">
         <v>45950</v>
       </c>
@@ -10494,8 +10590,9 @@
       <c r="N356" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="357" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O356" s="27"/>
+    </row>
+    <row r="357" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G357" s="3">
         <v>45950</v>
       </c>
@@ -10520,8 +10617,9 @@
       <c r="N357" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="358" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O357" s="27"/>
+    </row>
+    <row r="358" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G358" s="3"/>
       <c r="H358" s="4"/>
       <c r="I358" s="6"/>
@@ -10531,7 +10629,7 @@
       <c r="M358" s="4"/>
       <c r="N358" s="6"/>
     </row>
-    <row r="359" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G359" s="3">
         <v>45951</v>
       </c>
@@ -10556,8 +10654,9 @@
       <c r="N359" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="360" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O359" s="27"/>
+    </row>
+    <row r="360" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G360" s="3">
         <v>45951</v>
       </c>
@@ -10582,8 +10681,9 @@
       <c r="N360" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="361" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O360" s="27"/>
+    </row>
+    <row r="361" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G361" s="3">
         <v>45951</v>
       </c>
@@ -10608,8 +10708,9 @@
       <c r="N361" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="362" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O361" s="27"/>
+    </row>
+    <row r="362" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G362" s="3">
         <v>45951</v>
       </c>
@@ -10634,8 +10735,9 @@
       <c r="N362" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="363" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O362" s="27"/>
+    </row>
+    <row r="363" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G363" s="3">
         <v>45951</v>
       </c>
@@ -10660,8 +10762,9 @@
       <c r="N363" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="364" spans="7:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O363" s="27"/>
+    </row>
+    <row r="364" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G364" s="3">
         <v>45951</v>
       </c>
@@ -10686,8 +10789,9 @@
       <c r="N364" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="365" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O364" s="27"/>
+    </row>
+    <row r="365" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G365" s="3">
         <v>45952</v>
       </c>
@@ -10697,15 +10801,24 @@
       <c r="I365" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J365" s="4"/>
-      <c r="K365" s="9"/>
-      <c r="L365" s="4"/>
-      <c r="M365" s="4"/>
+      <c r="J365" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K365" s="9">
+        <v>218.9</v>
+      </c>
+      <c r="L365" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="M365" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N365" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="366" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O365" s="28"/>
+    </row>
+    <row r="366" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G366" s="3">
         <v>45952</v>
       </c>
@@ -10730,43 +10843,53 @@
       <c r="N366" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="367" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O366" s="27"/>
+    </row>
+    <row r="367" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G367" s="3">
         <v>45952</v>
       </c>
       <c r="H367" s="4" t="s">
-        <v>254</v>
+        <v>141</v>
       </c>
       <c r="I367" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J367" s="4"/>
-      <c r="K367" s="9"/>
-      <c r="L367" s="4"/>
-      <c r="M367" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="J367" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K367" s="9">
+        <v>170</v>
+      </c>
+      <c r="L367" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="M367" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N367" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="368" spans="7:14" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="O367" s="27"/>
+    </row>
+    <row r="368" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G368" s="3">
         <v>45952</v>
       </c>
       <c r="H368" s="4" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="I368" s="6" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K368" s="9">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="L368" s="4" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="M368" s="4" t="s">
         <v>8</v>
@@ -10774,90 +10897,119 @@
       <c r="N368" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="369" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O368" s="27"/>
+    </row>
+    <row r="369" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G369" s="3">
         <v>45952</v>
       </c>
       <c r="H369" s="4" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="I369" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J369" s="4"/>
-      <c r="K369" s="9"/>
-      <c r="L369" s="4"/>
-      <c r="M369" s="4"/>
+        <v>129</v>
+      </c>
+      <c r="J369" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K369" s="9">
+        <v>170</v>
+      </c>
+      <c r="L369" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="M369" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N369" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="370" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O369" s="27"/>
+    </row>
+    <row r="370" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G370" s="3">
         <v>45952</v>
       </c>
       <c r="H370" s="4" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="I370" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J370" s="4"/>
-      <c r="K370" s="9"/>
-      <c r="L370" s="4"/>
-      <c r="M370" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="J370" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K370" s="9">
+        <v>170</v>
+      </c>
+      <c r="L370" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M370" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N370" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="371" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O370" s="27"/>
+    </row>
+    <row r="371" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G371" s="3">
         <v>45952</v>
       </c>
       <c r="H371" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I371" s="6" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K371" s="9"/>
-      <c r="L371" s="4"/>
-      <c r="M371" s="4"/>
+        <v>234</v>
+      </c>
+      <c r="K371" s="9">
+        <v>220</v>
+      </c>
+      <c r="L371" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M371" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N371" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="372" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G372" s="3">
+      <c r="O371" s="27"/>
+    </row>
+    <row r="372" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G372" s="19">
         <v>45952</v>
       </c>
-      <c r="H372" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I372" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="J372" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="K372" s="9">
-        <v>220</v>
-      </c>
-      <c r="L372" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M372" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N372" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="373" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="H372" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="I372" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J372" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="K372" s="22">
+        <v>150</v>
+      </c>
+      <c r="L372" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="M372" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="N372" s="21">
+        <v>1</v>
+      </c>
+      <c r="O372" s="27" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="373" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G373" s="4"/>
       <c r="H373" s="4"/>
       <c r="I373" s="6"/>
@@ -10866,8 +11018,9 @@
       <c r="L373" s="4"/>
       <c r="M373" s="4"/>
       <c r="N373" s="6"/>
-    </row>
-    <row r="374" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="O373" s="27"/>
+    </row>
+    <row r="374" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G374" s="4"/>
       <c r="H374" s="4"/>
       <c r="I374" s="6"/>
@@ -10876,22 +11029,13 @@
       <c r="L374" s="4"/>
       <c r="M374" s="4"/>
       <c r="N374" s="6"/>
-    </row>
-    <row r="375" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G375" s="4"/>
-      <c r="H375" s="4"/>
-      <c r="I375" s="6"/>
-      <c r="J375" s="4"/>
-      <c r="K375" s="9"/>
-      <c r="L375" s="4"/>
-      <c r="M375" s="4"/>
-      <c r="N375" s="6"/>
+      <c r="O374" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="G5:N372" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="10" day="22" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2295" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A02DA4-45F1-47F9-9B61-F6E7269EF944}"/>
+  <xr:revisionPtr revIDLastSave="2391" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57400DA2-A8F2-4783-BE94-621E43F72E5B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$384</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="265">
   <si>
     <t>DATA</t>
   </si>
@@ -824,6 +824,15 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>HOTEL PAULISTA</t>
+  </si>
+  <si>
+    <t>HOTEL VITORIA</t>
+  </si>
+  <si>
+    <t>HOTEL BARBACENA</t>
   </si>
 </sst>
 </file>
@@ -870,7 +879,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -919,12 +928,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -994,6 +1016,7 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1329,10 +1352,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1" filterMode="1">
+  <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O374"/>
+  <dimension ref="G5:O386"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1375,7 +1398,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1402,7 +1425,7 @@
       </c>
       <c r="O6"/>
     </row>
-    <row r="7" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1429,7 +1452,7 @@
       </c>
       <c r="O7"/>
     </row>
-    <row r="8" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1456,7 +1479,7 @@
       </c>
       <c r="O8"/>
     </row>
-    <row r="9" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1483,7 +1506,7 @@
       </c>
       <c r="O9"/>
     </row>
-    <row r="10" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1510,7 +1533,7 @@
       </c>
       <c r="O10"/>
     </row>
-    <row r="11" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1537,7 +1560,7 @@
       </c>
       <c r="O11"/>
     </row>
-    <row r="12" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1564,7 +1587,7 @@
       </c>
       <c r="O12"/>
     </row>
-    <row r="13" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1591,7 +1614,7 @@
       </c>
       <c r="O13"/>
     </row>
-    <row r="14" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1618,7 +1641,7 @@
       </c>
       <c r="O14"/>
     </row>
-    <row r="15" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1645,7 +1668,7 @@
       </c>
       <c r="O15"/>
     </row>
-    <row r="16" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1672,7 +1695,7 @@
       </c>
       <c r="O16"/>
     </row>
-    <row r="17" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1698,7 +1721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1724,7 +1747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1750,7 +1773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1776,7 +1799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1802,7 +1825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1828,7 +1851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1854,7 +1877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1880,7 +1903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1906,7 +1929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1932,7 +1955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1958,7 +1981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -1984,7 +2007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -2010,7 +2033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -2036,7 +2059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -2062,7 +2085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2088,7 +2111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2114,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2140,7 +2163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2166,7 +2189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2192,7 +2215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2218,7 +2241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2244,7 +2267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2270,7 +2293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2296,7 +2319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2322,7 +2345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2348,7 +2371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2374,7 +2397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2400,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2426,7 +2449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2452,7 +2475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2478,7 +2501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2504,7 +2527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2530,7 +2553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2556,7 +2579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2582,7 +2605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2608,7 +2631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2634,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2660,7 +2683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2686,7 +2709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2712,7 +2735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2738,7 +2761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2764,7 +2787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2790,7 +2813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2816,7 +2839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2842,7 +2865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2868,7 +2891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2894,7 +2917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2920,7 +2943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2946,7 +2969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2972,7 +2995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -2998,7 +3021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -3024,7 +3047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -3050,7 +3073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3076,7 +3099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3102,7 +3125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3128,7 +3151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3154,7 +3177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3180,7 +3203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3206,7 +3229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3232,7 +3255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3258,7 +3281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3284,7 +3307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3310,7 +3333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3336,7 +3359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3362,7 +3385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3388,7 +3411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3414,7 +3437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3440,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3466,7 +3489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3492,7 +3515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3518,7 +3541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3544,7 +3567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3570,7 +3593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3596,7 +3619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3620,7 +3643,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3646,7 +3669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3672,7 +3695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3698,7 +3721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3724,7 +3747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3750,7 +3773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3776,7 +3799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3802,7 +3825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3828,7 +3851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3854,7 +3877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3880,7 +3903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3906,7 +3929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3932,7 +3955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3958,7 +3981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -3984,7 +4007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -4010,7 +4033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -4036,7 +4059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -4062,7 +4085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4088,7 +4111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4114,7 +4137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4140,7 +4163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4166,7 +4189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4192,7 +4215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4218,7 +4241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4244,7 +4267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4270,7 +4293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4296,7 +4319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4322,7 +4345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4348,7 +4371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4374,7 +4397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4400,7 +4423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4426,7 +4449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4452,7 +4475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4478,7 +4501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4504,7 +4527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4530,7 +4553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4556,7 +4579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4582,7 +4605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4608,7 +4631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4634,7 +4657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4660,7 +4683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4686,7 +4709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4712,7 +4735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4738,7 +4761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4764,7 +4787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4790,7 +4813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4816,7 +4839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4842,7 +4865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4868,7 +4891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4892,7 +4915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4918,7 +4941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4942,7 +4965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45903</v>
       </c>
@@ -4968,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -4994,7 +5017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -5020,7 +5043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -5046,7 +5069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -5072,7 +5095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5098,7 +5121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5124,7 +5147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5150,7 +5173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5176,7 +5199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45904</v>
       </c>
@@ -5202,7 +5225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5228,7 +5251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5254,7 +5277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5280,7 +5303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45908</v>
       </c>
@@ -5306,7 +5329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5332,7 +5355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5358,7 +5381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5384,7 +5407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5410,7 +5433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5436,7 +5459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45909</v>
       </c>
@@ -5462,7 +5485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5488,7 +5511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5508,7 +5531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5534,7 +5557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5560,7 +5583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5586,7 +5609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5612,7 +5635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45910</v>
       </c>
@@ -5638,7 +5661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5658,7 +5681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5684,7 +5707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5710,7 +5733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5736,7 +5759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5762,7 +5785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5788,7 +5811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5814,7 +5837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5840,7 +5863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5866,7 +5889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5892,7 +5915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5918,7 +5941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5944,7 +5967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45911</v>
       </c>
@@ -5970,7 +5993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -5996,7 +6019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -6022,7 +6045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -6048,7 +6071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -6074,7 +6097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6100,7 +6123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6126,7 +6149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45915</v>
       </c>
@@ -6152,7 +6175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6178,7 +6201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6204,7 +6227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6230,7 +6253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6256,7 +6279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45916</v>
       </c>
@@ -6282,7 +6305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6308,7 +6331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6334,7 +6357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6360,7 +6383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6386,7 +6409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6412,7 +6435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6438,7 +6461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45917</v>
       </c>
@@ -6464,7 +6487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6490,7 +6513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6516,7 +6539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6542,7 +6565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6568,7 +6591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6594,7 +6617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6620,7 +6643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6646,7 +6669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6672,7 +6695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6698,7 +6721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6724,7 +6747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6744,7 +6767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6770,7 +6793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45918</v>
       </c>
@@ -6796,7 +6819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6822,7 +6845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6848,7 +6871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6874,7 +6897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6900,7 +6923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6926,7 +6949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6952,7 +6975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45922</v>
       </c>
@@ -6978,7 +7001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -7004,7 +7027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -7030,7 +7053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -7056,7 +7079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -7082,7 +7105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7108,7 +7131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45923</v>
       </c>
@@ -7134,7 +7157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7160,7 +7183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7186,7 +7209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7212,7 +7235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7238,7 +7261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7264,7 +7287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7290,7 +7313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7316,7 +7339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45924</v>
       </c>
@@ -7342,7 +7365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7368,7 +7391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7394,7 +7417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7420,7 +7443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7446,7 +7469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7472,7 +7495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7498,7 +7521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7524,7 +7547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7550,7 +7573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7576,7 +7599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45925</v>
       </c>
@@ -7602,7 +7625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7628,7 +7651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7654,7 +7677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7680,7 +7703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7706,7 +7729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7732,7 +7755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7758,7 +7781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7784,7 +7807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45929</v>
       </c>
@@ -7810,7 +7833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7836,7 +7859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7862,7 +7885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7888,7 +7911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7915,7 +7938,7 @@
       </c>
       <c r="O257"/>
     </row>
-    <row r="258" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7942,7 +7965,7 @@
       </c>
       <c r="O258"/>
     </row>
-    <row r="259" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45930</v>
       </c>
@@ -10619,7 +10642,7 @@
       </c>
       <c r="O357" s="27"/>
     </row>
-    <row r="358" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G358" s="3"/>
       <c r="H358" s="4"/>
       <c r="I358" s="6"/>
@@ -11010,35 +11033,329 @@
       </c>
     </row>
     <row r="373" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G373" s="4"/>
-      <c r="H373" s="4"/>
-      <c r="I373" s="6"/>
-      <c r="J373" s="4"/>
-      <c r="K373" s="9"/>
-      <c r="L373" s="4"/>
-      <c r="M373" s="4"/>
-      <c r="N373" s="6"/>
+      <c r="G373" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H373" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I373" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J373" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K373" s="9">
+        <v>198</v>
+      </c>
+      <c r="L373" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M373" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N373" s="6">
+        <v>2</v>
+      </c>
       <c r="O373" s="27"/>
     </row>
     <row r="374" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G374" s="4"/>
-      <c r="H374" s="4"/>
-      <c r="I374" s="6"/>
-      <c r="J374" s="4"/>
-      <c r="K374" s="9"/>
-      <c r="L374" s="4"/>
-      <c r="M374" s="4"/>
-      <c r="N374" s="6"/>
+      <c r="G374" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H374" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I374" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J374" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K374" s="9">
+        <v>170</v>
+      </c>
+      <c r="L374" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M374" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N374" s="6">
+        <v>2</v>
+      </c>
       <c r="O374" s="27"/>
     </row>
+    <row r="375" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G375" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H375" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I375" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J375" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K375" s="9">
+        <v>150</v>
+      </c>
+      <c r="L375" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="M375" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N375" s="6">
+        <v>2</v>
+      </c>
+      <c r="O375" s="27"/>
+    </row>
+    <row r="376" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G376" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H376" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I376" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J376" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K376" s="9">
+        <v>200</v>
+      </c>
+      <c r="L376" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="M376" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N376" s="6">
+        <v>2</v>
+      </c>
+      <c r="O376" s="27"/>
+    </row>
+    <row r="377" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G377" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H377" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I377" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="J377" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="K377" s="9">
+        <v>190</v>
+      </c>
+      <c r="L377" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="M377" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N377" s="6">
+        <v>2</v>
+      </c>
+      <c r="O377" s="27"/>
+    </row>
+    <row r="378" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G378" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H378" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I378" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J378" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K378" s="9">
+        <v>240</v>
+      </c>
+      <c r="L378" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M378" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N378" s="6">
+        <v>2</v>
+      </c>
+      <c r="O378" s="27"/>
+    </row>
+    <row r="379" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G379" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H379" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I379" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="J379" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K379" s="9">
+        <v>150</v>
+      </c>
+      <c r="L379" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="M379" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N379" s="6">
+        <v>2</v>
+      </c>
+      <c r="O379" s="27"/>
+    </row>
+    <row r="380" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G380" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H380" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I380" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J380" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K380" s="9">
+        <v>280</v>
+      </c>
+      <c r="L380" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M380" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N380" s="6">
+        <v>2</v>
+      </c>
+      <c r="O380" s="27"/>
+    </row>
+    <row r="381" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G381" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H381" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I381" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="J381" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K381" s="9">
+        <v>200</v>
+      </c>
+      <c r="L381" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M381" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N381" s="6">
+        <v>2</v>
+      </c>
+      <c r="O381" s="27"/>
+    </row>
+    <row r="382" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G382" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H382" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I382" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J382" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K382" s="9">
+        <v>180</v>
+      </c>
+      <c r="L382" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M382" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N382" s="6">
+        <v>1</v>
+      </c>
+      <c r="O382" s="27"/>
+    </row>
+    <row r="383" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="O383" s="29"/>
+    </row>
+    <row r="384" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G384" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H384" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I384" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J384" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="K384" s="9">
+        <v>170</v>
+      </c>
+      <c r="L384" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M384" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N384" s="6">
+        <v>1</v>
+      </c>
+      <c r="O384" s="27"/>
+    </row>
+    <row r="385" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G385" s="4"/>
+      <c r="H385" s="4"/>
+      <c r="I385" s="6"/>
+      <c r="J385" s="4"/>
+      <c r="K385" s="9"/>
+      <c r="L385" s="4"/>
+      <c r="M385" s="4"/>
+      <c r="N385" s="6"/>
+      <c r="O385" s="27"/>
+    </row>
+    <row r="386" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G386" s="4"/>
+      <c r="H386" s="4"/>
+      <c r="I386" s="6"/>
+      <c r="J386" s="4"/>
+      <c r="K386" s="9"/>
+      <c r="L386" s="4"/>
+      <c r="M386" s="4"/>
+      <c r="N386" s="6"/>
+      <c r="O386" s="27"/>
+    </row>
   </sheetData>
-  <autoFilter ref="G5:N372" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" month="10" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="G5:N384" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
     <sortCondition ref="G6:G339"/>
   </sortState>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2391" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57400DA2-A8F2-4783-BE94-621E43F72E5B}"/>
+  <xr:revisionPtr revIDLastSave="2399" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACEBB2A5-DBDC-490F-BCB3-316D4B0A50DA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -1352,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1">
+  <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="G5:O386"/>
@@ -1398,7 +1398,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45873</v>
       </c>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="O6"/>
     </row>
-    <row r="7" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45873</v>
       </c>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="O7"/>
     </row>
-    <row r="8" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45873</v>
       </c>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="O8"/>
     </row>
-    <row r="9" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45873</v>
       </c>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9"/>
     </row>
-    <row r="10" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45875</v>
       </c>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="O10"/>
     </row>
-    <row r="11" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45875</v>
       </c>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="O11"/>
     </row>
-    <row r="12" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45875</v>
       </c>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="O12"/>
     </row>
-    <row r="13" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45875</v>
       </c>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="O13"/>
     </row>
-    <row r="14" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45875</v>
       </c>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="O14"/>
     </row>
-    <row r="15" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45875</v>
       </c>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="O15"/>
     </row>
-    <row r="16" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45875</v>
       </c>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O16"/>
     </row>
-    <row r="17" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45875</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45876</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45876</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45876</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45876</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45876</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45876</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45876</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45876</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45876</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45876</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45880</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45880</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G31" s="3">
         <v>45880</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45880</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45880</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45881</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45881</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45881</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45881</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45881</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45881</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45881</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
         <v>45882</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G42" s="3">
         <v>45882</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G43" s="3">
         <v>45882</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G44" s="3">
         <v>45882</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G45" s="3">
         <v>45882</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G46" s="3">
         <v>45882</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G47" s="3">
         <v>45883</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G48" s="3">
         <v>45883</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G49" s="3">
         <v>45883</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G50" s="3">
         <v>45883</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G51" s="3">
         <v>45883</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G52" s="3">
         <v>45883</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3">
         <v>45883</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G54" s="3">
         <v>45883</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G55" s="3">
         <v>45883</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G56" s="3">
         <v>45883</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G57" s="3">
         <v>45883</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G58" s="3">
         <v>45883</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G59" s="3">
         <v>45883</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <v>45883</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G61" s="3">
         <v>45883</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G62" s="3">
         <v>45883</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G63" s="3">
         <v>45887</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G64" s="3">
         <v>45887</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G65" s="3">
         <v>45887</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G66" s="3">
         <v>45887</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G67" s="3">
         <v>45887</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G68" s="3">
         <v>45887</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G69" s="3">
         <v>45887</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G70" s="3">
         <v>45888</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G71" s="3">
         <v>45888</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G72" s="3">
         <v>45888</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G73" s="3">
         <v>45888</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G74" s="3">
         <v>45888</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G75" s="3">
         <v>45889</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G76" s="3">
         <v>45889</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G77" s="3">
         <v>45889</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G78" s="3">
         <v>45889</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G79" s="3">
         <v>45889</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G80" s="3">
         <v>45889</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G81" s="3">
         <v>45889</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G82" s="3">
         <v>45890</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G83" s="3">
         <v>45890</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G84" s="3">
         <v>45890</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G85" s="3">
         <v>45890</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G86" s="3">
         <v>45890</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G87" s="3">
         <v>45890</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G88" s="3">
         <v>45890</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G89" s="3">
         <v>45890</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G90" s="3">
         <v>45890</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G91" s="3">
         <v>45890</v>
       </c>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G92" s="3">
         <v>45890</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G93" s="3">
         <v>45894</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G94" s="3">
         <v>45894</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G95" s="3">
         <v>45894</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G96" s="3">
         <v>45894</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G97" s="3">
         <v>45895</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G98" s="3">
         <v>45895</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G99" s="3">
         <v>45895</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G100" s="3">
         <v>45895</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G101" s="3">
         <v>45895</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G102" s="3">
         <v>45895</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G103" s="3">
         <v>45895</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G104" s="3">
         <v>45896</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G105" s="3">
         <v>45896</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G106" s="3">
         <v>45896</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G107" s="3">
         <v>45896</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G108" s="3">
         <v>45896</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G109" s="3">
         <v>45896</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G110" s="3">
         <v>45896</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G111" s="3">
         <v>45896</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G112" s="3">
         <v>45897</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G113" s="3">
         <v>45897</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G114" s="3">
         <v>45897</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G115" s="3">
         <v>45897</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G116" s="3">
         <v>45897</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G117" s="3">
         <v>45897</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G118" s="3">
         <v>45897</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G119" s="3">
         <v>45897</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G120" s="3">
         <v>45897</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G121" s="3">
         <v>45897</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G122" s="3">
         <v>45897</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G123" s="3">
         <v>45901</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G124" s="3">
         <v>45901</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G125" s="3">
         <v>45901</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G126" s="3">
         <v>45901</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G127" s="3">
         <v>45902</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G128" s="3">
         <v>45902</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G129" s="3">
         <v>45902</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G130" s="3">
         <v>45902</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G131" s="3">
         <v>45902</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G132" s="3">
         <v>45902</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G133" s="3">
         <v>45902</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G134" s="3">
         <v>45903</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G135" s="3">
         <v>45903</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G136" s="3">
         <v>45903</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G137" s="3">
         <v>45903</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G138" s="3">
         <v>45903</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G139" s="3">
         <v>45903</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G140" s="3">
         <v>45903</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G141" s="3">
         <v>45903</v>
       </c>
@@ -4941,7 +4941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G142" s="3">
         <v>45903</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G143" s="3">
         <v>45903</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G144" s="3">
         <v>45904</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G145" s="3">
         <v>45904</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G146" s="3">
         <v>45904</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G147" s="3">
         <v>45904</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G148" s="3">
         <v>45904</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G149" s="3">
         <v>45904</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G150" s="3">
         <v>45904</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G151" s="3">
         <v>45904</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G152" s="3">
         <v>45904</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G153" s="3">
         <v>45908</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G154" s="3">
         <v>45908</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G155" s="3">
         <v>45908</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G156" s="3">
         <v>45908</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G157" s="3">
         <v>45909</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G158" s="3">
         <v>45909</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G159" s="3">
         <v>45909</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G160" s="3">
         <v>45909</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G161" s="3">
         <v>45909</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G162" s="3">
         <v>45909</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G163" s="3">
         <v>45910</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G164" s="3">
         <v>45910</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G165" s="3">
         <v>45910</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G166" s="3">
         <v>45910</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G167" s="3">
         <v>45910</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G168" s="3">
         <v>45910</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G169" s="3">
         <v>45910</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G170" s="3">
         <v>45911</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G171" s="3">
         <v>45911</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G172" s="3">
         <v>45911</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G173" s="3">
         <v>45911</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G174" s="3">
         <v>45911</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G175" s="3">
         <v>45911</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G176" s="3">
         <v>45911</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G177" s="3">
         <v>45911</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G178" s="3">
         <v>45911</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G179" s="3">
         <v>45911</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G180" s="3">
         <v>45911</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G181" s="3">
         <v>45911</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G182" s="3">
         <v>45911</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G183" s="3">
         <v>45915</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G184" s="3">
         <v>45915</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G185" s="3">
         <v>45915</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G186" s="3">
         <v>45915</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G187" s="3">
         <v>45915</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G188" s="3">
         <v>45915</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G189" s="3">
         <v>45915</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G190" s="3">
         <v>45916</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G191" s="3">
         <v>45916</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G192" s="3">
         <v>45916</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G193" s="3">
         <v>45916</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G194" s="3">
         <v>45916</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G195" s="3">
         <v>45917</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G196" s="3">
         <v>45917</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G197" s="3">
         <v>45917</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G198" s="3">
         <v>45917</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G199" s="3">
         <v>45917</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G200" s="3">
         <v>45917</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G201" s="3">
         <v>45917</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G202" s="3">
         <v>45918</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G203" s="3">
         <v>45918</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G204" s="3">
         <v>45918</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G205" s="3">
         <v>45918</v>
       </c>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G206" s="3">
         <v>45918</v>
       </c>
@@ -6617,7 +6617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G207" s="3">
         <v>45918</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G208" s="3">
         <v>45918</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G209" s="3">
         <v>45918</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G210" s="3">
         <v>45918</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G211" s="3">
         <v>45918</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G212" s="3">
         <v>45918</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G213" s="3">
         <v>45918</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G214" s="3">
         <v>45918</v>
       </c>
@@ -6819,7 +6819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G215" s="3">
         <v>45922</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G216" s="3">
         <v>45922</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G217" s="3">
         <v>45922</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G218" s="3">
         <v>45922</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G219" s="3">
         <v>45922</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G220" s="3">
         <v>45922</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G221" s="3">
         <v>45922</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G222" s="3">
         <v>45923</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G223" s="3">
         <v>45923</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G224" s="3">
         <v>45923</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G225" s="3">
         <v>45923</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G226" s="3">
         <v>45923</v>
       </c>
@@ -7131,7 +7131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G227" s="3">
         <v>45923</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G228" s="3">
         <v>45924</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G229" s="3">
         <v>45924</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G230" s="3">
         <v>45924</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G231" s="3">
         <v>45924</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G232" s="3">
         <v>45924</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G233" s="3">
         <v>45924</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G234" s="3">
         <v>45924</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G235" s="3">
         <v>45924</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G236" s="3">
         <v>45925</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G237" s="3">
         <v>45925</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G238" s="3">
         <v>45925</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G239" s="3">
         <v>45925</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G240" s="3">
         <v>45925</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G241" s="3">
         <v>45925</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G242" s="3">
         <v>45925</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G243" s="3">
         <v>45925</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G244" s="3">
         <v>45925</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G245" s="3">
         <v>45925</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G246" s="3">
         <v>45925</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G247" s="3">
         <v>45929</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G248" s="3">
         <v>45929</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G249" s="3">
         <v>45929</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G250" s="3">
         <v>45929</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G251" s="3">
         <v>45929</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G252" s="3">
         <v>45929</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G253" s="3">
         <v>45929</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G254" s="3">
         <v>45930</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G255" s="3">
         <v>45930</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="7:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="G256" s="3">
         <v>45930</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G257" s="3">
         <v>45930</v>
       </c>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="O257"/>
     </row>
-    <row r="258" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G258" s="3">
         <v>45930</v>
       </c>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="O258"/>
     </row>
-    <row r="259" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G259" s="3">
         <v>45930</v>
       </c>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="O259"/>
     </row>
-    <row r="260" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="O273" s="4"/>
     </row>
-    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G279" s="3">
         <v>45933</v>
       </c>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G280" s="3">
         <v>45933</v>
       </c>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9504,32 +9504,34 @@
       </c>
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G316" s="3">
+    <row r="316" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G316" s="19">
         <v>45940</v>
       </c>
-      <c r="H316" s="4" t="s">
+      <c r="H316" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="I316" s="6" t="s">
+      <c r="I316" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="J316" s="4" t="s">
+      <c r="J316" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="K316" s="9">
+      <c r="K316" s="22">
         <v>220</v>
       </c>
-      <c r="L316" s="4" t="s">
+      <c r="L316" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="M316" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N316" s="6">
+      <c r="M316" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="N316" s="21">
         <v>1</v>
       </c>
-      <c r="O316" s="6"/>
+      <c r="O316" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="317" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
@@ -10453,7 +10455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G351" s="3">
         <v>45950</v>
       </c>
@@ -10480,7 +10482,7 @@
       </c>
       <c r="O351" s="27"/>
     </row>
-    <row r="352" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G352" s="3">
         <v>45950</v>
       </c>
@@ -10507,7 +10509,7 @@
       </c>
       <c r="O352" s="27"/>
     </row>
-    <row r="353" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G353" s="3">
         <v>45950</v>
       </c>
@@ -10534,7 +10536,7 @@
       </c>
       <c r="O353" s="27"/>
     </row>
-    <row r="354" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G354" s="3">
         <v>45950</v>
       </c>
@@ -10561,7 +10563,7 @@
       </c>
       <c r="O354" s="27"/>
     </row>
-    <row r="355" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G355" s="3">
         <v>45950</v>
       </c>
@@ -10588,7 +10590,7 @@
       </c>
       <c r="O355" s="27"/>
     </row>
-    <row r="356" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G356" s="3">
         <v>45950</v>
       </c>
@@ -10615,7 +10617,7 @@
       </c>
       <c r="O356" s="27"/>
     </row>
-    <row r="357" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G357" s="3">
         <v>45950</v>
       </c>
@@ -10642,7 +10644,7 @@
       </c>
       <c r="O357" s="27"/>
     </row>
-    <row r="358" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G358" s="3"/>
       <c r="H358" s="4"/>
       <c r="I358" s="6"/>
@@ -10652,7 +10654,7 @@
       <c r="M358" s="4"/>
       <c r="N358" s="6"/>
     </row>
-    <row r="359" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G359" s="3">
         <v>45951</v>
       </c>
@@ -10679,7 +10681,7 @@
       </c>
       <c r="O359" s="27"/>
     </row>
-    <row r="360" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G360" s="3">
         <v>45951</v>
       </c>
@@ -10706,7 +10708,7 @@
       </c>
       <c r="O360" s="27"/>
     </row>
-    <row r="361" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G361" s="3">
         <v>45951</v>
       </c>
@@ -10733,7 +10735,7 @@
       </c>
       <c r="O361" s="27"/>
     </row>
-    <row r="362" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G362" s="3">
         <v>45951</v>
       </c>
@@ -10760,7 +10762,7 @@
       </c>
       <c r="O362" s="27"/>
     </row>
-    <row r="363" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G363" s="3">
         <v>45951</v>
       </c>
@@ -10787,7 +10789,7 @@
       </c>
       <c r="O363" s="27"/>
     </row>
-    <row r="364" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G364" s="3">
         <v>45951</v>
       </c>
@@ -10814,7 +10816,7 @@
       </c>
       <c r="O364" s="27"/>
     </row>
-    <row r="365" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G365" s="3">
         <v>45952</v>
       </c>
@@ -10841,7 +10843,7 @@
       </c>
       <c r="O365" s="28"/>
     </row>
-    <row r="366" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G366" s="3">
         <v>45952</v>
       </c>
@@ -10868,7 +10870,7 @@
       </c>
       <c r="O366" s="27"/>
     </row>
-    <row r="367" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G367" s="3">
         <v>45952</v>
       </c>
@@ -10895,7 +10897,7 @@
       </c>
       <c r="O367" s="27"/>
     </row>
-    <row r="368" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G368" s="3">
         <v>45952</v>
       </c>
@@ -10922,7 +10924,7 @@
       </c>
       <c r="O368" s="27"/>
     </row>
-    <row r="369" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G369" s="3">
         <v>45952</v>
       </c>
@@ -10949,7 +10951,7 @@
       </c>
       <c r="O369" s="27"/>
     </row>
-    <row r="370" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G370" s="3">
         <v>45952</v>
       </c>
@@ -10976,7 +10978,7 @@
       </c>
       <c r="O370" s="27"/>
     </row>
-    <row r="371" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G371" s="3">
         <v>45952</v>
       </c>
@@ -11003,7 +11005,7 @@
       </c>
       <c r="O371" s="27"/>
     </row>
-    <row r="372" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G372" s="19">
         <v>45952</v>
       </c>
@@ -11032,7 +11034,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="373" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G373" s="3">
         <v>45953</v>
       </c>
@@ -11059,7 +11061,7 @@
       </c>
       <c r="O373" s="27"/>
     </row>
-    <row r="374" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G374" s="3">
         <v>45953</v>
       </c>
@@ -11086,7 +11088,7 @@
       </c>
       <c r="O374" s="27"/>
     </row>
-    <row r="375" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G375" s="3">
         <v>45953</v>
       </c>
@@ -11113,7 +11115,7 @@
       </c>
       <c r="O375" s="27"/>
     </row>
-    <row r="376" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G376" s="3">
         <v>45953</v>
       </c>
@@ -11140,7 +11142,7 @@
       </c>
       <c r="O376" s="27"/>
     </row>
-    <row r="377" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G377" s="3">
         <v>45953</v>
       </c>
@@ -11167,7 +11169,7 @@
       </c>
       <c r="O377" s="27"/>
     </row>
-    <row r="378" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G378" s="3">
         <v>45953</v>
       </c>
@@ -11194,7 +11196,7 @@
       </c>
       <c r="O378" s="27"/>
     </row>
-    <row r="379" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G379" s="3">
         <v>45953</v>
       </c>
@@ -11221,7 +11223,7 @@
       </c>
       <c r="O379" s="27"/>
     </row>
-    <row r="380" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G380" s="3">
         <v>45953</v>
       </c>
@@ -11248,7 +11250,7 @@
       </c>
       <c r="O380" s="27"/>
     </row>
-    <row r="381" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G381" s="3">
         <v>45953</v>
       </c>
@@ -11275,7 +11277,7 @@
       </c>
       <c r="O381" s="27"/>
     </row>
-    <row r="382" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G382" s="3">
         <v>45953</v>
       </c>
@@ -11302,10 +11304,10 @@
       </c>
       <c r="O382" s="27"/>
     </row>
-    <row r="383" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="O383" s="29"/>
     </row>
-    <row r="384" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G384" s="3">
         <v>45953</v>
       </c>
@@ -11355,7 +11357,17 @@
       <c r="O386" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N384" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}"/>
+  <autoFilter ref="G5:N384" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2025" month="10" day="13" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="14" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="15" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="16" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="17" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
     <sortCondition ref="G6:G339"/>
   </sortState>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2399" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACEBB2A5-DBDC-490F-BCB3-316D4B0A50DA}"/>
+  <xr:revisionPtr revIDLastSave="2401" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FCCFA95-2D75-4E70-8CD0-F8A1FAFF7A61}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G329" s="19">
         <v>45944</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G337" s="3">
         <v>45946</v>
       </c>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G338" s="3">
         <v>45946</v>
       </c>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G339" s="3">
         <v>45946</v>
       </c>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G340" s="3">
         <v>45946</v>
       </c>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G341" s="3">
         <v>45946</v>
       </c>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G342" s="3">
         <v>45946</v>
       </c>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G343" s="3">
         <v>45946</v>
       </c>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G344" s="3">
         <v>45946</v>
       </c>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G345" s="3">
         <v>45946</v>
       </c>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G347" s="3">
         <v>45946</v>
       </c>
@@ -10372,7 +10372,7 @@
       </c>
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G348" s="3">
         <v>45946</v>
       </c>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G349" s="3">
         <v>45946</v>
       </c>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G350" s="19">
         <v>45947</v>
       </c>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="O356" s="27"/>
     </row>
-    <row r="357" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G357" s="3">
         <v>45950</v>
       </c>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="O380" s="27"/>
     </row>
-    <row r="381" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G381" s="3">
         <v>45953</v>
       </c>
@@ -11360,11 +11360,12 @@
   <autoFilter ref="G5:N384" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="10" day="13" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="10" day="14" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="10" day="15" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="10" day="16" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="10" day="17" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="CRISTIANO"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2401" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FCCFA95-2D75-4E70-8CD0-F8A1FAFF7A61}"/>
+  <xr:revisionPtr revIDLastSave="2406" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9350F7B-74DC-4F83-807A-DA83B4C03AB8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="O259"/>
     </row>
-    <row r="260" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="O273" s="4"/>
     </row>
-    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
@@ -8505,61 +8505,65 @@
       </c>
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G279" s="3">
+    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G279" s="19">
         <v>45933</v>
       </c>
-      <c r="H279" s="4" t="s">
+      <c r="H279" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="I279" s="6" t="s">
+      <c r="I279" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="J279" s="4" t="s">
+      <c r="J279" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="K279" s="9">
+      <c r="K279" s="22">
         <v>230</v>
       </c>
-      <c r="L279" s="4" t="s">
+      <c r="L279" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="M279" s="4" t="s">
+      <c r="M279" s="20" t="s">
         <v>8</v>
       </c>
       <c r="N279" s="6">
         <v>1</v>
       </c>
-      <c r="O279" s="6"/>
-    </row>
-    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G280" s="3">
+      <c r="O279" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G280" s="19">
         <v>45933</v>
       </c>
-      <c r="H280" s="4" t="s">
+      <c r="H280" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="I280" s="6" t="s">
+      <c r="I280" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="J280" s="4" t="s">
+      <c r="J280" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K280" s="9">
+      <c r="K280" s="22">
         <v>200</v>
       </c>
-      <c r="L280" s="4" t="s">
+      <c r="L280" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M280" s="4" t="s">
+      <c r="M280" s="20" t="s">
         <v>8</v>
       </c>
       <c r="N280" s="6">
         <v>1</v>
       </c>
-      <c r="O280" s="6"/>
-    </row>
-    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O280" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8586,7 +8590,7 @@
       </c>
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8613,7 +8617,7 @@
       </c>
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8640,7 +8644,7 @@
       </c>
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8694,7 +8698,7 @@
       </c>
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8721,7 +8725,7 @@
       </c>
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8748,7 +8752,7 @@
       </c>
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8775,7 +8779,7 @@
       </c>
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8802,7 +8806,7 @@
       </c>
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8829,7 +8833,7 @@
       </c>
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8856,7 +8860,7 @@
       </c>
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8883,7 +8887,7 @@
       </c>
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8910,7 +8914,7 @@
       </c>
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8937,7 +8941,7 @@
       </c>
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8964,7 +8968,7 @@
       </c>
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8991,7 +8995,7 @@
       </c>
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -9018,7 +9022,7 @@
       </c>
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -9045,7 +9049,7 @@
       </c>
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -9072,7 +9076,7 @@
       </c>
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -9099,7 +9103,7 @@
       </c>
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9126,7 +9130,7 @@
       </c>
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
@@ -9153,7 +9157,7 @@
       </c>
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
@@ -9180,7 +9184,7 @@
       </c>
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
@@ -9207,7 +9211,7 @@
       </c>
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
@@ -9234,7 +9238,7 @@
       </c>
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
@@ -9261,7 +9265,7 @@
       </c>
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
@@ -9288,7 +9292,7 @@
       </c>
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
@@ -9315,7 +9319,7 @@
       </c>
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
@@ -9342,7 +9346,7 @@
       </c>
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9369,7 +9373,7 @@
       </c>
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9396,7 +9400,7 @@
       </c>
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9423,7 +9427,7 @@
       </c>
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9477,7 +9481,7 @@
       </c>
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9504,7 +9508,7 @@
       </c>
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G316" s="19">
         <v>45940</v>
       </c>
@@ -9533,7 +9537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
@@ -9560,7 +9564,7 @@
       </c>
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
@@ -9587,7 +9591,7 @@
       </c>
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
@@ -9614,7 +9618,7 @@
       </c>
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
@@ -9641,7 +9645,7 @@
       </c>
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
@@ -9695,7 +9699,7 @@
       </c>
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
@@ -9722,7 +9726,7 @@
       </c>
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
@@ -9749,7 +9753,7 @@
       </c>
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
@@ -9776,7 +9780,7 @@
       </c>
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
@@ -9803,7 +9807,7 @@
       </c>
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
@@ -9830,7 +9834,7 @@
       </c>
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
@@ -9857,7 +9861,7 @@
       </c>
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G329" s="19">
         <v>45944</v>
       </c>
@@ -9886,7 +9890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
@@ -9913,7 +9917,7 @@
       </c>
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
@@ -9940,7 +9944,7 @@
       </c>
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
@@ -9967,7 +9971,7 @@
       </c>
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
@@ -9994,7 +9998,7 @@
       </c>
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
@@ -10021,7 +10025,7 @@
       </c>
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
@@ -10048,7 +10052,7 @@
       </c>
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
@@ -10075,7 +10079,7 @@
       </c>
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G337" s="3">
         <v>45946</v>
       </c>
@@ -10102,7 +10106,7 @@
       </c>
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G338" s="3">
         <v>45946</v>
       </c>
@@ -10129,7 +10133,7 @@
       </c>
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G339" s="3">
         <v>45946</v>
       </c>
@@ -10156,7 +10160,7 @@
       </c>
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G340" s="3">
         <v>45946</v>
       </c>
@@ -10183,7 +10187,7 @@
       </c>
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G341" s="3">
         <v>45946</v>
       </c>
@@ -10210,7 +10214,7 @@
       </c>
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G342" s="3">
         <v>45946</v>
       </c>
@@ -10237,7 +10241,7 @@
       </c>
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G343" s="3">
         <v>45946</v>
       </c>
@@ -10264,7 +10268,7 @@
       </c>
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G344" s="3">
         <v>45946</v>
       </c>
@@ -10291,7 +10295,7 @@
       </c>
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G345" s="3">
         <v>45946</v>
       </c>
@@ -10345,7 +10349,7 @@
       </c>
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G347" s="3">
         <v>45946</v>
       </c>
@@ -10372,7 +10376,7 @@
       </c>
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G348" s="3">
         <v>45946</v>
       </c>
@@ -10399,7 +10403,7 @@
       </c>
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G349" s="3">
         <v>45946</v>
       </c>
@@ -10426,7 +10430,7 @@
       </c>
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G350" s="19">
         <v>45947</v>
       </c>
@@ -10455,7 +10459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G351" s="3">
         <v>45950</v>
       </c>
@@ -10482,7 +10486,7 @@
       </c>
       <c r="O351" s="27"/>
     </row>
-    <row r="352" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G352" s="3">
         <v>45950</v>
       </c>
@@ -10509,7 +10513,7 @@
       </c>
       <c r="O352" s="27"/>
     </row>
-    <row r="353" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G353" s="3">
         <v>45950</v>
       </c>
@@ -10536,7 +10540,7 @@
       </c>
       <c r="O353" s="27"/>
     </row>
-    <row r="354" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G354" s="3">
         <v>45950</v>
       </c>
@@ -10563,7 +10567,7 @@
       </c>
       <c r="O354" s="27"/>
     </row>
-    <row r="355" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G355" s="3">
         <v>45950</v>
       </c>
@@ -10590,7 +10594,7 @@
       </c>
       <c r="O355" s="27"/>
     </row>
-    <row r="356" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G356" s="3">
         <v>45950</v>
       </c>
@@ -10654,7 +10658,7 @@
       <c r="M358" s="4"/>
       <c r="N358" s="6"/>
     </row>
-    <row r="359" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G359" s="3">
         <v>45951</v>
       </c>
@@ -10681,7 +10685,7 @@
       </c>
       <c r="O359" s="27"/>
     </row>
-    <row r="360" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G360" s="3">
         <v>45951</v>
       </c>
@@ -10708,7 +10712,7 @@
       </c>
       <c r="O360" s="27"/>
     </row>
-    <row r="361" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G361" s="3">
         <v>45951</v>
       </c>
@@ -10735,7 +10739,7 @@
       </c>
       <c r="O361" s="27"/>
     </row>
-    <row r="362" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G362" s="3">
         <v>45951</v>
       </c>
@@ -10762,7 +10766,7 @@
       </c>
       <c r="O362" s="27"/>
     </row>
-    <row r="363" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G363" s="3">
         <v>45951</v>
       </c>
@@ -10789,7 +10793,7 @@
       </c>
       <c r="O363" s="27"/>
     </row>
-    <row r="364" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G364" s="3">
         <v>45951</v>
       </c>
@@ -10816,7 +10820,7 @@
       </c>
       <c r="O364" s="27"/>
     </row>
-    <row r="365" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G365" s="3">
         <v>45952</v>
       </c>
@@ -10843,7 +10847,7 @@
       </c>
       <c r="O365" s="28"/>
     </row>
-    <row r="366" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G366" s="3">
         <v>45952</v>
       </c>
@@ -10870,7 +10874,7 @@
       </c>
       <c r="O366" s="27"/>
     </row>
-    <row r="367" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G367" s="3">
         <v>45952</v>
       </c>
@@ -10897,7 +10901,7 @@
       </c>
       <c r="O367" s="27"/>
     </row>
-    <row r="368" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G368" s="3">
         <v>45952</v>
       </c>
@@ -10924,7 +10928,7 @@
       </c>
       <c r="O368" s="27"/>
     </row>
-    <row r="369" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G369" s="3">
         <v>45952</v>
       </c>
@@ -10951,7 +10955,7 @@
       </c>
       <c r="O369" s="27"/>
     </row>
-    <row r="370" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G370" s="3">
         <v>45952</v>
       </c>
@@ -10978,7 +10982,7 @@
       </c>
       <c r="O370" s="27"/>
     </row>
-    <row r="371" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G371" s="3">
         <v>45952</v>
       </c>
@@ -11005,7 +11009,7 @@
       </c>
       <c r="O371" s="27"/>
     </row>
-    <row r="372" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G372" s="19">
         <v>45952</v>
       </c>
@@ -11034,7 +11038,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="373" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G373" s="3">
         <v>45953</v>
       </c>
@@ -11061,7 +11065,7 @@
       </c>
       <c r="O373" s="27"/>
     </row>
-    <row r="374" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G374" s="3">
         <v>45953</v>
       </c>
@@ -11088,7 +11092,7 @@
       </c>
       <c r="O374" s="27"/>
     </row>
-    <row r="375" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G375" s="3">
         <v>45953</v>
       </c>
@@ -11115,7 +11119,7 @@
       </c>
       <c r="O375" s="27"/>
     </row>
-    <row r="376" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G376" s="3">
         <v>45953</v>
       </c>
@@ -11142,7 +11146,7 @@
       </c>
       <c r="O376" s="27"/>
     </row>
-    <row r="377" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G377" s="3">
         <v>45953</v>
       </c>
@@ -11169,7 +11173,7 @@
       </c>
       <c r="O377" s="27"/>
     </row>
-    <row r="378" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G378" s="3">
         <v>45953</v>
       </c>
@@ -11196,7 +11200,7 @@
       </c>
       <c r="O378" s="27"/>
     </row>
-    <row r="379" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G379" s="3">
         <v>45953</v>
       </c>
@@ -11223,7 +11227,7 @@
       </c>
       <c r="O379" s="27"/>
     </row>
-    <row r="380" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G380" s="3">
         <v>45953</v>
       </c>
@@ -11277,7 +11281,7 @@
       </c>
       <c r="O381" s="27"/>
     </row>
-    <row r="382" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G382" s="3">
         <v>45953</v>
       </c>
@@ -11307,7 +11311,7 @@
     <row r="383" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="O383" s="29"/>
     </row>
-    <row r="384" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G384" s="3">
         <v>45953</v>
       </c>
@@ -11363,11 +11367,6 @@
         <dateGroupItem year="2025" month="10" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="CRISTIANO"/>
-      </filters>
-    </filterColumn>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:N339">
     <sortCondition ref="G6:G339"/>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2406" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9350F7B-74DC-4F83-807A-DA83B4C03AB8}"/>
+  <xr:revisionPtr revIDLastSave="2488" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BBEAD03-6A20-4489-96FB-82D42DCD26A7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$N$384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$O$389</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="270">
   <si>
     <t>DATA</t>
   </si>
@@ -833,6 +833,21 @@
   </si>
   <si>
     <t>HOTEL BARBACENA</t>
+  </si>
+  <si>
+    <t>REGINALDO.MOREIRA</t>
+  </si>
+  <si>
+    <t>SETE LAGOAS</t>
+  </si>
+  <si>
+    <t>HOTEL BOM JESUS</t>
+  </si>
+  <si>
+    <t>POUSADA AGUIA LEAO</t>
+  </si>
+  <si>
+    <t>SANTA LUZIA</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1370,7 @@
   <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O386"/>
+  <dimension ref="G5:O392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -7992,7 +8007,7 @@
       </c>
       <c r="O259"/>
     </row>
-    <row r="260" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G260" s="3">
         <v>45931</v>
       </c>
@@ -8019,7 +8034,7 @@
       </c>
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G261" s="3">
         <v>45931</v>
       </c>
@@ -8046,7 +8061,7 @@
       </c>
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G262" s="3">
         <v>45931</v>
       </c>
@@ -8073,7 +8088,7 @@
       </c>
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G263" s="3">
         <v>45931</v>
       </c>
@@ -8100,7 +8115,7 @@
       </c>
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G264" s="3">
         <v>45931</v>
       </c>
@@ -8127,7 +8142,7 @@
       </c>
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G265" s="3">
         <v>45931</v>
       </c>
@@ -8154,7 +8169,7 @@
       </c>
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G266" s="3">
         <v>45931</v>
       </c>
@@ -8181,7 +8196,7 @@
       </c>
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G267" s="3">
         <v>45931</v>
       </c>
@@ -8208,7 +8223,7 @@
       </c>
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G268" s="3">
         <v>45932</v>
       </c>
@@ -8235,7 +8250,7 @@
       </c>
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G269" s="3">
         <v>45932</v>
       </c>
@@ -8262,7 +8277,7 @@
       </c>
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G270" s="3">
         <v>45932</v>
       </c>
@@ -8289,7 +8304,7 @@
       </c>
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G271" s="3">
         <v>45932</v>
       </c>
@@ -8316,7 +8331,7 @@
       </c>
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G272" s="3">
         <v>45932</v>
       </c>
@@ -8343,7 +8358,7 @@
       </c>
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G273" s="3">
         <v>45932</v>
       </c>
@@ -8370,7 +8385,7 @@
       </c>
       <c r="O273" s="4"/>
     </row>
-    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G274" s="3">
         <v>45932</v>
       </c>
@@ -8397,7 +8412,7 @@
       </c>
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G275" s="3">
         <v>45932</v>
       </c>
@@ -8424,7 +8439,7 @@
       </c>
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G276" s="3">
         <v>45932</v>
       </c>
@@ -8451,7 +8466,7 @@
       </c>
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G277" s="3">
         <v>45932</v>
       </c>
@@ -8478,7 +8493,7 @@
       </c>
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G278" s="3">
         <v>45932</v>
       </c>
@@ -8505,7 +8520,7 @@
       </c>
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G279" s="19">
         <v>45933</v>
       </c>
@@ -8534,7 +8549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G280" s="19">
         <v>45933</v>
       </c>
@@ -8563,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G281" s="3">
         <v>45936</v>
       </c>
@@ -8590,7 +8605,7 @@
       </c>
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G282" s="3">
         <v>45936</v>
       </c>
@@ -8617,7 +8632,7 @@
       </c>
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G283" s="3">
         <v>45936</v>
       </c>
@@ -8644,7 +8659,7 @@
       </c>
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G284" s="3">
         <v>45936</v>
       </c>
@@ -8671,7 +8686,7 @@
       </c>
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G285" s="3">
         <v>45936</v>
       </c>
@@ -8698,7 +8713,7 @@
       </c>
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G286" s="3">
         <v>45936</v>
       </c>
@@ -8725,7 +8740,7 @@
       </c>
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G287" s="3">
         <v>45936</v>
       </c>
@@ -8752,7 +8767,7 @@
       </c>
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G288" s="3">
         <v>45937</v>
       </c>
@@ -8779,7 +8794,7 @@
       </c>
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G289" s="3">
         <v>45937</v>
       </c>
@@ -8806,7 +8821,7 @@
       </c>
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G290" s="3">
         <v>45937</v>
       </c>
@@ -8833,7 +8848,7 @@
       </c>
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G291" s="3">
         <v>45937</v>
       </c>
@@ -8860,7 +8875,7 @@
       </c>
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G292" s="3">
         <v>45937</v>
       </c>
@@ -8887,7 +8902,7 @@
       </c>
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
         <v>45937</v>
       </c>
@@ -8914,7 +8929,7 @@
       </c>
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
         <v>45937</v>
       </c>
@@ -8941,7 +8956,7 @@
       </c>
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
         <v>45938</v>
       </c>
@@ -8968,7 +8983,7 @@
       </c>
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
         <v>45938</v>
       </c>
@@ -8995,7 +9010,7 @@
       </c>
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
         <v>45938</v>
       </c>
@@ -9022,7 +9037,7 @@
       </c>
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
         <v>45938</v>
       </c>
@@ -9049,7 +9064,7 @@
       </c>
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
         <v>45938</v>
       </c>
@@ -9076,7 +9091,7 @@
       </c>
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
         <v>45938</v>
       </c>
@@ -9103,7 +9118,7 @@
       </c>
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
         <v>45938</v>
       </c>
@@ -9130,7 +9145,7 @@
       </c>
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
         <v>45939</v>
       </c>
@@ -9157,7 +9172,7 @@
       </c>
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
         <v>45939</v>
       </c>
@@ -9184,7 +9199,7 @@
       </c>
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
         <v>45939</v>
       </c>
@@ -9211,7 +9226,7 @@
       </c>
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G305" s="3">
         <v>45939</v>
       </c>
@@ -9238,7 +9253,7 @@
       </c>
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
         <v>45939</v>
       </c>
@@ -9265,7 +9280,7 @@
       </c>
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G307" s="3">
         <v>45939</v>
       </c>
@@ -9292,7 +9307,7 @@
       </c>
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
         <v>45939</v>
       </c>
@@ -9319,7 +9334,7 @@
       </c>
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
         <v>45939</v>
       </c>
@@ -9346,7 +9361,7 @@
       </c>
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
         <v>45939</v>
       </c>
@@ -9373,7 +9388,7 @@
       </c>
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G311" s="3">
         <v>45939</v>
       </c>
@@ -9400,7 +9415,7 @@
       </c>
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
         <v>45939</v>
       </c>
@@ -9427,7 +9442,7 @@
       </c>
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G313" s="3">
         <v>45939</v>
       </c>
@@ -9454,7 +9469,7 @@
       </c>
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
         <v>45939</v>
       </c>
@@ -9481,7 +9496,7 @@
       </c>
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
         <v>45939</v>
       </c>
@@ -9508,7 +9523,7 @@
       </c>
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G316" s="19">
         <v>45940</v>
       </c>
@@ -9537,7 +9552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
         <v>45943</v>
       </c>
@@ -9564,7 +9579,7 @@
       </c>
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
         <v>45943</v>
       </c>
@@ -9591,7 +9606,7 @@
       </c>
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
         <v>45943</v>
       </c>
@@ -9618,7 +9633,7 @@
       </c>
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
         <v>45943</v>
       </c>
@@ -9645,7 +9660,7 @@
       </c>
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
         <v>45943</v>
       </c>
@@ -9672,7 +9687,7 @@
       </c>
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
         <v>45943</v>
       </c>
@@ -9699,7 +9714,7 @@
       </c>
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G323" s="3">
         <v>45944</v>
       </c>
@@ -9726,7 +9741,7 @@
       </c>
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
         <v>45944</v>
       </c>
@@ -9753,7 +9768,7 @@
       </c>
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
         <v>45944</v>
       </c>
@@ -9780,7 +9795,7 @@
       </c>
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
         <v>45944</v>
       </c>
@@ -9807,7 +9822,7 @@
       </c>
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
         <v>45944</v>
       </c>
@@ -9834,7 +9849,7 @@
       </c>
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
         <v>45944</v>
       </c>
@@ -9861,7 +9876,7 @@
       </c>
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G329" s="19">
         <v>45944</v>
       </c>
@@ -9890,7 +9905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
         <v>45945</v>
       </c>
@@ -9917,7 +9932,7 @@
       </c>
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
         <v>45945</v>
       </c>
@@ -9944,7 +9959,7 @@
       </c>
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
         <v>45945</v>
       </c>
@@ -9971,7 +9986,7 @@
       </c>
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G333" s="3">
         <v>45945</v>
       </c>
@@ -9998,7 +10013,7 @@
       </c>
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
         <v>45945</v>
       </c>
@@ -10025,7 +10040,7 @@
       </c>
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
         <v>45945</v>
       </c>
@@ -10052,7 +10067,7 @@
       </c>
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
         <v>45945</v>
       </c>
@@ -10079,7 +10094,7 @@
       </c>
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G337" s="3">
         <v>45946</v>
       </c>
@@ -10106,7 +10121,7 @@
       </c>
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G338" s="3">
         <v>45946</v>
       </c>
@@ -10133,7 +10148,7 @@
       </c>
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G339" s="3">
         <v>45946</v>
       </c>
@@ -10160,7 +10175,7 @@
       </c>
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G340" s="3">
         <v>45946</v>
       </c>
@@ -10187,7 +10202,7 @@
       </c>
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G341" s="3">
         <v>45946</v>
       </c>
@@ -10214,7 +10229,7 @@
       </c>
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G342" s="3">
         <v>45946</v>
       </c>
@@ -10241,7 +10256,7 @@
       </c>
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G343" s="3">
         <v>45946</v>
       </c>
@@ -10268,7 +10283,7 @@
       </c>
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G344" s="3">
         <v>45946</v>
       </c>
@@ -10295,7 +10310,7 @@
       </c>
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G345" s="3">
         <v>45946</v>
       </c>
@@ -10322,7 +10337,7 @@
       </c>
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G346" s="3">
         <v>45946</v>
       </c>
@@ -10349,7 +10364,7 @@
       </c>
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G347" s="3">
         <v>45946</v>
       </c>
@@ -10376,7 +10391,7 @@
       </c>
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G348" s="3">
         <v>45946</v>
       </c>
@@ -10403,7 +10418,7 @@
       </c>
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G349" s="3">
         <v>45946</v>
       </c>
@@ -10430,7 +10445,7 @@
       </c>
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G350" s="19">
         <v>45947</v>
       </c>
@@ -10459,7 +10474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G351" s="3">
         <v>45950</v>
       </c>
@@ -10486,7 +10501,7 @@
       </c>
       <c r="O351" s="27"/>
     </row>
-    <row r="352" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G352" s="3">
         <v>45950</v>
       </c>
@@ -10513,7 +10528,7 @@
       </c>
       <c r="O352" s="27"/>
     </row>
-    <row r="353" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G353" s="3">
         <v>45950</v>
       </c>
@@ -10540,7 +10555,7 @@
       </c>
       <c r="O353" s="27"/>
     </row>
-    <row r="354" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G354" s="3">
         <v>45950</v>
       </c>
@@ -10567,7 +10582,7 @@
       </c>
       <c r="O354" s="27"/>
     </row>
-    <row r="355" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G355" s="3">
         <v>45950</v>
       </c>
@@ -10594,7 +10609,7 @@
       </c>
       <c r="O355" s="27"/>
     </row>
-    <row r="356" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G356" s="3">
         <v>45950</v>
       </c>
@@ -10621,7 +10636,7 @@
       </c>
       <c r="O356" s="27"/>
     </row>
-    <row r="357" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G357" s="3">
         <v>45950</v>
       </c>
@@ -10649,87 +10664,103 @@
       <c r="O357" s="27"/>
     </row>
     <row r="358" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G358" s="3"/>
-      <c r="H358" s="4"/>
-      <c r="I358" s="6"/>
-      <c r="J358" s="4"/>
-      <c r="K358" s="9"/>
-      <c r="L358" s="4"/>
-      <c r="M358" s="4"/>
-      <c r="N358" s="6"/>
-    </row>
-    <row r="359" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G358" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H358" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I358" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J358" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K358" s="9">
+        <v>240</v>
+      </c>
+      <c r="L358" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M358" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N358" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G359" s="3">
         <v>45951</v>
       </c>
       <c r="H359" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I359" s="6" t="s">
-        <v>253</v>
+        <v>131</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>41</v>
+        <v>255</v>
       </c>
       <c r="K359" s="9">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="L359" s="4" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="M359" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N359" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O359" s="27"/>
     </row>
-    <row r="360" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G360" s="3">
         <v>45951</v>
       </c>
       <c r="H360" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I360" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>255</v>
+        <v>97</v>
       </c>
       <c r="K360" s="9">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="L360" s="4" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="M360" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N360" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O360" s="27"/>
     </row>
-    <row r="361" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G361" s="3">
         <v>45951</v>
       </c>
       <c r="H361" s="4" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="I361" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="K361" s="9">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="L361" s="4" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="M361" s="4" t="s">
         <v>8</v>
@@ -10739,105 +10770,105 @@
       </c>
       <c r="O361" s="27"/>
     </row>
-    <row r="362" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G362" s="3">
         <v>45951</v>
       </c>
       <c r="H362" s="4" t="s">
-        <v>254</v>
+        <v>146</v>
       </c>
       <c r="I362" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="K362" s="9">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="L362" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="M362" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N362" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O362" s="27"/>
     </row>
-    <row r="363" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G363" s="3">
         <v>45951</v>
       </c>
       <c r="H363" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I363" s="6" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K363" s="9">
         <v>160</v>
       </c>
       <c r="L363" s="4" t="s">
-        <v>16</v>
+        <v>239</v>
       </c>
       <c r="M363" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N363" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O363" s="27"/>
     </row>
-    <row r="364" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G364" s="3">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="H364" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I364" s="6" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="K364" s="9">
-        <v>160</v>
+        <v>218.9</v>
       </c>
       <c r="L364" s="4" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="M364" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N364" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O364" s="27"/>
     </row>
-    <row r="365" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G365" s="3">
         <v>45952</v>
       </c>
       <c r="H365" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I365" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="K365" s="9">
-        <v>218.9</v>
+        <v>160</v>
       </c>
       <c r="L365" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M365" s="4" t="s">
         <v>8</v>
@@ -10847,51 +10878,51 @@
       </c>
       <c r="O365" s="28"/>
     </row>
-    <row r="366" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G366" s="3">
         <v>45952</v>
       </c>
       <c r="H366" s="4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I366" s="6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="K366" s="9">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L366" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M366" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N366" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O366" s="27"/>
     </row>
-    <row r="367" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G367" s="3">
         <v>45952</v>
       </c>
       <c r="H367" s="4" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="I367" s="6" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K367" s="9">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="L367" s="4" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="M367" s="4" t="s">
         <v>8</v>
@@ -10901,24 +10932,24 @@
       </c>
       <c r="O367" s="27"/>
     </row>
-    <row r="368" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G368" s="3">
         <v>45952</v>
       </c>
       <c r="H368" s="4" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="I368" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K368" s="9">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="L368" s="4" t="s">
-        <v>256</v>
+        <v>218</v>
       </c>
       <c r="M368" s="4" t="s">
         <v>8</v>
@@ -10928,24 +10959,24 @@
       </c>
       <c r="O368" s="27"/>
     </row>
-    <row r="369" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G369" s="3">
         <v>45952</v>
       </c>
       <c r="H369" s="4" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="I369" s="6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="K369" s="9">
         <v>170</v>
       </c>
       <c r="L369" s="4" t="s">
-        <v>218</v>
+        <v>22</v>
       </c>
       <c r="M369" s="4" t="s">
         <v>8</v>
@@ -10955,24 +10986,24 @@
       </c>
       <c r="O369" s="27"/>
     </row>
-    <row r="370" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G370" s="3">
         <v>45952</v>
       </c>
       <c r="H370" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I370" s="6" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="K370" s="9">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="L370" s="4" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="M370" s="4" t="s">
         <v>8</v>
@@ -10982,80 +11013,80 @@
       </c>
       <c r="O370" s="27"/>
     </row>
-    <row r="371" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G371" s="3">
+    <row r="371" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G371" s="19">
         <v>45952</v>
       </c>
-      <c r="H371" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I371" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="J371" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="K371" s="9">
-        <v>220</v>
-      </c>
-      <c r="L371" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M371" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N371" s="6">
-        <v>3</v>
+      <c r="H371" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="I371" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J371" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="K371" s="22">
+        <v>150</v>
+      </c>
+      <c r="L371" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="M371" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="N371" s="21">
+        <v>1</v>
       </c>
       <c r="O371" s="27"/>
     </row>
-    <row r="372" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G372" s="19">
-        <v>45952</v>
-      </c>
-      <c r="H372" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="I372" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="J372" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="K372" s="22">
-        <v>150</v>
-      </c>
-      <c r="L372" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="M372" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="N372" s="21">
-        <v>1</v>
+    <row r="372" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G372" s="3">
+        <v>45953</v>
+      </c>
+      <c r="H372" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I372" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J372" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K372" s="9">
+        <v>198</v>
+      </c>
+      <c r="L372" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M372" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N372" s="6">
+        <v>2</v>
       </c>
       <c r="O372" s="27" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="373" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G373" s="3">
         <v>45953</v>
       </c>
       <c r="H373" s="4" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="I373" s="6" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="K373" s="9">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="L373" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M373" s="4" t="s">
         <v>8</v>
@@ -11065,24 +11096,24 @@
       </c>
       <c r="O373" s="27"/>
     </row>
-    <row r="374" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G374" s="3">
         <v>45953</v>
       </c>
       <c r="H374" s="4" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="I374" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K374" s="9">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="L374" s="4" t="s">
-        <v>32</v>
+        <v>263</v>
       </c>
       <c r="M374" s="4" t="s">
         <v>8</v>
@@ -11092,24 +11123,24 @@
       </c>
       <c r="O374" s="27"/>
     </row>
-    <row r="375" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G375" s="3">
         <v>45953</v>
       </c>
       <c r="H375" s="4" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="I375" s="6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="K375" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L375" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M375" s="4" t="s">
         <v>8</v>
@@ -11119,24 +11150,24 @@
       </c>
       <c r="O375" s="27"/>
     </row>
-    <row r="376" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G376" s="3">
         <v>45953</v>
       </c>
       <c r="H376" s="4" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="I376" s="6" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>66</v>
+        <v>237</v>
       </c>
       <c r="K376" s="9">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="L376" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M376" s="4" t="s">
         <v>8</v>
@@ -11146,24 +11177,24 @@
       </c>
       <c r="O376" s="27"/>
     </row>
-    <row r="377" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G377" s="3">
         <v>45953</v>
       </c>
       <c r="H377" s="4" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="I377" s="6" t="s">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>237</v>
+        <v>41</v>
       </c>
       <c r="K377" s="9">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="L377" s="4" t="s">
-        <v>264</v>
+        <v>119</v>
       </c>
       <c r="M377" s="4" t="s">
         <v>8</v>
@@ -11173,24 +11204,24 @@
       </c>
       <c r="O377" s="27"/>
     </row>
-    <row r="378" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G378" s="3">
         <v>45953</v>
       </c>
       <c r="H378" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I378" s="6" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>41</v>
+        <v>201</v>
       </c>
       <c r="K378" s="9">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="L378" s="4" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="M378" s="4" t="s">
         <v>8</v>
@@ -11200,24 +11231,24 @@
       </c>
       <c r="O378" s="27"/>
     </row>
-    <row r="379" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G379" s="3">
         <v>45953</v>
       </c>
       <c r="H379" s="4" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="I379" s="6" t="s">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>201</v>
+        <v>61</v>
       </c>
       <c r="K379" s="9">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="L379" s="4" t="s">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="M379" s="4" t="s">
         <v>8</v>
@@ -11227,24 +11258,24 @@
       </c>
       <c r="O379" s="27"/>
     </row>
-    <row r="380" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G380" s="3">
         <v>45953</v>
       </c>
       <c r="H380" s="4" t="s">
-        <v>254</v>
+        <v>155</v>
       </c>
       <c r="I380" s="6" t="s">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K380" s="9">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="L380" s="4" t="s">
-        <v>55</v>
+        <v>181</v>
       </c>
       <c r="M380" s="4" t="s">
         <v>8</v>
@@ -11254,51 +11285,51 @@
       </c>
       <c r="O380" s="27"/>
     </row>
-    <row r="381" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G381" s="3">
         <v>45953</v>
       </c>
       <c r="H381" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I381" s="6" t="s">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="K381" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="L381" s="4" t="s">
-        <v>181</v>
+        <v>103</v>
       </c>
       <c r="M381" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N381" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O381" s="27"/>
     </row>
-    <row r="382" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G382" s="3">
         <v>45953</v>
       </c>
       <c r="H382" s="4" t="s">
-        <v>146</v>
+        <v>245</v>
       </c>
       <c r="I382" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="K382" s="9">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L382" s="4" t="s">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="M382" s="4" t="s">
         <v>8</v>
@@ -11308,63 +11339,233 @@
       </c>
       <c r="O382" s="27"/>
     </row>
-    <row r="383" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G383" s="3">
+        <v>45957</v>
+      </c>
+      <c r="H383" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I383" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J383" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K383" s="9">
+        <v>220</v>
+      </c>
+      <c r="L383" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="M383" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N383" s="6">
+        <v>2</v>
+      </c>
       <c r="O383" s="29"/>
     </row>
     <row r="384" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G384" s="3">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="H384" s="4" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="I384" s="6" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>248</v>
+        <v>24</v>
       </c>
       <c r="K384" s="9">
+        <v>159</v>
+      </c>
+      <c r="L384" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M384" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N384" s="6">
+        <v>2</v>
+      </c>
+      <c r="O384" s="27"/>
+    </row>
+    <row r="385" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G385" s="3">
+        <v>45957</v>
+      </c>
+      <c r="H385" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I385" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J385" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K385" s="9">
+        <v>200</v>
+      </c>
+      <c r="L385" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="M385" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N385" s="6">
+        <v>2</v>
+      </c>
+      <c r="O385" s="27"/>
+    </row>
+    <row r="386" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G386" s="3">
+        <v>45957</v>
+      </c>
+      <c r="H386" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I386" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="J386" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="K386" s="9">
+        <v>175</v>
+      </c>
+      <c r="L386" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="M386" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N386" s="6">
+        <v>2</v>
+      </c>
+      <c r="O386" s="27"/>
+    </row>
+    <row r="387" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G387" s="3">
+        <v>45957</v>
+      </c>
+      <c r="H387" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I387" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J387" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K387" s="9">
+        <v>140</v>
+      </c>
+      <c r="L387" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="M387" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N387" s="6">
+        <v>2</v>
+      </c>
+      <c r="O387" s="27"/>
+    </row>
+    <row r="388" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G388" s="3">
+        <v>45957</v>
+      </c>
+      <c r="H388" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I388" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J388" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K388" s="9">
+        <v>180</v>
+      </c>
+      <c r="L388" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M388" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N388" s="6">
+        <v>4</v>
+      </c>
+      <c r="O388" s="27"/>
+    </row>
+    <row r="389" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G389" s="3">
+        <v>45957</v>
+      </c>
+      <c r="H389" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I389" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="J389" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K389" s="9">
         <v>170</v>
       </c>
-      <c r="L384" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="M384" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N384" s="6">
-        <v>1</v>
-      </c>
-      <c r="O384" s="27"/>
-    </row>
-    <row r="385" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G385" s="4"/>
-      <c r="H385" s="4"/>
-      <c r="I385" s="6"/>
-      <c r="J385" s="4"/>
-      <c r="K385" s="9"/>
-      <c r="L385" s="4"/>
-      <c r="M385" s="4"/>
-      <c r="N385" s="6"/>
-      <c r="O385" s="27"/>
-    </row>
-    <row r="386" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G386" s="4"/>
-      <c r="H386" s="4"/>
-      <c r="I386" s="6"/>
-      <c r="J386" s="4"/>
-      <c r="K386" s="9"/>
-      <c r="L386" s="4"/>
-      <c r="M386" s="4"/>
-      <c r="N386" s="6"/>
-      <c r="O386" s="27"/>
+      <c r="L389" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M389" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N389" s="6">
+        <v>2</v>
+      </c>
+      <c r="O389" s="27"/>
+    </row>
+    <row r="390" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G390" s="4"/>
+      <c r="H390" s="4"/>
+      <c r="I390" s="6"/>
+      <c r="J390" s="4"/>
+      <c r="K390" s="9"/>
+      <c r="L390" s="4"/>
+      <c r="M390" s="4"/>
+      <c r="N390" s="6"/>
+      <c r="O390" s="27"/>
+    </row>
+    <row r="391" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G391" s="4"/>
+      <c r="H391" s="4"/>
+      <c r="I391" s="6"/>
+      <c r="J391" s="4"/>
+      <c r="K391" s="9"/>
+      <c r="L391" s="4"/>
+      <c r="M391" s="4"/>
+      <c r="N391" s="6"/>
+      <c r="O391" s="27"/>
+    </row>
+    <row r="392" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G392" s="4"/>
+      <c r="H392" s="4"/>
+      <c r="I392" s="6"/>
+      <c r="J392" s="4"/>
+      <c r="K392" s="9"/>
+      <c r="L392" s="4"/>
+      <c r="M392" s="4"/>
+      <c r="N392" s="6"/>
+      <c r="O392" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="G5:N384" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:O389" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="2025" month="10" day="27" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2488" documentId="13_ncr:1_{E95D9CB3-09C0-4BE2-98CB-FDF0DD0373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BBEAD03-6A20-4489-96FB-82D42DCD26A7}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{26B40267-1D17-4F43-A747-F3AF1361A198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F75F6097-1719-484D-B058-F6814CEA406A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$O$389</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$G$5:$O$398</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="270">
   <si>
     <t>DATA</t>
   </si>
@@ -1370,7 +1370,7 @@
   <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O392"/>
+  <dimension ref="G5:O399"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="K389" s="9">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L389" s="4" t="s">
         <v>56</v>
@@ -11529,43 +11529,193 @@
       <c r="O389" s="27"/>
     </row>
     <row r="390" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G390" s="4"/>
-      <c r="H390" s="4"/>
-      <c r="I390" s="6"/>
+      <c r="G390" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H390" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I390" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="J390" s="4"/>
       <c r="K390" s="9"/>
       <c r="L390" s="4"/>
       <c r="M390" s="4"/>
-      <c r="N390" s="6"/>
+      <c r="N390" s="6">
+        <v>1</v>
+      </c>
       <c r="O390" s="27"/>
     </row>
     <row r="391" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G391" s="4"/>
-      <c r="H391" s="4"/>
-      <c r="I391" s="6"/>
+      <c r="G391" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H391" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I391" s="6" t="s">
+        <v>139</v>
+      </c>
       <c r="J391" s="4"/>
       <c r="K391" s="9"/>
       <c r="L391" s="4"/>
       <c r="M391" s="4"/>
-      <c r="N391" s="6"/>
+      <c r="N391" s="6">
+        <v>3</v>
+      </c>
       <c r="O391" s="27"/>
     </row>
     <row r="392" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G392" s="4"/>
-      <c r="H392" s="4"/>
-      <c r="I392" s="6"/>
+      <c r="G392" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H392" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I392" s="6" t="s">
+        <v>178</v>
+      </c>
       <c r="J392" s="4"/>
       <c r="K392" s="9"/>
       <c r="L392" s="4"/>
       <c r="M392" s="4"/>
-      <c r="N392" s="6"/>
+      <c r="N392" s="6">
+        <v>1</v>
+      </c>
       <c r="O392" s="27"/>
     </row>
+    <row r="393" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G393" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H393" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I393" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J393" s="4"/>
+      <c r="K393" s="9"/>
+      <c r="L393" s="4"/>
+      <c r="M393" s="4"/>
+      <c r="N393" s="6">
+        <v>1</v>
+      </c>
+      <c r="O393" s="27"/>
+    </row>
+    <row r="394" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G394" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H394" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I394" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J394" s="4"/>
+      <c r="K394" s="9"/>
+      <c r="L394" s="4"/>
+      <c r="M394" s="4"/>
+      <c r="N394" s="6">
+        <v>2</v>
+      </c>
+      <c r="O394" s="27"/>
+    </row>
+    <row r="395" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G395" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H395" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I395" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J395" s="4"/>
+      <c r="K395" s="9"/>
+      <c r="L395" s="4"/>
+      <c r="M395" s="4"/>
+      <c r="N395" s="6">
+        <v>3</v>
+      </c>
+      <c r="O395" s="27"/>
+    </row>
+    <row r="396" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G396" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H396" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I396" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="J396" s="4"/>
+      <c r="K396" s="9"/>
+      <c r="L396" s="4"/>
+      <c r="M396" s="4"/>
+      <c r="N396" s="6">
+        <v>2</v>
+      </c>
+      <c r="O396" s="27"/>
+    </row>
+    <row r="397" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G397" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H397" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I397" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J397" s="4"/>
+      <c r="K397" s="9"/>
+      <c r="L397" s="4"/>
+      <c r="M397" s="4"/>
+      <c r="N397" s="6">
+        <v>2</v>
+      </c>
+      <c r="O397" s="27"/>
+    </row>
+    <row r="398" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G398" s="3">
+        <v>45958</v>
+      </c>
+      <c r="H398" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I398" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J398" s="4"/>
+      <c r="K398" s="9"/>
+      <c r="L398" s="4"/>
+      <c r="M398" s="4"/>
+      <c r="N398" s="6">
+        <v>3</v>
+      </c>
+      <c r="O398" s="27"/>
+    </row>
+    <row r="399" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G399" s="4"/>
+      <c r="H399" s="4"/>
+      <c r="I399" s="6"/>
+      <c r="J399" s="4"/>
+      <c r="K399" s="9"/>
+      <c r="L399" s="4"/>
+      <c r="M399" s="4"/>
+      <c r="N399" s="6"/>
+      <c r="O399" s="27"/>
+    </row>
   </sheetData>
-  <autoFilter ref="G5:O389" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:O398" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
         <dateGroupItem year="2025" month="10" day="27" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="10" day="28" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="628" documentId="14_{26B40267-1D17-4F43-A747-F3AF1361A198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29527798-37B8-424B-84ED-6A189F904098}"/>
+  <xr:revisionPtr revIDLastSave="650" documentId="14_{26B40267-1D17-4F43-A747-F3AF1361A198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66725069-CD65-4A44-B7B3-AE978AD05254}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="345">
   <si>
     <t>DATA</t>
   </si>
@@ -1062,6 +1062,18 @@
   </si>
   <si>
     <t>HOTEL JOAOZINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CAFÉ PALACE</t>
+  </si>
+  <si>
+    <t>carmo do rio claro</t>
+  </si>
+  <si>
+    <t>pousada oasis</t>
+  </si>
+  <si>
+    <t>JOAO MONLEVADE</t>
   </si>
 </sst>
 </file>
@@ -12951,22 +12963,14 @@
       <c r="O429" s="25"/>
     </row>
     <row r="430" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G430" s="3">
-        <v>45965</v>
-      </c>
-      <c r="H430" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="I430" s="6" t="s">
-        <v>125</v>
-      </c>
+      <c r="G430" s="3"/>
+      <c r="H430" s="4"/>
+      <c r="I430" s="6"/>
       <c r="J430" s="4"/>
       <c r="K430" s="8"/>
       <c r="L430" s="4"/>
       <c r="M430" s="4"/>
-      <c r="N430" s="6">
-        <v>1</v>
-      </c>
+      <c r="N430" s="6"/>
       <c r="O430" s="25"/>
     </row>
     <row r="431" spans="7:15" x14ac:dyDescent="0.25">
@@ -12979,10 +12983,18 @@
       <c r="I431" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J431" s="4"/>
-      <c r="K431" s="8"/>
-      <c r="L431" s="4"/>
-      <c r="M431" s="4"/>
+      <c r="J431" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K431" s="8">
+        <v>180</v>
+      </c>
+      <c r="L431" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M431" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N431" s="6">
         <v>3</v>
       </c>
@@ -12998,10 +13010,18 @@
       <c r="I432" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="J432" s="4"/>
-      <c r="K432" s="8"/>
-      <c r="L432" s="4"/>
-      <c r="M432" s="4"/>
+      <c r="J432" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K432" s="8">
+        <v>240</v>
+      </c>
+      <c r="L432" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M432" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N432" s="6">
         <v>2</v>
       </c>
@@ -13015,12 +13035,20 @@
         <v>146</v>
       </c>
       <c r="I433" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J433" s="4"/>
-      <c r="K433" s="8"/>
-      <c r="L433" s="4"/>
-      <c r="M433" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="J433" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="K433" s="8">
+        <v>280</v>
+      </c>
+      <c r="L433" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="M433" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N433" s="6">
         <v>3</v>
       </c>
@@ -13036,10 +13064,18 @@
       <c r="I434" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="J434" s="4"/>
-      <c r="K434" s="8"/>
-      <c r="L434" s="4"/>
-      <c r="M434" s="4"/>
+      <c r="J434" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="K434" s="8">
+        <v>200</v>
+      </c>
+      <c r="L434" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="M434" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N434" s="6">
         <v>2</v>
       </c>
@@ -13055,9 +13091,15 @@
       <c r="I435" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="J435" s="4"/>
-      <c r="K435" s="8"/>
-      <c r="L435" s="4"/>
+      <c r="J435" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="K435" s="8">
+        <v>280</v>
+      </c>
+      <c r="L435" s="4" t="s">
+        <v>261</v>
+      </c>
       <c r="M435" s="4"/>
       <c r="N435" s="6">
         <v>2</v>

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="650" documentId="14_{26B40267-1D17-4F43-A747-F3AF1361A198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66725069-CD65-4A44-B7B3-AE978AD05254}"/>
+  <xr:revisionPtr revIDLastSave="764" documentId="14_{26B40267-1D17-4F43-A747-F3AF1361A198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D318BD8C-6BB6-4C96-B513-A9C3A49B0E5F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="NÚMERO DE HOTEIS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HOTEIS!$G$5:$O$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HOTEIS!$G$5:$O$455</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="356">
   <si>
     <t>DATA</t>
   </si>
@@ -1074,6 +1074,39 @@
   </si>
   <si>
     <t>JOAO MONLEVADE</t>
+  </si>
+  <si>
+    <t>WESLEY ANTONIO</t>
+  </si>
+  <si>
+    <t>HOTEL CAMPEAO</t>
+  </si>
+  <si>
+    <t>SAO JOAO EVANGELISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOTEL MIRIAN </t>
+  </si>
+  <si>
+    <t>HOTEL SANTOS DUMMOND</t>
+  </si>
+  <si>
+    <t>ELÓI MENDES</t>
+  </si>
+  <si>
+    <t>HOTEL FRATELLI</t>
+  </si>
+  <si>
+    <t>ÁGUAS CLARAS</t>
+  </si>
+  <si>
+    <t>douglas rodrigues</t>
+  </si>
+  <si>
+    <t>lucas gabriel</t>
+  </si>
+  <si>
+    <t>SÃO JOAO DEL REY</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1161,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1187,6 +1220,30 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1276,18 +1333,16 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
@@ -1627,7 +1682,7 @@
   <sheetPr codeName="Planilha1" filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O440"/>
+  <dimension ref="G5:O455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -9367,56 +9422,80 @@
       <c r="O291" s="6"/>
     </row>
     <row r="292" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="O292" s="25"/>
+      <c r="G292" s="3">
+        <v>45873</v>
+      </c>
+      <c r="H292" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I292" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J292" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="K292" s="8">
+        <v>110</v>
+      </c>
+      <c r="L292" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M292" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N292" s="4">
+        <v>2</v>
+      </c>
+      <c r="O292" s="6"/>
     </row>
     <row r="293" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G293" s="3">
-        <v>45873</v>
+        <v>45932</v>
       </c>
       <c r="H293" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="J293" s="13" t="s">
-        <v>100</v>
+        <v>133</v>
+      </c>
+      <c r="J293" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="K293" s="8">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="L293" s="4" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="M293" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N293" s="4">
+        <v>8</v>
+      </c>
+      <c r="N293" s="6">
         <v>2</v>
       </c>
       <c r="O293" s="6"/>
     </row>
     <row r="294" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G294" s="3">
-        <v>45932</v>
+        <v>45876</v>
       </c>
       <c r="H294" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J294" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K294" s="8">
-        <v>250</v>
-      </c>
-      <c r="L294" s="4" t="s">
-        <v>179</v>
+        <v>124</v>
+      </c>
+      <c r="J294" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="K294" s="9">
+        <v>100</v>
+      </c>
+      <c r="L294" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="M294" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N294" s="6">
         <v>2</v>
@@ -9425,21 +9504,21 @@
     </row>
     <row r="295" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G295" s="3">
-        <v>45876</v>
+        <v>45883</v>
       </c>
       <c r="H295" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I295" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="J295" s="21" t="s">
+      <c r="J295" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K295" s="9">
+      <c r="K295" s="5">
         <v>100</v>
       </c>
-      <c r="L295" s="7" t="s">
+      <c r="L295" s="4" t="s">
         <v>59</v>
       </c>
       <c r="M295" s="4" t="s">
@@ -9452,34 +9531,34 @@
     </row>
     <row r="296" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G296" s="3">
-        <v>45883</v>
+        <v>45889</v>
       </c>
       <c r="H296" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I296" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="J296" s="4" t="s">
+      <c r="J296" s="15" t="s">
         <v>64</v>
       </c>
       <c r="K296" s="5">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="L296" s="4" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="M296" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N296" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O296" s="6"/>
     </row>
     <row r="297" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G297" s="3">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>142</v>
@@ -9487,7 +9566,7 @@
       <c r="I297" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="J297" s="15" t="s">
+      <c r="J297" s="4" t="s">
         <v>64</v>
       </c>
       <c r="K297" s="5">
@@ -9506,7 +9585,7 @@
     </row>
     <row r="298" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G298" s="3">
-        <v>45896</v>
+        <v>45917</v>
       </c>
       <c r="H298" s="4" t="s">
         <v>142</v>
@@ -9517,8 +9596,8 @@
       <c r="J298" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K298" s="5">
-        <v>155</v>
+      <c r="K298" s="8">
+        <v>280</v>
       </c>
       <c r="L298" s="4" t="s">
         <v>103</v>
@@ -9533,7 +9612,7 @@
     </row>
     <row r="299" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G299" s="3">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>142</v>
@@ -9545,7 +9624,7 @@
         <v>64</v>
       </c>
       <c r="K299" s="8">
-        <v>280</v>
+        <v>205</v>
       </c>
       <c r="L299" s="4" t="s">
         <v>103</v>
@@ -9560,19 +9639,19 @@
     </row>
     <row r="300" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G300" s="3">
-        <v>45924</v>
+        <v>45939</v>
       </c>
       <c r="H300" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="I300" s="6" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="J300" s="4" t="s">
         <v>64</v>
       </c>
       <c r="K300" s="8">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="L300" s="4" t="s">
         <v>103</v>
@@ -9581,28 +9660,28 @@
         <v>8</v>
       </c>
       <c r="N300" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O300" s="6"/>
     </row>
     <row r="301" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G301" s="3">
-        <v>45939</v>
+        <v>45903</v>
       </c>
       <c r="H301" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>64</v>
+        <v>166</v>
       </c>
       <c r="K301" s="8">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="L301" s="4" t="s">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="M301" s="4" t="s">
         <v>8</v>
@@ -9614,72 +9693,72 @@
     </row>
     <row r="302" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G302" s="3">
-        <v>45903</v>
-      </c>
-      <c r="H302" s="4" t="s">
-        <v>137</v>
+        <v>45875</v>
+      </c>
+      <c r="H302" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="J302" s="4" t="s">
-        <v>166</v>
+        <v>126</v>
+      </c>
+      <c r="J302" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="K302" s="8">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="L302" s="4" t="s">
-        <v>167</v>
+        <v>48</v>
       </c>
       <c r="M302" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N302" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O302" s="6"/>
     </row>
     <row r="303" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G303" s="3">
-        <v>45875</v>
-      </c>
-      <c r="H303" s="7" t="s">
-        <v>144</v>
+        <v>45889</v>
+      </c>
+      <c r="H303" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I303" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="J303" s="21" t="s">
+      <c r="J303" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K303" s="8">
-        <v>85</v>
+      <c r="K303" s="5">
+        <v>170</v>
       </c>
       <c r="L303" s="4" t="s">
         <v>48</v>
       </c>
       <c r="M303" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N303" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O303" s="6"/>
     </row>
     <row r="304" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G304" s="3">
-        <v>45889</v>
+        <v>45903</v>
       </c>
       <c r="H304" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I304" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J304" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K304" s="5">
+      <c r="K304" s="8">
         <v>170</v>
       </c>
       <c r="L304" s="4" t="s">
@@ -9689,7 +9768,7 @@
         <v>8</v>
       </c>
       <c r="N304" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O304" s="6"/>
     </row>
@@ -9698,10 +9777,10 @@
         <v>45903</v>
       </c>
       <c r="H305" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I305" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="J305" s="4" t="s">
         <v>46</v>
@@ -9722,13 +9801,13 @@
     </row>
     <row r="306" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G306" s="3">
-        <v>45903</v>
+        <v>45910</v>
       </c>
       <c r="H306" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J306" s="4" t="s">
         <v>46</v>
@@ -9737,7 +9816,7 @@
         <v>170</v>
       </c>
       <c r="L306" s="4" t="s">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="M306" s="4" t="s">
         <v>8</v>
@@ -9752,10 +9831,10 @@
         <v>45910</v>
       </c>
       <c r="H307" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="J307" s="4" t="s">
         <v>46</v>
@@ -9776,7 +9855,7 @@
     </row>
     <row r="308" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G308" s="3">
-        <v>45910</v>
+        <v>45924</v>
       </c>
       <c r="H308" s="4" t="s">
         <v>138</v>
@@ -9791,7 +9870,7 @@
         <v>170</v>
       </c>
       <c r="L308" s="4" t="s">
-        <v>214</v>
+        <v>48</v>
       </c>
       <c r="M308" s="4" t="s">
         <v>8</v>
@@ -9803,22 +9882,22 @@
     </row>
     <row r="309" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G309" s="3">
-        <v>45924</v>
+        <v>45931</v>
       </c>
       <c r="H309" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I309" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J309" s="4" t="s">
-        <v>46</v>
+        <v>124</v>
+      </c>
+      <c r="J309" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="K309" s="8">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="L309" s="4" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="M309" s="4" t="s">
         <v>8</v>
@@ -9830,22 +9909,22 @@
     </row>
     <row r="310" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G310" s="3">
-        <v>45931</v>
+        <v>45938</v>
       </c>
       <c r="H310" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J310" s="15" t="s">
-        <v>64</v>
+        <v>135</v>
+      </c>
+      <c r="J310" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="K310" s="8">
-        <v>212</v>
+        <v>170</v>
       </c>
       <c r="L310" s="4" t="s">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="M310" s="4" t="s">
         <v>8</v>
@@ -9860,10 +9939,10 @@
         <v>45938</v>
       </c>
       <c r="H311" s="4" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="J311" s="4" t="s">
         <v>46</v>
@@ -9884,19 +9963,19 @@
     </row>
     <row r="312" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G312" s="3">
-        <v>45938</v>
+        <v>45945</v>
       </c>
       <c r="H312" s="4" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J312" s="4" t="s">
         <v>46</v>
       </c>
       <c r="K312" s="8">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="L312" s="4" t="s">
         <v>214</v>
@@ -9914,10 +9993,10 @@
         <v>45945</v>
       </c>
       <c r="H313" s="4" t="s">
-        <v>138</v>
+        <v>235</v>
       </c>
       <c r="I313" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="J313" s="4" t="s">
         <v>46</v>
@@ -9938,19 +10017,19 @@
     </row>
     <row r="314" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G314" s="3">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="H314" s="4" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="I314" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J314" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J314" s="15" t="s">
         <v>46</v>
       </c>
       <c r="K314" s="8">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="L314" s="4" t="s">
         <v>214</v>
@@ -9961,107 +10040,107 @@
       <c r="N314" s="6">
         <v>3</v>
       </c>
-      <c r="O314" s="6"/>
+      <c r="O314" s="25"/>
     </row>
     <row r="315" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G315" s="3">
-        <v>45952</v>
+        <v>45903</v>
       </c>
       <c r="H315" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I315" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J315" s="15" t="s">
-        <v>46</v>
+        <v>129</v>
+      </c>
+      <c r="J315" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="K315" s="8">
+        <v>140</v>
+      </c>
+      <c r="L315" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="L315" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="M315" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N315" s="6">
-        <v>3</v>
-      </c>
-      <c r="O315" s="25"/>
+        <v>2</v>
+      </c>
+      <c r="O315" s="6"/>
     </row>
     <row r="316" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G316" s="3">
-        <v>45903</v>
+        <v>45952</v>
       </c>
       <c r="H316" s="4" t="s">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="I316" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="K316" s="8">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="L316" s="4" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="M316" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N316" s="6">
-        <v>2</v>
-      </c>
-      <c r="O316" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="O316" s="25"/>
     </row>
     <row r="317" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G317" s="3">
-        <v>45952</v>
+        <v>45895</v>
       </c>
       <c r="H317" s="4" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="I317" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K317" s="8">
-        <v>170</v>
+        <v>13</v>
+      </c>
+      <c r="K317" s="5">
+        <v>200</v>
       </c>
       <c r="L317" s="4" t="s">
-        <v>214</v>
+        <v>12</v>
       </c>
       <c r="M317" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N317" s="6">
-        <v>3</v>
-      </c>
-      <c r="O317" s="25"/>
+        <v>2</v>
+      </c>
+      <c r="O317" s="6"/>
     </row>
     <row r="318" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G318" s="3">
-        <v>45895</v>
+        <v>45918</v>
       </c>
       <c r="H318" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I318" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J318" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K318" s="5">
+      <c r="K318" s="8">
         <v>200</v>
       </c>
       <c r="L318" s="4" t="s">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="M318" s="4" t="s">
         <v>8</v>
@@ -10073,45 +10152,45 @@
     </row>
     <row r="319" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G319" s="3">
-        <v>45918</v>
+        <v>45873</v>
       </c>
       <c r="H319" s="4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="I319" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K319" s="8">
-        <v>200</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="M319" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N319" s="6">
+        <v>7</v>
+      </c>
+      <c r="N319" s="4">
         <v>2</v>
       </c>
       <c r="O319" s="6"/>
     </row>
     <row r="320" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G320" s="3">
-        <v>45873</v>
+        <v>45876</v>
       </c>
       <c r="H320" s="4" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="I320" s="6" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J320" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K320" s="8">
+      <c r="K320" s="9">
         <v>74.900000000000006</v>
       </c>
       <c r="L320" s="4" t="s">
@@ -10120,25 +10199,25 @@
       <c r="M320" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N320" s="4">
+      <c r="N320" s="6">
         <v>2</v>
       </c>
       <c r="O320" s="6"/>
     </row>
     <row r="321" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G321" s="3">
-        <v>45876</v>
+        <v>45880</v>
       </c>
       <c r="H321" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I321" s="6" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="J321" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K321" s="9">
+      <c r="K321" s="5">
         <v>74.900000000000006</v>
       </c>
       <c r="L321" s="4" t="s">
@@ -10154,19 +10233,19 @@
     </row>
     <row r="322" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G322" s="3">
-        <v>45880</v>
+        <v>45883</v>
       </c>
       <c r="H322" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="I322" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="J322" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K322" s="5">
-        <v>74.900000000000006</v>
+        <v>129</v>
       </c>
       <c r="L322" s="4" t="s">
         <v>89</v>
@@ -10184,22 +10263,22 @@
         <v>45883</v>
       </c>
       <c r="H323" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J323" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K323" s="5">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="L323" s="4" t="s">
         <v>89</v>
       </c>
       <c r="M323" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N323" s="6">
         <v>2</v>
@@ -10208,13 +10287,13 @@
     </row>
     <row r="324" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G324" s="3">
-        <v>45883</v>
+        <v>45887</v>
       </c>
       <c r="H324" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="J324" s="4" t="s">
         <v>24</v>
@@ -10226,7 +10305,7 @@
         <v>89</v>
       </c>
       <c r="M324" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N324" s="6">
         <v>2</v>
@@ -10235,19 +10314,19 @@
     </row>
     <row r="325" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G325" s="3">
-        <v>45887</v>
+        <v>45890</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>149</v>
       </c>
       <c r="I325" s="6" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="J325" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K325" s="5">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L325" s="4" t="s">
         <v>89</v>
@@ -10262,7 +10341,7 @@
     </row>
     <row r="326" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G326" s="3">
-        <v>45890</v>
+        <v>45894</v>
       </c>
       <c r="H326" s="4" t="s">
         <v>149</v>
@@ -10274,13 +10353,13 @@
         <v>24</v>
       </c>
       <c r="K326" s="5">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="L326" s="4" t="s">
         <v>89</v>
       </c>
       <c r="M326" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N326" s="6">
         <v>2</v>
@@ -10289,10 +10368,10 @@
     </row>
     <row r="327" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G327" s="3">
-        <v>45894</v>
+        <v>45897</v>
       </c>
       <c r="H327" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I327" s="6" t="s">
         <v>121</v>
@@ -10300,8 +10379,8 @@
       <c r="J327" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K327" s="5">
-        <v>149</v>
+      <c r="K327" s="8">
+        <v>209</v>
       </c>
       <c r="L327" s="4" t="s">
         <v>89</v>
@@ -10316,10 +10395,10 @@
     </row>
     <row r="328" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G328" s="3">
-        <v>45897</v>
+        <v>45901</v>
       </c>
       <c r="H328" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I328" s="6" t="s">
         <v>121</v>
@@ -10343,15 +10422,15 @@
     </row>
     <row r="329" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G329" s="3">
-        <v>45901</v>
+        <v>45904</v>
       </c>
       <c r="H329" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I329" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="J329" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J329" s="15" t="s">
         <v>24</v>
       </c>
       <c r="K329" s="8">
@@ -10370,19 +10449,19 @@
     </row>
     <row r="330" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G330" s="3">
-        <v>45904</v>
+        <v>45908</v>
       </c>
       <c r="H330" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I330" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="J330" s="15" t="s">
+      <c r="I330" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J330" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K330" s="8">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="L330" s="4" t="s">
         <v>89</v>
@@ -10390,26 +10469,26 @@
       <c r="M330" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N330" s="6">
+      <c r="N330" s="4">
         <v>2</v>
       </c>
       <c r="O330" s="6"/>
     </row>
     <row r="331" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G331" s="3">
-        <v>45908</v>
+        <v>45911</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I331" s="4" t="s">
+      <c r="I331" s="6" t="s">
         <v>121</v>
       </c>
       <c r="J331" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K331" s="8">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="L331" s="4" t="s">
         <v>89</v>
@@ -10417,14 +10496,14 @@
       <c r="M331" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N331" s="4">
+      <c r="N331" s="6">
         <v>2</v>
       </c>
       <c r="O331" s="6"/>
     </row>
     <row r="332" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G332" s="3">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="H332" s="4" t="s">
         <v>156</v>
@@ -10454,16 +10533,16 @@
         <v>45915</v>
       </c>
       <c r="H333" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I333" s="6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J333" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K333" s="8">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="L333" s="4" t="s">
         <v>89</v>
@@ -10472,25 +10551,25 @@
         <v>8</v>
       </c>
       <c r="N333" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O333" s="6"/>
     </row>
     <row r="334" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G334" s="3">
-        <v>45915</v>
+        <v>45918</v>
       </c>
       <c r="H334" s="4" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I334" s="6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J334" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K334" s="8">
-        <v>259</v>
+        <v>159</v>
       </c>
       <c r="L334" s="4" t="s">
         <v>89</v>
@@ -10499,13 +10578,13 @@
         <v>8</v>
       </c>
       <c r="N334" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O334" s="6"/>
     </row>
     <row r="335" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G335" s="3">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>156</v>
@@ -10517,7 +10596,7 @@
         <v>24</v>
       </c>
       <c r="K335" s="8">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="L335" s="4" t="s">
         <v>89</v>
@@ -10532,13 +10611,13 @@
     </row>
     <row r="336" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G336" s="3">
-        <v>45922</v>
+        <v>45925</v>
       </c>
       <c r="H336" s="4" t="s">
         <v>156</v>
       </c>
       <c r="I336" s="6" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="J336" s="4" t="s">
         <v>24</v>
@@ -10559,7 +10638,7 @@
     </row>
     <row r="337" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G337" s="3">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>156</v>
@@ -10567,7 +10646,7 @@
       <c r="I337" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="J337" s="4" t="s">
+      <c r="J337" s="15" t="s">
         <v>24</v>
       </c>
       <c r="K337" s="8">
@@ -10586,22 +10665,22 @@
     </row>
     <row r="338" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G338" s="3">
-        <v>45929</v>
+        <v>45957</v>
       </c>
       <c r="H338" s="4" t="s">
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="I338" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="J338" s="15" t="s">
-        <v>24</v>
+        <v>130</v>
+      </c>
+      <c r="J338" s="4" t="s">
+        <v>260</v>
       </c>
       <c r="K338" s="8">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="L338" s="4" t="s">
-        <v>89</v>
+        <v>259</v>
       </c>
       <c r="M338" s="4" t="s">
         <v>8</v>
@@ -10609,25 +10688,25 @@
       <c r="N338" s="6">
         <v>2</v>
       </c>
-      <c r="O338" s="6"/>
+      <c r="O338" s="25"/>
     </row>
     <row r="339" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G339" s="3">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="H339" s="4" t="s">
-        <v>256</v>
+        <v>148</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J339" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="K339" s="8">
+        <v>176</v>
+      </c>
+      <c r="J339" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K339" s="10">
         <v>140</v>
       </c>
-      <c r="L339" s="4" t="s">
+      <c r="L339" s="1" t="s">
         <v>259</v>
       </c>
       <c r="M339" s="4" t="s">
@@ -10643,19 +10722,19 @@
         <v>45959</v>
       </c>
       <c r="H340" s="4" t="s">
-        <v>148</v>
+        <v>266</v>
       </c>
       <c r="I340" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="J340" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="K340" s="10">
-        <v>140</v>
-      </c>
-      <c r="L340" s="1" t="s">
-        <v>259</v>
+        <v>130</v>
+      </c>
+      <c r="J340" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="K340" s="8">
+        <v>220</v>
+      </c>
+      <c r="L340" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="M340" s="4" t="s">
         <v>8</v>
@@ -10667,22 +10746,22 @@
     </row>
     <row r="341" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G341" s="3">
-        <v>45959</v>
+        <v>45932</v>
       </c>
       <c r="H341" s="4" t="s">
-        <v>266</v>
+        <v>156</v>
       </c>
       <c r="I341" s="6" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>267</v>
+        <v>24</v>
       </c>
       <c r="K341" s="8">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="L341" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M341" s="4" t="s">
         <v>8</v>
@@ -10690,14 +10769,14 @@
       <c r="N341" s="6">
         <v>2</v>
       </c>
-      <c r="O341" s="25"/>
+      <c r="O341" s="6"/>
     </row>
     <row r="342" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G342" s="3">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="H342" s="4" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="I342" s="6" t="s">
         <v>189</v>
@@ -10721,7 +10800,7 @@
     </row>
     <row r="343" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G343" s="3">
-        <v>45936</v>
+        <v>45939</v>
       </c>
       <c r="H343" s="4" t="s">
         <v>207</v>
@@ -10733,10 +10812,10 @@
         <v>24</v>
       </c>
       <c r="K343" s="8">
-        <v>259</v>
+        <v>140</v>
       </c>
       <c r="L343" s="4" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="M343" s="4" t="s">
         <v>8</v>
@@ -10748,19 +10827,19 @@
     </row>
     <row r="344" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G344" s="3">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="H344" s="4" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="J344" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K344" s="8">
-        <v>140</v>
+        <v>259</v>
       </c>
       <c r="L344" s="4" t="s">
         <v>225</v>
@@ -10775,22 +10854,22 @@
     </row>
     <row r="345" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G345" s="3">
-        <v>45943</v>
+        <v>45946</v>
       </c>
       <c r="H345" s="4" t="s">
-        <v>138</v>
+        <v>240</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="J345" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K345" s="8">
-        <v>259</v>
+        <v>159</v>
       </c>
       <c r="L345" s="4" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="M345" s="4" t="s">
         <v>8</v>
@@ -10802,25 +10881,25 @@
     </row>
     <row r="346" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G346" s="3">
-        <v>45946</v>
+        <v>45896</v>
       </c>
       <c r="H346" s="4" t="s">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K346" s="8">
-        <v>159</v>
+        <v>108</v>
+      </c>
+      <c r="K346" s="5">
+        <v>55</v>
       </c>
       <c r="L346" s="4" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="M346" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N346" s="6">
         <v>2</v>
@@ -10829,7 +10908,7 @@
     </row>
     <row r="347" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G347" s="3">
-        <v>45896</v>
+        <v>45924</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>143</v>
@@ -10840,85 +10919,85 @@
       <c r="J347" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K347" s="5">
-        <v>55</v>
+      <c r="K347" s="8">
+        <v>110</v>
       </c>
       <c r="L347" s="4" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="M347" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N347" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O347" s="6"/>
     </row>
     <row r="348" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G348" s="3">
-        <v>45924</v>
-      </c>
-      <c r="H348" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="I348" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J348" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K348" s="8">
-        <v>110</v>
-      </c>
-      <c r="L348" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="M348" s="4" t="s">
+      <c r="G348" s="17">
+        <v>45947</v>
+      </c>
+      <c r="H348" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="I348" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="J348" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K348" s="20">
+        <v>259</v>
+      </c>
+      <c r="L348" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="M348" s="18" t="s">
         <v>8</v>
       </c>
       <c r="N348" s="6">
-        <v>3</v>
-      </c>
-      <c r="O348" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="O348" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="349" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G349" s="17">
-        <v>45947</v>
-      </c>
-      <c r="H349" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="I349" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="J349" s="18" t="s">
+      <c r="G349" s="3">
+        <v>45950</v>
+      </c>
+      <c r="H349" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I349" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J349" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K349" s="20">
-        <v>259</v>
-      </c>
-      <c r="L349" s="18" t="s">
+      <c r="K349" s="8">
+        <v>159</v>
+      </c>
+      <c r="L349" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="M349" s="18" t="s">
+      <c r="M349" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N349" s="6">
-        <v>1</v>
-      </c>
-      <c r="O349" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O349" s="25"/>
     </row>
     <row r="350" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G350" s="3">
-        <v>45950</v>
+        <v>45957</v>
       </c>
       <c r="H350" s="4" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="I350" s="6" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="J350" s="4" t="s">
         <v>24</v>
@@ -10939,22 +11018,22 @@
     </row>
     <row r="351" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G351" s="3">
-        <v>45957</v>
+        <v>45931</v>
       </c>
       <c r="H351" s="4" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="I351" s="6" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="K351" s="8">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="L351" s="4" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="M351" s="4" t="s">
         <v>8</v>
@@ -10962,29 +11041,29 @@
       <c r="N351" s="6">
         <v>2</v>
       </c>
-      <c r="O351" s="25"/>
+      <c r="O351" s="6"/>
     </row>
     <row r="352" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G352" s="3">
-        <v>45931</v>
+        <v>45889</v>
       </c>
       <c r="H352" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I352" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K352" s="8">
-        <v>110</v>
+        <v>241</v>
+      </c>
+      <c r="K352" s="5">
+        <v>130</v>
       </c>
       <c r="L352" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="M352" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N352" s="6">
         <v>2</v>
@@ -10993,7 +11072,7 @@
     </row>
     <row r="353" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G353" s="3">
-        <v>45889</v>
+        <v>45924</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>146</v>
@@ -11004,53 +11083,53 @@
       <c r="J353" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="K353" s="5">
-        <v>130</v>
+      <c r="K353" s="8">
+        <v>170</v>
       </c>
       <c r="L353" s="4" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="M353" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N353" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O353" s="6"/>
     </row>
     <row r="354" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G354" s="3">
-        <v>45924</v>
+        <v>45938</v>
       </c>
       <c r="H354" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I354" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="K354" s="8">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="L354" s="4" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="M354" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N354" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O354" s="6"/>
     </row>
     <row r="355" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G355" s="3">
-        <v>45938</v>
+        <v>45945</v>
       </c>
       <c r="H355" s="4" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="I355" s="6" t="s">
         <v>129</v>
@@ -11062,35 +11141,33 @@
         <v>160</v>
       </c>
       <c r="L355" s="4" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="M355" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N355" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O355" s="6"/>
     </row>
     <row r="356" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G356" s="3">
-        <v>45945</v>
+        <v>45903</v>
       </c>
       <c r="H356" s="4" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="I356" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="K356" s="8">
-        <v>160</v>
-      </c>
-      <c r="L356" s="4" t="s">
-        <v>239</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="L356" s="4"/>
       <c r="M356" s="4" t="s">
         <v>8</v>
       </c>
@@ -11101,7 +11178,7 @@
     </row>
     <row r="357" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G357" s="3">
-        <v>45903</v>
+        <v>45896</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>141</v>
@@ -11110,131 +11187,133 @@
         <v>132</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="K357" s="8">
-        <v>200</v>
-      </c>
-      <c r="L357" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="K357" s="5">
+        <v>120</v>
+      </c>
+      <c r="L357" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="M357" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N357" s="6">
         <v>2</v>
       </c>
-      <c r="O357" s="6"/>
+      <c r="O357"/>
     </row>
     <row r="358" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G358" s="3">
-        <v>45896</v>
+        <v>45952</v>
       </c>
       <c r="H358" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I358" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="K358" s="5">
-        <v>120</v>
+        <v>108</v>
+      </c>
+      <c r="K358" s="8">
+        <v>160</v>
       </c>
       <c r="L358" s="4" t="s">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="M358" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N358" s="6">
         <v>2</v>
       </c>
-      <c r="O358"/>
+      <c r="O358" s="25"/>
     </row>
     <row r="359" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G359" s="3">
-        <v>45952</v>
+        <v>45881</v>
       </c>
       <c r="H359" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I359" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K359" s="8">
+        <v>70</v>
+      </c>
+      <c r="K359" s="5">
         <v>160</v>
       </c>
       <c r="L359" s="4" t="s">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="M359" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N359" s="6">
-        <v>2</v>
-      </c>
-      <c r="O359" s="25"/>
+        <v>3</v>
+      </c>
+      <c r="O359" s="6"/>
     </row>
     <row r="360" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G360" s="3">
         <v>45881</v>
       </c>
       <c r="H360" s="4" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I360" s="6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="K360" s="5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="L360" s="4" t="s">
-        <v>69</v>
+        <v>228</v>
       </c>
       <c r="M360" s="4" t="s">
         <v>7</v>
       </c>
       <c r="N360" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O360" s="6"/>
     </row>
     <row r="361" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G361" s="3">
-        <v>45881</v>
+        <v>45896</v>
       </c>
       <c r="H361" s="4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I361" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J361" s="4" t="s">
         <v>107</v>
       </c>
       <c r="K361" s="5">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="L361" s="4" t="s">
         <v>228</v>
       </c>
       <c r="M361" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N361" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O361" s="6"/>
     </row>
     <row r="362" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G362" s="3">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="H362" s="4" t="s">
         <v>146</v>
@@ -11245,8 +11324,8 @@
       <c r="J362" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="K362" s="5">
-        <v>230</v>
+      <c r="K362" s="8">
+        <v>240</v>
       </c>
       <c r="L362" s="4" t="s">
         <v>228</v>
@@ -11276,7 +11355,7 @@
         <v>240</v>
       </c>
       <c r="L363" s="4" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="M363" s="4" t="s">
         <v>8</v>
@@ -11288,7 +11367,7 @@
     </row>
     <row r="364" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G364" s="3">
-        <v>45903</v>
+        <v>45918</v>
       </c>
       <c r="H364" s="4" t="s">
         <v>146</v>
@@ -11303,7 +11382,7 @@
         <v>240</v>
       </c>
       <c r="L364" s="4" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="M364" s="4" t="s">
         <v>8</v>
@@ -11311,11 +11390,11 @@
       <c r="N364" s="6">
         <v>1</v>
       </c>
-      <c r="O364" s="6"/>
+      <c r="O364" s="28"/>
     </row>
     <row r="365" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G365" s="3">
-        <v>45918</v>
+        <v>45925</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>146</v>
@@ -11330,7 +11409,7 @@
         <v>240</v>
       </c>
       <c r="L365" s="4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="M365" s="4" t="s">
         <v>8</v>
@@ -11338,11 +11417,11 @@
       <c r="N365" s="6">
         <v>1</v>
       </c>
-      <c r="O365" s="28"/>
+      <c r="O365" s="6"/>
     </row>
     <row r="366" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G366" s="3">
-        <v>45925</v>
+        <v>45946</v>
       </c>
       <c r="H366" s="4" t="s">
         <v>146</v>
@@ -11351,13 +11430,13 @@
         <v>128</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="K366" s="8">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="L366" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="M366" s="4" t="s">
         <v>8</v>
@@ -11369,34 +11448,34 @@
     </row>
     <row r="367" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G367" s="3">
-        <v>45946</v>
+        <v>45882</v>
       </c>
       <c r="H367" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I367" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="K367" s="8">
-        <v>170</v>
+        <v>77</v>
+      </c>
+      <c r="K367" s="5">
+        <v>175</v>
       </c>
       <c r="L367" s="4" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="M367" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N367" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O367" s="6"/>
     </row>
     <row r="368" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G368" s="3">
-        <v>45882</v>
+        <v>45888</v>
       </c>
       <c r="H368" s="4" t="s">
         <v>140</v>
@@ -11423,7 +11502,7 @@
     </row>
     <row r="369" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G369" s="3">
-        <v>45888</v>
+        <v>45902</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>140</v>
@@ -11434,7 +11513,7 @@
       <c r="J369" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K369" s="5">
+      <c r="K369" s="8">
         <v>175</v>
       </c>
       <c r="L369" s="4" t="s">
@@ -11450,7 +11529,7 @@
     </row>
     <row r="370" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G370" s="3">
-        <v>45902</v>
+        <v>45909</v>
       </c>
       <c r="H370" s="4" t="s">
         <v>140</v>
@@ -11477,7 +11556,7 @@
     </row>
     <row r="371" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G371" s="3">
-        <v>45909</v>
+        <v>45924</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>140</v>
@@ -11498,82 +11577,82 @@
         <v>7</v>
       </c>
       <c r="N371" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O371" s="6"/>
     </row>
     <row r="372" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G372" s="3">
-        <v>45924</v>
+        <v>45953</v>
       </c>
       <c r="H372" s="4" t="s">
-        <v>140</v>
+        <v>238</v>
       </c>
       <c r="I372" s="6" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>77</v>
+        <v>241</v>
       </c>
       <c r="K372" s="8">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L372" s="4" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="M372" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N372" s="6">
         <v>1</v>
       </c>
-      <c r="O372" s="6"/>
+      <c r="O372" s="25"/>
     </row>
     <row r="373" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G373" s="3">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="H373" s="4" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="I373" s="6" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="K373" s="8">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L373" s="4" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="M373" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N373" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O373" s="25"/>
     </row>
     <row r="374" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G374" s="3">
-        <v>45957</v>
+        <v>45939</v>
       </c>
       <c r="H374" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I374" s="6" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>257</v>
+        <v>107</v>
       </c>
       <c r="K374" s="8">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="L374" s="4" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="M374" s="4" t="s">
         <v>8</v>
@@ -11581,29 +11660,29 @@
       <c r="N374" s="6">
         <v>2</v>
       </c>
-      <c r="O374" s="25"/>
+      <c r="O374" s="6"/>
     </row>
     <row r="375" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G375" s="3">
-        <v>45939</v>
-      </c>
-      <c r="H375" s="4" t="s">
+        <v>45875</v>
+      </c>
+      <c r="H375" s="7" t="s">
         <v>146</v>
       </c>
       <c r="I375" s="6" t="s">
         <v>128</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="K375" s="8">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="L375" s="4" t="s">
-        <v>228</v>
+        <v>17</v>
       </c>
       <c r="M375" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N375" s="6">
         <v>2</v>
@@ -11612,9 +11691,9 @@
     </row>
     <row r="376" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G376" s="3">
-        <v>45875</v>
-      </c>
-      <c r="H376" s="7" t="s">
+        <v>45895</v>
+      </c>
+      <c r="H376" s="4" t="s">
         <v>146</v>
       </c>
       <c r="I376" s="6" t="s">
@@ -11623,7 +11702,7 @@
       <c r="J376" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="K376" s="8">
+      <c r="K376" s="5">
         <v>178</v>
       </c>
       <c r="L376" s="4" t="s">
@@ -11639,25 +11718,25 @@
     </row>
     <row r="377" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G377" s="3">
-        <v>45895</v>
+        <v>45938</v>
       </c>
       <c r="H377" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I377" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="K377" s="5">
-        <v>178</v>
+        <v>77</v>
+      </c>
+      <c r="K377" s="8">
+        <v>200</v>
       </c>
       <c r="L377" s="4" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="M377" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N377" s="6">
         <v>2</v>
@@ -11666,25 +11745,25 @@
     </row>
     <row r="378" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G378" s="3">
-        <v>45938</v>
+        <v>45876</v>
       </c>
       <c r="H378" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I378" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J378" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K378" s="8">
-        <v>200</v>
+        <v>126</v>
+      </c>
+      <c r="J378" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K378" s="9">
+        <v>75</v>
       </c>
       <c r="L378" s="4" t="s">
-        <v>216</v>
+        <v>43</v>
       </c>
       <c r="M378" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N378" s="6">
         <v>2</v>
@@ -11693,18 +11772,18 @@
     </row>
     <row r="379" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G379" s="3">
-        <v>45876</v>
+        <v>45883</v>
       </c>
       <c r="H379" s="4" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="I379" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J379" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="J379" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K379" s="9">
+      <c r="K379" s="5">
         <v>75</v>
       </c>
       <c r="L379" s="4" t="s">
@@ -11723,10 +11802,10 @@
         <v>45883</v>
       </c>
       <c r="H380" s="4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I380" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J380" s="4" t="s">
         <v>42</v>
@@ -11747,13 +11826,13 @@
     </row>
     <row r="381" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G381" s="3">
-        <v>45883</v>
+        <v>45890</v>
       </c>
       <c r="H381" s="4" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="I381" s="6" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J381" s="4" t="s">
         <v>42</v>
@@ -11774,34 +11853,34 @@
     </row>
     <row r="382" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G382" s="3">
-        <v>45890</v>
+        <v>45897</v>
       </c>
       <c r="H382" s="4" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I382" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J382" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K382" s="5">
-        <v>75</v>
+      <c r="K382" s="8">
+        <v>140</v>
       </c>
       <c r="L382" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M382" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N382" s="6">
         <v>2</v>
       </c>
-      <c r="O382" s="6"/>
+      <c r="O382" s="29"/>
     </row>
     <row r="383" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G383" s="3">
-        <v>45897</v>
+        <v>45918</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>138</v>
@@ -11813,7 +11892,7 @@
         <v>42</v>
       </c>
       <c r="K383" s="8">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L383" s="4" t="s">
         <v>43</v>
@@ -11824,11 +11903,11 @@
       <c r="N383" s="6">
         <v>2</v>
       </c>
-      <c r="O383" s="29"/>
+      <c r="O383" s="6"/>
     </row>
     <row r="384" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G384" s="3">
-        <v>45918</v>
+        <v>45925</v>
       </c>
       <c r="H384" s="4" t="s">
         <v>138</v>
@@ -11854,64 +11933,64 @@
       <c r="O384" s="6"/>
     </row>
     <row r="385" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G385" s="3">
-        <v>45925</v>
-      </c>
-      <c r="H385" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="I385" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J385" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K385" s="8">
+      <c r="G385" s="17">
+        <v>45952</v>
+      </c>
+      <c r="H385" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="I385" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="J385" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="K385" s="20">
         <v>150</v>
       </c>
-      <c r="L385" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M385" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N385" s="6">
-        <v>2</v>
-      </c>
-      <c r="O385" s="6"/>
+      <c r="L385" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="M385" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="N385" s="19">
+        <v>1</v>
+      </c>
+      <c r="O385" s="25" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="386" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G386" s="17">
-        <v>45952</v>
-      </c>
-      <c r="H386" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="I386" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="J386" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="K386" s="20">
-        <v>150</v>
-      </c>
-      <c r="L386" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="M386" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="N386" s="19">
-        <v>1</v>
-      </c>
-      <c r="O386" s="25" t="s">
-        <v>253</v>
-      </c>
+      <c r="G386" s="3">
+        <v>45951</v>
+      </c>
+      <c r="H386" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I386" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J386" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="K386" s="8">
+        <v>270</v>
+      </c>
+      <c r="L386" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M386" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N386" s="6">
+        <v>3</v>
+      </c>
+      <c r="O386" s="25"/>
     </row>
     <row r="387" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G387" s="3">
-        <v>45951</v>
+        <v>45944</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>146</v>
@@ -11920,7 +11999,7 @@
         <v>128</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="K387" s="8">
         <v>270</v>
@@ -11934,56 +12013,56 @@
       <c r="N387" s="6">
         <v>3</v>
       </c>
-      <c r="O387" s="25"/>
+      <c r="O387" s="6"/>
     </row>
     <row r="388" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G388" s="3">
-        <v>45944</v>
+        <v>45932</v>
       </c>
       <c r="H388" s="4" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="I388" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>234</v>
+        <v>42</v>
       </c>
       <c r="K388" s="8">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="L388" s="4" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="M388" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N388" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O388" s="6"/>
     </row>
     <row r="389" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G389" s="3">
-        <v>45932</v>
+        <v>45887</v>
       </c>
       <c r="H389" s="4" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="I389" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K389" s="8">
-        <v>150</v>
+        <v>91</v>
+      </c>
+      <c r="K389" s="5">
+        <v>135</v>
       </c>
       <c r="L389" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="M389" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N389" s="6">
         <v>2</v>
@@ -11992,22 +12071,22 @@
     </row>
     <row r="390" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G390" s="3">
-        <v>45887</v>
+        <v>45881</v>
       </c>
       <c r="H390" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I390" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="K390" s="5">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="L390" s="4" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="M390" s="4" t="s">
         <v>7</v>
@@ -12019,25 +12098,25 @@
     </row>
     <row r="391" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G391" s="3">
-        <v>45881</v>
+        <v>45939</v>
       </c>
       <c r="H391" s="4" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="I391" s="6" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K391" s="5">
-        <v>105</v>
+        <v>42</v>
+      </c>
+      <c r="K391" s="8">
+        <v>150</v>
       </c>
       <c r="L391" s="4" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="M391" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N391" s="6">
         <v>2</v>
@@ -12046,23 +12125,17 @@
     </row>
     <row r="392" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G392" s="3">
-        <v>45939</v>
+        <v>45910</v>
       </c>
       <c r="H392" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I392" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J392" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K392" s="8">
-        <v>150</v>
-      </c>
-      <c r="L392" s="4" t="s">
-        <v>43</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="J392" s="4"/>
+      <c r="K392" s="8"/>
+      <c r="L392" s="4"/>
       <c r="M392" s="4" t="s">
         <v>8</v>
       </c>
@@ -12073,13 +12146,13 @@
     </row>
     <row r="393" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G393" s="3">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H393" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I393" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J393" s="4"/>
       <c r="K393" s="8"/>
@@ -12094,13 +12167,13 @@
     </row>
     <row r="394" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G394" s="3">
-        <v>45911</v>
+        <v>45918</v>
       </c>
       <c r="H394" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I394" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J394" s="4"/>
       <c r="K394" s="8"/>
@@ -12114,125 +12187,131 @@
       <c r="O394" s="6"/>
     </row>
     <row r="395" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G395" s="3">
-        <v>45918</v>
-      </c>
-      <c r="H395" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="I395" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J395" s="4"/>
-      <c r="K395" s="8"/>
-      <c r="L395" s="4"/>
-      <c r="M395" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N395" s="6">
-        <v>2</v>
-      </c>
-      <c r="O395" s="6"/>
+      <c r="G395" s="30">
+        <v>45946</v>
+      </c>
+      <c r="H395" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="I395" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J395" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="K395" s="32">
+        <v>150</v>
+      </c>
+      <c r="L395" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="M395" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="N395" s="29">
+        <v>2</v>
+      </c>
+      <c r="O395" s="29"/>
     </row>
     <row r="396" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G396" s="30">
-        <v>45946</v>
-      </c>
-      <c r="H396" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="I396" s="29" t="s">
+        <v>45953</v>
+      </c>
+      <c r="H396" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="I396" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="J396" s="31" t="s">
+      <c r="J396" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K396" s="32">
+      <c r="K396" s="8">
         <v>150</v>
       </c>
       <c r="L396" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M396" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="N396" s="29">
-        <v>2</v>
-      </c>
-      <c r="O396" s="29"/>
+      <c r="M396" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N396" s="6">
+        <v>2</v>
+      </c>
+      <c r="O396" s="25"/>
     </row>
     <row r="397" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G397" s="30">
-        <v>45953</v>
+        <v>45937</v>
       </c>
       <c r="H397" s="4" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="I397" s="6" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="K397" s="8">
-        <v>150</v>
-      </c>
-      <c r="L397" s="31" t="s">
-        <v>43</v>
+        <v>140</v>
+      </c>
+      <c r="L397" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="M397" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N397" s="6">
-        <v>2</v>
-      </c>
-      <c r="O397" s="25"/>
+        <v>3</v>
+      </c>
+      <c r="O397" s="6"/>
     </row>
     <row r="398" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G398" s="30">
-        <v>45937</v>
+        <v>45959</v>
       </c>
       <c r="H398" s="4" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="I398" s="6" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="K398" s="8">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="L398" s="4" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="M398" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N398" s="6">
-        <v>3</v>
-      </c>
-      <c r="O398" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="O398" s="25"/>
     </row>
     <row r="399" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G399" s="30">
         <v>45959</v>
       </c>
       <c r="H399" s="4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I399" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J399" s="4" t="s">
-        <v>108</v>
+        <v>136</v>
+      </c>
+      <c r="J399" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="K399" s="8">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="L399" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M399" s="4" t="s">
         <v>8</v>
@@ -12247,25 +12326,25 @@
         <v>45959</v>
       </c>
       <c r="H400" s="4" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="I400" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J400" s="15" t="s">
-        <v>102</v>
+        <v>263</v>
+      </c>
+      <c r="J400" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K400" s="8">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="L400" s="4" t="s">
-        <v>269</v>
+        <v>103</v>
       </c>
       <c r="M400" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N400" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O400" s="25"/>
     </row>
@@ -12274,19 +12353,19 @@
         <v>45959</v>
       </c>
       <c r="H401" s="4" t="s">
-        <v>262</v>
+        <v>165</v>
       </c>
       <c r="I401" s="6" t="s">
-        <v>263</v>
+        <v>174</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K401" s="8">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="L401" s="4" t="s">
-        <v>103</v>
+        <v>236</v>
       </c>
       <c r="M401" s="4" t="s">
         <v>8</v>
@@ -12301,19 +12380,19 @@
         <v>45959</v>
       </c>
       <c r="H402" s="4" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I402" s="6" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K402" s="8">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="L402" s="4" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="M402" s="4" t="s">
         <v>8</v>
@@ -12327,25 +12406,25 @@
       <c r="G403" s="30">
         <v>45959</v>
       </c>
-      <c r="H403" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I403" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="J403" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K403" s="8">
-        <v>120</v>
-      </c>
-      <c r="L403" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="M403" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N403" s="6">
+      <c r="H403" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="I403" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="J403" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="K403" s="32">
+        <v>210</v>
+      </c>
+      <c r="L403" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="M403" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="N403" s="29">
         <v>3</v>
       </c>
       <c r="O403" s="25"/>
@@ -12354,58 +12433,70 @@
       <c r="G404" s="30">
         <v>45959</v>
       </c>
-      <c r="H404" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="I404" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="J404" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="K404" s="32">
-        <v>210</v>
-      </c>
-      <c r="L404" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="M404" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="N404" s="29">
-        <v>3</v>
-      </c>
+      <c r="H404" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="I404" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J404" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K404" s="8">
+        <v>280</v>
+      </c>
+      <c r="L404" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="M404" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N404" s="6"/>
       <c r="O404" s="25"/>
     </row>
     <row r="405" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G405" s="30"/>
-      <c r="H405" s="4"/>
-      <c r="I405" s="6"/>
-      <c r="J405" s="4"/>
-      <c r="K405" s="8"/>
-      <c r="L405" s="4"/>
-      <c r="M405" s="4"/>
+      <c r="G405" s="30">
+        <v>45960</v>
+      </c>
+      <c r="H405" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I405" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J405" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="K405" s="8">
+        <v>175</v>
+      </c>
+      <c r="L405" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="M405" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N405" s="6"/>
       <c r="O405" s="25"/>
     </row>
     <row r="406" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G406" s="30">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="H406" s="4" t="s">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="I406" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K406" s="8">
-        <v>280</v>
+        <v>180</v>
       </c>
       <c r="L406" s="4" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="M406" s="4" t="s">
         <v>8</v>
@@ -12414,56 +12505,98 @@
       <c r="O406" s="25"/>
     </row>
     <row r="407" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G407" s="33"/>
-      <c r="H407" s="33"/>
-      <c r="I407" s="28"/>
-      <c r="J407" s="33"/>
-      <c r="K407" s="34"/>
-      <c r="L407" s="33"/>
-      <c r="M407" s="33"/>
-      <c r="N407" s="28"/>
+      <c r="G407" s="30">
+        <v>45960</v>
+      </c>
+      <c r="H407" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I407" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J407" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K407" s="8">
+        <v>198</v>
+      </c>
+      <c r="L407" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="M407" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N407" s="6"/>
       <c r="O407" s="25"/>
     </row>
     <row r="408" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G408" s="4"/>
-      <c r="H408" s="4"/>
-      <c r="I408" s="6"/>
-      <c r="J408" s="4"/>
-      <c r="K408" s="8"/>
-      <c r="L408" s="4"/>
-      <c r="M408" s="4"/>
+      <c r="G408" s="30">
+        <v>45960</v>
+      </c>
+      <c r="H408" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I408" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J408" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K408" s="8">
+        <v>180</v>
+      </c>
+      <c r="L408" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="M408" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="N408" s="6"/>
       <c r="O408" s="25"/>
     </row>
     <row r="409" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G409" s="31"/>
-      <c r="H409" s="31"/>
-      <c r="I409" s="29"/>
-      <c r="J409" s="31"/>
-      <c r="K409" s="32"/>
-      <c r="L409" s="31"/>
-      <c r="M409" s="31"/>
-      <c r="N409" s="29"/>
+      <c r="G409" s="30">
+        <v>45960</v>
+      </c>
+      <c r="H409" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I409" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J409" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K409" s="8">
+        <v>150</v>
+      </c>
+      <c r="L409" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="M409" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N409" s="6"/>
       <c r="O409" s="25"/>
     </row>
     <row r="410" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G410" s="30">
         <v>45960</v>
       </c>
-      <c r="H410" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="I410" s="6" t="s">
-        <v>130</v>
+      <c r="H410" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I410" s="29" t="s">
+        <v>265</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="K410" s="8">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="L410" s="4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="M410" s="4" t="s">
         <v>8</v>
@@ -12476,19 +12609,19 @@
         <v>45960</v>
       </c>
       <c r="H411" s="4" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="I411" s="6" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="K411" s="8">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="L411" s="4" t="s">
-        <v>273</v>
+        <v>89</v>
       </c>
       <c r="M411" s="4" t="s">
         <v>8</v>
@@ -12501,19 +12634,19 @@
         <v>45960</v>
       </c>
       <c r="H412" s="4" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="I412" s="6" t="s">
-        <v>263</v>
+        <v>122</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="K412" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L412" s="4" t="s">
-        <v>272</v>
+        <v>12</v>
       </c>
       <c r="M412" s="4" t="s">
         <v>8</v>
@@ -12526,19 +12659,19 @@
         <v>45960</v>
       </c>
       <c r="H413" s="4" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="I413" s="6" t="s">
-        <v>174</v>
+        <v>271</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K413" s="8">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="L413" s="4" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="M413" s="4" t="s">
         <v>8</v>
@@ -12547,23 +12680,23 @@
       <c r="O413" s="25"/>
     </row>
     <row r="414" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G414" s="30">
+      <c r="G414" s="3">
         <v>45960</v>
       </c>
       <c r="H414" s="4" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="I414" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>42</v>
+        <v>277</v>
       </c>
       <c r="K414" s="8">
-        <v>150</v>
-      </c>
-      <c r="L414" s="31" t="s">
-        <v>43</v>
+        <v>200</v>
+      </c>
+      <c r="L414" s="4" t="s">
+        <v>278</v>
       </c>
       <c r="M414" s="4" t="s">
         <v>8</v>
@@ -12572,23 +12705,23 @@
       <c r="O414" s="25"/>
     </row>
     <row r="415" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G415" s="30">
+      <c r="G415" s="3">
         <v>45960</v>
       </c>
-      <c r="H415" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="I415" s="29" t="s">
-        <v>265</v>
+      <c r="H415" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I415" s="6" t="s">
+        <v>217</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K415" s="8">
         <v>220</v>
       </c>
       <c r="L415" s="4" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="M415" s="4" t="s">
         <v>8</v>
@@ -12597,23 +12730,23 @@
       <c r="O415" s="25"/>
     </row>
     <row r="416" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G416" s="30">
+      <c r="G416" s="3">
         <v>45960</v>
       </c>
       <c r="H416" s="4" t="s">
-        <v>240</v>
+        <v>146</v>
       </c>
       <c r="I416" s="6" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="K416" s="8">
-        <v>159</v>
+        <v>179.9</v>
       </c>
       <c r="L416" s="4" t="s">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="M416" s="4" t="s">
         <v>8</v>
@@ -12622,177 +12755,187 @@
       <c r="O416" s="25"/>
     </row>
     <row r="417" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G417" s="30">
-        <v>45960</v>
+      <c r="G417" s="3">
+        <v>45961</v>
       </c>
       <c r="H417" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I417" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>13</v>
+        <v>327</v>
       </c>
       <c r="K417" s="8">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="L417" s="4" t="s">
-        <v>12</v>
+        <v>328</v>
       </c>
       <c r="M417" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N417" s="6"/>
-      <c r="O417" s="25"/>
+      <c r="N417" s="6">
+        <v>1</v>
+      </c>
+      <c r="O417" s="25" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="418" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G418" s="30">
-        <v>45960</v>
+      <c r="G418" s="3">
+        <v>45964</v>
       </c>
       <c r="H418" s="4" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="I418" s="6" t="s">
-        <v>271</v>
+        <v>125</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="K418" s="8">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L418" s="4" t="s">
-        <v>242</v>
+        <v>337</v>
       </c>
       <c r="M418" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N418" s="6"/>
+      <c r="N418" s="6">
+        <v>2</v>
+      </c>
       <c r="O418" s="25"/>
     </row>
     <row r="419" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G419" s="3">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="H419" s="4" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="I419" s="6" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>277</v>
+        <v>70</v>
       </c>
       <c r="K419" s="8">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="L419" s="4" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="M419" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N419" s="6"/>
+      <c r="N419" s="6">
+        <v>2</v>
+      </c>
       <c r="O419" s="25"/>
     </row>
     <row r="420" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G420" s="3">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="H420" s="4" t="s">
-        <v>152</v>
+        <v>329</v>
       </c>
       <c r="I420" s="6" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>275</v>
+        <v>45</v>
       </c>
       <c r="K420" s="8">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L420" s="4" t="s">
-        <v>177</v>
+        <v>236</v>
       </c>
       <c r="M420" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N420" s="6"/>
+      <c r="N420" s="6">
+        <v>2</v>
+      </c>
       <c r="O420" s="25"/>
     </row>
     <row r="421" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G421" s="3">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="H421" s="4" t="s">
-        <v>146</v>
+        <v>330</v>
       </c>
       <c r="I421" s="6" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="K421" s="8">
-        <v>179.9</v>
+        <v>220</v>
       </c>
       <c r="L421" s="4" t="s">
-        <v>213</v>
+        <v>93</v>
       </c>
       <c r="M421" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N421" s="6"/>
+      <c r="N421" s="6">
+        <v>2</v>
+      </c>
       <c r="O421" s="25"/>
     </row>
     <row r="422" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G422" s="3">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="H422" s="4" t="s">
-        <v>146</v>
+        <v>331</v>
       </c>
       <c r="I422" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>327</v>
+        <v>25</v>
       </c>
       <c r="K422" s="8">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="L422" s="4" t="s">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="M422" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N422" s="6">
-        <v>1</v>
-      </c>
-      <c r="O422" s="25" t="s">
-        <v>253</v>
-      </c>
+      <c r="N422" s="4">
+        <v>4</v>
+      </c>
+      <c r="O422" s="25"/>
     </row>
     <row r="423" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G423" s="3">
         <v>45964</v>
       </c>
       <c r="H423" s="4" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="I423" s="6" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>66</v>
+        <v>334</v>
       </c>
       <c r="K423" s="8">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="L423" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M423" s="4" t="s">
         <v>8</v>
@@ -12807,73 +12950,73 @@
         <v>45964</v>
       </c>
       <c r="H424" s="4" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="I424" s="6" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>70</v>
+        <v>332</v>
       </c>
       <c r="K424" s="8">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="L424" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M424" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N424" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O424" s="25"/>
     </row>
     <row r="425" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G425" s="3">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H425" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I425" s="6" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K425" s="8">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="L425" s="4" t="s">
-        <v>236</v>
+        <v>101</v>
       </c>
       <c r="M425" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N425" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O425" s="25"/>
     </row>
     <row r="426" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G426" s="3">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H426" s="4" t="s">
-        <v>330</v>
+        <v>158</v>
       </c>
       <c r="I426" s="6" t="s">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>230</v>
+        <v>41</v>
       </c>
       <c r="K426" s="8">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L426" s="4" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="M426" s="4" t="s">
         <v>8</v>
@@ -12885,49 +13028,49 @@
     </row>
     <row r="427" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G427" s="3">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H427" s="4" t="s">
-        <v>331</v>
+        <v>146</v>
       </c>
       <c r="I427" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="K427" s="8">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="L427" s="4" t="s">
-        <v>273</v>
+        <v>341</v>
       </c>
       <c r="M427" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N427" s="4">
-        <v>4</v>
+      <c r="N427" s="6">
+        <v>3</v>
       </c>
       <c r="O427" s="25"/>
     </row>
     <row r="428" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G428" s="3">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H428" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I428" s="6" t="s">
-        <v>217</v>
+        <v>338</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="K428" s="8">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="L428" s="4" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="M428" s="4" t="s">
         <v>8</v>
@@ -12939,85 +13082,101 @@
     </row>
     <row r="429" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G429" s="3">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H429" s="4" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="I429" s="6" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="K429" s="8">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="L429" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="M429" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N429" s="6"/>
+        <v>261</v>
+      </c>
+      <c r="M429" s="4"/>
+      <c r="N429" s="6">
+        <v>2</v>
+      </c>
       <c r="O429" s="25"/>
     </row>
-    <row r="430" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G430" s="3"/>
-      <c r="H430" s="4"/>
-      <c r="I430" s="6"/>
-      <c r="J430" s="4"/>
-      <c r="K430" s="8"/>
-      <c r="L430" s="4"/>
-      <c r="M430" s="4"/>
-      <c r="N430" s="6"/>
+    <row r="430" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G430" s="3">
+        <v>45965</v>
+      </c>
+      <c r="H430" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I430" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J430" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K430" s="8">
+        <v>160</v>
+      </c>
+      <c r="L430" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="M430" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N430" s="6">
+        <v>3</v>
+      </c>
       <c r="O430" s="25"/>
     </row>
-    <row r="431" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G431" s="3">
         <v>45965</v>
       </c>
       <c r="H431" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I431" s="6" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>25</v>
+        <v>257</v>
       </c>
       <c r="K431" s="8">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="L431" s="4" t="s">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="M431" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N431" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O431" s="25"/>
     </row>
-    <row r="432" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G432" s="3">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="H432" s="4" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="I432" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>41</v>
+        <v>230</v>
       </c>
       <c r="K432" s="8">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="L432" s="4" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="M432" s="4" t="s">
         <v>8</v>
@@ -13027,140 +13186,62 @@
       </c>
       <c r="O432" s="25"/>
     </row>
-    <row r="433" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G433" s="3">
-        <v>45965</v>
-      </c>
-      <c r="H433" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="I433" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J433" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="K433" s="8">
-        <v>280</v>
-      </c>
-      <c r="L433" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="M433" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N433" s="6">
-        <v>3</v>
-      </c>
+    <row r="433" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G433" s="4"/>
+      <c r="H433" s="4"/>
+      <c r="I433" s="6"/>
+      <c r="J433" s="4"/>
+      <c r="K433" s="8"/>
+      <c r="L433" s="4"/>
+      <c r="M433" s="4"/>
+      <c r="N433" s="6"/>
       <c r="O433" s="25"/>
     </row>
-    <row r="434" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G434" s="3">
-        <v>45965</v>
-      </c>
-      <c r="H434" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I434" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="J434" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="K434" s="8">
-        <v>200</v>
-      </c>
-      <c r="L434" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="M434" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N434" s="6">
-        <v>2</v>
-      </c>
+    <row r="434" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G434" s="4"/>
+      <c r="H434" s="4"/>
+      <c r="I434" s="6"/>
+      <c r="J434" s="4"/>
+      <c r="K434" s="8"/>
+      <c r="L434" s="4"/>
+      <c r="M434" s="4"/>
+      <c r="N434" s="6"/>
       <c r="O434" s="25"/>
     </row>
-    <row r="435" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G435" s="3">
-        <v>45965</v>
-      </c>
-      <c r="H435" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I435" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="J435" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="K435" s="8">
-        <v>280</v>
-      </c>
-      <c r="L435" s="4" t="s">
-        <v>261</v>
-      </c>
+    <row r="435" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G435" s="4"/>
+      <c r="H435" s="4"/>
+      <c r="I435" s="6"/>
+      <c r="J435" s="4"/>
+      <c r="K435" s="8"/>
+      <c r="L435" s="4"/>
       <c r="M435" s="4"/>
-      <c r="N435" s="6">
-        <v>2</v>
-      </c>
+      <c r="N435" s="6"/>
       <c r="O435" s="25"/>
     </row>
-    <row r="436" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G436" s="3">
-        <v>45965</v>
-      </c>
-      <c r="H436" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="I436" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J436" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K436" s="8">
-        <v>160</v>
-      </c>
-      <c r="L436" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="M436" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N436" s="6">
-        <v>3</v>
-      </c>
+    <row r="436" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G436" s="4"/>
+      <c r="H436" s="4"/>
+      <c r="I436" s="6"/>
+      <c r="J436" s="4"/>
+      <c r="K436" s="8"/>
+      <c r="L436" s="4"/>
+      <c r="M436" s="4"/>
+      <c r="N436" s="6"/>
       <c r="O436" s="25"/>
     </row>
-    <row r="437" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G437" s="3">
-        <v>45965</v>
-      </c>
-      <c r="H437" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="I437" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="J437" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="K437" s="8">
-        <v>205</v>
-      </c>
-      <c r="L437" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="M437" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N437" s="6">
-        <v>1</v>
-      </c>
+    <row r="437" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G437" s="4"/>
+      <c r="H437" s="4"/>
+      <c r="I437" s="6"/>
+      <c r="J437" s="4"/>
+      <c r="K437" s="8"/>
+      <c r="L437" s="4"/>
+      <c r="M437" s="4"/>
+      <c r="N437" s="6"/>
       <c r="O437" s="25"/>
     </row>
-    <row r="438" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="G438" s="4"/>
       <c r="H438" s="4"/>
       <c r="I438" s="6"/>
@@ -13171,33 +13252,369 @@
       <c r="N438" s="6"/>
       <c r="O438" s="25"/>
     </row>
-    <row r="439" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G439" s="4"/>
-      <c r="H439" s="4"/>
-      <c r="I439" s="6"/>
-      <c r="J439" s="4"/>
-      <c r="K439" s="8"/>
-      <c r="L439" s="4"/>
+    <row r="439" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G439" s="3">
+        <v>45966</v>
+      </c>
+      <c r="H439" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="I439" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J439" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K439" s="8">
+        <v>170</v>
+      </c>
+      <c r="L439" s="4" t="s">
+        <v>346</v>
+      </c>
       <c r="M439" s="4"/>
-      <c r="N439" s="6"/>
+      <c r="N439" s="6">
+        <v>3</v>
+      </c>
       <c r="O439" s="25"/>
     </row>
-    <row r="440" spans="7:15" x14ac:dyDescent="0.25">
-      <c r="G440" s="4"/>
-      <c r="H440" s="4"/>
-      <c r="I440" s="6"/>
-      <c r="J440" s="4"/>
-      <c r="K440" s="8"/>
-      <c r="L440" s="4"/>
+    <row r="440" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G440" s="35">
+        <v>45966</v>
+      </c>
+      <c r="H440" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="I440" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J440" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K440" s="8">
+        <v>150</v>
+      </c>
+      <c r="L440" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="M440" s="4"/>
-      <c r="N440" s="6"/>
+      <c r="N440" s="6">
+        <v>2</v>
+      </c>
       <c r="O440" s="25"/>
     </row>
+    <row r="441" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G441" s="35">
+        <v>45966</v>
+      </c>
+      <c r="H441" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I441" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J441" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="K441" s="8">
+        <v>220</v>
+      </c>
+      <c r="L441" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="M441" s="4"/>
+      <c r="N441" s="6">
+        <v>2</v>
+      </c>
+      <c r="O441" s="25"/>
+    </row>
+    <row r="442" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G442" s="35">
+        <v>45966</v>
+      </c>
+      <c r="H442" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I442" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J442" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="K442" s="8">
+        <v>160</v>
+      </c>
+      <c r="L442" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="M442" s="4"/>
+      <c r="N442" s="6">
+        <v>2</v>
+      </c>
+      <c r="O442" s="25"/>
+    </row>
+    <row r="443" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G443" s="35">
+        <v>45966</v>
+      </c>
+      <c r="H443" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I443" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J443" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K443" s="8">
+        <v>200</v>
+      </c>
+      <c r="L443" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="M443" s="4"/>
+      <c r="N443" s="6">
+        <v>2</v>
+      </c>
+      <c r="O443" s="25"/>
+    </row>
+    <row r="444" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G444" s="3">
+        <v>45966</v>
+      </c>
+      <c r="H444" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I444" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J444" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K444" s="8">
+        <v>170</v>
+      </c>
+      <c r="L444" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="M444" s="4"/>
+      <c r="N444" s="6">
+        <v>3</v>
+      </c>
+      <c r="O444" s="25"/>
+    </row>
+    <row r="445" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G445" s="3">
+        <v>45966</v>
+      </c>
+      <c r="H445" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I445" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J445" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K445" s="8">
+        <v>170</v>
+      </c>
+      <c r="L445" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="M445" s="4"/>
+      <c r="N445" s="6">
+        <v>3</v>
+      </c>
+      <c r="O445" s="25"/>
+    </row>
+    <row r="446" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G446" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H446" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="I446" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J446" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K446" s="8">
+        <v>200</v>
+      </c>
+      <c r="L446" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M446" s="4"/>
+      <c r="N446" s="6">
+        <v>2</v>
+      </c>
+      <c r="O446" s="25"/>
+    </row>
+    <row r="447" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G447" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H447" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I447" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J447" s="4"/>
+      <c r="K447" s="8"/>
+      <c r="L447" s="4"/>
+      <c r="M447" s="4"/>
+      <c r="N447" s="6">
+        <v>1</v>
+      </c>
+      <c r="O447" s="25"/>
+    </row>
+    <row r="448" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G448" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H448" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I448" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J448" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K448" s="8">
+        <v>180</v>
+      </c>
+      <c r="L448" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M448" s="4"/>
+      <c r="N448" s="6">
+        <v>2</v>
+      </c>
+      <c r="O448" s="25"/>
+    </row>
+    <row r="449" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G449" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H449" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I449" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J449" s="4"/>
+      <c r="K449" s="8"/>
+      <c r="L449" s="4"/>
+      <c r="M449" s="4"/>
+      <c r="N449" s="6">
+        <v>2</v>
+      </c>
+      <c r="O449" s="25"/>
+    </row>
+    <row r="450" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G450" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H450" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I450" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J450" s="4"/>
+      <c r="K450" s="8"/>
+      <c r="L450" s="4"/>
+      <c r="M450" s="4"/>
+      <c r="N450" s="6">
+        <v>2</v>
+      </c>
+      <c r="O450" s="25"/>
+    </row>
+    <row r="451" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G451" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H451" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="I451" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J451" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="K451" s="8">
+        <v>159</v>
+      </c>
+      <c r="L451" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M451" s="4"/>
+      <c r="N451" s="6"/>
+      <c r="O451" s="25"/>
+    </row>
+    <row r="452" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G452" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H452" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I452" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="J452" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K452" s="10">
+        <v>240</v>
+      </c>
+      <c r="L452" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="453" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G453" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H453" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I453" s="36" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="454" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G454" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H454" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I454" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="455" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G455" s="3">
+        <v>45967</v>
+      </c>
+      <c r="H455" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I455" s="36" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="G5:O437" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
+  <autoFilter ref="G5:O455" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2025" month="11" day="4" dateTimeGrouping="day"/>
+        <dateGroupItem year="2025" month="11" day="6" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G67:O409">
@@ -13217,9 +13634,9 @@
   <dimension ref="B3:D50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5703125" style="36" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" style="34" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
@@ -13284,7 +13701,7 @@
       <c r="C8" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="33" t="s">
         <v>286</v>
       </c>
     </row>
@@ -13740,7 +14157,7 @@
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B50" s="36" t="s">
+      <c r="B50" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C50" s="7" t="s">

--- a/data/reserva de hoteis.xlsx
+++ b/data/reserva de hoteis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="764" documentId="14_{26B40267-1D17-4F43-A747-F3AF1361A198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D318BD8C-6BB6-4C96-B513-A9C3A49B0E5F}"/>
+  <xr:revisionPtr revIDLastSave="820" documentId="14_{26B40267-1D17-4F43-A747-F3AF1361A198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58B3EAD5-153A-4563-BC8B-899A0225BD3D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72B7B767-51BF-4851-A118-4A4FFA047337}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="NÚMERO DE HOTEIS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HOTEIS!$G$5:$O$455</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HOTEIS!$G$5:$P$457</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2804" uniqueCount="362">
   <si>
     <t>DATA</t>
   </si>
@@ -650,9 +650,6 @@
     <t>PERDÕES</t>
   </si>
   <si>
-    <t>MEDIEVAL 2</t>
-  </si>
-  <si>
     <t>LAGOA DA PRATA</t>
   </si>
   <si>
@@ -1107,6 +1104,27 @@
   </si>
   <si>
     <t>SÃO JOAO DEL REY</t>
+  </si>
+  <si>
+    <t>hotel feliz 2</t>
+  </si>
+  <si>
+    <t>itabira</t>
+  </si>
+  <si>
+    <t>POUSADA VITORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRES CORAÇÕES </t>
+  </si>
+  <si>
+    <t>HOTEL VITORIA</t>
+  </si>
+  <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
+    <t>TRANSPORTE</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1360,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
@@ -1679,10 +1699,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF69182-D7BE-468C-B7FF-43AE3F66B93B}">
-  <sheetPr codeName="Planilha1" filterMode="1">
+  <sheetPr codeName="Planilha1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G5:O455"/>
+  <dimension ref="G5:P466"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
@@ -1694,9 +1714,10 @@
     <col min="13" max="13" width="14.28515625" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" customWidth="1"/>
     <col min="15" max="15" width="20.140625" style="22" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="7:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1722,10 +1743,13 @@
         <v>20</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="6" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+      <c r="P5" s="36" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G6" s="3">
         <v>45880</v>
       </c>
@@ -1751,8 +1775,11 @@
         <v>2</v>
       </c>
       <c r="O6"/>
-    </row>
-    <row r="7" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G7" s="3">
         <v>45887</v>
       </c>
@@ -1778,8 +1805,11 @@
         <v>2</v>
       </c>
       <c r="O7"/>
-    </row>
-    <row r="8" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G8" s="3">
         <v>45894</v>
       </c>
@@ -1805,8 +1835,11 @@
         <v>2</v>
       </c>
       <c r="O8"/>
-    </row>
-    <row r="9" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P8" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="9" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G9" s="3">
         <v>45897</v>
       </c>
@@ -1832,8 +1865,11 @@
         <v>2</v>
       </c>
       <c r="O9"/>
-    </row>
-    <row r="10" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P9" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>45901</v>
       </c>
@@ -1859,8 +1895,11 @@
         <v>2</v>
       </c>
       <c r="O10"/>
-    </row>
-    <row r="11" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="11" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G11" s="3">
         <v>45908</v>
       </c>
@@ -1886,8 +1925,11 @@
         <v>2</v>
       </c>
       <c r="O11"/>
-    </row>
-    <row r="12" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>45915</v>
       </c>
@@ -1913,8 +1955,11 @@
         <v>2</v>
       </c>
       <c r="O12"/>
-    </row>
-    <row r="13" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="13" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G13" s="3">
         <v>45918</v>
       </c>
@@ -1940,8 +1985,11 @@
         <v>2</v>
       </c>
       <c r="O13"/>
-    </row>
-    <row r="14" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G14" s="3">
         <v>45922</v>
       </c>
@@ -1967,8 +2015,11 @@
         <v>3</v>
       </c>
       <c r="O14"/>
-    </row>
-    <row r="15" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G15" s="3">
         <v>45929</v>
       </c>
@@ -1994,8 +2045,11 @@
         <v>2</v>
       </c>
       <c r="O15"/>
-    </row>
-    <row r="16" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="16" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G16" s="3">
         <v>45932</v>
       </c>
@@ -2021,8 +2075,11 @@
         <v>2</v>
       </c>
       <c r="O16"/>
-    </row>
-    <row r="17" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P16" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="17" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G17" s="3">
         <v>45936</v>
       </c>
@@ -2048,8 +2105,11 @@
         <v>2</v>
       </c>
       <c r="O17"/>
-    </row>
-    <row r="18" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P17" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="18" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
         <v>45946</v>
       </c>
@@ -2075,8 +2135,11 @@
         <v>2</v>
       </c>
       <c r="O18"/>
-    </row>
-    <row r="19" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G19" s="3">
         <v>45950</v>
       </c>
@@ -2084,7 +2147,7 @@
         <v>152</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>27</v>
@@ -2101,8 +2164,11 @@
       <c r="N19" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="20" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G20" s="3">
         <v>45957</v>
       </c>
@@ -2110,7 +2176,7 @@
         <v>152</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>27</v>
@@ -2127,8 +2193,11 @@
       <c r="N20" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="21" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G21" s="3">
         <v>45882</v>
       </c>
@@ -2154,8 +2223,11 @@
         <v>2</v>
       </c>
       <c r="O21"/>
-    </row>
-    <row r="22" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P21" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G22" s="3">
         <v>45931</v>
       </c>
@@ -2181,8 +2253,11 @@
         <v>2</v>
       </c>
       <c r="O22"/>
-    </row>
-    <row r="23" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P22" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G23" s="3">
         <v>45938</v>
       </c>
@@ -2208,8 +2283,11 @@
         <v>3</v>
       </c>
       <c r="O23"/>
-    </row>
-    <row r="24" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P23" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G24" s="3">
         <v>45876</v>
       </c>
@@ -2235,8 +2313,11 @@
         <v>2</v>
       </c>
       <c r="O24"/>
-    </row>
-    <row r="25" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P24" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="25" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G25" s="3">
         <v>45883</v>
       </c>
@@ -2262,8 +2343,11 @@
         <v>2</v>
       </c>
       <c r="O25"/>
-    </row>
-    <row r="26" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G26" s="3">
         <v>45890</v>
       </c>
@@ -2289,8 +2373,11 @@
         <v>2</v>
       </c>
       <c r="O26"/>
-    </row>
-    <row r="27" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P26" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G27" s="3">
         <v>45890</v>
       </c>
@@ -2316,8 +2403,11 @@
         <v>2</v>
       </c>
       <c r="O27"/>
-    </row>
-    <row r="28" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P27" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
         <v>45904</v>
       </c>
@@ -2343,8 +2433,11 @@
         <v>2</v>
       </c>
       <c r="O28"/>
-    </row>
-    <row r="29" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P28" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G29" s="3">
         <v>45918</v>
       </c>
@@ -2370,8 +2463,11 @@
         <v>2</v>
       </c>
       <c r="O29"/>
-    </row>
-    <row r="30" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P29" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G30" s="3">
         <v>45925</v>
       </c>
@@ -2397,25 +2493,28 @@
         <v>2</v>
       </c>
       <c r="O30"/>
-    </row>
-    <row r="31" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P30" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="31" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G31" s="17">
         <v>45940</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I31" s="19" t="s">
         <v>189</v>
       </c>
       <c r="J31" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K31" s="20">
         <v>220</v>
       </c>
       <c r="L31" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M31" s="18" t="s">
         <v>8</v>
@@ -2426,25 +2525,28 @@
       <c r="O31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P31" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="32" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G32" s="3">
         <v>45953</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>189</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K32" s="8">
         <v>190</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>8</v>
@@ -2452,8 +2554,11 @@
       <c r="N32" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P32" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="33" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G33" s="3">
         <v>45946</v>
       </c>
@@ -2461,7 +2566,7 @@
         <v>152</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>83</v>
@@ -2479,8 +2584,11 @@
         <v>2</v>
       </c>
       <c r="O33"/>
-    </row>
-    <row r="34" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P33" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="34" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G34" s="3">
         <v>45875</v>
       </c>
@@ -2506,8 +2614,11 @@
         <v>3</v>
       </c>
       <c r="O34"/>
-    </row>
-    <row r="35" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P34" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G35" s="3">
         <v>45882</v>
       </c>
@@ -2533,8 +2644,11 @@
         <v>2</v>
       </c>
       <c r="O35"/>
-    </row>
-    <row r="36" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P35" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="36" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <v>45876</v>
       </c>
@@ -2560,8 +2674,11 @@
         <v>2</v>
       </c>
       <c r="O36"/>
-    </row>
-    <row r="37" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P36" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="37" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G37" s="3">
         <v>45888</v>
       </c>
@@ -2587,8 +2704,11 @@
         <v>3</v>
       </c>
       <c r="O37"/>
-    </row>
-    <row r="38" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P37" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="38" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
         <v>45909</v>
       </c>
@@ -2614,8 +2734,11 @@
         <v>2</v>
       </c>
       <c r="O38"/>
-    </row>
-    <row r="39" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P38" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="39" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
         <v>45904</v>
       </c>
@@ -2641,8 +2764,11 @@
         <v>2</v>
       </c>
       <c r="O39"/>
-    </row>
-    <row r="40" spans="7:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="P39" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="40" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
         <v>45883</v>
       </c>
@@ -266